--- a/dados/metas.xlsx
+++ b/dados/metas.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pmemaquinascnh.sharepoint.com/sites/Marketing-PME/Shared Documents/Inteligência Comercial/Projeto Horizonte/MatrizPerformanceDashboard/dados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.sa\Documents\dashboard-oportunidades\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_D8D321458D197A2693872782FF60A7498525228C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C998579F-6DEA-49A6-AD76-4BE2D2DCB2F2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9C60BC-231E-40F1-8914-CBA45405E77C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$R$240</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="80">
   <si>
     <t>CÓD</t>
   </si>
@@ -380,10 +383,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -647,10 +646,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R246"/>
+  <dimension ref="A1:R240"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="18" width="9.140625" style="4"/>
+    <col min="1" max="1" width="9.140625" style="4"/>
+    <col min="2" max="2" width="20.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="18" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -8557,10 +8559,46 @@
         <v>46</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
+      </c>
+      <c r="D142" s="4">
+        <v>2</v>
+      </c>
+      <c r="E142" s="4">
+        <v>2</v>
+      </c>
+      <c r="F142" s="4">
+        <v>3</v>
+      </c>
+      <c r="G142" s="4">
+        <v>3</v>
+      </c>
+      <c r="H142" s="4">
+        <v>2</v>
+      </c>
+      <c r="I142" s="4">
+        <v>3</v>
+      </c>
+      <c r="J142" s="4">
+        <v>2</v>
+      </c>
+      <c r="K142" s="4">
+        <v>3</v>
+      </c>
+      <c r="L142" s="4">
+        <v>3</v>
+      </c>
+      <c r="M142" s="4">
+        <v>2</v>
+      </c>
+      <c r="N142" s="4">
+        <v>2</v>
+      </c>
+      <c r="O142" s="4">
+        <v>2</v>
       </c>
       <c r="P142" s="4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q142" s="4" t="s">
         <v>48</v>
@@ -8577,10 +8615,46 @@
         <v>49</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
+      </c>
+      <c r="D143" s="4">
+        <v>5</v>
+      </c>
+      <c r="E143" s="4">
+        <v>5</v>
+      </c>
+      <c r="F143" s="4">
+        <v>6</v>
+      </c>
+      <c r="G143" s="4">
+        <v>7</v>
+      </c>
+      <c r="H143" s="4">
+        <v>6</v>
+      </c>
+      <c r="I143" s="4">
+        <v>7</v>
+      </c>
+      <c r="J143" s="4">
+        <v>5</v>
+      </c>
+      <c r="K143" s="4">
+        <v>8</v>
+      </c>
+      <c r="L143" s="4">
+        <v>7</v>
+      </c>
+      <c r="M143" s="4">
+        <v>5</v>
+      </c>
+      <c r="N143" s="4">
+        <v>4</v>
+      </c>
+      <c r="O143" s="4">
+        <v>5</v>
       </c>
       <c r="P143" s="4">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q143" s="4" t="s">
         <v>48</v>
@@ -8597,10 +8671,46 @@
         <v>50</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
+      </c>
+      <c r="D144" s="4">
+        <v>0</v>
+      </c>
+      <c r="E144" s="4">
+        <v>0</v>
+      </c>
+      <c r="F144" s="4">
+        <v>2</v>
+      </c>
+      <c r="G144" s="4">
+        <v>3</v>
+      </c>
+      <c r="H144" s="4">
+        <v>3</v>
+      </c>
+      <c r="I144" s="4">
+        <v>4</v>
+      </c>
+      <c r="J144" s="4">
+        <v>4</v>
+      </c>
+      <c r="K144" s="4">
+        <v>4</v>
+      </c>
+      <c r="L144" s="4">
+        <v>4</v>
+      </c>
+      <c r="M144" s="4">
+        <v>4</v>
+      </c>
+      <c r="N144" s="4">
+        <v>4</v>
+      </c>
+      <c r="O144" s="4">
+        <v>3</v>
       </c>
       <c r="P144" s="4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q144" s="4" t="s">
         <v>48</v>
@@ -8617,10 +8727,46 @@
         <v>51</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
+      </c>
+      <c r="D145" s="4">
+        <v>3</v>
+      </c>
+      <c r="E145" s="4">
+        <v>3</v>
+      </c>
+      <c r="F145" s="4">
+        <v>4</v>
+      </c>
+      <c r="G145" s="4">
+        <v>4</v>
+      </c>
+      <c r="H145" s="4">
+        <v>3</v>
+      </c>
+      <c r="I145" s="4">
+        <v>4</v>
+      </c>
+      <c r="J145" s="4">
+        <v>3</v>
+      </c>
+      <c r="K145" s="4">
+        <v>4</v>
+      </c>
+      <c r="L145" s="4">
+        <v>4</v>
+      </c>
+      <c r="M145" s="4">
+        <v>3</v>
+      </c>
+      <c r="N145" s="4">
+        <v>2</v>
+      </c>
+      <c r="O145" s="4">
+        <v>3</v>
       </c>
       <c r="P145" s="4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q145" s="4" t="s">
         <v>48</v>
@@ -8637,10 +8783,46 @@
         <v>52</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
+      </c>
+      <c r="D146" s="4">
+        <v>5</v>
+      </c>
+      <c r="E146" s="4">
+        <v>5</v>
+      </c>
+      <c r="F146" s="4">
+        <v>6</v>
+      </c>
+      <c r="G146" s="4">
+        <v>7</v>
+      </c>
+      <c r="H146" s="4">
+        <v>6</v>
+      </c>
+      <c r="I146" s="4">
+        <v>7</v>
+      </c>
+      <c r="J146" s="4">
+        <v>5</v>
+      </c>
+      <c r="K146" s="4">
+        <v>8</v>
+      </c>
+      <c r="L146" s="4">
+        <v>7</v>
+      </c>
+      <c r="M146" s="4">
+        <v>5</v>
+      </c>
+      <c r="N146" s="4">
+        <v>4</v>
+      </c>
+      <c r="O146" s="4">
+        <v>5</v>
       </c>
       <c r="P146" s="4">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q146" s="4" t="s">
         <v>48</v>
@@ -8657,10 +8839,46 @@
         <v>53</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
+      </c>
+      <c r="D147" s="4">
+        <v>0</v>
+      </c>
+      <c r="E147" s="4">
+        <v>0</v>
+      </c>
+      <c r="F147" s="4">
+        <v>1</v>
+      </c>
+      <c r="G147" s="4">
+        <v>2</v>
+      </c>
+      <c r="H147" s="4">
+        <v>3</v>
+      </c>
+      <c r="I147" s="4">
+        <v>2</v>
+      </c>
+      <c r="J147" s="4">
+        <v>3</v>
+      </c>
+      <c r="K147" s="4">
+        <v>3</v>
+      </c>
+      <c r="L147" s="4">
+        <v>3</v>
+      </c>
+      <c r="M147" s="4">
+        <v>3</v>
+      </c>
+      <c r="N147" s="4">
+        <v>3</v>
+      </c>
+      <c r="O147" s="4">
+        <v>2</v>
       </c>
       <c r="P147" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q147" s="4" t="s">
         <v>48</v>
@@ -8677,46 +8895,46 @@
         <v>46</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D148" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E148" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F148" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G148" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H148" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I148" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J148" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K148" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L148" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M148" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N148" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O148" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P148" s="4">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="Q148" s="4" t="s">
         <v>48</v>
@@ -8733,46 +8951,46 @@
         <v>49</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D149" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E149" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F149" s="4">
+        <v>0</v>
+      </c>
+      <c r="G149" s="4">
+        <v>0</v>
+      </c>
+      <c r="H149" s="4">
+        <v>1</v>
+      </c>
+      <c r="I149" s="4">
+        <v>1</v>
+      </c>
+      <c r="J149" s="4">
+        <v>1</v>
+      </c>
+      <c r="K149" s="4">
+        <v>0</v>
+      </c>
+      <c r="L149" s="4">
+        <v>1</v>
+      </c>
+      <c r="M149" s="4">
+        <v>0</v>
+      </c>
+      <c r="N149" s="4">
+        <v>1</v>
+      </c>
+      <c r="O149" s="4">
+        <v>0</v>
+      </c>
+      <c r="P149" s="4">
         <v>6</v>
-      </c>
-      <c r="G149" s="4">
-        <v>7</v>
-      </c>
-      <c r="H149" s="4">
-        <v>6</v>
-      </c>
-      <c r="I149" s="4">
-        <v>7</v>
-      </c>
-      <c r="J149" s="4">
-        <v>5</v>
-      </c>
-      <c r="K149" s="4">
-        <v>8</v>
-      </c>
-      <c r="L149" s="4">
-        <v>7</v>
-      </c>
-      <c r="M149" s="4">
-        <v>5</v>
-      </c>
-      <c r="N149" s="4">
-        <v>4</v>
-      </c>
-      <c r="O149" s="4">
-        <v>5</v>
-      </c>
-      <c r="P149" s="4">
-        <v>70</v>
       </c>
       <c r="Q149" s="4" t="s">
         <v>48</v>
@@ -8789,7 +9007,7 @@
         <v>50</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D150" s="4">
         <v>0</v>
@@ -8798,37 +9016,37 @@
         <v>0</v>
       </c>
       <c r="F150" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G150" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H150" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I150" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J150" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K150" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L150" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M150" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N150" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O150" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P150" s="4">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="Q150" s="4" t="s">
         <v>48</v>
@@ -8845,46 +9063,46 @@
         <v>51</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D151" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E151" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F151" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G151" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H151" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I151" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J151" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K151" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L151" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M151" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N151" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O151" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P151" s="4">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="Q151" s="4" t="s">
         <v>48</v>
@@ -8901,46 +9119,46 @@
         <v>52</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D152" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E152" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F152" s="4">
+        <v>0</v>
+      </c>
+      <c r="G152" s="4">
+        <v>0</v>
+      </c>
+      <c r="H152" s="4">
+        <v>1</v>
+      </c>
+      <c r="I152" s="4">
+        <v>1</v>
+      </c>
+      <c r="J152" s="4">
+        <v>1</v>
+      </c>
+      <c r="K152" s="4">
+        <v>0</v>
+      </c>
+      <c r="L152" s="4">
+        <v>1</v>
+      </c>
+      <c r="M152" s="4">
+        <v>0</v>
+      </c>
+      <c r="N152" s="4">
+        <v>1</v>
+      </c>
+      <c r="O152" s="4">
+        <v>0</v>
+      </c>
+      <c r="P152" s="4">
         <v>6</v>
-      </c>
-      <c r="G152" s="4">
-        <v>7</v>
-      </c>
-      <c r="H152" s="4">
-        <v>6</v>
-      </c>
-      <c r="I152" s="4">
-        <v>7</v>
-      </c>
-      <c r="J152" s="4">
-        <v>5</v>
-      </c>
-      <c r="K152" s="4">
-        <v>8</v>
-      </c>
-      <c r="L152" s="4">
-        <v>7</v>
-      </c>
-      <c r="M152" s="4">
-        <v>5</v>
-      </c>
-      <c r="N152" s="4">
-        <v>4</v>
-      </c>
-      <c r="O152" s="4">
-        <v>5</v>
-      </c>
-      <c r="P152" s="4">
-        <v>70</v>
       </c>
       <c r="Q152" s="4" t="s">
         <v>48</v>
@@ -8957,7 +9175,7 @@
         <v>53</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D153" s="4">
         <v>0</v>
@@ -8969,34 +9187,34 @@
         <v>1</v>
       </c>
       <c r="G153" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H153" s="4">
+        <v>0</v>
+      </c>
+      <c r="I153" s="4">
+        <v>1</v>
+      </c>
+      <c r="J153" s="4">
+        <v>0</v>
+      </c>
+      <c r="K153" s="4">
+        <v>0</v>
+      </c>
+      <c r="L153" s="4">
+        <v>1</v>
+      </c>
+      <c r="M153" s="4">
+        <v>0</v>
+      </c>
+      <c r="N153" s="4">
+        <v>0</v>
+      </c>
+      <c r="O153" s="4">
+        <v>0</v>
+      </c>
+      <c r="P153" s="4">
         <v>3</v>
-      </c>
-      <c r="I153" s="4">
-        <v>2</v>
-      </c>
-      <c r="J153" s="4">
-        <v>3</v>
-      </c>
-      <c r="K153" s="4">
-        <v>3</v>
-      </c>
-      <c r="L153" s="4">
-        <v>3</v>
-      </c>
-      <c r="M153" s="4">
-        <v>3</v>
-      </c>
-      <c r="N153" s="4">
-        <v>3</v>
-      </c>
-      <c r="O153" s="4">
-        <v>2</v>
-      </c>
-      <c r="P153" s="4">
-        <v>25</v>
       </c>
       <c r="Q153" s="4" t="s">
         <v>48</v>
@@ -9007,55 +9225,55 @@
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
-        <v>221003</v>
+        <v>240035</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D154" s="4">
-        <v>0</v>
+        <v>440120</v>
       </c>
       <c r="E154" s="4">
-        <v>1</v>
+        <v>408683</v>
       </c>
       <c r="F154" s="4">
-        <v>0</v>
+        <v>458084</v>
       </c>
       <c r="G154" s="4">
-        <v>0</v>
+        <v>395210</v>
       </c>
       <c r="H154" s="4">
-        <v>1</v>
+        <v>619760</v>
       </c>
       <c r="I154" s="4">
-        <v>1</v>
+        <v>574850</v>
       </c>
       <c r="J154" s="4">
-        <v>1</v>
+        <v>440120</v>
       </c>
       <c r="K154" s="4">
-        <v>0</v>
+        <v>633234</v>
       </c>
       <c r="L154" s="4">
-        <v>1</v>
+        <v>642216</v>
       </c>
       <c r="M154" s="4">
-        <v>0</v>
+        <v>588323</v>
       </c>
       <c r="N154" s="4">
-        <v>1</v>
+        <v>386228</v>
       </c>
       <c r="O154" s="4">
-        <v>0</v>
+        <v>413174</v>
       </c>
       <c r="P154" s="4">
-        <v>6</v>
+        <v>6000002</v>
       </c>
       <c r="Q154" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="R154" s="4" t="s">
         <v>21</v>
@@ -9063,13 +9281,13 @@
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
-        <v>220939</v>
+        <v>240035</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D155" s="4">
         <v>0</v>
@@ -9081,37 +9299,37 @@
         <v>0</v>
       </c>
       <c r="G155" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H155" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I155" s="4">
         <v>1</v>
       </c>
       <c r="J155" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K155" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L155" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M155" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N155" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O155" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P155" s="4">
         <v>6</v>
       </c>
       <c r="Q155" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="R155" s="4" t="s">
         <v>21</v>
@@ -9119,55 +9337,55 @@
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
-        <v>221035</v>
+        <v>240035</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D156" s="4">
         <v>0</v>
       </c>
       <c r="E156" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H156" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I156" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J156" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K156" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L156" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N156" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O156" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P156" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q156" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="R156" s="4" t="s">
         <v>21</v>
@@ -9175,55 +9393,55 @@
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
-        <v>220973</v>
+        <v>240035</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D157" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E157" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F157" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G157" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H157" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I157" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J157" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K157" s="4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L157" s="4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M157" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N157" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O157" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P157" s="4">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="Q157" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="R157" s="4" t="s">
         <v>21</v>
@@ -9231,81 +9449,81 @@
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
-        <v>220904</v>
+        <v>2417</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D158" s="4">
-        <v>0</v>
+        <v>330090</v>
       </c>
       <c r="E158" s="4">
-        <v>1</v>
+        <v>306512</v>
       </c>
       <c r="F158" s="4">
-        <v>0</v>
+        <v>343563</v>
       </c>
       <c r="G158" s="4">
-        <v>0</v>
+        <v>296407</v>
       </c>
       <c r="H158" s="4">
-        <v>1</v>
+        <v>464820</v>
       </c>
       <c r="I158" s="4">
-        <v>1</v>
+        <v>431138</v>
       </c>
       <c r="J158" s="4">
-        <v>1</v>
+        <v>330090</v>
       </c>
       <c r="K158" s="4">
-        <v>0</v>
+        <v>474925</v>
       </c>
       <c r="L158" s="4">
-        <v>1</v>
+        <v>481662</v>
       </c>
       <c r="M158" s="4">
-        <v>0</v>
+        <v>441243</v>
       </c>
       <c r="N158" s="4">
-        <v>1</v>
+        <v>289670</v>
       </c>
       <c r="O158" s="4">
-        <v>0</v>
+        <v>309880</v>
       </c>
       <c r="P158" s="4">
-        <v>6</v>
+        <v>4500000</v>
       </c>
       <c r="Q158" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="R158" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
-        <v>220999</v>
+        <v>2417</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D159" s="4">
         <v>0</v>
       </c>
       <c r="E159" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G159" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H159" s="4">
         <v>0</v>
@@ -9317,25 +9535,25 @@
         <v>0</v>
       </c>
       <c r="K159" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L159" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M159" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N159" s="4">
         <v>0</v>
       </c>
       <c r="O159" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P159" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q159" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="R159" s="4" t="s">
         <v>21</v>
@@ -9343,52 +9561,52 @@
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
-        <v>240035</v>
+        <v>2417</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D160" s="4">
-        <v>440120</v>
+        <v>0</v>
       </c>
       <c r="E160" s="4">
-        <v>408683</v>
+        <v>1</v>
       </c>
       <c r="F160" s="4">
-        <v>458084</v>
+        <v>0</v>
       </c>
       <c r="G160" s="4">
-        <v>395210</v>
+        <v>1</v>
       </c>
       <c r="H160" s="4">
-        <v>619760</v>
+        <v>0</v>
       </c>
       <c r="I160" s="4">
-        <v>574850</v>
+        <v>1</v>
       </c>
       <c r="J160" s="4">
-        <v>440120</v>
+        <v>0</v>
       </c>
       <c r="K160" s="4">
-        <v>633234</v>
+        <v>1</v>
       </c>
       <c r="L160" s="4">
-        <v>642216</v>
+        <v>0</v>
       </c>
       <c r="M160" s="4">
-        <v>588323</v>
+        <v>1</v>
       </c>
       <c r="N160" s="4">
-        <v>386228</v>
+        <v>0</v>
       </c>
       <c r="O160" s="4">
-        <v>413174</v>
+        <v>1</v>
       </c>
       <c r="P160" s="4">
-        <v>6000002</v>
+        <v>6</v>
       </c>
       <c r="Q160" s="4" t="s">
         <v>58</v>
@@ -9399,52 +9617,52 @@
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
-        <v>240035</v>
+        <v>2417</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D161" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E161" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F161" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G161" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H161" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I161" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J161" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K161" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L161" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M161" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N161" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O161" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P161" s="4">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="Q161" s="4" t="s">
         <v>58</v>
@@ -9455,52 +9673,52 @@
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
-        <v>240035</v>
+        <v>2425</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D162" s="4">
-        <v>0</v>
+        <v>330090</v>
       </c>
       <c r="E162" s="4">
-        <v>1</v>
+        <v>306512</v>
       </c>
       <c r="F162" s="4">
-        <v>0</v>
+        <v>343563</v>
       </c>
       <c r="G162" s="4">
-        <v>1</v>
+        <v>296407</v>
       </c>
       <c r="H162" s="4">
-        <v>0</v>
+        <v>464820</v>
       </c>
       <c r="I162" s="4">
-        <v>1</v>
+        <v>431138</v>
       </c>
       <c r="J162" s="4">
-        <v>0</v>
+        <v>330090</v>
       </c>
       <c r="K162" s="4">
-        <v>1</v>
+        <v>474925</v>
       </c>
       <c r="L162" s="4">
-        <v>0</v>
+        <v>481662</v>
       </c>
       <c r="M162" s="4">
-        <v>1</v>
+        <v>441243</v>
       </c>
       <c r="N162" s="4">
-        <v>0</v>
+        <v>289670</v>
       </c>
       <c r="O162" s="4">
-        <v>1</v>
+        <v>309880</v>
       </c>
       <c r="P162" s="4">
-        <v>6</v>
+        <v>4500000</v>
       </c>
       <c r="Q162" s="4" t="s">
         <v>58</v>
@@ -9511,52 +9729,52 @@
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
-        <v>240035</v>
+        <v>2425</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D163" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E163" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F163" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G163" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H163" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I163" s="4">
+        <v>1</v>
+      </c>
+      <c r="J163" s="4">
+        <v>0</v>
+      </c>
+      <c r="K163" s="4">
+        <v>1</v>
+      </c>
+      <c r="L163" s="4">
+        <v>0</v>
+      </c>
+      <c r="M163" s="4">
+        <v>1</v>
+      </c>
+      <c r="N163" s="4">
+        <v>0</v>
+      </c>
+      <c r="O163" s="4">
+        <v>1</v>
+      </c>
+      <c r="P163" s="4">
         <v>6</v>
-      </c>
-      <c r="J163" s="4">
-        <v>4</v>
-      </c>
-      <c r="K163" s="4">
-        <v>7</v>
-      </c>
-      <c r="L163" s="4">
-        <v>9</v>
-      </c>
-      <c r="M163" s="4">
-        <v>6</v>
-      </c>
-      <c r="N163" s="4">
-        <v>5</v>
-      </c>
-      <c r="O163" s="4">
-        <v>3</v>
-      </c>
-      <c r="P163" s="4">
-        <v>60</v>
       </c>
       <c r="Q163" s="4" t="s">
         <v>58</v>
@@ -9567,52 +9785,52 @@
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
-        <v>2417</v>
+        <v>2425</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D164" s="4">
-        <v>330090</v>
+        <v>0</v>
       </c>
       <c r="E164" s="4">
-        <v>306512</v>
+        <v>1</v>
       </c>
       <c r="F164" s="4">
-        <v>343563</v>
+        <v>0</v>
       </c>
       <c r="G164" s="4">
-        <v>296407</v>
+        <v>1</v>
       </c>
       <c r="H164" s="4">
-        <v>464820</v>
+        <v>0</v>
       </c>
       <c r="I164" s="4">
-        <v>431138</v>
+        <v>1</v>
       </c>
       <c r="J164" s="4">
-        <v>330090</v>
+        <v>0</v>
       </c>
       <c r="K164" s="4">
-        <v>474925</v>
+        <v>1</v>
       </c>
       <c r="L164" s="4">
-        <v>481662</v>
+        <v>0</v>
       </c>
       <c r="M164" s="4">
-        <v>441243</v>
+        <v>1</v>
       </c>
       <c r="N164" s="4">
-        <v>289670</v>
+        <v>0</v>
       </c>
       <c r="O164" s="4">
-        <v>309880</v>
+        <v>1</v>
       </c>
       <c r="P164" s="4">
-        <v>4500000</v>
+        <v>6</v>
       </c>
       <c r="Q164" s="4" t="s">
         <v>58</v>
@@ -9623,52 +9841,52 @@
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
-        <v>2417</v>
+        <v>2425</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D165" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E165" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F165" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G165" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H165" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I165" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J165" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K165" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L165" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M165" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N165" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O165" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P165" s="4">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="Q165" s="4" t="s">
         <v>58</v>
@@ -9679,52 +9897,52 @@
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
-        <v>2417</v>
+        <v>240048</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D166" s="4">
-        <v>0</v>
+        <v>183383</v>
       </c>
       <c r="E166" s="4">
-        <v>1</v>
+        <v>170284</v>
       </c>
       <c r="F166" s="4">
-        <v>0</v>
+        <v>190868</v>
       </c>
       <c r="G166" s="4">
-        <v>1</v>
+        <v>164671</v>
       </c>
       <c r="H166" s="4">
-        <v>0</v>
+        <v>258234</v>
       </c>
       <c r="I166" s="4">
-        <v>1</v>
+        <v>239521</v>
       </c>
       <c r="J166" s="4">
-        <v>0</v>
+        <v>183383</v>
       </c>
       <c r="K166" s="4">
-        <v>1</v>
+        <v>263847</v>
       </c>
       <c r="L166" s="4">
-        <v>0</v>
+        <v>267590</v>
       </c>
       <c r="M166" s="4">
-        <v>1</v>
+        <v>245135</v>
       </c>
       <c r="N166" s="4">
-        <v>0</v>
+        <v>160928</v>
       </c>
       <c r="O166" s="4">
-        <v>1</v>
+        <v>172156</v>
       </c>
       <c r="P166" s="4">
-        <v>6</v>
+        <v>2500000</v>
       </c>
       <c r="Q166" s="4" t="s">
         <v>58</v>
@@ -9735,52 +9953,52 @@
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
-        <v>2417</v>
+        <v>240048</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D167" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E167" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F167" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G167" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H167" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I167" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J167" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K167" s="4">
+        <v>1</v>
+      </c>
+      <c r="L167" s="4">
+        <v>0</v>
+      </c>
+      <c r="M167" s="4">
+        <v>1</v>
+      </c>
+      <c r="N167" s="4">
+        <v>0</v>
+      </c>
+      <c r="O167" s="4">
+        <v>1</v>
+      </c>
+      <c r="P167" s="4">
         <v>6</v>
-      </c>
-      <c r="L167" s="4">
-        <v>8</v>
-      </c>
-      <c r="M167" s="4">
-        <v>4</v>
-      </c>
-      <c r="N167" s="4">
-        <v>3</v>
-      </c>
-      <c r="O167" s="4">
-        <v>3</v>
-      </c>
-      <c r="P167" s="4">
-        <v>50</v>
       </c>
       <c r="Q167" s="4" t="s">
         <v>58</v>
@@ -9791,52 +10009,52 @@
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
-        <v>2425</v>
+        <v>240048</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D168" s="4">
-        <v>330090</v>
+        <v>0</v>
       </c>
       <c r="E168" s="4">
-        <v>306512</v>
+        <v>1</v>
       </c>
       <c r="F168" s="4">
-        <v>343563</v>
+        <v>0</v>
       </c>
       <c r="G168" s="4">
-        <v>296407</v>
+        <v>1</v>
       </c>
       <c r="H168" s="4">
-        <v>464820</v>
+        <v>0</v>
       </c>
       <c r="I168" s="4">
-        <v>431138</v>
+        <v>1</v>
       </c>
       <c r="J168" s="4">
-        <v>330090</v>
+        <v>0</v>
       </c>
       <c r="K168" s="4">
-        <v>474925</v>
+        <v>1</v>
       </c>
       <c r="L168" s="4">
-        <v>481662</v>
+        <v>0</v>
       </c>
       <c r="M168" s="4">
-        <v>441243</v>
+        <v>1</v>
       </c>
       <c r="N168" s="4">
-        <v>289670</v>
+        <v>0</v>
       </c>
       <c r="O168" s="4">
-        <v>309880</v>
+        <v>1</v>
       </c>
       <c r="P168" s="4">
-        <v>4500000</v>
+        <v>6</v>
       </c>
       <c r="Q168" s="4" t="s">
         <v>58</v>
@@ -9847,52 +10065,52 @@
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
-        <v>2425</v>
+        <v>240048</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D169" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E169" s="4">
         <v>1</v>
       </c>
       <c r="F169" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G169" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H169" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169" s="4">
         <v>1</v>
       </c>
       <c r="J169" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K169" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L169" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M169" s="4">
         <v>1</v>
       </c>
       <c r="N169" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O169" s="4">
         <v>1</v>
       </c>
       <c r="P169" s="4">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q169" s="4" t="s">
         <v>58</v>
@@ -9903,276 +10121,276 @@
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
-        <v>2425</v>
+        <v>240060</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D170" s="4">
-        <v>0</v>
+        <v>88024</v>
       </c>
       <c r="E170" s="4">
-        <v>1</v>
+        <v>81737</v>
       </c>
       <c r="F170" s="4">
-        <v>0</v>
+        <v>91617</v>
       </c>
       <c r="G170" s="4">
-        <v>1</v>
+        <v>79042</v>
       </c>
       <c r="H170" s="4">
-        <v>0</v>
+        <v>123952</v>
       </c>
       <c r="I170" s="4">
-        <v>1</v>
+        <v>114970</v>
       </c>
       <c r="J170" s="4">
-        <v>0</v>
+        <v>88024</v>
       </c>
       <c r="K170" s="4">
-        <v>1</v>
+        <v>126647</v>
       </c>
       <c r="L170" s="4">
-        <v>0</v>
+        <v>128443</v>
       </c>
       <c r="M170" s="4">
-        <v>1</v>
+        <v>117665</v>
       </c>
       <c r="N170" s="4">
-        <v>0</v>
+        <v>77246</v>
       </c>
       <c r="O170" s="4">
-        <v>1</v>
+        <v>82635</v>
       </c>
       <c r="P170" s="4">
-        <v>6</v>
+        <v>1200002</v>
       </c>
       <c r="Q170" s="4" t="s">
         <v>58</v>
       </c>
       <c r="R170" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
-        <v>2425</v>
+        <v>240060</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D171" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E171" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F171" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G171" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H171" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I171" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J171" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K171" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L171" s="4">
+        <v>0</v>
+      </c>
+      <c r="M171" s="4">
+        <v>1</v>
+      </c>
+      <c r="N171" s="4">
+        <v>0</v>
+      </c>
+      <c r="O171" s="4">
+        <v>1</v>
+      </c>
+      <c r="P171" s="4">
         <v>6</v>
-      </c>
-      <c r="M171" s="4">
-        <v>3</v>
-      </c>
-      <c r="N171" s="4">
-        <v>3</v>
-      </c>
-      <c r="O171" s="4">
-        <v>2</v>
-      </c>
-      <c r="P171" s="4">
-        <v>40</v>
       </c>
       <c r="Q171" s="4" t="s">
         <v>58</v>
       </c>
       <c r="R171" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
-        <v>240048</v>
+        <v>240060</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D172" s="4">
-        <v>183383</v>
+        <v>0</v>
       </c>
       <c r="E172" s="4">
-        <v>170284</v>
+        <v>1</v>
       </c>
       <c r="F172" s="4">
-        <v>190868</v>
+        <v>0</v>
       </c>
       <c r="G172" s="4">
-        <v>164671</v>
+        <v>1</v>
       </c>
       <c r="H172" s="4">
-        <v>258234</v>
+        <v>0</v>
       </c>
       <c r="I172" s="4">
-        <v>239521</v>
+        <v>1</v>
       </c>
       <c r="J172" s="4">
-        <v>183383</v>
+        <v>0</v>
       </c>
       <c r="K172" s="4">
-        <v>263847</v>
+        <v>1</v>
       </c>
       <c r="L172" s="4">
-        <v>267590</v>
+        <v>0</v>
       </c>
       <c r="M172" s="4">
-        <v>245135</v>
+        <v>1</v>
       </c>
       <c r="N172" s="4">
-        <v>160928</v>
+        <v>0</v>
       </c>
       <c r="O172" s="4">
-        <v>172156</v>
+        <v>1</v>
       </c>
       <c r="P172" s="4">
-        <v>2500000</v>
+        <v>6</v>
       </c>
       <c r="Q172" s="4" t="s">
         <v>58</v>
       </c>
       <c r="R172" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
-        <v>240048</v>
+        <v>240060</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D173" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E173" s="4">
         <v>1</v>
       </c>
       <c r="F173" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G173" s="4">
         <v>1</v>
       </c>
       <c r="H173" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I173" s="4">
         <v>1</v>
       </c>
       <c r="J173" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K173" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L173" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M173" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N173" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O173" s="4">
         <v>1</v>
       </c>
       <c r="P173" s="4">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q173" s="4" t="s">
         <v>58</v>
       </c>
       <c r="R173" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
-        <v>240048</v>
+        <v>2419</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D174" s="4">
-        <v>0</v>
+        <v>256737</v>
       </c>
       <c r="E174" s="4">
-        <v>1</v>
+        <v>238398</v>
       </c>
       <c r="F174" s="4">
-        <v>0</v>
+        <v>267216</v>
       </c>
       <c r="G174" s="4">
-        <v>1</v>
+        <v>230539</v>
       </c>
       <c r="H174" s="4">
-        <v>0</v>
+        <v>361527</v>
       </c>
       <c r="I174" s="4">
-        <v>1</v>
+        <v>335329</v>
       </c>
       <c r="J174" s="4">
-        <v>0</v>
+        <v>256737</v>
       </c>
       <c r="K174" s="4">
-        <v>1</v>
+        <v>369386</v>
       </c>
       <c r="L174" s="4">
-        <v>0</v>
+        <v>374626</v>
       </c>
       <c r="M174" s="4">
-        <v>1</v>
+        <v>343189</v>
       </c>
       <c r="N174" s="4">
-        <v>0</v>
+        <v>225299</v>
       </c>
       <c r="O174" s="4">
-        <v>1</v>
+        <v>241018</v>
       </c>
       <c r="P174" s="4">
-        <v>6</v>
+        <v>3500001</v>
       </c>
       <c r="Q174" s="4" t="s">
         <v>58</v>
@@ -10183,52 +10401,52 @@
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
-        <v>240048</v>
+        <v>2419</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D175" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E175" s="4">
         <v>1</v>
       </c>
       <c r="F175" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G175" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H175" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I175" s="4">
         <v>1</v>
       </c>
       <c r="J175" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K175" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L175" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M175" s="4">
         <v>1</v>
       </c>
       <c r="N175" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O175" s="4">
         <v>1</v>
       </c>
       <c r="P175" s="4">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q175" s="4" t="s">
         <v>58</v>
@@ -10239,276 +10457,276 @@
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
-        <v>240060</v>
+        <v>2419</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D176" s="4">
-        <v>88024</v>
+        <v>0</v>
       </c>
       <c r="E176" s="4">
-        <v>81737</v>
+        <v>1</v>
       </c>
       <c r="F176" s="4">
-        <v>91617</v>
+        <v>0</v>
       </c>
       <c r="G176" s="4">
-        <v>79042</v>
+        <v>1</v>
       </c>
       <c r="H176" s="4">
-        <v>123952</v>
+        <v>0</v>
       </c>
       <c r="I176" s="4">
-        <v>114970</v>
+        <v>1</v>
       </c>
       <c r="J176" s="4">
-        <v>88024</v>
+        <v>0</v>
       </c>
       <c r="K176" s="4">
-        <v>126647</v>
+        <v>1</v>
       </c>
       <c r="L176" s="4">
-        <v>128443</v>
+        <v>0</v>
       </c>
       <c r="M176" s="4">
-        <v>117665</v>
+        <v>1</v>
       </c>
       <c r="N176" s="4">
-        <v>77246</v>
+        <v>0</v>
       </c>
       <c r="O176" s="4">
-        <v>82635</v>
+        <v>1</v>
       </c>
       <c r="P176" s="4">
-        <v>1200002</v>
+        <v>6</v>
       </c>
       <c r="Q176" s="4" t="s">
         <v>58</v>
       </c>
       <c r="R176" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
-        <v>240060</v>
+        <v>2419</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D177" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E177" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F177" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G177" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H177" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I177" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J177" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K177" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L177" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M177" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N177" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O177" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P177" s="4">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="Q177" s="4" t="s">
         <v>58</v>
       </c>
       <c r="R177" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
-        <v>240060</v>
+        <v>240058</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D178" s="4">
-        <v>0</v>
+        <v>176048</v>
       </c>
       <c r="E178" s="4">
-        <v>1</v>
+        <v>163473</v>
       </c>
       <c r="F178" s="4">
-        <v>0</v>
+        <v>183234</v>
       </c>
       <c r="G178" s="4">
-        <v>1</v>
+        <v>158084</v>
       </c>
       <c r="H178" s="4">
-        <v>0</v>
+        <v>247904</v>
       </c>
       <c r="I178" s="4">
-        <v>1</v>
+        <v>229940</v>
       </c>
       <c r="J178" s="4">
-        <v>0</v>
+        <v>176048</v>
       </c>
       <c r="K178" s="4">
-        <v>1</v>
+        <v>253293</v>
       </c>
       <c r="L178" s="4">
-        <v>0</v>
+        <v>256886</v>
       </c>
       <c r="M178" s="4">
-        <v>1</v>
+        <v>235329</v>
       </c>
       <c r="N178" s="4">
-        <v>0</v>
+        <v>154491</v>
       </c>
       <c r="O178" s="4">
-        <v>1</v>
+        <v>165269</v>
       </c>
       <c r="P178" s="4">
-        <v>6</v>
+        <v>2399999</v>
       </c>
       <c r="Q178" s="4" t="s">
         <v>58</v>
       </c>
       <c r="R178" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
-        <v>240060</v>
+        <v>240058</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D179" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E179" s="4">
         <v>1</v>
       </c>
       <c r="F179" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G179" s="4">
         <v>1</v>
       </c>
       <c r="H179" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I179" s="4">
         <v>1</v>
       </c>
       <c r="J179" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K179" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L179" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M179" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N179" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O179" s="4">
         <v>1</v>
       </c>
       <c r="P179" s="4">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q179" s="4" t="s">
         <v>58</v>
       </c>
       <c r="R179" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
-        <v>2419</v>
+        <v>240058</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D180" s="4">
-        <v>256737</v>
+        <v>0</v>
       </c>
       <c r="E180" s="4">
-        <v>238398</v>
+        <v>1</v>
       </c>
       <c r="F180" s="4">
-        <v>267216</v>
+        <v>0</v>
       </c>
       <c r="G180" s="4">
-        <v>230539</v>
+        <v>1</v>
       </c>
       <c r="H180" s="4">
-        <v>361527</v>
+        <v>0</v>
       </c>
       <c r="I180" s="4">
-        <v>335329</v>
+        <v>1</v>
       </c>
       <c r="J180" s="4">
-        <v>256737</v>
+        <v>0</v>
       </c>
       <c r="K180" s="4">
-        <v>369386</v>
+        <v>1</v>
       </c>
       <c r="L180" s="4">
-        <v>374626</v>
+        <v>0</v>
       </c>
       <c r="M180" s="4">
-        <v>343189</v>
+        <v>1</v>
       </c>
       <c r="N180" s="4">
-        <v>225299</v>
+        <v>0</v>
       </c>
       <c r="O180" s="4">
-        <v>241018</v>
+        <v>1</v>
       </c>
       <c r="P180" s="4">
-        <v>3500001</v>
+        <v>6</v>
       </c>
       <c r="Q180" s="4" t="s">
         <v>58</v>
@@ -10519,52 +10737,52 @@
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
-        <v>2419</v>
+        <v>240058</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D181" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E181" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F181" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G181" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H181" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I181" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J181" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K181" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L181" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M181" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N181" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O181" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P181" s="4">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="Q181" s="4" t="s">
         <v>58</v>
@@ -10575,55 +10793,55 @@
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
-        <v>2419</v>
+        <v>230305</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D182" s="4">
-        <v>0</v>
+        <v>299114</v>
       </c>
       <c r="E182" s="4">
-        <v>1</v>
+        <v>319055</v>
       </c>
       <c r="F182" s="4">
-        <v>0</v>
+        <v>445347</v>
       </c>
       <c r="G182" s="4">
-        <v>1</v>
+        <v>458641</v>
       </c>
       <c r="H182" s="4">
-        <v>0</v>
+        <v>405465</v>
       </c>
       <c r="I182" s="4">
-        <v>1</v>
+        <v>438700</v>
       </c>
       <c r="J182" s="4">
-        <v>0</v>
+        <v>392171</v>
       </c>
       <c r="K182" s="4">
-        <v>1</v>
+        <v>438700</v>
       </c>
       <c r="L182" s="4">
-        <v>0</v>
+        <v>398818</v>
       </c>
       <c r="M182" s="4">
-        <v>1</v>
+        <v>252585</v>
       </c>
       <c r="N182" s="4">
-        <v>0</v>
+        <v>212703</v>
       </c>
       <c r="O182" s="4">
-        <v>1</v>
+        <v>438700</v>
       </c>
       <c r="P182" s="4">
-        <v>6</v>
+        <v>4499999</v>
       </c>
       <c r="Q182" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="R182" s="4" t="s">
         <v>21</v>
@@ -10631,55 +10849,55 @@
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
-        <v>2419</v>
+        <v>230305</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D183" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F183" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G183" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H183" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I183" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J183" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K183" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L183" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M183" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N183" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O183" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P183" s="4">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="Q183" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="R183" s="4" t="s">
         <v>21</v>
@@ -10687,55 +10905,55 @@
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
-        <v>240058</v>
+        <v>230305</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D184" s="4">
-        <v>176048</v>
+        <v>0</v>
       </c>
       <c r="E184" s="4">
-        <v>163473</v>
+        <v>1</v>
       </c>
       <c r="F184" s="4">
-        <v>183234</v>
+        <v>0</v>
       </c>
       <c r="G184" s="4">
-        <v>158084</v>
+        <v>0</v>
       </c>
       <c r="H184" s="4">
-        <v>247904</v>
+        <v>1</v>
       </c>
       <c r="I184" s="4">
-        <v>229940</v>
+        <v>0</v>
       </c>
       <c r="J184" s="4">
-        <v>176048</v>
+        <v>1</v>
       </c>
       <c r="K184" s="4">
-        <v>253293</v>
+        <v>0</v>
       </c>
       <c r="L184" s="4">
-        <v>256886</v>
+        <v>1</v>
       </c>
       <c r="M184" s="4">
-        <v>235329</v>
+        <v>0</v>
       </c>
       <c r="N184" s="4">
-        <v>154491</v>
+        <v>1</v>
       </c>
       <c r="O184" s="4">
-        <v>165269</v>
+        <v>0</v>
       </c>
       <c r="P184" s="4">
-        <v>2399999</v>
+        <v>5</v>
       </c>
       <c r="Q184" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="R184" s="4" t="s">
         <v>21</v>
@@ -10743,55 +10961,19 @@
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
-        <v>240058</v>
+        <v>230305</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D185" s="4">
-        <v>0</v>
-      </c>
-      <c r="E185" s="4">
-        <v>1</v>
-      </c>
-      <c r="F185" s="4">
-        <v>0</v>
-      </c>
-      <c r="G185" s="4">
-        <v>1</v>
-      </c>
-      <c r="H185" s="4">
-        <v>0</v>
-      </c>
-      <c r="I185" s="4">
-        <v>1</v>
-      </c>
-      <c r="J185" s="4">
-        <v>0</v>
-      </c>
-      <c r="K185" s="4">
-        <v>1</v>
-      </c>
-      <c r="L185" s="4">
-        <v>0</v>
-      </c>
-      <c r="M185" s="4">
-        <v>1</v>
-      </c>
-      <c r="N185" s="4">
-        <v>0</v>
-      </c>
-      <c r="O185" s="4">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="P185" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q185" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="R185" s="4" t="s">
         <v>21</v>
@@ -10799,55 +10981,55 @@
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
-        <v>240058</v>
+        <v>230305</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D186" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E186" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F186" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G186" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H186" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I186" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J186" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K186" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L186" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M186" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N186" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O186" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P186" s="4">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="Q186" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="R186" s="4" t="s">
         <v>21</v>
@@ -10855,55 +11037,55 @@
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
-        <v>240058</v>
+        <v>230305</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D187" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E187" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F187" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G187" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H187" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I187" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J187" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K187" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L187" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M187" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N187" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O187" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P187" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="Q187" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="R187" s="4" t="s">
         <v>21</v>
@@ -10911,10 +11093,10 @@
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
-        <v>230305</v>
+        <v>230307</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>19</v>
@@ -10967,10 +11149,10 @@
     </row>
     <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
-        <v>230305</v>
+        <v>230307</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>23</v>
@@ -11023,10 +11205,10 @@
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
-        <v>230305</v>
+        <v>230307</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>24</v>
@@ -11079,10 +11261,10 @@
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
-        <v>230305</v>
+        <v>230307</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>56</v>
@@ -11099,10 +11281,10 @@
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
-        <v>230305</v>
+        <v>230307</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>28</v>
@@ -11117,7 +11299,7 @@
         <v>2</v>
       </c>
       <c r="G192" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H192" s="4">
         <v>2</v>
@@ -11135,16 +11317,16 @@
         <v>2</v>
       </c>
       <c r="M192" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N192" s="4">
+        <v>1</v>
+      </c>
+      <c r="O192" s="4">
         <v>2</v>
       </c>
-      <c r="O192" s="4">
-        <v>3</v>
-      </c>
       <c r="P192" s="4">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Q192" s="4" t="s">
         <v>66</v>
@@ -11155,10 +11337,10 @@
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
-        <v>230305</v>
+        <v>230307</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>39</v>
@@ -11211,10 +11393,10 @@
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" s="4">
-        <v>230307</v>
+        <v>230306</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>19</v>
@@ -11267,10 +11449,10 @@
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
-        <v>230307</v>
+        <v>230306</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>23</v>
@@ -11323,10 +11505,10 @@
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
-        <v>230307</v>
+        <v>230306</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C196" s="4" t="s">
         <v>24</v>
@@ -11379,10 +11561,10 @@
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
-        <v>230307</v>
+        <v>230306</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>56</v>
@@ -11399,10 +11581,10 @@
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
-        <v>230307</v>
+        <v>230306</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>28</v>
@@ -11417,7 +11599,7 @@
         <v>2</v>
       </c>
       <c r="G198" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H198" s="4">
         <v>2</v>
@@ -11435,16 +11617,16 @@
         <v>2</v>
       </c>
       <c r="M198" s="4">
+        <v>3</v>
+      </c>
+      <c r="N198" s="4">
         <v>2</v>
       </c>
-      <c r="N198" s="4">
-        <v>1</v>
-      </c>
       <c r="O198" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P198" s="4">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q198" s="4" t="s">
         <v>66</v>
@@ -11455,10 +11637,10 @@
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
-        <v>230307</v>
+        <v>230306</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>39</v>
@@ -11511,10 +11693,10 @@
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" s="4">
-        <v>230306</v>
+        <v>230301</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>19</v>
@@ -11567,10 +11749,10 @@
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
-        <v>230306</v>
+        <v>230301</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>23</v>
@@ -11623,10 +11805,10 @@
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
-        <v>230306</v>
+        <v>230301</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C202" s="4" t="s">
         <v>24</v>
@@ -11679,10 +11861,10 @@
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
-        <v>230306</v>
+        <v>230301</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C203" s="4" t="s">
         <v>56</v>
@@ -11699,10 +11881,10 @@
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
-        <v>230306</v>
+        <v>230301</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>28</v>
@@ -11755,10 +11937,10 @@
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
-        <v>230306</v>
+        <v>230301</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>39</v>
@@ -11811,55 +11993,55 @@
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" s="4">
-        <v>230301</v>
+        <v>280037</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D206" s="4">
-        <v>299114</v>
+        <v>80233</v>
       </c>
       <c r="E206" s="4">
-        <v>319055</v>
+        <v>132558</v>
       </c>
       <c r="F206" s="4">
-        <v>445347</v>
+        <v>125581</v>
       </c>
       <c r="G206" s="4">
-        <v>458641</v>
+        <v>102907</v>
       </c>
       <c r="H206" s="4">
-        <v>405465</v>
+        <v>66279</v>
       </c>
       <c r="I206" s="4">
-        <v>438700</v>
+        <v>125581</v>
       </c>
       <c r="J206" s="4">
-        <v>392171</v>
+        <v>120349</v>
       </c>
       <c r="K206" s="4">
-        <v>438700</v>
+        <v>162209</v>
       </c>
       <c r="L206" s="4">
-        <v>398818</v>
+        <v>134302</v>
       </c>
       <c r="M206" s="4">
-        <v>252585</v>
+        <v>139535</v>
       </c>
       <c r="N206" s="4">
-        <v>212703</v>
+        <v>76745</v>
       </c>
       <c r="O206" s="4">
-        <v>438700</v>
+        <v>83721</v>
       </c>
       <c r="P206" s="4">
-        <v>4499999</v>
+        <v>1350000</v>
       </c>
       <c r="Q206" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="R206" s="4" t="s">
         <v>21</v>
@@ -11867,55 +12049,55 @@
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
-        <v>230301</v>
+        <v>280037</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D207" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E207" s="4">
         <v>1</v>
       </c>
       <c r="F207" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G207" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H207" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I207" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J207" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K207" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L207" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M207" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N207" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O207" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P207" s="4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Q207" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="R207" s="4" t="s">
         <v>21</v>
@@ -11923,13 +12105,13 @@
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" s="4">
-        <v>230301</v>
+        <v>280037</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D208" s="4">
         <v>0</v>
@@ -11938,7 +12120,7 @@
         <v>1</v>
       </c>
       <c r="F208" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G208" s="4">
         <v>0</v>
@@ -11947,31 +12129,31 @@
         <v>1</v>
       </c>
       <c r="I208" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J208" s="4">
         <v>1</v>
       </c>
       <c r="K208" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L208" s="4">
         <v>1</v>
       </c>
       <c r="M208" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N208" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O208" s="4">
         <v>0</v>
       </c>
       <c r="P208" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q208" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="R208" s="4" t="s">
         <v>21</v>
@@ -11979,19 +12161,55 @@
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
-        <v>230301</v>
+        <v>280037</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>56</v>
+        <v>24</v>
+      </c>
+      <c r="D209" s="4">
+        <v>0</v>
+      </c>
+      <c r="E209" s="4">
+        <v>1</v>
+      </c>
+      <c r="F209" s="4">
+        <v>0</v>
+      </c>
+      <c r="G209" s="4">
+        <v>0</v>
+      </c>
+      <c r="H209" s="4">
+        <v>0</v>
+      </c>
+      <c r="I209" s="4">
+        <v>1</v>
+      </c>
+      <c r="J209" s="4">
+        <v>0</v>
+      </c>
+      <c r="K209" s="4">
+        <v>0</v>
+      </c>
+      <c r="L209" s="4">
+        <v>1</v>
+      </c>
+      <c r="M209" s="4">
+        <v>0</v>
+      </c>
+      <c r="N209" s="4">
+        <v>0</v>
+      </c>
+      <c r="O209" s="4">
+        <v>1</v>
       </c>
       <c r="P209" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q209" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="R209" s="4" t="s">
         <v>21</v>
@@ -11999,55 +12217,55 @@
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" s="4">
-        <v>230301</v>
+        <v>280037</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D210" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E210" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F210" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G210" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H210" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I210" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J210" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K210" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L210" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M210" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N210" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O210" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P210" s="4">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="Q210" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="R210" s="4" t="s">
         <v>21</v>
@@ -12055,13 +12273,13 @@
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
-        <v>230301</v>
+        <v>280037</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D211" s="4">
         <v>0</v>
@@ -12070,40 +12288,40 @@
         <v>1</v>
       </c>
       <c r="F211" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G211" s="4">
         <v>0</v>
       </c>
       <c r="H211" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I211" s="4">
         <v>0</v>
       </c>
       <c r="J211" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K211" s="4">
         <v>0</v>
       </c>
       <c r="L211" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M211" s="4">
         <v>0</v>
       </c>
       <c r="N211" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O211" s="4">
         <v>0</v>
       </c>
       <c r="P211" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q211" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="R211" s="4" t="s">
         <v>21</v>
@@ -12117,46 +12335,46 @@
         <v>70</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D212" s="4">
-        <v>80233</v>
+        <v>0</v>
       </c>
       <c r="E212" s="4">
-        <v>132558</v>
+        <v>0</v>
       </c>
       <c r="F212" s="4">
-        <v>125581</v>
+        <v>0</v>
       </c>
       <c r="G212" s="4">
-        <v>102907</v>
+        <v>0</v>
       </c>
       <c r="H212" s="4">
-        <v>66279</v>
+        <v>0</v>
       </c>
       <c r="I212" s="4">
-        <v>125581</v>
+        <v>0</v>
       </c>
       <c r="J212" s="4">
-        <v>120349</v>
+        <v>0</v>
       </c>
       <c r="K212" s="4">
-        <v>162209</v>
+        <v>0</v>
       </c>
       <c r="L212" s="4">
-        <v>134302</v>
+        <v>1</v>
       </c>
       <c r="M212" s="4">
-        <v>139535</v>
+        <v>0</v>
       </c>
       <c r="N212" s="4">
-        <v>76745</v>
+        <v>0</v>
       </c>
       <c r="O212" s="4">
-        <v>83721</v>
+        <v>0</v>
       </c>
       <c r="P212" s="4">
-        <v>1350000</v>
+        <v>1</v>
       </c>
       <c r="Q212" s="4" t="s">
         <v>71</v>
@@ -12173,46 +12391,46 @@
         <v>70</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D213" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E213" s="4">
         <v>1</v>
       </c>
       <c r="F213" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G213" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H213" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I213" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J213" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K213" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L213" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M213" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N213" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O213" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P213" s="4">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q213" s="4" t="s">
         <v>71</v>
@@ -12229,46 +12447,46 @@
         <v>70</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D214" s="4">
-        <v>0</v>
+        <v>95090</v>
       </c>
       <c r="E214" s="4">
-        <v>1</v>
+        <v>157106</v>
       </c>
       <c r="F214" s="4">
-        <v>1</v>
+        <v>148837</v>
       </c>
       <c r="G214" s="4">
-        <v>0</v>
+        <v>121964</v>
       </c>
       <c r="H214" s="4">
-        <v>1</v>
+        <v>78553</v>
       </c>
       <c r="I214" s="4">
-        <v>1</v>
+        <v>148837</v>
       </c>
       <c r="J214" s="4">
-        <v>1</v>
+        <v>142636</v>
       </c>
       <c r="K214" s="4">
-        <v>1</v>
+        <v>192248</v>
       </c>
       <c r="L214" s="4">
-        <v>1</v>
+        <v>159173</v>
       </c>
       <c r="M214" s="4">
-        <v>1</v>
+        <v>165375</v>
       </c>
       <c r="N214" s="4">
-        <v>0</v>
+        <v>90956</v>
       </c>
       <c r="O214" s="4">
-        <v>0</v>
+        <v>99225</v>
       </c>
       <c r="P214" s="4">
-        <v>8</v>
+        <v>1600000</v>
       </c>
       <c r="Q214" s="4" t="s">
         <v>71</v>
@@ -12279,55 +12497,55 @@
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
-        <v>280037</v>
+        <v>2712</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D215" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="E215" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="F215" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G215" s="4">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="H215" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="I215" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="J215" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="K215" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="L215" s="4">
-        <v>1</v>
+        <v>300000</v>
       </c>
       <c r="M215" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="N215" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O215" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="P215" s="4">
-        <v>4</v>
+        <v>2200000</v>
       </c>
       <c r="Q215" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="R215" s="4" t="s">
         <v>21</v>
@@ -12335,37 +12553,37 @@
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
-        <v>280037</v>
+        <v>2712</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D216" s="4">
         <v>0</v>
       </c>
       <c r="E216" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F216" s="4">
         <v>0</v>
       </c>
       <c r="G216" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H216" s="4">
         <v>0</v>
       </c>
       <c r="I216" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J216" s="4">
         <v>0</v>
       </c>
       <c r="K216" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L216" s="4">
         <v>0</v>
@@ -12377,13 +12595,13 @@
         <v>0</v>
       </c>
       <c r="O216" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P216" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q216" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="R216" s="4" t="s">
         <v>21</v>
@@ -12391,13 +12609,13 @@
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
-        <v>280037</v>
+        <v>2712</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D217" s="4">
         <v>0</v>
@@ -12406,40 +12624,40 @@
         <v>1</v>
       </c>
       <c r="F217" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G217" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H217" s="4">
         <v>0</v>
       </c>
       <c r="I217" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J217" s="4">
         <v>0</v>
       </c>
       <c r="K217" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L217" s="4">
         <v>0</v>
       </c>
       <c r="M217" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N217" s="4">
         <v>0</v>
       </c>
       <c r="O217" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P217" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q217" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="R217" s="4" t="s">
         <v>21</v>
@@ -12447,55 +12665,55 @@
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
-        <v>280037</v>
+        <v>2712</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D218" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E218" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F218" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G218" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H218" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I218" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J218" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K218" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L218" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M218" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N218" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O218" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P218" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q218" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="R218" s="4" t="s">
         <v>21</v>
@@ -12503,55 +12721,55 @@
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
-        <v>280037</v>
+        <v>2712</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D219" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E219" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F219" s="4">
         <v>1</v>
       </c>
       <c r="G219" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H219" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I219" s="4">
         <v>1</v>
       </c>
       <c r="J219" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K219" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L219" s="4">
         <v>1</v>
       </c>
       <c r="M219" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N219" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O219" s="4">
         <v>1</v>
       </c>
       <c r="P219" s="4">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Q219" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="R219" s="4" t="s">
         <v>21</v>
@@ -12559,55 +12777,55 @@
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
-        <v>280037</v>
+        <v>270018</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D220" s="4">
-        <v>95090</v>
+        <v>0</v>
       </c>
       <c r="E220" s="4">
-        <v>157106</v>
+        <v>0</v>
       </c>
       <c r="F220" s="4">
-        <v>148837</v>
+        <v>200000</v>
       </c>
       <c r="G220" s="4">
-        <v>121964</v>
+        <v>100000</v>
       </c>
       <c r="H220" s="4">
-        <v>78553</v>
+        <v>100000</v>
       </c>
       <c r="I220" s="4">
-        <v>148837</v>
+        <v>100000</v>
       </c>
       <c r="J220" s="4">
-        <v>142636</v>
+        <v>200000</v>
       </c>
       <c r="K220" s="4">
-        <v>192248</v>
+        <v>200000</v>
       </c>
       <c r="L220" s="4">
-        <v>159173</v>
+        <v>200000</v>
       </c>
       <c r="M220" s="4">
-        <v>165375</v>
+        <v>200000</v>
       </c>
       <c r="N220" s="4">
-        <v>90956</v>
+        <v>100000</v>
       </c>
       <c r="O220" s="4">
-        <v>99225</v>
+        <v>100000</v>
       </c>
       <c r="P220" s="4">
-        <v>1600000</v>
+        <v>1500000</v>
       </c>
       <c r="Q220" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="R220" s="4" t="s">
         <v>21</v>
@@ -12615,52 +12833,52 @@
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
-        <v>2712</v>
+        <v>270018</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D221" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="E221" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="F221" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G221" s="4">
-        <v>300000</v>
+        <v>1</v>
       </c>
       <c r="H221" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="I221" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="J221" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="K221" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="L221" s="4">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="M221" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="N221" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="O221" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="P221" s="4">
-        <v>2200000</v>
+        <v>5</v>
       </c>
       <c r="Q221" s="4" t="s">
         <v>73</v>
@@ -12671,19 +12889,19 @@
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
-        <v>2712</v>
+        <v>270018</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D222" s="4">
         <v>0</v>
       </c>
       <c r="E222" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F222" s="4">
         <v>0</v>
@@ -12701,7 +12919,7 @@
         <v>0</v>
       </c>
       <c r="K222" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L222" s="4">
         <v>0</v>
@@ -12716,7 +12934,7 @@
         <v>1</v>
       </c>
       <c r="P222" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q222" s="4" t="s">
         <v>73</v>
@@ -12727,52 +12945,52 @@
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
-        <v>2712</v>
+        <v>270018</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D223" s="4">
         <v>0</v>
       </c>
       <c r="E223" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F223" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G223" s="4">
         <v>1</v>
       </c>
       <c r="H223" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I223" s="4">
         <v>1</v>
       </c>
       <c r="J223" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K223" s="4">
         <v>1</v>
       </c>
       <c r="L223" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M223" s="4">
         <v>1</v>
       </c>
       <c r="N223" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O223" s="4">
         <v>1</v>
       </c>
       <c r="P223" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q223" s="4" t="s">
         <v>73</v>
@@ -12783,52 +13001,52 @@
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
-        <v>2712</v>
+        <v>270018</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D224" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E224" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F224" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G224" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H224" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I224" s="4">
         <v>1</v>
       </c>
       <c r="J224" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K224" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L224" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M224" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N224" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O224" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P224" s="4">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="Q224" s="4" t="s">
         <v>73</v>
@@ -12839,52 +13057,52 @@
     </row>
     <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
-        <v>2712</v>
+        <v>270035</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D225" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="E225" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="F225" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="G225" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H225" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="I225" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="J225" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="K225" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="L225" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="M225" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="N225" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="O225" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="P225" s="4">
-        <v>4</v>
+        <v>1700000</v>
       </c>
       <c r="Q225" s="4" t="s">
         <v>73</v>
@@ -12895,52 +13113,52 @@
     </row>
     <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
-        <v>270018</v>
+        <v>270035</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D226" s="4">
         <v>0</v>
       </c>
       <c r="E226" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F226" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G226" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="H226" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="I226" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="J226" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="K226" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="L226" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="M226" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="N226" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="O226" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="P226" s="4">
-        <v>1500000</v>
+        <v>6</v>
       </c>
       <c r="Q226" s="4" t="s">
         <v>73</v>
@@ -12951,19 +13169,19 @@
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
-        <v>270018</v>
+        <v>270035</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D227" s="4">
         <v>0</v>
       </c>
       <c r="E227" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F227" s="4">
         <v>0</v>
@@ -12996,7 +13214,7 @@
         <v>1</v>
       </c>
       <c r="P227" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q227" s="4" t="s">
         <v>73</v>
@@ -13007,52 +13225,52 @@
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
-        <v>270018</v>
+        <v>270035</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D228" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E228" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F228" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G228" s="4">
         <v>1</v>
       </c>
       <c r="H228" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I228" s="4">
         <v>1</v>
       </c>
       <c r="J228" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K228" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L228" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M228" s="4">
         <v>1</v>
       </c>
       <c r="N228" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O228" s="4">
         <v>1</v>
       </c>
       <c r="P228" s="4">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q228" s="4" t="s">
         <v>73</v>
@@ -13063,13 +13281,13 @@
     </row>
     <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
-        <v>270018</v>
+        <v>270035</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D229" s="4">
         <v>0</v>
@@ -13081,34 +13299,34 @@
         <v>1</v>
       </c>
       <c r="G229" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H229" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I229" s="4">
         <v>1</v>
       </c>
       <c r="J229" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K229" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L229" s="4">
         <v>1</v>
       </c>
       <c r="M229" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N229" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O229" s="4">
         <v>1</v>
       </c>
       <c r="P229" s="4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q229" s="4" t="s">
         <v>73</v>
@@ -13119,52 +13337,52 @@
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
-        <v>270018</v>
+        <v>270029</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D230" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="E230" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="F230" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="G230" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H230" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="I230" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="J230" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="K230" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="L230" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="M230" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="N230" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="O230" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="P230" s="4">
-        <v>4</v>
+        <v>1700000</v>
       </c>
       <c r="Q230" s="4" t="s">
         <v>73</v>
@@ -13175,52 +13393,52 @@
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
-        <v>270035</v>
+        <v>270029</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D231" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="E231" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="F231" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G231" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="H231" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="I231" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="J231" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="K231" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="L231" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="M231" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="N231" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="O231" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="P231" s="4">
-        <v>1700000</v>
+        <v>6</v>
       </c>
       <c r="Q231" s="4" t="s">
         <v>73</v>
@@ -13231,13 +13449,13 @@
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
-        <v>270035</v>
+        <v>270029</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D232" s="4">
         <v>0</v>
@@ -13287,52 +13505,52 @@
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
-        <v>270035</v>
+        <v>270029</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D233" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E233" s="4">
         <v>1</v>
       </c>
       <c r="F233" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G233" s="4">
         <v>1</v>
       </c>
       <c r="H233" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I233" s="4">
         <v>1</v>
       </c>
       <c r="J233" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K233" s="4">
         <v>1</v>
       </c>
       <c r="L233" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M233" s="4">
         <v>1</v>
       </c>
       <c r="N233" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O233" s="4">
         <v>1</v>
       </c>
       <c r="P233" s="4">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q233" s="4" t="s">
         <v>73</v>
@@ -13343,52 +13561,52 @@
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
-        <v>270035</v>
+        <v>270029</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D234" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E234" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F234" s="4">
         <v>1</v>
       </c>
       <c r="G234" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H234" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I234" s="4">
         <v>1</v>
       </c>
       <c r="J234" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K234" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L234" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M234" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N234" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O234" s="4">
         <v>1</v>
       </c>
       <c r="P234" s="4">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Q234" s="4" t="s">
         <v>73</v>
@@ -13399,25 +13617,25 @@
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
-        <v>270035</v>
+        <v>212910</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D235" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E235" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F235" s="4">
         <v>1</v>
       </c>
       <c r="G235" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H235" s="4">
         <v>0</v>
@@ -13426,28 +13644,28 @@
         <v>1</v>
       </c>
       <c r="J235" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K235" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L235" s="4">
         <v>1</v>
       </c>
       <c r="M235" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N235" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O235" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P235" s="4">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="Q235" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="R235" s="4" t="s">
         <v>21</v>
@@ -13455,55 +13673,55 @@
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
-        <v>270029</v>
+        <v>212910</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C236" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D236" s="4">
-        <v>100000</v>
+        <v>133333</v>
       </c>
       <c r="E236" s="4">
-        <v>100000</v>
+        <v>315152</v>
       </c>
       <c r="F236" s="4">
-        <v>200000</v>
+        <v>60606</v>
       </c>
       <c r="G236" s="4">
-        <v>100000</v>
+        <v>109091</v>
       </c>
       <c r="H236" s="4">
-        <v>100000</v>
+        <v>169697</v>
       </c>
       <c r="I236" s="4">
-        <v>100000</v>
+        <v>157576</v>
       </c>
       <c r="J236" s="4">
-        <v>200000</v>
+        <v>181818</v>
       </c>
       <c r="K236" s="4">
-        <v>200000</v>
+        <v>254545</v>
       </c>
       <c r="L236" s="4">
-        <v>200000</v>
+        <v>230303</v>
       </c>
       <c r="M236" s="4">
-        <v>200000</v>
+        <v>193939</v>
       </c>
       <c r="N236" s="4">
-        <v>100000</v>
+        <v>121213</v>
       </c>
       <c r="O236" s="4">
-        <v>100000</v>
+        <v>72727</v>
       </c>
       <c r="P236" s="4">
-        <v>1700000</v>
+        <v>2000000</v>
       </c>
       <c r="Q236" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="R236" s="4" t="s">
         <v>21</v>
@@ -13511,10 +13729,10 @@
     </row>
     <row r="237" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
-        <v>270029</v>
+        <v>212910</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>23</v>
@@ -13541,7 +13759,7 @@
         <v>0</v>
       </c>
       <c r="K237" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L237" s="4">
         <v>0</v>
@@ -13556,10 +13774,10 @@
         <v>1</v>
       </c>
       <c r="P237" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q237" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="R237" s="4" t="s">
         <v>21</v>
@@ -13567,55 +13785,55 @@
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
-        <v>270029</v>
+        <v>212876</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D238" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E238" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F238" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G238" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H238" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I238" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J238" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K238" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L238" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M238" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N238" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O238" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P238" s="4">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="Q238" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="R238" s="4" t="s">
         <v>21</v>
@@ -13623,55 +13841,55 @@
     </row>
     <row r="239" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
-        <v>270029</v>
+        <v>212876</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D239" s="4">
-        <v>1</v>
+        <v>222222</v>
       </c>
       <c r="E239" s="4">
-        <v>1</v>
+        <v>130719</v>
       </c>
       <c r="F239" s="4">
-        <v>1</v>
+        <v>222222</v>
       </c>
       <c r="G239" s="4">
-        <v>1</v>
+        <v>156863</v>
       </c>
       <c r="H239" s="4">
-        <v>1</v>
+        <v>222222</v>
       </c>
       <c r="I239" s="4">
-        <v>1</v>
+        <v>91503</v>
       </c>
       <c r="J239" s="4">
-        <v>1</v>
+        <v>209150</v>
       </c>
       <c r="K239" s="4">
-        <v>1</v>
+        <v>261438</v>
       </c>
       <c r="L239" s="4">
-        <v>2</v>
+        <v>143791</v>
       </c>
       <c r="M239" s="4">
-        <v>1</v>
+        <v>91504</v>
       </c>
       <c r="N239" s="4">
-        <v>1</v>
+        <v>143791</v>
       </c>
       <c r="O239" s="4">
-        <v>1</v>
+        <v>104575</v>
       </c>
       <c r="P239" s="4">
-        <v>13</v>
+        <v>2000000</v>
       </c>
       <c r="Q239" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="R239" s="4" t="s">
         <v>21</v>
@@ -13679,25 +13897,25 @@
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
-        <v>270029</v>
+        <v>212876</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D240" s="4">
         <v>0</v>
       </c>
       <c r="E240" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F240" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G240" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H240" s="4">
         <v>0</v>
@@ -13712,10 +13930,10 @@
         <v>0</v>
       </c>
       <c r="L240" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M240" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N240" s="4">
         <v>0</v>
@@ -13724,348 +13942,12 @@
         <v>1</v>
       </c>
       <c r="P240" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q240" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="R240" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A241" s="4">
-        <v>212910</v>
-      </c>
-      <c r="B241" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C241" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D241" s="4">
-        <v>1</v>
-      </c>
-      <c r="E241" s="4">
-        <v>5</v>
-      </c>
-      <c r="F241" s="4">
-        <v>1</v>
-      </c>
-      <c r="G241" s="4">
-        <v>1</v>
-      </c>
-      <c r="H241" s="4">
-        <v>0</v>
-      </c>
-      <c r="I241" s="4">
-        <v>1</v>
-      </c>
-      <c r="J241" s="4">
-        <v>2</v>
-      </c>
-      <c r="K241" s="4">
-        <v>2</v>
-      </c>
-      <c r="L241" s="4">
-        <v>1</v>
-      </c>
-      <c r="M241" s="4">
-        <v>2</v>
-      </c>
-      <c r="N241" s="4">
-        <v>1</v>
-      </c>
-      <c r="O241" s="4">
-        <v>0</v>
-      </c>
-      <c r="P241" s="4">
-        <v>17</v>
-      </c>
-      <c r="Q241" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R241" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A242" s="4">
-        <v>212910</v>
-      </c>
-      <c r="B242" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C242" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D242" s="4">
-        <v>133333</v>
-      </c>
-      <c r="E242" s="4">
-        <v>315152</v>
-      </c>
-      <c r="F242" s="4">
-        <v>60606</v>
-      </c>
-      <c r="G242" s="4">
-        <v>109091</v>
-      </c>
-      <c r="H242" s="4">
-        <v>169697</v>
-      </c>
-      <c r="I242" s="4">
-        <v>157576</v>
-      </c>
-      <c r="J242" s="4">
-        <v>181818</v>
-      </c>
-      <c r="K242" s="4">
-        <v>254545</v>
-      </c>
-      <c r="L242" s="4">
-        <v>230303</v>
-      </c>
-      <c r="M242" s="4">
-        <v>193939</v>
-      </c>
-      <c r="N242" s="4">
-        <v>121213</v>
-      </c>
-      <c r="O242" s="4">
-        <v>72727</v>
-      </c>
-      <c r="P242" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="Q242" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R242" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A243" s="4">
-        <v>212910</v>
-      </c>
-      <c r="B243" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C243" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D243" s="4">
-        <v>0</v>
-      </c>
-      <c r="E243" s="4">
-        <v>1</v>
-      </c>
-      <c r="F243" s="4">
-        <v>0</v>
-      </c>
-      <c r="G243" s="4">
-        <v>1</v>
-      </c>
-      <c r="H243" s="4">
-        <v>0</v>
-      </c>
-      <c r="I243" s="4">
-        <v>1</v>
-      </c>
-      <c r="J243" s="4">
-        <v>0</v>
-      </c>
-      <c r="K243" s="4">
-        <v>0</v>
-      </c>
-      <c r="L243" s="4">
-        <v>0</v>
-      </c>
-      <c r="M243" s="4">
-        <v>1</v>
-      </c>
-      <c r="N243" s="4">
-        <v>0</v>
-      </c>
-      <c r="O243" s="4">
-        <v>1</v>
-      </c>
-      <c r="P243" s="4">
-        <v>5</v>
-      </c>
-      <c r="Q243" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R243" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A244" s="4">
-        <v>212876</v>
-      </c>
-      <c r="B244" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C244" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D244" s="4">
-        <v>4</v>
-      </c>
-      <c r="E244" s="4">
-        <v>3</v>
-      </c>
-      <c r="F244" s="4">
-        <v>3</v>
-      </c>
-      <c r="G244" s="4">
-        <v>3</v>
-      </c>
-      <c r="H244" s="4">
-        <v>2</v>
-      </c>
-      <c r="I244" s="4">
-        <v>4</v>
-      </c>
-      <c r="J244" s="4">
-        <v>4</v>
-      </c>
-      <c r="K244" s="4">
-        <v>4</v>
-      </c>
-      <c r="L244" s="4">
-        <v>2</v>
-      </c>
-      <c r="M244" s="4">
-        <v>3</v>
-      </c>
-      <c r="N244" s="4">
-        <v>3</v>
-      </c>
-      <c r="O244" s="4">
-        <v>3</v>
-      </c>
-      <c r="P244" s="4">
-        <v>38</v>
-      </c>
-      <c r="Q244" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R244" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A245" s="4">
-        <v>212876</v>
-      </c>
-      <c r="B245" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C245" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D245" s="4">
-        <v>222222</v>
-      </c>
-      <c r="E245" s="4">
-        <v>130719</v>
-      </c>
-      <c r="F245" s="4">
-        <v>222222</v>
-      </c>
-      <c r="G245" s="4">
-        <v>156863</v>
-      </c>
-      <c r="H245" s="4">
-        <v>222222</v>
-      </c>
-      <c r="I245" s="4">
-        <v>91503</v>
-      </c>
-      <c r="J245" s="4">
-        <v>209150</v>
-      </c>
-      <c r="K245" s="4">
-        <v>261438</v>
-      </c>
-      <c r="L245" s="4">
-        <v>143791</v>
-      </c>
-      <c r="M245" s="4">
-        <v>91504</v>
-      </c>
-      <c r="N245" s="4">
-        <v>143791</v>
-      </c>
-      <c r="O245" s="4">
-        <v>104575</v>
-      </c>
-      <c r="P245" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="Q245" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R245" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A246" s="4">
-        <v>212876</v>
-      </c>
-      <c r="B246" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C246" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D246" s="4">
-        <v>0</v>
-      </c>
-      <c r="E246" s="4">
-        <v>1</v>
-      </c>
-      <c r="F246" s="4">
-        <v>0</v>
-      </c>
-      <c r="G246" s="4">
-        <v>1</v>
-      </c>
-      <c r="H246" s="4">
-        <v>0</v>
-      </c>
-      <c r="I246" s="4">
-        <v>1</v>
-      </c>
-      <c r="J246" s="4">
-        <v>0</v>
-      </c>
-      <c r="K246" s="4">
-        <v>0</v>
-      </c>
-      <c r="L246" s="4">
-        <v>0</v>
-      </c>
-      <c r="M246" s="4">
-        <v>1</v>
-      </c>
-      <c r="N246" s="4">
-        <v>0</v>
-      </c>
-      <c r="O246" s="4">
-        <v>1</v>
-      </c>
-      <c r="P246" s="4">
-        <v>5</v>
-      </c>
-      <c r="Q246" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R246" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -14075,6 +13957,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
@@ -14083,15 +13974,6 @@
     <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14290,6 +14172,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -14306,14 +14196,21 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BDC8EFC-C946-4B3C-B84E-1270F018751C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
+    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BDC8EFC-C946-4B3C-B84E-1270F018751C}"/>
 </file>
--- a/dados/metas.xlsx
+++ b/dados/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.sa\Documents\dashboard-oportunidades\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9C60BC-231E-40F1-8914-CBA45405E77C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1BDF74-1019-44C6-ADA7-F0D708365B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$R$240</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$R$236</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="79">
   <si>
     <t>CÓD</t>
   </si>
@@ -207,9 +207,6 @@
   </si>
   <si>
     <t>MASTER GRAOS</t>
-  </si>
-  <si>
-    <t>MECANIZAÇÃO DO CAFÉ</t>
   </si>
   <si>
     <t>CARLOS.NUNES</t>
@@ -646,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R240"/>
+  <dimension ref="A1:R236"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
@@ -9228,7 +9225,7 @@
         <v>240035</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>19</v>
@@ -9273,7 +9270,7 @@
         <v>6000002</v>
       </c>
       <c r="Q154" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R154" s="4" t="s">
         <v>21</v>
@@ -9284,7 +9281,7 @@
         <v>240035</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>23</v>
@@ -9329,7 +9326,7 @@
         <v>6</v>
       </c>
       <c r="Q155" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R155" s="4" t="s">
         <v>21</v>
@@ -9340,7 +9337,7 @@
         <v>240035</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>24</v>
@@ -9385,7 +9382,7 @@
         <v>6</v>
       </c>
       <c r="Q156" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R156" s="4" t="s">
         <v>21</v>
@@ -9396,7 +9393,7 @@
         <v>240035</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>28</v>
@@ -9441,7 +9438,7 @@
         <v>60</v>
       </c>
       <c r="Q157" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R157" s="4" t="s">
         <v>21</v>
@@ -9452,7 +9449,7 @@
         <v>2417</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>19</v>
@@ -9497,7 +9494,7 @@
         <v>4500000</v>
       </c>
       <c r="Q158" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R158" s="4" t="s">
         <v>21</v>
@@ -9508,7 +9505,7 @@
         <v>2417</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>23</v>
@@ -9553,7 +9550,7 @@
         <v>6</v>
       </c>
       <c r="Q159" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R159" s="4" t="s">
         <v>21</v>
@@ -9564,7 +9561,7 @@
         <v>2417</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>24</v>
@@ -9609,7 +9606,7 @@
         <v>6</v>
       </c>
       <c r="Q160" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R160" s="4" t="s">
         <v>21</v>
@@ -9620,7 +9617,7 @@
         <v>2417</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>28</v>
@@ -9665,7 +9662,7 @@
         <v>50</v>
       </c>
       <c r="Q161" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R161" s="4" t="s">
         <v>21</v>
@@ -9676,7 +9673,7 @@
         <v>2425</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>19</v>
@@ -9721,7 +9718,7 @@
         <v>4500000</v>
       </c>
       <c r="Q162" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R162" s="4" t="s">
         <v>21</v>
@@ -9732,7 +9729,7 @@
         <v>2425</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>23</v>
@@ -9777,7 +9774,7 @@
         <v>6</v>
       </c>
       <c r="Q163" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R163" s="4" t="s">
         <v>21</v>
@@ -9788,7 +9785,7 @@
         <v>2425</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>24</v>
@@ -9833,7 +9830,7 @@
         <v>6</v>
       </c>
       <c r="Q164" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R164" s="4" t="s">
         <v>21</v>
@@ -9844,7 +9841,7 @@
         <v>2425</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>28</v>
@@ -9889,7 +9886,7 @@
         <v>40</v>
       </c>
       <c r="Q165" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R165" s="4" t="s">
         <v>21</v>
@@ -9900,7 +9897,7 @@
         <v>240048</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>19</v>
@@ -9945,7 +9942,7 @@
         <v>2500000</v>
       </c>
       <c r="Q166" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R166" s="4" t="s">
         <v>21</v>
@@ -9956,7 +9953,7 @@
         <v>240048</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>23</v>
@@ -10001,7 +9998,7 @@
         <v>6</v>
       </c>
       <c r="Q167" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R167" s="4" t="s">
         <v>21</v>
@@ -10012,7 +10009,7 @@
         <v>240048</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>24</v>
@@ -10057,7 +10054,7 @@
         <v>6</v>
       </c>
       <c r="Q168" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R168" s="4" t="s">
         <v>21</v>
@@ -10068,7 +10065,7 @@
         <v>240048</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>28</v>
@@ -10113,7 +10110,7 @@
         <v>15</v>
       </c>
       <c r="Q169" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R169" s="4" t="s">
         <v>21</v>
@@ -10124,7 +10121,7 @@
         <v>240060</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>19</v>
@@ -10169,7 +10166,7 @@
         <v>1200002</v>
       </c>
       <c r="Q170" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R170" s="4" t="s">
         <v>34</v>
@@ -10180,7 +10177,7 @@
         <v>240060</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>23</v>
@@ -10225,7 +10222,7 @@
         <v>6</v>
       </c>
       <c r="Q171" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R171" s="4" t="s">
         <v>34</v>
@@ -10236,7 +10233,7 @@
         <v>240060</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>24</v>
@@ -10281,7 +10278,7 @@
         <v>6</v>
       </c>
       <c r="Q172" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R172" s="4" t="s">
         <v>34</v>
@@ -10292,7 +10289,7 @@
         <v>240060</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>28</v>
@@ -10337,7 +10334,7 @@
         <v>15</v>
       </c>
       <c r="Q173" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R173" s="4" t="s">
         <v>34</v>
@@ -10348,7 +10345,7 @@
         <v>2419</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>19</v>
@@ -10393,7 +10390,7 @@
         <v>3500001</v>
       </c>
       <c r="Q174" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R174" s="4" t="s">
         <v>21</v>
@@ -10404,7 +10401,7 @@
         <v>2419</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>23</v>
@@ -10449,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="Q175" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R175" s="4" t="s">
         <v>21</v>
@@ -10460,7 +10457,7 @@
         <v>2419</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>24</v>
@@ -10505,7 +10502,7 @@
         <v>6</v>
       </c>
       <c r="Q176" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R176" s="4" t="s">
         <v>21</v>
@@ -10516,7 +10513,7 @@
         <v>2419</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>28</v>
@@ -10561,7 +10558,7 @@
         <v>40</v>
       </c>
       <c r="Q177" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R177" s="4" t="s">
         <v>21</v>
@@ -10572,7 +10569,7 @@
         <v>240058</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>19</v>
@@ -10617,7 +10614,7 @@
         <v>2399999</v>
       </c>
       <c r="Q178" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R178" s="4" t="s">
         <v>21</v>
@@ -10628,7 +10625,7 @@
         <v>240058</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>23</v>
@@ -10673,7 +10670,7 @@
         <v>6</v>
       </c>
       <c r="Q179" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R179" s="4" t="s">
         <v>21</v>
@@ -10684,7 +10681,7 @@
         <v>240058</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>24</v>
@@ -10729,7 +10726,7 @@
         <v>6</v>
       </c>
       <c r="Q180" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R180" s="4" t="s">
         <v>21</v>
@@ -10740,7 +10737,7 @@
         <v>240058</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>28</v>
@@ -10785,7 +10782,7 @@
         <v>30</v>
       </c>
       <c r="Q181" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R181" s="4" t="s">
         <v>21</v>
@@ -10796,7 +10793,7 @@
         <v>230305</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>19</v>
@@ -10841,7 +10838,7 @@
         <v>4499999</v>
       </c>
       <c r="Q182" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R182" s="4" t="s">
         <v>21</v>
@@ -10852,7 +10849,7 @@
         <v>230305</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>23</v>
@@ -10897,7 +10894,7 @@
         <v>12</v>
       </c>
       <c r="Q183" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R183" s="4" t="s">
         <v>21</v>
@@ -10908,7 +10905,7 @@
         <v>230305</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>24</v>
@@ -10953,7 +10950,7 @@
         <v>5</v>
       </c>
       <c r="Q184" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R184" s="4" t="s">
         <v>21</v>
@@ -10964,16 +10961,52 @@
         <v>230305</v>
       </c>
       <c r="B185" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D185" s="4">
+        <v>1</v>
+      </c>
+      <c r="E185" s="4">
+        <v>2</v>
+      </c>
+      <c r="F185" s="4">
+        <v>2</v>
+      </c>
+      <c r="G185" s="4">
+        <v>3</v>
+      </c>
+      <c r="H185" s="4">
+        <v>2</v>
+      </c>
+      <c r="I185" s="4">
+        <v>2</v>
+      </c>
+      <c r="J185" s="4">
+        <v>2</v>
+      </c>
+      <c r="K185" s="4">
+        <v>3</v>
+      </c>
+      <c r="L185" s="4">
+        <v>2</v>
+      </c>
+      <c r="M185" s="4">
+        <v>3</v>
+      </c>
+      <c r="N185" s="4">
+        <v>2</v>
+      </c>
+      <c r="O185" s="4">
+        <v>3</v>
+      </c>
+      <c r="P185" s="4">
+        <v>27</v>
+      </c>
+      <c r="Q185" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="P185" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q185" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="R185" s="4" t="s">
         <v>21</v>
@@ -10984,52 +11017,52 @@
         <v>230305</v>
       </c>
       <c r="B186" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D186" s="4">
+        <v>0</v>
+      </c>
+      <c r="E186" s="4">
+        <v>1</v>
+      </c>
+      <c r="F186" s="4">
+        <v>0</v>
+      </c>
+      <c r="G186" s="4">
+        <v>0</v>
+      </c>
+      <c r="H186" s="4">
+        <v>1</v>
+      </c>
+      <c r="I186" s="4">
+        <v>0</v>
+      </c>
+      <c r="J186" s="4">
+        <v>1</v>
+      </c>
+      <c r="K186" s="4">
+        <v>0</v>
+      </c>
+      <c r="L186" s="4">
+        <v>1</v>
+      </c>
+      <c r="M186" s="4">
+        <v>0</v>
+      </c>
+      <c r="N186" s="4">
+        <v>1</v>
+      </c>
+      <c r="O186" s="4">
+        <v>0</v>
+      </c>
+      <c r="P186" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q186" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D186" s="4">
-        <v>1</v>
-      </c>
-      <c r="E186" s="4">
-        <v>2</v>
-      </c>
-      <c r="F186" s="4">
-        <v>2</v>
-      </c>
-      <c r="G186" s="4">
-        <v>3</v>
-      </c>
-      <c r="H186" s="4">
-        <v>2</v>
-      </c>
-      <c r="I186" s="4">
-        <v>2</v>
-      </c>
-      <c r="J186" s="4">
-        <v>2</v>
-      </c>
-      <c r="K186" s="4">
-        <v>3</v>
-      </c>
-      <c r="L186" s="4">
-        <v>2</v>
-      </c>
-      <c r="M186" s="4">
-        <v>3</v>
-      </c>
-      <c r="N186" s="4">
-        <v>2</v>
-      </c>
-      <c r="O186" s="4">
-        <v>3</v>
-      </c>
-      <c r="P186" s="4">
-        <v>27</v>
-      </c>
-      <c r="Q186" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="R186" s="4" t="s">
         <v>21</v>
@@ -11037,55 +11070,55 @@
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
-        <v>230305</v>
+        <v>230307</v>
       </c>
       <c r="B187" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D187" s="4">
+        <v>299114</v>
+      </c>
+      <c r="E187" s="4">
+        <v>319055</v>
+      </c>
+      <c r="F187" s="4">
+        <v>445347</v>
+      </c>
+      <c r="G187" s="4">
+        <v>458641</v>
+      </c>
+      <c r="H187" s="4">
+        <v>405465</v>
+      </c>
+      <c r="I187" s="4">
+        <v>438700</v>
+      </c>
+      <c r="J187" s="4">
+        <v>392171</v>
+      </c>
+      <c r="K187" s="4">
+        <v>438700</v>
+      </c>
+      <c r="L187" s="4">
+        <v>398818</v>
+      </c>
+      <c r="M187" s="4">
+        <v>252585</v>
+      </c>
+      <c r="N187" s="4">
+        <v>212703</v>
+      </c>
+      <c r="O187" s="4">
+        <v>438700</v>
+      </c>
+      <c r="P187" s="4">
+        <v>4499999</v>
+      </c>
+      <c r="Q187" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="C187" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D187" s="4">
-        <v>0</v>
-      </c>
-      <c r="E187" s="4">
-        <v>1</v>
-      </c>
-      <c r="F187" s="4">
-        <v>0</v>
-      </c>
-      <c r="G187" s="4">
-        <v>0</v>
-      </c>
-      <c r="H187" s="4">
-        <v>1</v>
-      </c>
-      <c r="I187" s="4">
-        <v>0</v>
-      </c>
-      <c r="J187" s="4">
-        <v>1</v>
-      </c>
-      <c r="K187" s="4">
-        <v>0</v>
-      </c>
-      <c r="L187" s="4">
-        <v>1</v>
-      </c>
-      <c r="M187" s="4">
-        <v>0</v>
-      </c>
-      <c r="N187" s="4">
-        <v>1</v>
-      </c>
-      <c r="O187" s="4">
-        <v>0</v>
-      </c>
-      <c r="P187" s="4">
-        <v>5</v>
-      </c>
-      <c r="Q187" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="R187" s="4" t="s">
         <v>21</v>
@@ -11096,52 +11129,52 @@
         <v>230307</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D188" s="4">
-        <v>299114</v>
+        <v>1</v>
       </c>
       <c r="E188" s="4">
-        <v>319055</v>
+        <v>1</v>
       </c>
       <c r="F188" s="4">
-        <v>445347</v>
+        <v>1</v>
       </c>
       <c r="G188" s="4">
-        <v>458641</v>
+        <v>1</v>
       </c>
       <c r="H188" s="4">
-        <v>405465</v>
+        <v>1</v>
       </c>
       <c r="I188" s="4">
-        <v>438700</v>
+        <v>1</v>
       </c>
       <c r="J188" s="4">
-        <v>392171</v>
+        <v>1</v>
       </c>
       <c r="K188" s="4">
-        <v>438700</v>
+        <v>1</v>
       </c>
       <c r="L188" s="4">
-        <v>398818</v>
+        <v>1</v>
       </c>
       <c r="M188" s="4">
-        <v>252585</v>
+        <v>1</v>
       </c>
       <c r="N188" s="4">
-        <v>212703</v>
+        <v>1</v>
       </c>
       <c r="O188" s="4">
-        <v>438700</v>
+        <v>1</v>
       </c>
       <c r="P188" s="4">
-        <v>4499999</v>
+        <v>12</v>
       </c>
       <c r="Q188" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R188" s="4" t="s">
         <v>21</v>
@@ -11152,52 +11185,52 @@
         <v>230307</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D189" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E189" s="4">
         <v>1</v>
       </c>
       <c r="F189" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G189" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H189" s="4">
         <v>1</v>
       </c>
       <c r="I189" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J189" s="4">
         <v>1</v>
       </c>
       <c r="K189" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L189" s="4">
         <v>1</v>
       </c>
       <c r="M189" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N189" s="4">
         <v>1</v>
       </c>
       <c r="O189" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P189" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q189" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R189" s="4" t="s">
         <v>21</v>
@@ -11208,52 +11241,52 @@
         <v>230307</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D190" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E190" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F190" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G190" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H190" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I190" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J190" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K190" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L190" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M190" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N190" s="4">
         <v>1</v>
       </c>
       <c r="O190" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P190" s="4">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="Q190" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R190" s="4" t="s">
         <v>21</v>
@@ -11264,16 +11297,52 @@
         <v>230307</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>56</v>
+        <v>39</v>
+      </c>
+      <c r="D191" s="4">
+        <v>0</v>
+      </c>
+      <c r="E191" s="4">
+        <v>1</v>
+      </c>
+      <c r="F191" s="4">
+        <v>0</v>
+      </c>
+      <c r="G191" s="4">
+        <v>0</v>
+      </c>
+      <c r="H191" s="4">
+        <v>1</v>
+      </c>
+      <c r="I191" s="4">
+        <v>0</v>
+      </c>
+      <c r="J191" s="4">
+        <v>1</v>
+      </c>
+      <c r="K191" s="4">
+        <v>0</v>
+      </c>
+      <c r="L191" s="4">
+        <v>1</v>
+      </c>
+      <c r="M191" s="4">
+        <v>0</v>
+      </c>
+      <c r="N191" s="4">
+        <v>1</v>
+      </c>
+      <c r="O191" s="4">
+        <v>0</v>
       </c>
       <c r="P191" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q191" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R191" s="4" t="s">
         <v>21</v>
@@ -11281,55 +11350,55 @@
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
-        <v>230307</v>
+        <v>230306</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D192" s="4">
-        <v>1</v>
+        <v>299114</v>
       </c>
       <c r="E192" s="4">
-        <v>2</v>
+        <v>319055</v>
       </c>
       <c r="F192" s="4">
-        <v>2</v>
+        <v>445347</v>
       </c>
       <c r="G192" s="4">
-        <v>2</v>
+        <v>458641</v>
       </c>
       <c r="H192" s="4">
-        <v>2</v>
+        <v>405465</v>
       </c>
       <c r="I192" s="4">
-        <v>2</v>
+        <v>438700</v>
       </c>
       <c r="J192" s="4">
-        <v>2</v>
+        <v>392171</v>
       </c>
       <c r="K192" s="4">
-        <v>3</v>
+        <v>438700</v>
       </c>
       <c r="L192" s="4">
-        <v>2</v>
+        <v>398818</v>
       </c>
       <c r="M192" s="4">
-        <v>2</v>
+        <v>252585</v>
       </c>
       <c r="N192" s="4">
-        <v>1</v>
+        <v>212703</v>
       </c>
       <c r="O192" s="4">
-        <v>2</v>
+        <v>438700</v>
       </c>
       <c r="P192" s="4">
-        <v>23</v>
+        <v>4499999</v>
       </c>
       <c r="Q192" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R192" s="4" t="s">
         <v>21</v>
@@ -11337,55 +11406,55 @@
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
-        <v>230307</v>
+        <v>230306</v>
       </c>
       <c r="B193" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D193" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E193" s="4">
         <v>1</v>
       </c>
       <c r="F193" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G193" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H193" s="4">
         <v>1</v>
       </c>
       <c r="I193" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J193" s="4">
         <v>1</v>
       </c>
       <c r="K193" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L193" s="4">
         <v>1</v>
       </c>
       <c r="M193" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N193" s="4">
         <v>1</v>
       </c>
       <c r="O193" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P193" s="4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q193" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R193" s="4" t="s">
         <v>21</v>
@@ -11396,52 +11465,52 @@
         <v>230306</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D194" s="4">
-        <v>299114</v>
+        <v>0</v>
       </c>
       <c r="E194" s="4">
-        <v>319055</v>
+        <v>1</v>
       </c>
       <c r="F194" s="4">
-        <v>445347</v>
+        <v>0</v>
       </c>
       <c r="G194" s="4">
-        <v>458641</v>
+        <v>0</v>
       </c>
       <c r="H194" s="4">
-        <v>405465</v>
+        <v>1</v>
       </c>
       <c r="I194" s="4">
-        <v>438700</v>
+        <v>0</v>
       </c>
       <c r="J194" s="4">
-        <v>392171</v>
+        <v>1</v>
       </c>
       <c r="K194" s="4">
-        <v>438700</v>
+        <v>0</v>
       </c>
       <c r="L194" s="4">
-        <v>398818</v>
+        <v>1</v>
       </c>
       <c r="M194" s="4">
-        <v>252585</v>
+        <v>0</v>
       </c>
       <c r="N194" s="4">
-        <v>212703</v>
+        <v>1</v>
       </c>
       <c r="O194" s="4">
-        <v>438700</v>
+        <v>0</v>
       </c>
       <c r="P194" s="4">
-        <v>4499999</v>
+        <v>5</v>
       </c>
       <c r="Q194" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R194" s="4" t="s">
         <v>21</v>
@@ -11452,52 +11521,52 @@
         <v>230306</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D195" s="4">
         <v>1</v>
       </c>
       <c r="E195" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F195" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G195" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H195" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I195" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J195" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K195" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L195" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M195" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N195" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O195" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P195" s="4">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="Q195" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R195" s="4" t="s">
         <v>21</v>
@@ -11508,10 +11577,10 @@
         <v>230306</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D196" s="4">
         <v>0</v>
@@ -11553,7 +11622,7 @@
         <v>5</v>
       </c>
       <c r="Q196" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R196" s="4" t="s">
         <v>21</v>
@@ -11561,19 +11630,55 @@
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
-        <v>230306</v>
+        <v>230301</v>
       </c>
       <c r="B197" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>56</v>
+        <v>19</v>
+      </c>
+      <c r="D197" s="4">
+        <v>299114</v>
+      </c>
+      <c r="E197" s="4">
+        <v>319055</v>
+      </c>
+      <c r="F197" s="4">
+        <v>445347</v>
+      </c>
+      <c r="G197" s="4">
+        <v>458641</v>
+      </c>
+      <c r="H197" s="4">
+        <v>405465</v>
+      </c>
+      <c r="I197" s="4">
+        <v>438700</v>
+      </c>
+      <c r="J197" s="4">
+        <v>392171</v>
+      </c>
+      <c r="K197" s="4">
+        <v>438700</v>
+      </c>
+      <c r="L197" s="4">
+        <v>398818</v>
+      </c>
+      <c r="M197" s="4">
+        <v>252585</v>
+      </c>
+      <c r="N197" s="4">
+        <v>212703</v>
+      </c>
+      <c r="O197" s="4">
+        <v>438700</v>
       </c>
       <c r="P197" s="4">
-        <v>0</v>
+        <v>4499999</v>
       </c>
       <c r="Q197" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R197" s="4" t="s">
         <v>21</v>
@@ -11581,55 +11686,55 @@
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
-        <v>230306</v>
+        <v>230301</v>
       </c>
       <c r="B198" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D198" s="4">
         <v>1</v>
       </c>
       <c r="E198" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F198" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G198" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H198" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I198" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J198" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K198" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L198" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M198" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N198" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O198" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P198" s="4">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="Q198" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R198" s="4" t="s">
         <v>21</v>
@@ -11637,13 +11742,13 @@
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
-        <v>230306</v>
+        <v>230301</v>
       </c>
       <c r="B199" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D199" s="4">
         <v>0</v>
@@ -11685,7 +11790,7 @@
         <v>5</v>
       </c>
       <c r="Q199" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R199" s="4" t="s">
         <v>21</v>
@@ -11696,52 +11801,52 @@
         <v>230301</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D200" s="4">
-        <v>299114</v>
+        <v>1</v>
       </c>
       <c r="E200" s="4">
-        <v>319055</v>
+        <v>2</v>
       </c>
       <c r="F200" s="4">
-        <v>445347</v>
+        <v>2</v>
       </c>
       <c r="G200" s="4">
-        <v>458641</v>
+        <v>3</v>
       </c>
       <c r="H200" s="4">
-        <v>405465</v>
+        <v>2</v>
       </c>
       <c r="I200" s="4">
-        <v>438700</v>
+        <v>2</v>
       </c>
       <c r="J200" s="4">
-        <v>392171</v>
+        <v>2</v>
       </c>
       <c r="K200" s="4">
-        <v>438700</v>
+        <v>3</v>
       </c>
       <c r="L200" s="4">
-        <v>398818</v>
+        <v>2</v>
       </c>
       <c r="M200" s="4">
-        <v>252585</v>
+        <v>3</v>
       </c>
       <c r="N200" s="4">
-        <v>212703</v>
+        <v>2</v>
       </c>
       <c r="O200" s="4">
-        <v>438700</v>
+        <v>3</v>
       </c>
       <c r="P200" s="4">
-        <v>4499999</v>
+        <v>27</v>
       </c>
       <c r="Q200" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R200" s="4" t="s">
         <v>21</v>
@@ -11752,52 +11857,52 @@
         <v>230301</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D201" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E201" s="4">
         <v>1</v>
       </c>
       <c r="F201" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G201" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H201" s="4">
         <v>1</v>
       </c>
       <c r="I201" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J201" s="4">
         <v>1</v>
       </c>
       <c r="K201" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L201" s="4">
         <v>1</v>
       </c>
       <c r="M201" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N201" s="4">
         <v>1</v>
       </c>
       <c r="O201" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P201" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q201" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R201" s="4" t="s">
         <v>21</v>
@@ -11805,55 +11910,55 @@
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
-        <v>230301</v>
+        <v>280037</v>
       </c>
       <c r="B202" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D202" s="4">
-        <v>0</v>
+        <v>80233</v>
       </c>
       <c r="E202" s="4">
-        <v>1</v>
+        <v>132558</v>
       </c>
       <c r="F202" s="4">
-        <v>0</v>
+        <v>125581</v>
       </c>
       <c r="G202" s="4">
-        <v>0</v>
+        <v>102907</v>
       </c>
       <c r="H202" s="4">
-        <v>1</v>
+        <v>66279</v>
       </c>
       <c r="I202" s="4">
-        <v>0</v>
+        <v>125581</v>
       </c>
       <c r="J202" s="4">
-        <v>1</v>
+        <v>120349</v>
       </c>
       <c r="K202" s="4">
-        <v>0</v>
+        <v>162209</v>
       </c>
       <c r="L202" s="4">
-        <v>1</v>
+        <v>134302</v>
       </c>
       <c r="M202" s="4">
-        <v>0</v>
+        <v>139535</v>
       </c>
       <c r="N202" s="4">
-        <v>1</v>
+        <v>76745</v>
       </c>
       <c r="O202" s="4">
-        <v>0</v>
+        <v>83721</v>
       </c>
       <c r="P202" s="4">
-        <v>5</v>
+        <v>1350000</v>
       </c>
       <c r="Q202" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="R202" s="4" t="s">
         <v>21</v>
@@ -11861,19 +11966,55 @@
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
-        <v>230301</v>
+        <v>280037</v>
       </c>
       <c r="B203" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>56</v>
+        <v>22</v>
+      </c>
+      <c r="D203" s="4">
+        <v>0</v>
+      </c>
+      <c r="E203" s="4">
+        <v>1</v>
+      </c>
+      <c r="F203" s="4">
+        <v>0</v>
+      </c>
+      <c r="G203" s="4">
+        <v>0</v>
+      </c>
+      <c r="H203" s="4">
+        <v>0</v>
+      </c>
+      <c r="I203" s="4">
+        <v>0</v>
+      </c>
+      <c r="J203" s="4">
+        <v>0</v>
+      </c>
+      <c r="K203" s="4">
+        <v>0</v>
+      </c>
+      <c r="L203" s="4">
+        <v>0</v>
+      </c>
+      <c r="M203" s="4">
+        <v>0</v>
+      </c>
+      <c r="N203" s="4">
+        <v>0</v>
+      </c>
+      <c r="O203" s="4">
+        <v>0</v>
       </c>
       <c r="P203" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q203" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="R203" s="4" t="s">
         <v>21</v>
@@ -11881,55 +12022,55 @@
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
-        <v>230301</v>
+        <v>280037</v>
       </c>
       <c r="B204" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D204" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E204" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F204" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G204" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H204" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I204" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J204" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K204" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L204" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M204" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N204" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O204" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P204" s="4">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="Q204" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="R204" s="4" t="s">
         <v>21</v>
@@ -11937,13 +12078,13 @@
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
-        <v>230301</v>
+        <v>280037</v>
       </c>
       <c r="B205" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D205" s="4">
         <v>0</v>
@@ -11958,13 +12099,13 @@
         <v>0</v>
       </c>
       <c r="H205" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I205" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J205" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K205" s="4">
         <v>0</v>
@@ -11976,16 +12117,16 @@
         <v>0</v>
       </c>
       <c r="N205" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O205" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P205" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q205" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="R205" s="4" t="s">
         <v>21</v>
@@ -11996,52 +12137,52 @@
         <v>280037</v>
       </c>
       <c r="B206" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D206" s="4">
+        <v>0</v>
+      </c>
+      <c r="E206" s="4">
+        <v>0</v>
+      </c>
+      <c r="F206" s="4">
+        <v>0</v>
+      </c>
+      <c r="G206" s="4">
+        <v>0</v>
+      </c>
+      <c r="H206" s="4">
+        <v>0</v>
+      </c>
+      <c r="I206" s="4">
+        <v>0</v>
+      </c>
+      <c r="J206" s="4">
+        <v>0</v>
+      </c>
+      <c r="K206" s="4">
+        <v>0</v>
+      </c>
+      <c r="L206" s="4">
+        <v>0</v>
+      </c>
+      <c r="M206" s="4">
+        <v>1</v>
+      </c>
+      <c r="N206" s="4">
+        <v>0</v>
+      </c>
+      <c r="O206" s="4">
+        <v>0</v>
+      </c>
+      <c r="P206" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q206" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="C206" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D206" s="4">
-        <v>80233</v>
-      </c>
-      <c r="E206" s="4">
-        <v>132558</v>
-      </c>
-      <c r="F206" s="4">
-        <v>125581</v>
-      </c>
-      <c r="G206" s="4">
-        <v>102907</v>
-      </c>
-      <c r="H206" s="4">
-        <v>66279</v>
-      </c>
-      <c r="I206" s="4">
-        <v>125581</v>
-      </c>
-      <c r="J206" s="4">
-        <v>120349</v>
-      </c>
-      <c r="K206" s="4">
-        <v>162209</v>
-      </c>
-      <c r="L206" s="4">
-        <v>134302</v>
-      </c>
-      <c r="M206" s="4">
-        <v>139535</v>
-      </c>
-      <c r="N206" s="4">
-        <v>76745</v>
-      </c>
-      <c r="O206" s="4">
-        <v>83721</v>
-      </c>
-      <c r="P206" s="4">
-        <v>1350000</v>
-      </c>
-      <c r="Q206" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="R206" s="4" t="s">
         <v>21</v>
@@ -12052,52 +12193,52 @@
         <v>280037</v>
       </c>
       <c r="B207" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D207" s="4">
+        <v>0</v>
+      </c>
+      <c r="E207" s="4">
+        <v>1</v>
+      </c>
+      <c r="F207" s="4">
+        <v>1</v>
+      </c>
+      <c r="G207" s="4">
+        <v>0</v>
+      </c>
+      <c r="H207" s="4">
+        <v>0</v>
+      </c>
+      <c r="I207" s="4">
+        <v>0</v>
+      </c>
+      <c r="J207" s="4">
+        <v>0</v>
+      </c>
+      <c r="K207" s="4">
+        <v>0</v>
+      </c>
+      <c r="L207" s="4">
+        <v>0</v>
+      </c>
+      <c r="M207" s="4">
+        <v>0</v>
+      </c>
+      <c r="N207" s="4">
+        <v>0</v>
+      </c>
+      <c r="O207" s="4">
+        <v>0</v>
+      </c>
+      <c r="P207" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q207" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="C207" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D207" s="4">
-        <v>0</v>
-      </c>
-      <c r="E207" s="4">
-        <v>1</v>
-      </c>
-      <c r="F207" s="4">
-        <v>0</v>
-      </c>
-      <c r="G207" s="4">
-        <v>0</v>
-      </c>
-      <c r="H207" s="4">
-        <v>0</v>
-      </c>
-      <c r="I207" s="4">
-        <v>0</v>
-      </c>
-      <c r="J207" s="4">
-        <v>0</v>
-      </c>
-      <c r="K207" s="4">
-        <v>0</v>
-      </c>
-      <c r="L207" s="4">
-        <v>0</v>
-      </c>
-      <c r="M207" s="4">
-        <v>0</v>
-      </c>
-      <c r="N207" s="4">
-        <v>0</v>
-      </c>
-      <c r="O207" s="4">
-        <v>0</v>
-      </c>
-      <c r="P207" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q207" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="R207" s="4" t="s">
         <v>21</v>
@@ -12108,52 +12249,52 @@
         <v>280037</v>
       </c>
       <c r="B208" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D208" s="4">
+        <v>0</v>
+      </c>
+      <c r="E208" s="4">
+        <v>0</v>
+      </c>
+      <c r="F208" s="4">
+        <v>0</v>
+      </c>
+      <c r="G208" s="4">
+        <v>0</v>
+      </c>
+      <c r="H208" s="4">
+        <v>0</v>
+      </c>
+      <c r="I208" s="4">
+        <v>0</v>
+      </c>
+      <c r="J208" s="4">
+        <v>0</v>
+      </c>
+      <c r="K208" s="4">
+        <v>0</v>
+      </c>
+      <c r="L208" s="4">
+        <v>1</v>
+      </c>
+      <c r="M208" s="4">
+        <v>0</v>
+      </c>
+      <c r="N208" s="4">
+        <v>0</v>
+      </c>
+      <c r="O208" s="4">
+        <v>0</v>
+      </c>
+      <c r="P208" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q208" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D208" s="4">
-        <v>0</v>
-      </c>
-      <c r="E208" s="4">
-        <v>1</v>
-      </c>
-      <c r="F208" s="4">
-        <v>1</v>
-      </c>
-      <c r="G208" s="4">
-        <v>0</v>
-      </c>
-      <c r="H208" s="4">
-        <v>1</v>
-      </c>
-      <c r="I208" s="4">
-        <v>1</v>
-      </c>
-      <c r="J208" s="4">
-        <v>1</v>
-      </c>
-      <c r="K208" s="4">
-        <v>1</v>
-      </c>
-      <c r="L208" s="4">
-        <v>1</v>
-      </c>
-      <c r="M208" s="4">
-        <v>1</v>
-      </c>
-      <c r="N208" s="4">
-        <v>0</v>
-      </c>
-      <c r="O208" s="4">
-        <v>0</v>
-      </c>
-      <c r="P208" s="4">
-        <v>8</v>
-      </c>
-      <c r="Q208" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="R208" s="4" t="s">
         <v>21</v>
@@ -12164,52 +12305,52 @@
         <v>280037</v>
       </c>
       <c r="B209" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D209" s="4">
+        <v>1</v>
+      </c>
+      <c r="E209" s="4">
+        <v>1</v>
+      </c>
+      <c r="F209" s="4">
+        <v>1</v>
+      </c>
+      <c r="G209" s="4">
+        <v>1</v>
+      </c>
+      <c r="H209" s="4">
+        <v>1</v>
+      </c>
+      <c r="I209" s="4">
+        <v>1</v>
+      </c>
+      <c r="J209" s="4">
+        <v>1</v>
+      </c>
+      <c r="K209" s="4">
+        <v>1</v>
+      </c>
+      <c r="L209" s="4">
+        <v>1</v>
+      </c>
+      <c r="M209" s="4">
+        <v>1</v>
+      </c>
+      <c r="N209" s="4">
+        <v>1</v>
+      </c>
+      <c r="O209" s="4">
+        <v>1</v>
+      </c>
+      <c r="P209" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q209" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="C209" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D209" s="4">
-        <v>0</v>
-      </c>
-      <c r="E209" s="4">
-        <v>1</v>
-      </c>
-      <c r="F209" s="4">
-        <v>0</v>
-      </c>
-      <c r="G209" s="4">
-        <v>0</v>
-      </c>
-      <c r="H209" s="4">
-        <v>0</v>
-      </c>
-      <c r="I209" s="4">
-        <v>1</v>
-      </c>
-      <c r="J209" s="4">
-        <v>0</v>
-      </c>
-      <c r="K209" s="4">
-        <v>0</v>
-      </c>
-      <c r="L209" s="4">
-        <v>1</v>
-      </c>
-      <c r="M209" s="4">
-        <v>0</v>
-      </c>
-      <c r="N209" s="4">
-        <v>0</v>
-      </c>
-      <c r="O209" s="4">
-        <v>1</v>
-      </c>
-      <c r="P209" s="4">
-        <v>4</v>
-      </c>
-      <c r="Q209" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="R209" s="4" t="s">
         <v>21</v>
@@ -12220,52 +12361,52 @@
         <v>280037</v>
       </c>
       <c r="B210" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D210" s="4">
+        <v>95090</v>
+      </c>
+      <c r="E210" s="4">
+        <v>157106</v>
+      </c>
+      <c r="F210" s="4">
+        <v>148837</v>
+      </c>
+      <c r="G210" s="4">
+        <v>121964</v>
+      </c>
+      <c r="H210" s="4">
+        <v>78553</v>
+      </c>
+      <c r="I210" s="4">
+        <v>148837</v>
+      </c>
+      <c r="J210" s="4">
+        <v>142636</v>
+      </c>
+      <c r="K210" s="4">
+        <v>192248</v>
+      </c>
+      <c r="L210" s="4">
+        <v>159173</v>
+      </c>
+      <c r="M210" s="4">
+        <v>165375</v>
+      </c>
+      <c r="N210" s="4">
+        <v>90956</v>
+      </c>
+      <c r="O210" s="4">
+        <v>99225</v>
+      </c>
+      <c r="P210" s="4">
+        <v>1600000</v>
+      </c>
+      <c r="Q210" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D210" s="4">
-        <v>0</v>
-      </c>
-      <c r="E210" s="4">
-        <v>0</v>
-      </c>
-      <c r="F210" s="4">
-        <v>0</v>
-      </c>
-      <c r="G210" s="4">
-        <v>0</v>
-      </c>
-      <c r="H210" s="4">
-        <v>0</v>
-      </c>
-      <c r="I210" s="4">
-        <v>0</v>
-      </c>
-      <c r="J210" s="4">
-        <v>0</v>
-      </c>
-      <c r="K210" s="4">
-        <v>0</v>
-      </c>
-      <c r="L210" s="4">
-        <v>0</v>
-      </c>
-      <c r="M210" s="4">
-        <v>1</v>
-      </c>
-      <c r="N210" s="4">
-        <v>0</v>
-      </c>
-      <c r="O210" s="4">
-        <v>0</v>
-      </c>
-      <c r="P210" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q210" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="R210" s="4" t="s">
         <v>21</v>
@@ -12273,55 +12414,55 @@
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
-        <v>280037</v>
+        <v>2712</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D211" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="E211" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="F211" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="G211" s="4">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="H211" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="I211" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="J211" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="K211" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="L211" s="4">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="M211" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="N211" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O211" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="P211" s="4">
-        <v>2</v>
+        <v>2200000</v>
       </c>
       <c r="Q211" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R211" s="4" t="s">
         <v>21</v>
@@ -12329,55 +12470,55 @@
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
-        <v>280037</v>
+        <v>2712</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D212" s="4">
         <v>0</v>
       </c>
       <c r="E212" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F212" s="4">
         <v>0</v>
       </c>
       <c r="G212" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H212" s="4">
         <v>0</v>
       </c>
       <c r="I212" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J212" s="4">
         <v>0</v>
       </c>
       <c r="K212" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L212" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M212" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N212" s="4">
         <v>0</v>
       </c>
       <c r="O212" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P212" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q212" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R212" s="4" t="s">
         <v>21</v>
@@ -12385,55 +12526,55 @@
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
-        <v>280037</v>
+        <v>2712</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D213" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E213" s="4">
         <v>1</v>
       </c>
       <c r="F213" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G213" s="4">
         <v>1</v>
       </c>
       <c r="H213" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I213" s="4">
         <v>1</v>
       </c>
       <c r="J213" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K213" s="4">
         <v>1</v>
       </c>
       <c r="L213" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M213" s="4">
         <v>1</v>
       </c>
       <c r="N213" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O213" s="4">
         <v>1</v>
       </c>
       <c r="P213" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q213" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R213" s="4" t="s">
         <v>21</v>
@@ -12441,55 +12582,55 @@
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
-        <v>280037</v>
+        <v>2712</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D214" s="4">
-        <v>95090</v>
+        <v>1</v>
       </c>
       <c r="E214" s="4">
-        <v>157106</v>
+        <v>1</v>
       </c>
       <c r="F214" s="4">
-        <v>148837</v>
+        <v>2</v>
       </c>
       <c r="G214" s="4">
-        <v>121964</v>
+        <v>3</v>
       </c>
       <c r="H214" s="4">
-        <v>78553</v>
+        <v>1</v>
       </c>
       <c r="I214" s="4">
-        <v>148837</v>
+        <v>1</v>
       </c>
       <c r="J214" s="4">
-        <v>142636</v>
+        <v>1</v>
       </c>
       <c r="K214" s="4">
-        <v>192248</v>
+        <v>2</v>
       </c>
       <c r="L214" s="4">
-        <v>159173</v>
+        <v>3</v>
       </c>
       <c r="M214" s="4">
-        <v>165375</v>
+        <v>1</v>
       </c>
       <c r="N214" s="4">
-        <v>90956</v>
+        <v>2</v>
       </c>
       <c r="O214" s="4">
-        <v>99225</v>
+        <v>2</v>
       </c>
       <c r="P214" s="4">
-        <v>1600000</v>
+        <v>20</v>
       </c>
       <c r="Q214" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R214" s="4" t="s">
         <v>21</v>
@@ -12500,52 +12641,52 @@
         <v>2712</v>
       </c>
       <c r="B215" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D215" s="4">
+        <v>0</v>
+      </c>
+      <c r="E215" s="4">
+        <v>0</v>
+      </c>
+      <c r="F215" s="4">
+        <v>1</v>
+      </c>
+      <c r="G215" s="4">
+        <v>0</v>
+      </c>
+      <c r="H215" s="4">
+        <v>0</v>
+      </c>
+      <c r="I215" s="4">
+        <v>1</v>
+      </c>
+      <c r="J215" s="4">
+        <v>0</v>
+      </c>
+      <c r="K215" s="4">
+        <v>0</v>
+      </c>
+      <c r="L215" s="4">
+        <v>1</v>
+      </c>
+      <c r="M215" s="4">
+        <v>0</v>
+      </c>
+      <c r="N215" s="4">
+        <v>0</v>
+      </c>
+      <c r="O215" s="4">
+        <v>1</v>
+      </c>
+      <c r="P215" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q215" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="C215" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D215" s="4">
-        <v>100000</v>
-      </c>
-      <c r="E215" s="4">
-        <v>100000</v>
-      </c>
-      <c r="F215" s="4">
-        <v>200000</v>
-      </c>
-      <c r="G215" s="4">
-        <v>300000</v>
-      </c>
-      <c r="H215" s="4">
-        <v>100000</v>
-      </c>
-      <c r="I215" s="4">
-        <v>100000</v>
-      </c>
-      <c r="J215" s="4">
-        <v>200000</v>
-      </c>
-      <c r="K215" s="4">
-        <v>200000</v>
-      </c>
-      <c r="L215" s="4">
-        <v>300000</v>
-      </c>
-      <c r="M215" s="4">
-        <v>200000</v>
-      </c>
-      <c r="N215" s="4">
-        <v>200000</v>
-      </c>
-      <c r="O215" s="4">
-        <v>200000</v>
-      </c>
-      <c r="P215" s="4">
-        <v>2200000</v>
-      </c>
-      <c r="Q215" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="R215" s="4" t="s">
         <v>21</v>
@@ -12553,55 +12694,55 @@
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
-        <v>2712</v>
+        <v>270018</v>
       </c>
       <c r="B216" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D216" s="4">
+        <v>0</v>
+      </c>
+      <c r="E216" s="4">
+        <v>0</v>
+      </c>
+      <c r="F216" s="4">
+        <v>200000</v>
+      </c>
+      <c r="G216" s="4">
+        <v>100000</v>
+      </c>
+      <c r="H216" s="4">
+        <v>100000</v>
+      </c>
+      <c r="I216" s="4">
+        <v>100000</v>
+      </c>
+      <c r="J216" s="4">
+        <v>200000</v>
+      </c>
+      <c r="K216" s="4">
+        <v>200000</v>
+      </c>
+      <c r="L216" s="4">
+        <v>200000</v>
+      </c>
+      <c r="M216" s="4">
+        <v>200000</v>
+      </c>
+      <c r="N216" s="4">
+        <v>100000</v>
+      </c>
+      <c r="O216" s="4">
+        <v>100000</v>
+      </c>
+      <c r="P216" s="4">
+        <v>1500000</v>
+      </c>
+      <c r="Q216" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="C216" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D216" s="4">
-        <v>0</v>
-      </c>
-      <c r="E216" s="4">
-        <v>1</v>
-      </c>
-      <c r="F216" s="4">
-        <v>0</v>
-      </c>
-      <c r="G216" s="4">
-        <v>1</v>
-      </c>
-      <c r="H216" s="4">
-        <v>0</v>
-      </c>
-      <c r="I216" s="4">
-        <v>1</v>
-      </c>
-      <c r="J216" s="4">
-        <v>0</v>
-      </c>
-      <c r="K216" s="4">
-        <v>1</v>
-      </c>
-      <c r="L216" s="4">
-        <v>0</v>
-      </c>
-      <c r="M216" s="4">
-        <v>1</v>
-      </c>
-      <c r="N216" s="4">
-        <v>0</v>
-      </c>
-      <c r="O216" s="4">
-        <v>1</v>
-      </c>
-      <c r="P216" s="4">
-        <v>6</v>
-      </c>
-      <c r="Q216" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="R216" s="4" t="s">
         <v>21</v>
@@ -12609,55 +12750,55 @@
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
-        <v>2712</v>
+        <v>270018</v>
       </c>
       <c r="B217" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D217" s="4">
+        <v>0</v>
+      </c>
+      <c r="E217" s="4">
+        <v>0</v>
+      </c>
+      <c r="F217" s="4">
+        <v>0</v>
+      </c>
+      <c r="G217" s="4">
+        <v>1</v>
+      </c>
+      <c r="H217" s="4">
+        <v>0</v>
+      </c>
+      <c r="I217" s="4">
+        <v>1</v>
+      </c>
+      <c r="J217" s="4">
+        <v>0</v>
+      </c>
+      <c r="K217" s="4">
+        <v>1</v>
+      </c>
+      <c r="L217" s="4">
+        <v>0</v>
+      </c>
+      <c r="M217" s="4">
+        <v>1</v>
+      </c>
+      <c r="N217" s="4">
+        <v>0</v>
+      </c>
+      <c r="O217" s="4">
+        <v>1</v>
+      </c>
+      <c r="P217" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q217" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="C217" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D217" s="4">
-        <v>0</v>
-      </c>
-      <c r="E217" s="4">
-        <v>1</v>
-      </c>
-      <c r="F217" s="4">
-        <v>0</v>
-      </c>
-      <c r="G217" s="4">
-        <v>1</v>
-      </c>
-      <c r="H217" s="4">
-        <v>0</v>
-      </c>
-      <c r="I217" s="4">
-        <v>1</v>
-      </c>
-      <c r="J217" s="4">
-        <v>0</v>
-      </c>
-      <c r="K217" s="4">
-        <v>1</v>
-      </c>
-      <c r="L217" s="4">
-        <v>0</v>
-      </c>
-      <c r="M217" s="4">
-        <v>1</v>
-      </c>
-      <c r="N217" s="4">
-        <v>0</v>
-      </c>
-      <c r="O217" s="4">
-        <v>1</v>
-      </c>
-      <c r="P217" s="4">
-        <v>6</v>
-      </c>
-      <c r="Q217" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="R217" s="4" t="s">
         <v>21</v>
@@ -12665,55 +12806,55 @@
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
-        <v>2712</v>
+        <v>270018</v>
       </c>
       <c r="B218" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D218" s="4">
+        <v>0</v>
+      </c>
+      <c r="E218" s="4">
+        <v>0</v>
+      </c>
+      <c r="F218" s="4">
+        <v>0</v>
+      </c>
+      <c r="G218" s="4">
+        <v>1</v>
+      </c>
+      <c r="H218" s="4">
+        <v>0</v>
+      </c>
+      <c r="I218" s="4">
+        <v>1</v>
+      </c>
+      <c r="J218" s="4">
+        <v>0</v>
+      </c>
+      <c r="K218" s="4">
+        <v>0</v>
+      </c>
+      <c r="L218" s="4">
+        <v>0</v>
+      </c>
+      <c r="M218" s="4">
+        <v>1</v>
+      </c>
+      <c r="N218" s="4">
+        <v>0</v>
+      </c>
+      <c r="O218" s="4">
+        <v>1</v>
+      </c>
+      <c r="P218" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q218" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="C218" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D218" s="4">
-        <v>1</v>
-      </c>
-      <c r="E218" s="4">
-        <v>1</v>
-      </c>
-      <c r="F218" s="4">
-        <v>2</v>
-      </c>
-      <c r="G218" s="4">
-        <v>3</v>
-      </c>
-      <c r="H218" s="4">
-        <v>1</v>
-      </c>
-      <c r="I218" s="4">
-        <v>1</v>
-      </c>
-      <c r="J218" s="4">
-        <v>1</v>
-      </c>
-      <c r="K218" s="4">
-        <v>2</v>
-      </c>
-      <c r="L218" s="4">
-        <v>3</v>
-      </c>
-      <c r="M218" s="4">
-        <v>1</v>
-      </c>
-      <c r="N218" s="4">
-        <v>2</v>
-      </c>
-      <c r="O218" s="4">
-        <v>2</v>
-      </c>
-      <c r="P218" s="4">
-        <v>20</v>
-      </c>
-      <c r="Q218" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="R218" s="4" t="s">
         <v>21</v>
@@ -12721,55 +12862,55 @@
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
-        <v>2712</v>
+        <v>270018</v>
       </c>
       <c r="B219" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D219" s="4">
+        <v>0</v>
+      </c>
+      <c r="E219" s="4">
+        <v>0</v>
+      </c>
+      <c r="F219" s="4">
+        <v>1</v>
+      </c>
+      <c r="G219" s="4">
+        <v>1</v>
+      </c>
+      <c r="H219" s="4">
+        <v>1</v>
+      </c>
+      <c r="I219" s="4">
+        <v>1</v>
+      </c>
+      <c r="J219" s="4">
+        <v>1</v>
+      </c>
+      <c r="K219" s="4">
+        <v>1</v>
+      </c>
+      <c r="L219" s="4">
+        <v>1</v>
+      </c>
+      <c r="M219" s="4">
+        <v>1</v>
+      </c>
+      <c r="N219" s="4">
+        <v>1</v>
+      </c>
+      <c r="O219" s="4">
+        <v>1</v>
+      </c>
+      <c r="P219" s="4">
+        <v>10</v>
+      </c>
+      <c r="Q219" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="C219" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D219" s="4">
-        <v>0</v>
-      </c>
-      <c r="E219" s="4">
-        <v>0</v>
-      </c>
-      <c r="F219" s="4">
-        <v>1</v>
-      </c>
-      <c r="G219" s="4">
-        <v>0</v>
-      </c>
-      <c r="H219" s="4">
-        <v>0</v>
-      </c>
-      <c r="I219" s="4">
-        <v>1</v>
-      </c>
-      <c r="J219" s="4">
-        <v>0</v>
-      </c>
-      <c r="K219" s="4">
-        <v>0</v>
-      </c>
-      <c r="L219" s="4">
-        <v>1</v>
-      </c>
-      <c r="M219" s="4">
-        <v>0</v>
-      </c>
-      <c r="N219" s="4">
-        <v>0</v>
-      </c>
-      <c r="O219" s="4">
-        <v>1</v>
-      </c>
-      <c r="P219" s="4">
-        <v>4</v>
-      </c>
-      <c r="Q219" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="R219" s="4" t="s">
         <v>21</v>
@@ -12780,10 +12921,10 @@
         <v>270018</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D220" s="4">
         <v>0</v>
@@ -12792,40 +12933,40 @@
         <v>0</v>
       </c>
       <c r="F220" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="G220" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H220" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="I220" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="J220" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="K220" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="L220" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="M220" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="N220" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="O220" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="P220" s="4">
-        <v>1500000</v>
+        <v>4</v>
       </c>
       <c r="Q220" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R220" s="4" t="s">
         <v>21</v>
@@ -12833,55 +12974,55 @@
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
-        <v>270018</v>
+        <v>270035</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D221" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="E221" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="F221" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G221" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="H221" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="I221" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="J221" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="K221" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="L221" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="M221" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="N221" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="O221" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="P221" s="4">
-        <v>5</v>
+        <v>1700000</v>
       </c>
       <c r="Q221" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R221" s="4" t="s">
         <v>21</v>
@@ -12889,19 +13030,19 @@
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
-        <v>270018</v>
+        <v>270035</v>
       </c>
       <c r="B222" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D222" s="4">
         <v>0</v>
       </c>
       <c r="E222" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F222" s="4">
         <v>0</v>
@@ -12919,7 +13060,7 @@
         <v>0</v>
       </c>
       <c r="K222" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L222" s="4">
         <v>0</v>
@@ -12934,10 +13075,10 @@
         <v>1</v>
       </c>
       <c r="P222" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q222" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R222" s="4" t="s">
         <v>21</v>
@@ -12945,55 +13086,55 @@
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
-        <v>270018</v>
+        <v>270035</v>
       </c>
       <c r="B223" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D223" s="4">
         <v>0</v>
       </c>
       <c r="E223" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F223" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G223" s="4">
         <v>1</v>
       </c>
       <c r="H223" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I223" s="4">
         <v>1</v>
       </c>
       <c r="J223" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K223" s="4">
         <v>1</v>
       </c>
       <c r="L223" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M223" s="4">
         <v>1</v>
       </c>
       <c r="N223" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O223" s="4">
         <v>1</v>
       </c>
       <c r="P223" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q223" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R223" s="4" t="s">
         <v>21</v>
@@ -13001,55 +13142,55 @@
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
-        <v>270018</v>
+        <v>270035</v>
       </c>
       <c r="B224" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D224" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E224" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F224" s="4">
         <v>1</v>
       </c>
       <c r="G224" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H224" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I224" s="4">
         <v>1</v>
       </c>
       <c r="J224" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K224" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L224" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M224" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N224" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O224" s="4">
         <v>1</v>
       </c>
       <c r="P224" s="4">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q224" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R224" s="4" t="s">
         <v>21</v>
@@ -13060,52 +13201,52 @@
         <v>270035</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D225" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="E225" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="F225" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="G225" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H225" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="I225" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="J225" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="K225" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="L225" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="M225" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="N225" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="O225" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="P225" s="4">
-        <v>1700000</v>
+        <v>4</v>
       </c>
       <c r="Q225" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R225" s="4" t="s">
         <v>21</v>
@@ -13113,55 +13254,55 @@
     </row>
     <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
-        <v>270035</v>
+        <v>270029</v>
       </c>
       <c r="B226" s="4" t="s">
         <v>75</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D226" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="E226" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="F226" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G226" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="H226" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="I226" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="J226" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="K226" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="L226" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="M226" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="N226" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="O226" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="P226" s="4">
-        <v>6</v>
+        <v>1700000</v>
       </c>
       <c r="Q226" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R226" s="4" t="s">
         <v>21</v>
@@ -13169,13 +13310,13 @@
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
-        <v>270035</v>
+        <v>270029</v>
       </c>
       <c r="B227" s="4" t="s">
         <v>75</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D227" s="4">
         <v>0</v>
@@ -13217,7 +13358,7 @@
         <v>6</v>
       </c>
       <c r="Q227" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R227" s="4" t="s">
         <v>21</v>
@@ -13225,55 +13366,55 @@
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
-        <v>270035</v>
+        <v>270029</v>
       </c>
       <c r="B228" s="4" t="s">
         <v>75</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D228" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E228" s="4">
         <v>1</v>
       </c>
       <c r="F228" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G228" s="4">
         <v>1</v>
       </c>
       <c r="H228" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I228" s="4">
         <v>1</v>
       </c>
       <c r="J228" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K228" s="4">
         <v>1</v>
       </c>
       <c r="L228" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M228" s="4">
         <v>1</v>
       </c>
       <c r="N228" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O228" s="4">
         <v>1</v>
       </c>
       <c r="P228" s="4">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q228" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R228" s="4" t="s">
         <v>21</v>
@@ -13281,55 +13422,55 @@
     </row>
     <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
-        <v>270035</v>
+        <v>270029</v>
       </c>
       <c r="B229" s="4" t="s">
         <v>75</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D229" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E229" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F229" s="4">
         <v>1</v>
       </c>
       <c r="G229" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H229" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I229" s="4">
         <v>1</v>
       </c>
       <c r="J229" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K229" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L229" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M229" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N229" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O229" s="4">
         <v>1</v>
       </c>
       <c r="P229" s="4">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q229" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R229" s="4" t="s">
         <v>21</v>
@@ -13340,52 +13481,52 @@
         <v>270029</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D230" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="E230" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="F230" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="G230" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H230" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="I230" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="J230" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="K230" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="L230" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="M230" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="N230" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="O230" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="P230" s="4">
-        <v>1700000</v>
+        <v>4</v>
       </c>
       <c r="Q230" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R230" s="4" t="s">
         <v>21</v>
@@ -13393,22 +13534,22 @@
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
-        <v>270029</v>
+        <v>212910</v>
       </c>
       <c r="B231" s="4" t="s">
         <v>76</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D231" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E231" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F231" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G231" s="4">
         <v>1</v>
@@ -13420,28 +13561,28 @@
         <v>1</v>
       </c>
       <c r="J231" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K231" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L231" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M231" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N231" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O231" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P231" s="4">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="Q231" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R231" s="4" t="s">
         <v>21</v>
@@ -13449,55 +13590,55 @@
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
-        <v>270029</v>
+        <v>212910</v>
       </c>
       <c r="B232" s="4" t="s">
         <v>76</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D232" s="4">
-        <v>0</v>
+        <v>133333</v>
       </c>
       <c r="E232" s="4">
-        <v>1</v>
+        <v>315152</v>
       </c>
       <c r="F232" s="4">
-        <v>0</v>
+        <v>60606</v>
       </c>
       <c r="G232" s="4">
-        <v>1</v>
+        <v>109091</v>
       </c>
       <c r="H232" s="4">
-        <v>0</v>
+        <v>169697</v>
       </c>
       <c r="I232" s="4">
-        <v>1</v>
+        <v>157576</v>
       </c>
       <c r="J232" s="4">
-        <v>0</v>
+        <v>181818</v>
       </c>
       <c r="K232" s="4">
-        <v>1</v>
+        <v>254545</v>
       </c>
       <c r="L232" s="4">
-        <v>0</v>
+        <v>230303</v>
       </c>
       <c r="M232" s="4">
-        <v>1</v>
+        <v>193939</v>
       </c>
       <c r="N232" s="4">
-        <v>0</v>
+        <v>121213</v>
       </c>
       <c r="O232" s="4">
-        <v>1</v>
+        <v>72727</v>
       </c>
       <c r="P232" s="4">
-        <v>6</v>
+        <v>2000000</v>
       </c>
       <c r="Q232" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R232" s="4" t="s">
         <v>21</v>
@@ -13505,55 +13646,55 @@
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
-        <v>270029</v>
+        <v>212910</v>
       </c>
       <c r="B233" s="4" t="s">
         <v>76</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D233" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E233" s="4">
         <v>1</v>
       </c>
       <c r="F233" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G233" s="4">
         <v>1</v>
       </c>
       <c r="H233" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I233" s="4">
         <v>1</v>
       </c>
       <c r="J233" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K233" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L233" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M233" s="4">
         <v>1</v>
       </c>
       <c r="N233" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O233" s="4">
         <v>1</v>
       </c>
       <c r="P233" s="4">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Q233" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R233" s="4" t="s">
         <v>21</v>
@@ -13561,55 +13702,55 @@
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
-        <v>270029</v>
+        <v>212876</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D234" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E234" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F234" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G234" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H234" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I234" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J234" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K234" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L234" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M234" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N234" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O234" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P234" s="4">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="Q234" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R234" s="4" t="s">
         <v>21</v>
@@ -13617,55 +13758,55 @@
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
-        <v>212910</v>
+        <v>212876</v>
       </c>
       <c r="B235" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D235" s="4">
+        <v>222222</v>
+      </c>
+      <c r="E235" s="4">
+        <v>130719</v>
+      </c>
+      <c r="F235" s="4">
+        <v>222222</v>
+      </c>
+      <c r="G235" s="4">
+        <v>156863</v>
+      </c>
+      <c r="H235" s="4">
+        <v>222222</v>
+      </c>
+      <c r="I235" s="4">
+        <v>91503</v>
+      </c>
+      <c r="J235" s="4">
+        <v>209150</v>
+      </c>
+      <c r="K235" s="4">
+        <v>261438</v>
+      </c>
+      <c r="L235" s="4">
+        <v>143791</v>
+      </c>
+      <c r="M235" s="4">
+        <v>91504</v>
+      </c>
+      <c r="N235" s="4">
+        <v>143791</v>
+      </c>
+      <c r="O235" s="4">
+        <v>104575</v>
+      </c>
+      <c r="P235" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="Q235" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="C235" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D235" s="4">
-        <v>1</v>
-      </c>
-      <c r="E235" s="4">
-        <v>5</v>
-      </c>
-      <c r="F235" s="4">
-        <v>1</v>
-      </c>
-      <c r="G235" s="4">
-        <v>1</v>
-      </c>
-      <c r="H235" s="4">
-        <v>0</v>
-      </c>
-      <c r="I235" s="4">
-        <v>1</v>
-      </c>
-      <c r="J235" s="4">
-        <v>2</v>
-      </c>
-      <c r="K235" s="4">
-        <v>2</v>
-      </c>
-      <c r="L235" s="4">
-        <v>1</v>
-      </c>
-      <c r="M235" s="4">
-        <v>2</v>
-      </c>
-      <c r="N235" s="4">
-        <v>1</v>
-      </c>
-      <c r="O235" s="4">
-        <v>0</v>
-      </c>
-      <c r="P235" s="4">
-        <v>17</v>
-      </c>
-      <c r="Q235" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="R235" s="4" t="s">
         <v>21</v>
@@ -13673,281 +13814,57 @@
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
-        <v>212910</v>
+        <v>212876</v>
       </c>
       <c r="B236" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D236" s="4">
+        <v>0</v>
+      </c>
+      <c r="E236" s="4">
+        <v>1</v>
+      </c>
+      <c r="F236" s="4">
+        <v>0</v>
+      </c>
+      <c r="G236" s="4">
+        <v>1</v>
+      </c>
+      <c r="H236" s="4">
+        <v>0</v>
+      </c>
+      <c r="I236" s="4">
+        <v>1</v>
+      </c>
+      <c r="J236" s="4">
+        <v>0</v>
+      </c>
+      <c r="K236" s="4">
+        <v>0</v>
+      </c>
+      <c r="L236" s="4">
+        <v>0</v>
+      </c>
+      <c r="M236" s="4">
+        <v>1</v>
+      </c>
+      <c r="N236" s="4">
+        <v>0</v>
+      </c>
+      <c r="O236" s="4">
+        <v>1</v>
+      </c>
+      <c r="P236" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q236" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C236" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D236" s="4">
-        <v>133333</v>
-      </c>
-      <c r="E236" s="4">
-        <v>315152</v>
-      </c>
-      <c r="F236" s="4">
-        <v>60606</v>
-      </c>
-      <c r="G236" s="4">
-        <v>109091</v>
-      </c>
-      <c r="H236" s="4">
-        <v>169697</v>
-      </c>
-      <c r="I236" s="4">
-        <v>157576</v>
-      </c>
-      <c r="J236" s="4">
-        <v>181818</v>
-      </c>
-      <c r="K236" s="4">
-        <v>254545</v>
-      </c>
-      <c r="L236" s="4">
-        <v>230303</v>
-      </c>
-      <c r="M236" s="4">
-        <v>193939</v>
-      </c>
-      <c r="N236" s="4">
-        <v>121213</v>
-      </c>
-      <c r="O236" s="4">
-        <v>72727</v>
-      </c>
-      <c r="P236" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="Q236" s="4" t="s">
-        <v>78</v>
-      </c>
       <c r="R236" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A237" s="4">
-        <v>212910</v>
-      </c>
-      <c r="B237" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C237" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D237" s="4">
-        <v>0</v>
-      </c>
-      <c r="E237" s="4">
-        <v>1</v>
-      </c>
-      <c r="F237" s="4">
-        <v>0</v>
-      </c>
-      <c r="G237" s="4">
-        <v>1</v>
-      </c>
-      <c r="H237" s="4">
-        <v>0</v>
-      </c>
-      <c r="I237" s="4">
-        <v>1</v>
-      </c>
-      <c r="J237" s="4">
-        <v>0</v>
-      </c>
-      <c r="K237" s="4">
-        <v>0</v>
-      </c>
-      <c r="L237" s="4">
-        <v>0</v>
-      </c>
-      <c r="M237" s="4">
-        <v>1</v>
-      </c>
-      <c r="N237" s="4">
-        <v>0</v>
-      </c>
-      <c r="O237" s="4">
-        <v>1</v>
-      </c>
-      <c r="P237" s="4">
-        <v>5</v>
-      </c>
-      <c r="Q237" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R237" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A238" s="4">
-        <v>212876</v>
-      </c>
-      <c r="B238" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C238" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D238" s="4">
-        <v>4</v>
-      </c>
-      <c r="E238" s="4">
-        <v>3</v>
-      </c>
-      <c r="F238" s="4">
-        <v>3</v>
-      </c>
-      <c r="G238" s="4">
-        <v>3</v>
-      </c>
-      <c r="H238" s="4">
-        <v>2</v>
-      </c>
-      <c r="I238" s="4">
-        <v>4</v>
-      </c>
-      <c r="J238" s="4">
-        <v>4</v>
-      </c>
-      <c r="K238" s="4">
-        <v>4</v>
-      </c>
-      <c r="L238" s="4">
-        <v>2</v>
-      </c>
-      <c r="M238" s="4">
-        <v>3</v>
-      </c>
-      <c r="N238" s="4">
-        <v>3</v>
-      </c>
-      <c r="O238" s="4">
-        <v>3</v>
-      </c>
-      <c r="P238" s="4">
-        <v>38</v>
-      </c>
-      <c r="Q238" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R238" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A239" s="4">
-        <v>212876</v>
-      </c>
-      <c r="B239" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C239" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D239" s="4">
-        <v>222222</v>
-      </c>
-      <c r="E239" s="4">
-        <v>130719</v>
-      </c>
-      <c r="F239" s="4">
-        <v>222222</v>
-      </c>
-      <c r="G239" s="4">
-        <v>156863</v>
-      </c>
-      <c r="H239" s="4">
-        <v>222222</v>
-      </c>
-      <c r="I239" s="4">
-        <v>91503</v>
-      </c>
-      <c r="J239" s="4">
-        <v>209150</v>
-      </c>
-      <c r="K239" s="4">
-        <v>261438</v>
-      </c>
-      <c r="L239" s="4">
-        <v>143791</v>
-      </c>
-      <c r="M239" s="4">
-        <v>91504</v>
-      </c>
-      <c r="N239" s="4">
-        <v>143791</v>
-      </c>
-      <c r="O239" s="4">
-        <v>104575</v>
-      </c>
-      <c r="P239" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="Q239" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R239" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A240" s="4">
-        <v>212876</v>
-      </c>
-      <c r="B240" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C240" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D240" s="4">
-        <v>0</v>
-      </c>
-      <c r="E240" s="4">
-        <v>1</v>
-      </c>
-      <c r="F240" s="4">
-        <v>0</v>
-      </c>
-      <c r="G240" s="4">
-        <v>1</v>
-      </c>
-      <c r="H240" s="4">
-        <v>0</v>
-      </c>
-      <c r="I240" s="4">
-        <v>1</v>
-      </c>
-      <c r="J240" s="4">
-        <v>0</v>
-      </c>
-      <c r="K240" s="4">
-        <v>0</v>
-      </c>
-      <c r="L240" s="4">
-        <v>0</v>
-      </c>
-      <c r="M240" s="4">
-        <v>1</v>
-      </c>
-      <c r="N240" s="4">
-        <v>0</v>
-      </c>
-      <c r="O240" s="4">
-        <v>1</v>
-      </c>
-      <c r="P240" s="4">
-        <v>5</v>
-      </c>
-      <c r="Q240" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R240" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -13966,17 +13883,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B96036E30F13644F923D207E371C305D" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d197ceb99055fd1a93a3a14aec1bdd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f76aa77c-8923-4724-9a6d-d588cc513697" xmlns:ns3="89c54d5b-05ac-45d5-9242-aabb385cc5ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b86266bfd619f312673123d0bd20d23" ns2:_="" ns3:_="">
     <xsd:import namespace="f76aa77c-8923-4724-9a6d-d588cc513697"/>
@@ -14171,6 +14077,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
   <ds:schemaRefs>
@@ -14180,23 +14097,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BDC8EFC-C946-4B3C-B84E-1270F018751C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14213,4 +14113,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/dados/metas.xlsx
+++ b/dados/metas.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.sa\Documents\dashboard-oportunidades\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1BDF74-1019-44C6-ADA7-F0D708365B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DE449A-755E-477D-985A-0F21147DD0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Plan1" sheetId="1" r:id="rId1"/>
+    <sheet name="CONSULTOR" sheetId="1" r:id="rId1"/>
+    <sheet name="LOJA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$R$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CONSULTOR!$A$1:$R$236</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="92">
   <si>
     <t>CÓD</t>
   </si>
@@ -277,12 +278,54 @@
   <si>
     <t>GUILHERME.SANTOS</t>
   </si>
+  <si>
+    <t>NOME</t>
+  </si>
+  <si>
+    <t>REGIÃO</t>
+  </si>
+  <si>
+    <t>PME - VENDA NOVA</t>
+  </si>
+  <si>
+    <t>SUDESTE</t>
+  </si>
+  <si>
+    <t>PME - TEIXEIRA</t>
+  </si>
+  <si>
+    <t>PME - MANHUAÇU</t>
+  </si>
+  <si>
+    <t>PME - GOV VALADARES</t>
+  </si>
+  <si>
+    <t>PME - LINHARES</t>
+  </si>
+  <si>
+    <t>PME - BOM JESUS</t>
+  </si>
+  <si>
+    <t>CERRADO</t>
+  </si>
+  <si>
+    <t>PME - LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>PME - URUÇUÍ</t>
+  </si>
+  <si>
+    <t>PME - TANGUÁ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -299,6 +342,23 @@
     <font>
       <b/>
       <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -349,7 +409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -362,6 +422,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13873,6 +13951,5700 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BF59FEE-C513-4F8C-BD0F-7D91A396A946}">
+  <dimension ref="A1:R176"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>18</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="5">
+        <v>3</v>
+      </c>
+      <c r="E2" s="5">
+        <v>3</v>
+      </c>
+      <c r="F2" s="5">
+        <v>5</v>
+      </c>
+      <c r="G2" s="5">
+        <v>6</v>
+      </c>
+      <c r="H2" s="5">
+        <v>4</v>
+      </c>
+      <c r="I2" s="5">
+        <v>4</v>
+      </c>
+      <c r="J2" s="5">
+        <v>4</v>
+      </c>
+      <c r="K2" s="5">
+        <v>5</v>
+      </c>
+      <c r="L2" s="5">
+        <v>8</v>
+      </c>
+      <c r="M2" s="5">
+        <v>4</v>
+      </c>
+      <c r="N2" s="5">
+        <v>5</v>
+      </c>
+      <c r="O2" s="5">
+        <v>5</v>
+      </c>
+      <c r="P2" s="6">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>18</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="5">
+        <v>300000</v>
+      </c>
+      <c r="E3" s="5">
+        <v>300000</v>
+      </c>
+      <c r="F3" s="5">
+        <v>800000</v>
+      </c>
+      <c r="G3" s="5">
+        <v>600000</v>
+      </c>
+      <c r="H3" s="5">
+        <v>400000</v>
+      </c>
+      <c r="I3" s="5">
+        <v>400000</v>
+      </c>
+      <c r="J3" s="5">
+        <v>800000</v>
+      </c>
+      <c r="K3" s="5">
+        <v>800000</v>
+      </c>
+      <c r="L3" s="5">
+        <v>900000</v>
+      </c>
+      <c r="M3" s="5">
+        <v>800000</v>
+      </c>
+      <c r="N3" s="5">
+        <v>500000</v>
+      </c>
+      <c r="O3" s="5">
+        <v>500000</v>
+      </c>
+      <c r="P3" s="6">
+        <v>7100000</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="6">
+        <v>16</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>18</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>3</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>4</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>3</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>4</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="6">
+        <v>22</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>18</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>4</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>4</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>4</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>4</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5">
+        <v>4</v>
+      </c>
+      <c r="P6" s="6">
+        <v>23</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5">
+        <v>8</v>
+      </c>
+      <c r="F7" s="5">
+        <v>8</v>
+      </c>
+      <c r="G7" s="5">
+        <v>11</v>
+      </c>
+      <c r="H7" s="5">
+        <v>8</v>
+      </c>
+      <c r="I7" s="5">
+        <v>8</v>
+      </c>
+      <c r="J7" s="5">
+        <v>8</v>
+      </c>
+      <c r="K7" s="5">
+        <v>12</v>
+      </c>
+      <c r="L7" s="5">
+        <v>8</v>
+      </c>
+      <c r="M7" s="5">
+        <v>11</v>
+      </c>
+      <c r="N7" s="5">
+        <v>7</v>
+      </c>
+      <c r="O7" s="5">
+        <v>11</v>
+      </c>
+      <c r="P7" s="6">
+        <v>104</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1196456</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1276220</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1781388</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1834564</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1621860</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1754800</v>
+      </c>
+      <c r="J8" s="5">
+        <v>1568684</v>
+      </c>
+      <c r="K8" s="5">
+        <v>1754800</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1595272</v>
+      </c>
+      <c r="M8" s="5">
+        <v>1010340</v>
+      </c>
+      <c r="N8" s="5">
+        <v>850812</v>
+      </c>
+      <c r="O8" s="5">
+        <v>1754800</v>
+      </c>
+      <c r="P8" s="6">
+        <v>17999996</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>4</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>4</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>4</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>4</v>
+      </c>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="6">
+        <v>20</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>4</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>4</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>4</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>4</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>4</v>
+      </c>
+      <c r="O10" s="5">
+        <v>0</v>
+      </c>
+      <c r="P10" s="6">
+        <v>20</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="5">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5">
+        <v>4</v>
+      </c>
+      <c r="F11" s="5">
+        <v>4</v>
+      </c>
+      <c r="G11" s="5">
+        <v>4</v>
+      </c>
+      <c r="H11" s="5">
+        <v>4</v>
+      </c>
+      <c r="I11" s="5">
+        <v>4</v>
+      </c>
+      <c r="J11" s="5">
+        <v>4</v>
+      </c>
+      <c r="K11" s="5">
+        <v>4</v>
+      </c>
+      <c r="L11" s="5">
+        <v>4</v>
+      </c>
+      <c r="M11" s="5">
+        <v>4</v>
+      </c>
+      <c r="N11" s="5">
+        <v>4</v>
+      </c>
+      <c r="O11" s="5">
+        <v>4</v>
+      </c>
+      <c r="P11" s="6">
+        <v>48</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>16</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="5">
+        <v>14</v>
+      </c>
+      <c r="E12" s="5">
+        <v>18</v>
+      </c>
+      <c r="F12" s="5">
+        <v>15</v>
+      </c>
+      <c r="G12" s="5">
+        <v>19</v>
+      </c>
+      <c r="H12" s="5">
+        <v>22</v>
+      </c>
+      <c r="I12" s="5">
+        <v>23</v>
+      </c>
+      <c r="J12" s="5">
+        <v>18</v>
+      </c>
+      <c r="K12" s="5">
+        <v>31</v>
+      </c>
+      <c r="L12" s="5">
+        <v>37</v>
+      </c>
+      <c r="M12" s="5">
+        <v>21</v>
+      </c>
+      <c r="N12" s="5">
+        <v>18</v>
+      </c>
+      <c r="O12" s="5">
+        <v>14</v>
+      </c>
+      <c r="P12" s="6">
+        <v>250</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="R12" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>16</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1804492</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1675599</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1878145</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1620360</v>
+      </c>
+      <c r="H13" s="5">
+        <v>2541017</v>
+      </c>
+      <c r="I13" s="5">
+        <v>2356886</v>
+      </c>
+      <c r="J13" s="5">
+        <v>1804492</v>
+      </c>
+      <c r="K13" s="5">
+        <v>2596257</v>
+      </c>
+      <c r="L13" s="5">
+        <v>2633085</v>
+      </c>
+      <c r="M13" s="5">
+        <v>2412127</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1583532</v>
+      </c>
+      <c r="O13" s="5">
+        <v>1694012</v>
+      </c>
+      <c r="P13" s="6">
+        <v>24600004</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="R13" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>16</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>7</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>7</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>7</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>7</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>7</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5">
+        <v>7</v>
+      </c>
+      <c r="P14" s="6">
+        <v>42</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="R14" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>16</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>7</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>7</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>7</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>7</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>7</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+      <c r="O15" s="5">
+        <v>7</v>
+      </c>
+      <c r="P15" s="6">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="R15" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>34</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>4</v>
+      </c>
+      <c r="F16" s="5">
+        <v>4</v>
+      </c>
+      <c r="G16" s="5">
+        <v>4</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5">
+        <v>2</v>
+      </c>
+      <c r="J16" s="5">
+        <v>5</v>
+      </c>
+      <c r="K16" s="5">
+        <v>4</v>
+      </c>
+      <c r="L16" s="5">
+        <v>6</v>
+      </c>
+      <c r="M16" s="5">
+        <v>5</v>
+      </c>
+      <c r="N16" s="5">
+        <v>4</v>
+      </c>
+      <c r="O16" s="5">
+        <v>3</v>
+      </c>
+      <c r="P16" s="6">
+        <v>42</v>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>34</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="5">
+        <v>110000</v>
+      </c>
+      <c r="E17" s="5">
+        <v>450000</v>
+      </c>
+      <c r="F17" s="5">
+        <v>360000</v>
+      </c>
+      <c r="G17" s="5">
+        <v>380000</v>
+      </c>
+      <c r="H17" s="5">
+        <v>210000</v>
+      </c>
+      <c r="I17" s="5">
+        <v>110000</v>
+      </c>
+      <c r="J17" s="5">
+        <v>430000</v>
+      </c>
+      <c r="K17" s="5">
+        <v>390000</v>
+      </c>
+      <c r="L17" s="5">
+        <v>590000</v>
+      </c>
+      <c r="M17" s="5">
+        <v>630000</v>
+      </c>
+      <c r="N17" s="5">
+        <v>490000</v>
+      </c>
+      <c r="O17" s="5">
+        <v>350000</v>
+      </c>
+      <c r="P17" s="6">
+        <v>4500000</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>34</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
+        <v>4</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5">
+        <v>4</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5">
+        <v>4</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
+        <v>4</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5">
+        <v>4</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5">
+        <v>4</v>
+      </c>
+      <c r="P18" s="6">
+        <v>24</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>34</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5">
+        <v>4</v>
+      </c>
+      <c r="F19" s="5">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5">
+        <v>4</v>
+      </c>
+      <c r="H19" s="5">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5">
+        <v>4</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5">
+        <v>4</v>
+      </c>
+      <c r="N19" s="5">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5">
+        <v>4</v>
+      </c>
+      <c r="P19" s="6">
+        <v>20</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>9</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="5">
+        <v>15</v>
+      </c>
+      <c r="E20" s="5">
+        <v>15</v>
+      </c>
+      <c r="F20" s="5">
+        <v>22</v>
+      </c>
+      <c r="G20" s="5">
+        <v>26</v>
+      </c>
+      <c r="H20" s="5">
+        <v>23</v>
+      </c>
+      <c r="I20" s="5">
+        <v>27</v>
+      </c>
+      <c r="J20" s="5">
+        <v>22</v>
+      </c>
+      <c r="K20" s="5">
+        <v>30</v>
+      </c>
+      <c r="L20" s="5">
+        <v>28</v>
+      </c>
+      <c r="M20" s="5">
+        <v>22</v>
+      </c>
+      <c r="N20" s="5">
+        <v>19</v>
+      </c>
+      <c r="O20" s="5">
+        <v>20</v>
+      </c>
+      <c r="P20" s="6">
+        <v>269</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="R20" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>9</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="5">
+        <v>2</v>
+      </c>
+      <c r="E21" s="5">
+        <v>4</v>
+      </c>
+      <c r="F21" s="5">
+        <v>3</v>
+      </c>
+      <c r="G21" s="5">
+        <v>2</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5">
+        <v>4</v>
+      </c>
+      <c r="N21" s="5">
+        <v>5</v>
+      </c>
+      <c r="O21" s="5">
+        <v>1</v>
+      </c>
+      <c r="P21" s="6">
+        <v>21</v>
+      </c>
+      <c r="Q21" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="R21" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>9</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="5">
+        <v>11</v>
+      </c>
+      <c r="E22" s="5">
+        <v>16</v>
+      </c>
+      <c r="F22" s="5">
+        <v>22</v>
+      </c>
+      <c r="G22" s="5">
+        <v>17</v>
+      </c>
+      <c r="H22" s="5">
+        <v>3</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <v>8</v>
+      </c>
+      <c r="M22" s="5">
+        <v>13</v>
+      </c>
+      <c r="N22" s="5">
+        <v>18</v>
+      </c>
+      <c r="O22" s="5">
+        <v>15</v>
+      </c>
+      <c r="P22" s="6">
+        <v>123</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="R22" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>9</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5">
+        <v>3</v>
+      </c>
+      <c r="F23" s="5">
+        <v>3</v>
+      </c>
+      <c r="G23" s="5">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5">
+        <v>0</v>
+      </c>
+      <c r="I23" s="5">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5">
+        <v>0</v>
+      </c>
+      <c r="M23" s="5">
+        <v>2</v>
+      </c>
+      <c r="N23" s="5">
+        <v>4</v>
+      </c>
+      <c r="O23" s="5">
+        <v>0</v>
+      </c>
+      <c r="P23" s="6">
+        <v>12</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="R23" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>9</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1795118</v>
+      </c>
+      <c r="E24" s="5">
+        <v>2092705</v>
+      </c>
+      <c r="F24" s="5">
+        <v>4787743</v>
+      </c>
+      <c r="G24" s="5">
+        <v>4751782.666666667</v>
+      </c>
+      <c r="H24" s="5">
+        <v>4628360</v>
+      </c>
+      <c r="I24" s="5">
+        <v>4097639.6666666665</v>
+      </c>
+      <c r="J24" s="5">
+        <v>4677728</v>
+      </c>
+      <c r="K24" s="5">
+        <v>4788810</v>
+      </c>
+      <c r="L24" s="5">
+        <v>4492595</v>
+      </c>
+      <c r="M24" s="5">
+        <v>3204880.6666666665</v>
+      </c>
+      <c r="N24" s="5">
+        <v>2681021</v>
+      </c>
+      <c r="O24" s="5">
+        <v>3001617</v>
+      </c>
+      <c r="P24" s="6">
+        <v>45000000</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="R24" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>9</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="5">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5">
+        <v>4</v>
+      </c>
+      <c r="F25" s="5">
+        <v>2</v>
+      </c>
+      <c r="G25" s="5">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5">
+        <v>5</v>
+      </c>
+      <c r="I25" s="5">
+        <v>5</v>
+      </c>
+      <c r="J25" s="5">
+        <v>5</v>
+      </c>
+      <c r="K25" s="5">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5">
+        <v>6</v>
+      </c>
+      <c r="M25" s="5">
+        <v>0</v>
+      </c>
+      <c r="N25" s="5">
+        <v>5</v>
+      </c>
+      <c r="O25" s="5">
+        <v>0</v>
+      </c>
+      <c r="P25" s="6">
+        <v>32</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="R25" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>9</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="5">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5">
+        <v>4</v>
+      </c>
+      <c r="F26" s="5">
+        <v>2</v>
+      </c>
+      <c r="G26" s="5">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5">
+        <v>5</v>
+      </c>
+      <c r="I26" s="5">
+        <v>5</v>
+      </c>
+      <c r="J26" s="5">
+        <v>4</v>
+      </c>
+      <c r="K26" s="5">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5">
+        <v>6</v>
+      </c>
+      <c r="M26" s="5">
+        <v>1</v>
+      </c>
+      <c r="N26" s="5">
+        <v>5</v>
+      </c>
+      <c r="O26" s="5">
+        <v>0</v>
+      </c>
+      <c r="P26" s="6">
+        <v>32</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="R26" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>9</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="5">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5">
+        <v>4</v>
+      </c>
+      <c r="F27" s="5">
+        <v>2</v>
+      </c>
+      <c r="G27" s="5">
+        <v>6</v>
+      </c>
+      <c r="H27" s="5">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5">
+        <v>6</v>
+      </c>
+      <c r="J27" s="5">
+        <v>0</v>
+      </c>
+      <c r="K27" s="5">
+        <v>6</v>
+      </c>
+      <c r="L27" s="5">
+        <v>6</v>
+      </c>
+      <c r="M27" s="5">
+        <v>0</v>
+      </c>
+      <c r="N27" s="5">
+        <v>6</v>
+      </c>
+      <c r="O27" s="5">
+        <v>0</v>
+      </c>
+      <c r="P27" s="6">
+        <v>36</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="R27" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>19</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="5">
+        <v>2</v>
+      </c>
+      <c r="E28" s="5">
+        <v>2</v>
+      </c>
+      <c r="F28" s="5">
+        <v>2</v>
+      </c>
+      <c r="G28" s="5">
+        <v>2</v>
+      </c>
+      <c r="H28" s="5">
+        <v>2</v>
+      </c>
+      <c r="I28" s="5">
+        <v>2</v>
+      </c>
+      <c r="J28" s="5">
+        <v>2</v>
+      </c>
+      <c r="K28" s="5">
+        <v>2</v>
+      </c>
+      <c r="L28" s="5">
+        <v>2</v>
+      </c>
+      <c r="M28" s="5">
+        <v>2</v>
+      </c>
+      <c r="N28" s="5">
+        <v>2</v>
+      </c>
+      <c r="O28" s="5">
+        <v>2</v>
+      </c>
+      <c r="P28" s="6">
+        <v>24</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R28" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>19</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="5">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5">
+        <v>0</v>
+      </c>
+      <c r="H29" s="5">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5">
+        <v>0</v>
+      </c>
+      <c r="J29" s="5">
+        <v>0</v>
+      </c>
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5">
+        <v>0</v>
+      </c>
+      <c r="M29" s="5">
+        <v>2</v>
+      </c>
+      <c r="N29" s="5">
+        <v>0</v>
+      </c>
+      <c r="O29" s="5">
+        <v>0</v>
+      </c>
+      <c r="P29" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R29" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>19</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="5">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5">
+        <v>2</v>
+      </c>
+      <c r="F30" s="5">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5">
+        <v>0</v>
+      </c>
+      <c r="M30" s="5">
+        <v>0</v>
+      </c>
+      <c r="N30" s="5">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5">
+        <v>0</v>
+      </c>
+      <c r="P30" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q30" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R30" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>19</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="5">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5">
+        <v>0</v>
+      </c>
+      <c r="I31" s="5">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5">
+        <v>0</v>
+      </c>
+      <c r="K31" s="5">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5">
+        <v>2</v>
+      </c>
+      <c r="M31" s="5">
+        <v>0</v>
+      </c>
+      <c r="N31" s="5">
+        <v>0</v>
+      </c>
+      <c r="O31" s="5">
+        <v>0</v>
+      </c>
+      <c r="P31" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R31" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>19</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="5">
+        <v>0</v>
+      </c>
+      <c r="E32" s="5">
+        <v>2</v>
+      </c>
+      <c r="F32" s="5">
+        <v>2</v>
+      </c>
+      <c r="G32" s="5">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5">
+        <v>0</v>
+      </c>
+      <c r="P32" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R32" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>19</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="5">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5">
+        <v>2</v>
+      </c>
+      <c r="F33" s="5">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5">
+        <v>0</v>
+      </c>
+      <c r="I33" s="5">
+        <v>2</v>
+      </c>
+      <c r="J33" s="5">
+        <v>0</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <v>2</v>
+      </c>
+      <c r="M33" s="5">
+        <v>0</v>
+      </c>
+      <c r="N33" s="5">
+        <v>0</v>
+      </c>
+      <c r="O33" s="5">
+        <v>2</v>
+      </c>
+      <c r="P33" s="6">
+        <v>8</v>
+      </c>
+      <c r="Q33" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R33" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>19</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="5">
+        <v>190180</v>
+      </c>
+      <c r="E34" s="5">
+        <v>314212</v>
+      </c>
+      <c r="F34" s="5">
+        <v>297674</v>
+      </c>
+      <c r="G34" s="5">
+        <v>243928</v>
+      </c>
+      <c r="H34" s="5">
+        <v>157106</v>
+      </c>
+      <c r="I34" s="5">
+        <v>297674</v>
+      </c>
+      <c r="J34" s="5">
+        <v>285272</v>
+      </c>
+      <c r="K34" s="5">
+        <v>384496</v>
+      </c>
+      <c r="L34" s="5">
+        <v>318346</v>
+      </c>
+      <c r="M34" s="5">
+        <v>330750</v>
+      </c>
+      <c r="N34" s="5">
+        <v>181912</v>
+      </c>
+      <c r="O34" s="5">
+        <v>198450</v>
+      </c>
+      <c r="P34" s="6">
+        <v>3200000</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R34" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>19</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="5">
+        <v>160466</v>
+      </c>
+      <c r="E35" s="5">
+        <v>265116</v>
+      </c>
+      <c r="F35" s="5">
+        <v>251162</v>
+      </c>
+      <c r="G35" s="5">
+        <v>205814</v>
+      </c>
+      <c r="H35" s="5">
+        <v>132558</v>
+      </c>
+      <c r="I35" s="5">
+        <v>251162</v>
+      </c>
+      <c r="J35" s="5">
+        <v>240698</v>
+      </c>
+      <c r="K35" s="5">
+        <v>324418</v>
+      </c>
+      <c r="L35" s="5">
+        <v>268604</v>
+      </c>
+      <c r="M35" s="5">
+        <v>279070</v>
+      </c>
+      <c r="N35" s="5">
+        <v>153490</v>
+      </c>
+      <c r="O35" s="5">
+        <v>167442</v>
+      </c>
+      <c r="P35" s="6">
+        <v>2700000</v>
+      </c>
+      <c r="Q35" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R35" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>19</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="5">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5">
+        <v>2</v>
+      </c>
+      <c r="F36" s="5">
+        <v>2</v>
+      </c>
+      <c r="G36" s="5">
+        <v>0</v>
+      </c>
+      <c r="H36" s="5">
+        <v>2</v>
+      </c>
+      <c r="I36" s="5">
+        <v>2</v>
+      </c>
+      <c r="J36" s="5">
+        <v>2</v>
+      </c>
+      <c r="K36" s="5">
+        <v>2</v>
+      </c>
+      <c r="L36" s="5">
+        <v>2</v>
+      </c>
+      <c r="M36" s="5">
+        <v>2</v>
+      </c>
+      <c r="N36" s="5">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5">
+        <v>0</v>
+      </c>
+      <c r="P36" s="6">
+        <v>16</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R36" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>19</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="5">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5">
+        <v>0</v>
+      </c>
+      <c r="I37" s="5">
+        <v>0</v>
+      </c>
+      <c r="J37" s="5">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5">
+        <v>0</v>
+      </c>
+      <c r="M37" s="5">
+        <v>0</v>
+      </c>
+      <c r="N37" s="5">
+        <v>0</v>
+      </c>
+      <c r="O37" s="5">
+        <v>0</v>
+      </c>
+      <c r="P37" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R37" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A38" s="9">
+        <v>17</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="9">
+        <v>6</v>
+      </c>
+      <c r="E38" s="9">
+        <v>8</v>
+      </c>
+      <c r="F38" s="9">
+        <v>8</v>
+      </c>
+      <c r="G38" s="9">
+        <v>7</v>
+      </c>
+      <c r="H38" s="9">
+        <v>7</v>
+      </c>
+      <c r="I38" s="9">
+        <v>8</v>
+      </c>
+      <c r="J38" s="9">
+        <v>8</v>
+      </c>
+      <c r="K38" s="9">
+        <v>10</v>
+      </c>
+      <c r="L38" s="9">
+        <v>10</v>
+      </c>
+      <c r="M38" s="9">
+        <v>11</v>
+      </c>
+      <c r="N38" s="9">
+        <v>7</v>
+      </c>
+      <c r="O38" s="9">
+        <v>7</v>
+      </c>
+      <c r="P38" s="10">
+        <v>97</v>
+      </c>
+      <c r="Q38" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R38" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A39" s="9">
+        <v>17</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D39" s="9">
+        <v>0</v>
+      </c>
+      <c r="E39" s="9">
+        <v>1</v>
+      </c>
+      <c r="F39" s="9">
+        <v>2</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0</v>
+      </c>
+      <c r="H39" s="9">
+        <v>2</v>
+      </c>
+      <c r="I39" s="9">
+        <v>0</v>
+      </c>
+      <c r="J39" s="9">
+        <v>0</v>
+      </c>
+      <c r="K39" s="9">
+        <v>4</v>
+      </c>
+      <c r="L39" s="9">
+        <v>0</v>
+      </c>
+      <c r="M39" s="9">
+        <v>0</v>
+      </c>
+      <c r="N39" s="9">
+        <v>1</v>
+      </c>
+      <c r="O39" s="9">
+        <v>0</v>
+      </c>
+      <c r="P39" s="10">
+        <v>9</v>
+      </c>
+      <c r="Q39" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R39" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A40" s="9">
+        <v>17</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="9">
+        <v>2</v>
+      </c>
+      <c r="E40" s="9">
+        <v>6</v>
+      </c>
+      <c r="F40" s="9">
+        <v>1</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
+      <c r="H40" s="9">
+        <v>0</v>
+      </c>
+      <c r="I40" s="9">
+        <v>2</v>
+      </c>
+      <c r="J40" s="9">
+        <v>0</v>
+      </c>
+      <c r="K40" s="9">
+        <v>3</v>
+      </c>
+      <c r="L40" s="9">
+        <v>4</v>
+      </c>
+      <c r="M40" s="9">
+        <v>4</v>
+      </c>
+      <c r="N40" s="9">
+        <v>2</v>
+      </c>
+      <c r="O40" s="9">
+        <v>2</v>
+      </c>
+      <c r="P40" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q40" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R40" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A41" s="9">
+        <v>17</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" s="9">
+        <v>0</v>
+      </c>
+      <c r="E41" s="9">
+        <v>2</v>
+      </c>
+      <c r="F41" s="9">
+        <v>0</v>
+      </c>
+      <c r="G41" s="9">
+        <v>0</v>
+      </c>
+      <c r="H41" s="9">
+        <v>0</v>
+      </c>
+      <c r="I41" s="9">
+        <v>0</v>
+      </c>
+      <c r="J41" s="9">
+        <v>0</v>
+      </c>
+      <c r="K41" s="9">
+        <v>3</v>
+      </c>
+      <c r="L41" s="9">
+        <v>1</v>
+      </c>
+      <c r="M41" s="9">
+        <v>5</v>
+      </c>
+      <c r="N41" s="9">
+        <v>0</v>
+      </c>
+      <c r="O41" s="9">
+        <v>0</v>
+      </c>
+      <c r="P41" s="10">
+        <v>11</v>
+      </c>
+      <c r="Q41" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R41" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A42" s="9">
+        <v>17</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" s="9">
+        <v>2</v>
+      </c>
+      <c r="E42" s="9">
+        <v>5</v>
+      </c>
+      <c r="F42" s="9">
+        <v>2</v>
+      </c>
+      <c r="G42" s="9">
+        <v>0</v>
+      </c>
+      <c r="H42" s="9">
+        <v>0</v>
+      </c>
+      <c r="I42" s="9">
+        <v>2</v>
+      </c>
+      <c r="J42" s="9">
+        <v>0</v>
+      </c>
+      <c r="K42" s="9">
+        <v>3</v>
+      </c>
+      <c r="L42" s="9">
+        <v>4</v>
+      </c>
+      <c r="M42" s="9">
+        <v>5</v>
+      </c>
+      <c r="N42" s="9">
+        <v>2</v>
+      </c>
+      <c r="O42" s="9">
+        <v>2</v>
+      </c>
+      <c r="P42" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q42" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R42" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A43" s="9">
+        <v>17</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="9">
+        <v>0</v>
+      </c>
+      <c r="E43" s="9">
+        <v>6</v>
+      </c>
+      <c r="F43" s="9">
+        <v>1</v>
+      </c>
+      <c r="G43" s="9">
+        <v>0</v>
+      </c>
+      <c r="H43" s="9">
+        <v>4</v>
+      </c>
+      <c r="I43" s="9">
+        <v>0</v>
+      </c>
+      <c r="J43" s="9">
+        <v>4</v>
+      </c>
+      <c r="K43" s="9">
+        <v>5</v>
+      </c>
+      <c r="L43" s="9">
+        <v>0</v>
+      </c>
+      <c r="M43" s="9">
+        <v>0</v>
+      </c>
+      <c r="N43" s="9">
+        <v>1</v>
+      </c>
+      <c r="O43" s="9">
+        <v>0</v>
+      </c>
+      <c r="P43" s="10">
+        <v>24</v>
+      </c>
+      <c r="Q43" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R43" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A44" s="9">
+        <v>17</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="9">
+        <v>891473</v>
+      </c>
+      <c r="E44" s="9">
+        <v>1472867</v>
+      </c>
+      <c r="F44" s="9">
+        <v>1395350</v>
+      </c>
+      <c r="G44" s="9">
+        <v>838501</v>
+      </c>
+      <c r="H44" s="9">
+        <v>740051</v>
+      </c>
+      <c r="I44" s="9">
+        <v>1023256</v>
+      </c>
+      <c r="J44" s="9">
+        <v>1380620</v>
+      </c>
+      <c r="K44" s="9">
+        <v>1321706</v>
+      </c>
+      <c r="L44" s="9">
+        <v>1294315</v>
+      </c>
+      <c r="M44" s="9">
+        <v>1136951</v>
+      </c>
+      <c r="N44" s="9">
+        <v>1125323</v>
+      </c>
+      <c r="O44" s="9">
+        <v>882171</v>
+      </c>
+      <c r="P44" s="10">
+        <v>15000000</v>
+      </c>
+      <c r="Q44" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R44" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A45" s="9">
+        <v>17</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="9">
+        <v>576486</v>
+      </c>
+      <c r="E45" s="9">
+        <v>952455</v>
+      </c>
+      <c r="F45" s="9">
+        <v>902326</v>
+      </c>
+      <c r="G45" s="9">
+        <v>656952</v>
+      </c>
+      <c r="H45" s="9">
+        <v>448036</v>
+      </c>
+      <c r="I45" s="9">
+        <v>806280</v>
+      </c>
+      <c r="J45" s="9">
+        <v>776434</v>
+      </c>
+      <c r="K45" s="9">
+        <v>1045195</v>
+      </c>
+      <c r="L45" s="9">
+        <v>866021</v>
+      </c>
+      <c r="M45" s="9">
+        <v>915865</v>
+      </c>
+      <c r="N45" s="9">
+        <v>507726</v>
+      </c>
+      <c r="O45" s="9">
+        <v>547520</v>
+      </c>
+      <c r="P45" s="10">
+        <v>9700004</v>
+      </c>
+      <c r="Q45" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R45" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A46" s="9">
+        <v>17</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" s="9">
+        <v>0</v>
+      </c>
+      <c r="E46" s="9">
+        <v>6</v>
+      </c>
+      <c r="F46" s="9">
+        <v>0</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0</v>
+      </c>
+      <c r="H46" s="9">
+        <v>5</v>
+      </c>
+      <c r="I46" s="9">
+        <v>4</v>
+      </c>
+      <c r="J46" s="9">
+        <v>5</v>
+      </c>
+      <c r="K46" s="9">
+        <v>0</v>
+      </c>
+      <c r="L46" s="9">
+        <v>3</v>
+      </c>
+      <c r="M46" s="9">
+        <v>2</v>
+      </c>
+      <c r="N46" s="9">
+        <v>0</v>
+      </c>
+      <c r="O46" s="9">
+        <v>0</v>
+      </c>
+      <c r="P46" s="10">
+        <v>28</v>
+      </c>
+      <c r="Q46" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R46" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A47" s="9">
+        <v>17</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" s="9">
+        <v>6</v>
+      </c>
+      <c r="E47" s="9">
+        <v>6</v>
+      </c>
+      <c r="F47" s="9">
+        <v>6</v>
+      </c>
+      <c r="G47" s="9">
+        <v>5</v>
+      </c>
+      <c r="H47" s="9">
+        <v>5</v>
+      </c>
+      <c r="I47" s="9">
+        <v>5</v>
+      </c>
+      <c r="J47" s="9">
+        <v>5</v>
+      </c>
+      <c r="K47" s="9">
+        <v>5</v>
+      </c>
+      <c r="L47" s="9">
+        <v>5</v>
+      </c>
+      <c r="M47" s="9">
+        <v>5</v>
+      </c>
+      <c r="N47" s="9">
+        <v>5</v>
+      </c>
+      <c r="O47" s="9">
+        <v>5</v>
+      </c>
+      <c r="P47" s="10">
+        <v>72</v>
+      </c>
+      <c r="Q47" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R47" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>30</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" s="5">
+        <v>1</v>
+      </c>
+      <c r="E48" s="5">
+        <v>1</v>
+      </c>
+      <c r="F48" s="5">
+        <v>1</v>
+      </c>
+      <c r="G48" s="5">
+        <v>1</v>
+      </c>
+      <c r="H48" s="5">
+        <v>1</v>
+      </c>
+      <c r="I48" s="5">
+        <v>1</v>
+      </c>
+      <c r="J48" s="5">
+        <v>1</v>
+      </c>
+      <c r="K48" s="5">
+        <v>1</v>
+      </c>
+      <c r="L48" s="5">
+        <v>1</v>
+      </c>
+      <c r="M48" s="5">
+        <v>1</v>
+      </c>
+      <c r="N48" s="5">
+        <v>1</v>
+      </c>
+      <c r="O48" s="5">
+        <v>1</v>
+      </c>
+      <c r="P48" s="6">
+        <v>12</v>
+      </c>
+      <c r="Q48" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R48" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>30</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" s="7">
+        <v>0</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0</v>
+      </c>
+      <c r="F49" s="7">
+        <v>0</v>
+      </c>
+      <c r="G49" s="7">
+        <v>0</v>
+      </c>
+      <c r="H49" s="7">
+        <v>0</v>
+      </c>
+      <c r="I49" s="7">
+        <v>0</v>
+      </c>
+      <c r="J49" s="7">
+        <v>0</v>
+      </c>
+      <c r="K49" s="7">
+        <v>0</v>
+      </c>
+      <c r="L49" s="7">
+        <v>0</v>
+      </c>
+      <c r="M49" s="7">
+        <v>1</v>
+      </c>
+      <c r="N49" s="7">
+        <v>0</v>
+      </c>
+      <c r="O49" s="7">
+        <v>0</v>
+      </c>
+      <c r="P49" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R49" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <v>30</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="5">
+        <v>0</v>
+      </c>
+      <c r="E50" s="5">
+        <v>1</v>
+      </c>
+      <c r="F50" s="5">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5">
+        <v>0</v>
+      </c>
+      <c r="H50" s="5">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5">
+        <v>0</v>
+      </c>
+      <c r="M50" s="5">
+        <v>0</v>
+      </c>
+      <c r="N50" s="5">
+        <v>0</v>
+      </c>
+      <c r="O50" s="5">
+        <v>0</v>
+      </c>
+      <c r="P50" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R50" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>30</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" s="5">
+        <v>0</v>
+      </c>
+      <c r="E51" s="5">
+        <v>0</v>
+      </c>
+      <c r="F51" s="5">
+        <v>0</v>
+      </c>
+      <c r="G51" s="5">
+        <v>0</v>
+      </c>
+      <c r="H51" s="5">
+        <v>0</v>
+      </c>
+      <c r="I51" s="5">
+        <v>0</v>
+      </c>
+      <c r="J51" s="5">
+        <v>0</v>
+      </c>
+      <c r="K51" s="5">
+        <v>0</v>
+      </c>
+      <c r="L51" s="5">
+        <v>1</v>
+      </c>
+      <c r="M51" s="5">
+        <v>0</v>
+      </c>
+      <c r="N51" s="5">
+        <v>0</v>
+      </c>
+      <c r="O51" s="5">
+        <v>0</v>
+      </c>
+      <c r="P51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R51" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <v>30</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52" s="5">
+        <v>0</v>
+      </c>
+      <c r="E52" s="5">
+        <v>1</v>
+      </c>
+      <c r="F52" s="5">
+        <v>1</v>
+      </c>
+      <c r="G52" s="5">
+        <v>0</v>
+      </c>
+      <c r="H52" s="5">
+        <v>0</v>
+      </c>
+      <c r="I52" s="5">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5">
+        <v>0</v>
+      </c>
+      <c r="M52" s="5">
+        <v>0</v>
+      </c>
+      <c r="N52" s="5">
+        <v>0</v>
+      </c>
+      <c r="O52" s="5">
+        <v>0</v>
+      </c>
+      <c r="P52" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q52" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R52" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <v>30</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" s="7">
+        <v>0</v>
+      </c>
+      <c r="E53" s="7">
+        <v>1</v>
+      </c>
+      <c r="F53" s="7">
+        <v>0</v>
+      </c>
+      <c r="G53" s="7">
+        <v>0</v>
+      </c>
+      <c r="H53" s="7">
+        <v>0</v>
+      </c>
+      <c r="I53" s="7">
+        <v>1</v>
+      </c>
+      <c r="J53" s="7">
+        <v>0</v>
+      </c>
+      <c r="K53" s="7">
+        <v>0</v>
+      </c>
+      <c r="L53" s="7">
+        <v>1</v>
+      </c>
+      <c r="M53" s="7">
+        <v>0</v>
+      </c>
+      <c r="N53" s="7">
+        <v>0</v>
+      </c>
+      <c r="O53" s="7">
+        <v>1</v>
+      </c>
+      <c r="P53" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q53" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R53" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
+        <v>30</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" s="5">
+        <v>95090</v>
+      </c>
+      <c r="E54" s="5">
+        <v>157106</v>
+      </c>
+      <c r="F54" s="5">
+        <v>148837</v>
+      </c>
+      <c r="G54" s="5">
+        <v>121964</v>
+      </c>
+      <c r="H54" s="5">
+        <v>78553</v>
+      </c>
+      <c r="I54" s="5">
+        <v>148837</v>
+      </c>
+      <c r="J54" s="5">
+        <v>142636</v>
+      </c>
+      <c r="K54" s="5">
+        <v>192248</v>
+      </c>
+      <c r="L54" s="5">
+        <v>159173</v>
+      </c>
+      <c r="M54" s="5">
+        <v>165375</v>
+      </c>
+      <c r="N54" s="5">
+        <v>90956</v>
+      </c>
+      <c r="O54" s="5">
+        <v>99225</v>
+      </c>
+      <c r="P54" s="6">
+        <v>1600000</v>
+      </c>
+      <c r="Q54" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R54" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
+        <v>30</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" s="5">
+        <v>80233</v>
+      </c>
+      <c r="E55" s="5">
+        <v>132558</v>
+      </c>
+      <c r="F55" s="5">
+        <v>125581</v>
+      </c>
+      <c r="G55" s="5">
+        <v>102907</v>
+      </c>
+      <c r="H55" s="5">
+        <v>66279</v>
+      </c>
+      <c r="I55" s="5">
+        <v>125581</v>
+      </c>
+      <c r="J55" s="5">
+        <v>120349</v>
+      </c>
+      <c r="K55" s="5">
+        <v>162209</v>
+      </c>
+      <c r="L55" s="5">
+        <v>134302</v>
+      </c>
+      <c r="M55" s="5">
+        <v>139535</v>
+      </c>
+      <c r="N55" s="5">
+        <v>76745</v>
+      </c>
+      <c r="O55" s="5">
+        <v>83721</v>
+      </c>
+      <c r="P55" s="6">
+        <v>1350000</v>
+      </c>
+      <c r="Q55" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R55" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
+        <v>30</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" s="5">
+        <v>0</v>
+      </c>
+      <c r="E56" s="5">
+        <v>1</v>
+      </c>
+      <c r="F56" s="5">
+        <v>1</v>
+      </c>
+      <c r="G56" s="5">
+        <v>0</v>
+      </c>
+      <c r="H56" s="5">
+        <v>1</v>
+      </c>
+      <c r="I56" s="5">
+        <v>1</v>
+      </c>
+      <c r="J56" s="5">
+        <v>1</v>
+      </c>
+      <c r="K56" s="5">
+        <v>1</v>
+      </c>
+      <c r="L56" s="5">
+        <v>1</v>
+      </c>
+      <c r="M56" s="5">
+        <v>1</v>
+      </c>
+      <c r="N56" s="5">
+        <v>0</v>
+      </c>
+      <c r="O56" s="5">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6">
+        <v>8</v>
+      </c>
+      <c r="Q56" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R56" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A57" s="5">
+        <v>30</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" s="5">
+        <v>0</v>
+      </c>
+      <c r="E57" s="5">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5">
+        <v>0</v>
+      </c>
+      <c r="G57" s="5">
+        <v>0</v>
+      </c>
+      <c r="H57" s="5">
+        <v>0</v>
+      </c>
+      <c r="I57" s="5">
+        <v>0</v>
+      </c>
+      <c r="J57" s="5">
+        <v>0</v>
+      </c>
+      <c r="K57" s="5">
+        <v>0</v>
+      </c>
+      <c r="L57" s="5">
+        <v>0</v>
+      </c>
+      <c r="M57" s="5">
+        <v>0</v>
+      </c>
+      <c r="N57" s="5">
+        <v>0</v>
+      </c>
+      <c r="O57" s="5">
+        <v>0</v>
+      </c>
+      <c r="P57" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R57" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" s="5">
+        <v>11</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" s="5">
+        <v>5</v>
+      </c>
+      <c r="E58" s="5">
+        <v>8</v>
+      </c>
+      <c r="F58" s="5">
+        <v>4</v>
+      </c>
+      <c r="G58" s="5">
+        <v>4</v>
+      </c>
+      <c r="H58" s="5">
+        <v>2</v>
+      </c>
+      <c r="I58" s="5">
+        <v>5</v>
+      </c>
+      <c r="J58" s="5">
+        <v>6</v>
+      </c>
+      <c r="K58" s="5">
+        <v>6</v>
+      </c>
+      <c r="L58" s="5">
+        <v>3</v>
+      </c>
+      <c r="M58" s="5">
+        <v>5</v>
+      </c>
+      <c r="N58" s="5">
+        <v>4</v>
+      </c>
+      <c r="O58" s="5">
+        <v>3</v>
+      </c>
+      <c r="P58" s="6">
+        <v>55</v>
+      </c>
+      <c r="Q58" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="R58" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>11</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" s="5">
+        <v>355555</v>
+      </c>
+      <c r="E59" s="5">
+        <v>445871</v>
+      </c>
+      <c r="F59" s="5">
+        <v>282828</v>
+      </c>
+      <c r="G59" s="5">
+        <v>265954</v>
+      </c>
+      <c r="H59" s="5">
+        <v>391919</v>
+      </c>
+      <c r="I59" s="5">
+        <v>249079</v>
+      </c>
+      <c r="J59" s="5">
+        <v>390968</v>
+      </c>
+      <c r="K59" s="5">
+        <v>515983</v>
+      </c>
+      <c r="L59" s="5">
+        <v>374094</v>
+      </c>
+      <c r="M59" s="5">
+        <v>285443</v>
+      </c>
+      <c r="N59" s="5">
+        <v>265004</v>
+      </c>
+      <c r="O59" s="5">
+        <v>177302</v>
+      </c>
+      <c r="P59" s="6">
+        <v>4000000</v>
+      </c>
+      <c r="Q59" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="R59" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>11</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" s="5">
+        <v>0</v>
+      </c>
+      <c r="E60" s="5">
+        <v>2</v>
+      </c>
+      <c r="F60" s="5">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5">
+        <v>2</v>
+      </c>
+      <c r="H60" s="5">
+        <v>0</v>
+      </c>
+      <c r="I60" s="5">
+        <v>2</v>
+      </c>
+      <c r="J60" s="5">
+        <v>0</v>
+      </c>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5">
+        <v>0</v>
+      </c>
+      <c r="M60" s="5">
+        <v>2</v>
+      </c>
+      <c r="N60" s="5">
+        <v>0</v>
+      </c>
+      <c r="O60" s="5">
+        <v>2</v>
+      </c>
+      <c r="P60" s="6">
+        <v>10</v>
+      </c>
+      <c r="Q60" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="R60" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="6"/>
+      <c r="Q61" s="5"/>
+      <c r="R61" s="5"/>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="5"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="6"/>
+      <c r="Q62" s="5"/>
+      <c r="R62" s="5"/>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A63" s="5"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="6"/>
+      <c r="Q63" s="5"/>
+      <c r="R63" s="5"/>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="5"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="6"/>
+      <c r="Q64" s="5"/>
+      <c r="R64" s="5"/>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A65" s="5"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="5"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="6"/>
+      <c r="Q65" s="5"/>
+      <c r="R65" s="5"/>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A66" s="5"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="6"/>
+      <c r="Q66" s="5"/>
+      <c r="R66" s="5"/>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A67" s="5"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="7"/>
+      <c r="J67" s="7"/>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
+      <c r="M67" s="7"/>
+      <c r="N67" s="7"/>
+      <c r="O67" s="7"/>
+      <c r="P67" s="6"/>
+      <c r="Q67" s="5"/>
+      <c r="R67" s="5"/>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A68" s="5"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="6"/>
+      <c r="Q68" s="5"/>
+      <c r="R68" s="5"/>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A69" s="5"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="6"/>
+      <c r="Q69" s="5"/>
+      <c r="R69" s="5"/>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A70" s="5"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="6"/>
+      <c r="Q70" s="5"/>
+      <c r="R70" s="5"/>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A71" s="5"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="5"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="6"/>
+      <c r="Q71" s="5"/>
+      <c r="R71" s="5"/>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A72" s="5"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="6"/>
+      <c r="Q72" s="5"/>
+      <c r="R72" s="5"/>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A73" s="5"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="6"/>
+      <c r="Q73" s="5"/>
+      <c r="R73" s="5"/>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="6"/>
+      <c r="Q74" s="5"/>
+      <c r="R74" s="5"/>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="5"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="6"/>
+      <c r="Q75" s="5"/>
+      <c r="R75" s="5"/>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A76" s="5"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="5"/>
+      <c r="L76" s="5"/>
+      <c r="M76" s="5"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="6"/>
+      <c r="Q76" s="5"/>
+      <c r="R76" s="5"/>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="5"/>
+      <c r="L77" s="5"/>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="6"/>
+      <c r="Q77" s="5"/>
+      <c r="R77" s="5"/>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A78" s="5"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="5"/>
+      <c r="M78" s="5"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="6"/>
+      <c r="Q78" s="5"/>
+      <c r="R78" s="5"/>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A79" s="5"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="5"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="6"/>
+      <c r="Q79" s="5"/>
+      <c r="R79" s="5"/>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A80" s="5"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="5"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="6"/>
+      <c r="Q80" s="5"/>
+      <c r="R80" s="5"/>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A81" s="5"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5"/>
+      <c r="K81" s="5"/>
+      <c r="L81" s="5"/>
+      <c r="M81" s="5"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="6"/>
+      <c r="Q81" s="5"/>
+      <c r="R81" s="5"/>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A82" s="5"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
+      <c r="L82" s="5"/>
+      <c r="M82" s="5"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="6"/>
+      <c r="Q82" s="5"/>
+      <c r="R82" s="5"/>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A83" s="5"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="5"/>
+      <c r="F83" s="5"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="5"/>
+      <c r="K83" s="5"/>
+      <c r="L83" s="5"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="6"/>
+      <c r="Q83" s="5"/>
+      <c r="R83" s="5"/>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A84" s="5"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="5"/>
+      <c r="K84" s="5"/>
+      <c r="L84" s="5"/>
+      <c r="M84" s="5"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="6"/>
+      <c r="Q84" s="5"/>
+      <c r="R84" s="5"/>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A85" s="5"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="5"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="5"/>
+      <c r="J85" s="5"/>
+      <c r="K85" s="5"/>
+      <c r="L85" s="5"/>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="5"/>
+      <c r="P85" s="6"/>
+      <c r="Q85" s="5"/>
+      <c r="R85" s="5"/>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A86" s="5"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="5"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="5"/>
+      <c r="L86" s="5"/>
+      <c r="M86" s="5"/>
+      <c r="N86" s="5"/>
+      <c r="O86" s="5"/>
+      <c r="P86" s="6"/>
+      <c r="Q86" s="5"/>
+      <c r="R86" s="5"/>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A87" s="5"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="5"/>
+      <c r="K87" s="5"/>
+      <c r="L87" s="5"/>
+      <c r="M87" s="5"/>
+      <c r="N87" s="5"/>
+      <c r="O87" s="5"/>
+      <c r="P87" s="6"/>
+      <c r="Q87" s="5"/>
+      <c r="R87" s="5"/>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A88" s="5"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5"/>
+      <c r="L88" s="5"/>
+      <c r="M88" s="5"/>
+      <c r="N88" s="5"/>
+      <c r="O88" s="5"/>
+      <c r="P88" s="6"/>
+      <c r="Q88" s="5"/>
+      <c r="R88" s="5"/>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A89" s="5"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="5"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="5"/>
+      <c r="K89" s="5"/>
+      <c r="L89" s="5"/>
+      <c r="M89" s="5"/>
+      <c r="N89" s="5"/>
+      <c r="O89" s="5"/>
+      <c r="P89" s="6"/>
+      <c r="Q89" s="5"/>
+      <c r="R89" s="5"/>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A90" s="5"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="5"/>
+      <c r="L90" s="5"/>
+      <c r="M90" s="5"/>
+      <c r="N90" s="5"/>
+      <c r="O90" s="5"/>
+      <c r="P90" s="6"/>
+      <c r="Q90" s="5"/>
+      <c r="R90" s="5"/>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A91" s="5"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="5"/>
+      <c r="K91" s="5"/>
+      <c r="L91" s="5"/>
+      <c r="M91" s="5"/>
+      <c r="N91" s="5"/>
+      <c r="O91" s="5"/>
+      <c r="P91" s="6"/>
+      <c r="Q91" s="5"/>
+      <c r="R91" s="5"/>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A92" s="5"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5"/>
+      <c r="L92" s="5"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="5"/>
+      <c r="O92" s="5"/>
+      <c r="P92" s="6"/>
+      <c r="Q92" s="5"/>
+      <c r="R92" s="5"/>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A93" s="5"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5"/>
+      <c r="K93" s="5"/>
+      <c r="L93" s="5"/>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="5"/>
+      <c r="P93" s="6"/>
+      <c r="Q93" s="5"/>
+      <c r="R93" s="5"/>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A94" s="5"/>
+      <c r="B94" s="5"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+      <c r="K94" s="5"/>
+      <c r="L94" s="5"/>
+      <c r="M94" s="5"/>
+      <c r="N94" s="5"/>
+      <c r="O94" s="5"/>
+      <c r="P94" s="6"/>
+      <c r="Q94" s="5"/>
+      <c r="R94" s="5"/>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A95" s="5"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="5"/>
+      <c r="K95" s="5"/>
+      <c r="L95" s="5"/>
+      <c r="M95" s="5"/>
+      <c r="N95" s="5"/>
+      <c r="O95" s="5"/>
+      <c r="P95" s="6"/>
+      <c r="Q95" s="5"/>
+      <c r="R95" s="5"/>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A96" s="5"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5"/>
+      <c r="K96" s="5"/>
+      <c r="L96" s="5"/>
+      <c r="M96" s="5"/>
+      <c r="N96" s="5"/>
+      <c r="O96" s="5"/>
+      <c r="P96" s="6"/>
+      <c r="Q96" s="5"/>
+      <c r="R96" s="5"/>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A97" s="5"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="5"/>
+      <c r="K97" s="5"/>
+      <c r="L97" s="5"/>
+      <c r="M97" s="5"/>
+      <c r="N97" s="5"/>
+      <c r="O97" s="5"/>
+      <c r="P97" s="6"/>
+      <c r="Q97" s="5"/>
+      <c r="R97" s="5"/>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A98" s="5"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="5"/>
+      <c r="L98" s="5"/>
+      <c r="M98" s="5"/>
+      <c r="N98" s="5"/>
+      <c r="O98" s="5"/>
+      <c r="P98" s="6"/>
+      <c r="Q98" s="5"/>
+      <c r="R98" s="5"/>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A99" s="5"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="5"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="5"/>
+      <c r="K99" s="5"/>
+      <c r="L99" s="5"/>
+      <c r="M99" s="5"/>
+      <c r="N99" s="5"/>
+      <c r="O99" s="5"/>
+      <c r="P99" s="6"/>
+      <c r="Q99" s="5"/>
+      <c r="R99" s="5"/>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A100" s="5"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="5"/>
+      <c r="K100" s="5"/>
+      <c r="L100" s="5"/>
+      <c r="M100" s="5"/>
+      <c r="N100" s="5"/>
+      <c r="O100" s="5"/>
+      <c r="P100" s="6"/>
+      <c r="Q100" s="5"/>
+      <c r="R100" s="5"/>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A101" s="5"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="5"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="5"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5"/>
+      <c r="I101" s="5"/>
+      <c r="J101" s="5"/>
+      <c r="K101" s="5"/>
+      <c r="L101" s="5"/>
+      <c r="M101" s="5"/>
+      <c r="N101" s="5"/>
+      <c r="O101" s="5"/>
+      <c r="P101" s="6"/>
+      <c r="Q101" s="5"/>
+      <c r="R101" s="5"/>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A102" s="5"/>
+      <c r="B102" s="5"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="5"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
+      <c r="I102" s="5"/>
+      <c r="J102" s="5"/>
+      <c r="K102" s="5"/>
+      <c r="L102" s="5"/>
+      <c r="M102" s="5"/>
+      <c r="N102" s="5"/>
+      <c r="O102" s="5"/>
+      <c r="P102" s="6"/>
+      <c r="Q102" s="5"/>
+      <c r="R102" s="5"/>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A103" s="5"/>
+      <c r="B103" s="5"/>
+      <c r="C103" s="5"/>
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
+      <c r="I103" s="5"/>
+      <c r="J103" s="5"/>
+      <c r="K103" s="5"/>
+      <c r="L103" s="5"/>
+      <c r="M103" s="5"/>
+      <c r="N103" s="5"/>
+      <c r="O103" s="5"/>
+      <c r="P103" s="6"/>
+      <c r="Q103" s="5"/>
+      <c r="R103" s="5"/>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A104" s="5"/>
+      <c r="B104" s="5"/>
+      <c r="C104" s="5"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="5"/>
+      <c r="L104" s="5"/>
+      <c r="M104" s="5"/>
+      <c r="N104" s="5"/>
+      <c r="O104" s="5"/>
+      <c r="P104" s="6"/>
+      <c r="Q104" s="5"/>
+      <c r="R104" s="5"/>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A105" s="5"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5"/>
+      <c r="I105" s="5"/>
+      <c r="J105" s="5"/>
+      <c r="K105" s="5"/>
+      <c r="L105" s="5"/>
+      <c r="M105" s="5"/>
+      <c r="N105" s="5"/>
+      <c r="O105" s="5"/>
+      <c r="P105" s="6"/>
+      <c r="Q105" s="5"/>
+      <c r="R105" s="5"/>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A106" s="5"/>
+      <c r="B106" s="5"/>
+      <c r="C106" s="5"/>
+      <c r="D106" s="5"/>
+      <c r="E106" s="5"/>
+      <c r="F106" s="5"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5"/>
+      <c r="I106" s="5"/>
+      <c r="J106" s="5"/>
+      <c r="K106" s="5"/>
+      <c r="L106" s="5"/>
+      <c r="M106" s="5"/>
+      <c r="N106" s="5"/>
+      <c r="O106" s="5"/>
+      <c r="P106" s="6"/>
+      <c r="Q106" s="5"/>
+      <c r="R106" s="5"/>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A107" s="5"/>
+      <c r="B107" s="5"/>
+      <c r="C107" s="5"/>
+      <c r="D107" s="5"/>
+      <c r="E107" s="5"/>
+      <c r="F107" s="5"/>
+      <c r="G107" s="5"/>
+      <c r="H107" s="5"/>
+      <c r="I107" s="5"/>
+      <c r="J107" s="5"/>
+      <c r="K107" s="5"/>
+      <c r="L107" s="5"/>
+      <c r="M107" s="5"/>
+      <c r="N107" s="5"/>
+      <c r="O107" s="5"/>
+      <c r="P107" s="6"/>
+      <c r="Q107" s="5"/>
+      <c r="R107" s="5"/>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A108" s="5"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="5"/>
+      <c r="E108" s="5"/>
+      <c r="F108" s="5"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="5"/>
+      <c r="I108" s="5"/>
+      <c r="J108" s="5"/>
+      <c r="K108" s="5"/>
+      <c r="L108" s="5"/>
+      <c r="M108" s="5"/>
+      <c r="N108" s="5"/>
+      <c r="O108" s="5"/>
+      <c r="P108" s="6"/>
+      <c r="Q108" s="5"/>
+      <c r="R108" s="5"/>
+    </row>
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A109" s="5"/>
+      <c r="B109" s="5"/>
+      <c r="C109" s="5"/>
+      <c r="D109" s="5"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="5"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="5"/>
+      <c r="I109" s="5"/>
+      <c r="J109" s="5"/>
+      <c r="K109" s="5"/>
+      <c r="L109" s="5"/>
+      <c r="M109" s="5"/>
+      <c r="N109" s="5"/>
+      <c r="O109" s="5"/>
+      <c r="P109" s="6"/>
+      <c r="Q109" s="5"/>
+      <c r="R109" s="5"/>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A110" s="5"/>
+      <c r="B110" s="5"/>
+      <c r="C110" s="5"/>
+      <c r="D110" s="5"/>
+      <c r="E110" s="5"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="5"/>
+      <c r="H110" s="5"/>
+      <c r="I110" s="5"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5"/>
+      <c r="L110" s="5"/>
+      <c r="M110" s="5"/>
+      <c r="N110" s="5"/>
+      <c r="O110" s="5"/>
+      <c r="P110" s="6"/>
+      <c r="Q110" s="5"/>
+      <c r="R110" s="5"/>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A111" s="5"/>
+      <c r="B111" s="5"/>
+      <c r="C111" s="5"/>
+      <c r="D111" s="5"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="5"/>
+      <c r="H111" s="5"/>
+      <c r="I111" s="5"/>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
+      <c r="L111" s="5"/>
+      <c r="M111" s="5"/>
+      <c r="N111" s="5"/>
+      <c r="O111" s="5"/>
+      <c r="P111" s="6"/>
+      <c r="Q111" s="5"/>
+      <c r="R111" s="5"/>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A112" s="5"/>
+      <c r="B112" s="5"/>
+      <c r="C112" s="5"/>
+      <c r="D112" s="5"/>
+      <c r="E112" s="5"/>
+      <c r="F112" s="5"/>
+      <c r="G112" s="5"/>
+      <c r="H112" s="5"/>
+      <c r="I112" s="5"/>
+      <c r="J112" s="5"/>
+      <c r="K112" s="5"/>
+      <c r="L112" s="5"/>
+      <c r="M112" s="5"/>
+      <c r="N112" s="5"/>
+      <c r="O112" s="5"/>
+      <c r="P112" s="6"/>
+      <c r="Q112" s="5"/>
+      <c r="R112" s="5"/>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A113" s="5"/>
+      <c r="B113" s="5"/>
+      <c r="C113" s="5"/>
+      <c r="D113" s="5"/>
+      <c r="E113" s="5"/>
+      <c r="F113" s="5"/>
+      <c r="G113" s="5"/>
+      <c r="H113" s="5"/>
+      <c r="I113" s="5"/>
+      <c r="J113" s="5"/>
+      <c r="K113" s="5"/>
+      <c r="L113" s="5"/>
+      <c r="M113" s="5"/>
+      <c r="N113" s="5"/>
+      <c r="O113" s="5"/>
+      <c r="P113" s="6"/>
+      <c r="Q113" s="5"/>
+      <c r="R113" s="5"/>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A114" s="5"/>
+      <c r="B114" s="5"/>
+      <c r="C114" s="5"/>
+      <c r="D114" s="5"/>
+      <c r="E114" s="5"/>
+      <c r="F114" s="5"/>
+      <c r="G114" s="5"/>
+      <c r="H114" s="5"/>
+      <c r="I114" s="5"/>
+      <c r="J114" s="5"/>
+      <c r="K114" s="5"/>
+      <c r="L114" s="5"/>
+      <c r="M114" s="5"/>
+      <c r="N114" s="5"/>
+      <c r="O114" s="5"/>
+      <c r="P114" s="6"/>
+      <c r="Q114" s="5"/>
+      <c r="R114" s="5"/>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A115" s="5"/>
+      <c r="B115" s="5"/>
+      <c r="C115" s="5"/>
+      <c r="D115" s="5"/>
+      <c r="E115" s="5"/>
+      <c r="F115" s="5"/>
+      <c r="G115" s="5"/>
+      <c r="H115" s="5"/>
+      <c r="I115" s="5"/>
+      <c r="J115" s="5"/>
+      <c r="K115" s="5"/>
+      <c r="L115" s="5"/>
+      <c r="M115" s="5"/>
+      <c r="N115" s="5"/>
+      <c r="O115" s="5"/>
+      <c r="P115" s="6"/>
+      <c r="Q115" s="5"/>
+      <c r="R115" s="5"/>
+    </row>
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A116" s="5"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="5"/>
+      <c r="D116" s="5"/>
+      <c r="E116" s="5"/>
+      <c r="F116" s="5"/>
+      <c r="G116" s="5"/>
+      <c r="H116" s="5"/>
+      <c r="I116" s="5"/>
+      <c r="J116" s="5"/>
+      <c r="K116" s="5"/>
+      <c r="L116" s="5"/>
+      <c r="M116" s="5"/>
+      <c r="N116" s="5"/>
+      <c r="O116" s="5"/>
+      <c r="P116" s="6"/>
+      <c r="Q116" s="5"/>
+      <c r="R116" s="5"/>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A117" s="5"/>
+      <c r="B117" s="5"/>
+      <c r="C117" s="5"/>
+      <c r="D117" s="5"/>
+      <c r="E117" s="5"/>
+      <c r="F117" s="5"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="5"/>
+      <c r="I117" s="5"/>
+      <c r="J117" s="5"/>
+      <c r="K117" s="5"/>
+      <c r="L117" s="5"/>
+      <c r="M117" s="5"/>
+      <c r="N117" s="5"/>
+      <c r="O117" s="5"/>
+      <c r="P117" s="6"/>
+      <c r="Q117" s="5"/>
+      <c r="R117" s="5"/>
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A118" s="5"/>
+      <c r="B118" s="5"/>
+      <c r="C118" s="5"/>
+      <c r="D118" s="5"/>
+      <c r="E118" s="5"/>
+      <c r="F118" s="5"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="5"/>
+      <c r="I118" s="5"/>
+      <c r="J118" s="5"/>
+      <c r="K118" s="5"/>
+      <c r="L118" s="5"/>
+      <c r="M118" s="5"/>
+      <c r="N118" s="5"/>
+      <c r="O118" s="5"/>
+      <c r="P118" s="6"/>
+      <c r="Q118" s="5"/>
+      <c r="R118" s="5"/>
+    </row>
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A119" s="5"/>
+      <c r="B119" s="5"/>
+      <c r="C119" s="5"/>
+      <c r="D119" s="5"/>
+      <c r="E119" s="5"/>
+      <c r="F119" s="5"/>
+      <c r="G119" s="5"/>
+      <c r="H119" s="5"/>
+      <c r="I119" s="5"/>
+      <c r="J119" s="5"/>
+      <c r="K119" s="5"/>
+      <c r="L119" s="5"/>
+      <c r="M119" s="5"/>
+      <c r="N119" s="5"/>
+      <c r="O119" s="5"/>
+      <c r="P119" s="6"/>
+      <c r="Q119" s="5"/>
+      <c r="R119" s="5"/>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A120" s="5"/>
+      <c r="B120" s="5"/>
+      <c r="C120" s="5"/>
+      <c r="D120" s="5"/>
+      <c r="E120" s="5"/>
+      <c r="F120" s="5"/>
+      <c r="G120" s="5"/>
+      <c r="H120" s="5"/>
+      <c r="I120" s="5"/>
+      <c r="J120" s="5"/>
+      <c r="K120" s="5"/>
+      <c r="L120" s="5"/>
+      <c r="M120" s="5"/>
+      <c r="N120" s="5"/>
+      <c r="O120" s="5"/>
+      <c r="P120" s="6"/>
+      <c r="Q120" s="5"/>
+      <c r="R120" s="5"/>
+    </row>
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A121" s="5"/>
+      <c r="B121" s="5"/>
+      <c r="C121" s="5"/>
+      <c r="D121" s="5"/>
+      <c r="E121" s="5"/>
+      <c r="F121" s="5"/>
+      <c r="G121" s="5"/>
+      <c r="H121" s="5"/>
+      <c r="I121" s="5"/>
+      <c r="J121" s="5"/>
+      <c r="K121" s="5"/>
+      <c r="L121" s="5"/>
+      <c r="M121" s="5"/>
+      <c r="N121" s="5"/>
+      <c r="O121" s="5"/>
+      <c r="P121" s="6"/>
+      <c r="Q121" s="5"/>
+      <c r="R121" s="5"/>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A122" s="5"/>
+      <c r="B122" s="5"/>
+      <c r="C122" s="5"/>
+      <c r="D122" s="5"/>
+      <c r="E122" s="5"/>
+      <c r="F122" s="5"/>
+      <c r="G122" s="5"/>
+      <c r="H122" s="5"/>
+      <c r="I122" s="5"/>
+      <c r="J122" s="5"/>
+      <c r="K122" s="5"/>
+      <c r="L122" s="5"/>
+      <c r="M122" s="5"/>
+      <c r="N122" s="5"/>
+      <c r="O122" s="5"/>
+      <c r="P122" s="6"/>
+      <c r="Q122" s="5"/>
+      <c r="R122" s="5"/>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A123" s="5"/>
+      <c r="B123" s="5"/>
+      <c r="C123" s="5"/>
+      <c r="D123" s="5"/>
+      <c r="E123" s="5"/>
+      <c r="F123" s="5"/>
+      <c r="G123" s="5"/>
+      <c r="H123" s="5"/>
+      <c r="I123" s="5"/>
+      <c r="J123" s="5"/>
+      <c r="K123" s="5"/>
+      <c r="L123" s="5"/>
+      <c r="M123" s="5"/>
+      <c r="N123" s="5"/>
+      <c r="O123" s="5"/>
+      <c r="P123" s="6"/>
+      <c r="Q123" s="5"/>
+      <c r="R123" s="5"/>
+    </row>
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A124" s="5"/>
+      <c r="B124" s="5"/>
+      <c r="C124" s="5"/>
+      <c r="D124" s="5"/>
+      <c r="E124" s="5"/>
+      <c r="F124" s="5"/>
+      <c r="G124" s="5"/>
+      <c r="H124" s="5"/>
+      <c r="I124" s="5"/>
+      <c r="J124" s="5"/>
+      <c r="K124" s="5"/>
+      <c r="L124" s="5"/>
+      <c r="M124" s="5"/>
+      <c r="N124" s="5"/>
+      <c r="O124" s="5"/>
+      <c r="P124" s="6"/>
+      <c r="Q124" s="5"/>
+      <c r="R124" s="5"/>
+    </row>
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A125" s="5"/>
+      <c r="B125" s="5"/>
+      <c r="C125" s="5"/>
+      <c r="D125" s="5"/>
+      <c r="E125" s="5"/>
+      <c r="F125" s="5"/>
+      <c r="G125" s="5"/>
+      <c r="H125" s="5"/>
+      <c r="I125" s="5"/>
+      <c r="J125" s="5"/>
+      <c r="K125" s="5"/>
+      <c r="L125" s="5"/>
+      <c r="M125" s="5"/>
+      <c r="N125" s="5"/>
+      <c r="O125" s="5"/>
+      <c r="P125" s="6"/>
+      <c r="Q125" s="5"/>
+      <c r="R125" s="5"/>
+    </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A126" s="5"/>
+      <c r="B126" s="5"/>
+      <c r="C126" s="5"/>
+      <c r="D126" s="5"/>
+      <c r="E126" s="5"/>
+      <c r="F126" s="5"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="5"/>
+      <c r="I126" s="5"/>
+      <c r="J126" s="5"/>
+      <c r="K126" s="5"/>
+      <c r="L126" s="5"/>
+      <c r="M126" s="5"/>
+      <c r="N126" s="5"/>
+      <c r="O126" s="5"/>
+      <c r="P126" s="6"/>
+      <c r="Q126" s="5"/>
+      <c r="R126" s="5"/>
+    </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A127" s="5"/>
+      <c r="B127" s="5"/>
+      <c r="C127" s="5"/>
+      <c r="D127" s="5"/>
+      <c r="E127" s="5"/>
+      <c r="F127" s="5"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="5"/>
+      <c r="I127" s="5"/>
+      <c r="J127" s="5"/>
+      <c r="K127" s="5"/>
+      <c r="L127" s="5"/>
+      <c r="M127" s="5"/>
+      <c r="N127" s="5"/>
+      <c r="O127" s="5"/>
+      <c r="P127" s="6"/>
+      <c r="Q127" s="5"/>
+      <c r="R127" s="5"/>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A128" s="5"/>
+      <c r="B128" s="5"/>
+      <c r="C128" s="5"/>
+      <c r="D128" s="5"/>
+      <c r="E128" s="5"/>
+      <c r="F128" s="5"/>
+      <c r="G128" s="5"/>
+      <c r="H128" s="5"/>
+      <c r="I128" s="5"/>
+      <c r="J128" s="5"/>
+      <c r="K128" s="5"/>
+      <c r="L128" s="5"/>
+      <c r="M128" s="5"/>
+      <c r="N128" s="5"/>
+      <c r="O128" s="5"/>
+      <c r="P128" s="6"/>
+      <c r="Q128" s="5"/>
+      <c r="R128" s="5"/>
+    </row>
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A129" s="5"/>
+      <c r="B129" s="5"/>
+      <c r="C129" s="5"/>
+      <c r="D129" s="5"/>
+      <c r="E129" s="5"/>
+      <c r="F129" s="5"/>
+      <c r="G129" s="5"/>
+      <c r="H129" s="5"/>
+      <c r="I129" s="5"/>
+      <c r="J129" s="5"/>
+      <c r="K129" s="5"/>
+      <c r="L129" s="5"/>
+      <c r="M129" s="5"/>
+      <c r="N129" s="5"/>
+      <c r="O129" s="5"/>
+      <c r="P129" s="6"/>
+      <c r="Q129" s="5"/>
+      <c r="R129" s="5"/>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A130" s="5"/>
+      <c r="B130" s="5"/>
+      <c r="C130" s="5"/>
+      <c r="D130" s="5"/>
+      <c r="E130" s="5"/>
+      <c r="F130" s="5"/>
+      <c r="G130" s="5"/>
+      <c r="H130" s="5"/>
+      <c r="I130" s="5"/>
+      <c r="J130" s="5"/>
+      <c r="K130" s="5"/>
+      <c r="L130" s="5"/>
+      <c r="M130" s="5"/>
+      <c r="N130" s="5"/>
+      <c r="O130" s="5"/>
+      <c r="P130" s="6"/>
+      <c r="Q130" s="5"/>
+      <c r="R130" s="5"/>
+    </row>
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A131" s="5"/>
+      <c r="B131" s="5"/>
+      <c r="C131" s="5"/>
+      <c r="D131" s="5"/>
+      <c r="E131" s="5"/>
+      <c r="F131" s="5"/>
+      <c r="G131" s="5"/>
+      <c r="H131" s="5"/>
+      <c r="I131" s="5"/>
+      <c r="J131" s="5"/>
+      <c r="K131" s="5"/>
+      <c r="L131" s="5"/>
+      <c r="M131" s="5"/>
+      <c r="N131" s="5"/>
+      <c r="O131" s="5"/>
+      <c r="P131" s="6"/>
+      <c r="Q131" s="5"/>
+      <c r="R131" s="5"/>
+    </row>
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A132" s="5"/>
+      <c r="B132" s="5"/>
+      <c r="C132" s="5"/>
+      <c r="D132" s="5"/>
+      <c r="E132" s="5"/>
+      <c r="F132" s="5"/>
+      <c r="G132" s="5"/>
+      <c r="H132" s="5"/>
+      <c r="I132" s="5"/>
+      <c r="J132" s="5"/>
+      <c r="K132" s="5"/>
+      <c r="L132" s="5"/>
+      <c r="M132" s="5"/>
+      <c r="N132" s="5"/>
+      <c r="O132" s="5"/>
+      <c r="P132" s="6"/>
+      <c r="Q132" s="5"/>
+      <c r="R132" s="5"/>
+    </row>
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A133" s="5"/>
+      <c r="B133" s="5"/>
+      <c r="C133" s="5"/>
+      <c r="D133" s="5"/>
+      <c r="E133" s="5"/>
+      <c r="F133" s="5"/>
+      <c r="G133" s="5"/>
+      <c r="H133" s="5"/>
+      <c r="I133" s="5"/>
+      <c r="J133" s="5"/>
+      <c r="K133" s="5"/>
+      <c r="L133" s="5"/>
+      <c r="M133" s="5"/>
+      <c r="N133" s="5"/>
+      <c r="O133" s="5"/>
+      <c r="P133" s="6"/>
+      <c r="Q133" s="5"/>
+      <c r="R133" s="5"/>
+    </row>
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A134" s="5"/>
+      <c r="B134" s="5"/>
+      <c r="C134" s="5"/>
+      <c r="D134" s="5"/>
+      <c r="E134" s="5"/>
+      <c r="F134" s="5"/>
+      <c r="G134" s="5"/>
+      <c r="H134" s="5"/>
+      <c r="I134" s="5"/>
+      <c r="J134" s="5"/>
+      <c r="K134" s="5"/>
+      <c r="L134" s="5"/>
+      <c r="M134" s="5"/>
+      <c r="N134" s="5"/>
+      <c r="O134" s="5"/>
+      <c r="P134" s="6"/>
+      <c r="Q134" s="5"/>
+      <c r="R134" s="5"/>
+    </row>
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A135" s="5"/>
+      <c r="B135" s="5"/>
+      <c r="C135" s="5"/>
+      <c r="D135" s="5"/>
+      <c r="E135" s="5"/>
+      <c r="F135" s="5"/>
+      <c r="G135" s="5"/>
+      <c r="H135" s="5"/>
+      <c r="I135" s="5"/>
+      <c r="J135" s="5"/>
+      <c r="K135" s="5"/>
+      <c r="L135" s="5"/>
+      <c r="M135" s="5"/>
+      <c r="N135" s="5"/>
+      <c r="O135" s="5"/>
+      <c r="P135" s="6"/>
+      <c r="Q135" s="5"/>
+      <c r="R135" s="5"/>
+    </row>
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A136" s="5"/>
+      <c r="B136" s="5"/>
+      <c r="C136" s="5"/>
+      <c r="D136" s="5"/>
+      <c r="E136" s="5"/>
+      <c r="F136" s="5"/>
+      <c r="G136" s="5"/>
+      <c r="H136" s="5"/>
+      <c r="I136" s="5"/>
+      <c r="J136" s="5"/>
+      <c r="K136" s="5"/>
+      <c r="L136" s="5"/>
+      <c r="M136" s="5"/>
+      <c r="N136" s="5"/>
+      <c r="O136" s="5"/>
+      <c r="P136" s="6"/>
+      <c r="Q136" s="5"/>
+      <c r="R136" s="5"/>
+    </row>
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A137" s="5"/>
+      <c r="B137" s="5"/>
+      <c r="C137" s="5"/>
+      <c r="D137" s="5"/>
+      <c r="E137" s="5"/>
+      <c r="F137" s="5"/>
+      <c r="G137" s="5"/>
+      <c r="H137" s="5"/>
+      <c r="I137" s="5"/>
+      <c r="J137" s="5"/>
+      <c r="K137" s="5"/>
+      <c r="L137" s="5"/>
+      <c r="M137" s="5"/>
+      <c r="N137" s="5"/>
+      <c r="O137" s="5"/>
+      <c r="P137" s="6"/>
+      <c r="Q137" s="5"/>
+      <c r="R137" s="5"/>
+    </row>
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A138" s="5"/>
+      <c r="B138" s="5"/>
+      <c r="C138" s="5"/>
+      <c r="D138" s="5"/>
+      <c r="E138" s="5"/>
+      <c r="F138" s="5"/>
+      <c r="G138" s="5"/>
+      <c r="H138" s="5"/>
+      <c r="I138" s="5"/>
+      <c r="J138" s="5"/>
+      <c r="K138" s="5"/>
+      <c r="L138" s="5"/>
+      <c r="M138" s="5"/>
+      <c r="N138" s="5"/>
+      <c r="O138" s="5"/>
+      <c r="P138" s="6"/>
+      <c r="Q138" s="5"/>
+      <c r="R138" s="5"/>
+    </row>
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A139" s="8"/>
+      <c r="B139" s="5"/>
+      <c r="C139" s="5"/>
+      <c r="D139" s="5"/>
+      <c r="E139" s="5"/>
+      <c r="F139" s="5"/>
+      <c r="G139" s="5"/>
+      <c r="H139" s="5"/>
+      <c r="I139" s="5"/>
+      <c r="J139" s="5"/>
+      <c r="K139" s="5"/>
+      <c r="L139" s="5"/>
+      <c r="M139" s="5"/>
+      <c r="N139" s="5"/>
+      <c r="O139" s="5"/>
+      <c r="P139" s="6"/>
+      <c r="Q139" s="5"/>
+      <c r="R139" s="5"/>
+    </row>
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A140" s="8"/>
+      <c r="B140" s="5"/>
+      <c r="C140" s="5"/>
+      <c r="D140" s="5"/>
+      <c r="E140" s="5"/>
+      <c r="F140" s="5"/>
+      <c r="G140" s="5"/>
+      <c r="H140" s="5"/>
+      <c r="I140" s="5"/>
+      <c r="J140" s="5"/>
+      <c r="K140" s="5"/>
+      <c r="L140" s="5"/>
+      <c r="M140" s="5"/>
+      <c r="N140" s="5"/>
+      <c r="O140" s="5"/>
+      <c r="P140" s="6"/>
+      <c r="Q140" s="5"/>
+      <c r="R140" s="5"/>
+    </row>
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A141" s="8"/>
+      <c r="B141" s="5"/>
+      <c r="C141" s="5"/>
+      <c r="D141" s="5"/>
+      <c r="E141" s="5"/>
+      <c r="F141" s="5"/>
+      <c r="G141" s="5"/>
+      <c r="H141" s="5"/>
+      <c r="I141" s="5"/>
+      <c r="J141" s="5"/>
+      <c r="K141" s="5"/>
+      <c r="L141" s="5"/>
+      <c r="M141" s="5"/>
+      <c r="N141" s="5"/>
+      <c r="O141" s="5"/>
+      <c r="P141" s="6"/>
+      <c r="Q141" s="5"/>
+      <c r="R141" s="5"/>
+    </row>
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A142" s="8"/>
+      <c r="B142" s="5"/>
+      <c r="C142" s="5"/>
+      <c r="D142" s="5"/>
+      <c r="E142" s="5"/>
+      <c r="F142" s="5"/>
+      <c r="G142" s="5"/>
+      <c r="H142" s="5"/>
+      <c r="I142" s="5"/>
+      <c r="J142" s="5"/>
+      <c r="K142" s="5"/>
+      <c r="L142" s="5"/>
+      <c r="M142" s="5"/>
+      <c r="N142" s="5"/>
+      <c r="O142" s="5"/>
+      <c r="P142" s="6"/>
+      <c r="Q142" s="5"/>
+      <c r="R142" s="5"/>
+    </row>
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A143" s="8"/>
+      <c r="B143" s="5"/>
+      <c r="C143" s="5"/>
+      <c r="D143" s="5"/>
+      <c r="E143" s="5"/>
+      <c r="F143" s="5"/>
+      <c r="G143" s="5"/>
+      <c r="H143" s="5"/>
+      <c r="I143" s="5"/>
+      <c r="J143" s="5"/>
+      <c r="K143" s="5"/>
+      <c r="L143" s="5"/>
+      <c r="M143" s="5"/>
+      <c r="N143" s="5"/>
+      <c r="O143" s="5"/>
+      <c r="P143" s="6"/>
+      <c r="Q143" s="5"/>
+      <c r="R143" s="5"/>
+    </row>
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A144" s="8"/>
+      <c r="B144" s="5"/>
+      <c r="C144" s="5"/>
+      <c r="D144" s="5"/>
+      <c r="E144" s="5"/>
+      <c r="F144" s="5"/>
+      <c r="G144" s="5"/>
+      <c r="H144" s="5"/>
+      <c r="I144" s="5"/>
+      <c r="J144" s="5"/>
+      <c r="K144" s="5"/>
+      <c r="L144" s="5"/>
+      <c r="M144" s="5"/>
+      <c r="N144" s="5"/>
+      <c r="O144" s="5"/>
+      <c r="P144" s="6"/>
+      <c r="Q144" s="5"/>
+      <c r="R144" s="5"/>
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A145" s="8"/>
+      <c r="B145" s="5"/>
+      <c r="C145" s="5"/>
+      <c r="D145" s="5"/>
+      <c r="E145" s="5"/>
+      <c r="F145" s="5"/>
+      <c r="G145" s="5"/>
+      <c r="H145" s="5"/>
+      <c r="I145" s="5"/>
+      <c r="J145" s="5"/>
+      <c r="K145" s="5"/>
+      <c r="L145" s="5"/>
+      <c r="M145" s="5"/>
+      <c r="N145" s="5"/>
+      <c r="O145" s="5"/>
+      <c r="P145" s="6"/>
+      <c r="Q145" s="5"/>
+      <c r="R145" s="5"/>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A146" s="8"/>
+      <c r="B146" s="5"/>
+      <c r="C146" s="5"/>
+      <c r="D146" s="5"/>
+      <c r="E146" s="5"/>
+      <c r="F146" s="5"/>
+      <c r="G146" s="5"/>
+      <c r="H146" s="5"/>
+      <c r="I146" s="5"/>
+      <c r="J146" s="5"/>
+      <c r="K146" s="5"/>
+      <c r="L146" s="5"/>
+      <c r="M146" s="5"/>
+      <c r="N146" s="5"/>
+      <c r="O146" s="5"/>
+      <c r="P146" s="6"/>
+      <c r="Q146" s="5"/>
+      <c r="R146" s="5"/>
+    </row>
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A147" s="8"/>
+      <c r="B147" s="5"/>
+      <c r="C147" s="5"/>
+      <c r="D147" s="5"/>
+      <c r="E147" s="5"/>
+      <c r="F147" s="5"/>
+      <c r="G147" s="5"/>
+      <c r="H147" s="5"/>
+      <c r="I147" s="5"/>
+      <c r="J147" s="5"/>
+      <c r="K147" s="5"/>
+      <c r="L147" s="5"/>
+      <c r="M147" s="5"/>
+      <c r="N147" s="5"/>
+      <c r="O147" s="5"/>
+      <c r="P147" s="6"/>
+      <c r="Q147" s="5"/>
+      <c r="R147" s="5"/>
+    </row>
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A148" s="8"/>
+      <c r="B148" s="5"/>
+      <c r="C148" s="5"/>
+      <c r="D148" s="5"/>
+      <c r="E148" s="5"/>
+      <c r="F148" s="5"/>
+      <c r="G148" s="5"/>
+      <c r="H148" s="5"/>
+      <c r="I148" s="5"/>
+      <c r="J148" s="5"/>
+      <c r="K148" s="5"/>
+      <c r="L148" s="5"/>
+      <c r="M148" s="5"/>
+      <c r="N148" s="5"/>
+      <c r="O148" s="5"/>
+      <c r="P148" s="6"/>
+      <c r="Q148" s="5"/>
+      <c r="R148" s="5"/>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A149" s="5"/>
+      <c r="B149" s="5"/>
+      <c r="C149" s="5"/>
+      <c r="D149" s="5"/>
+      <c r="E149" s="5"/>
+      <c r="F149" s="5"/>
+      <c r="G149" s="5"/>
+      <c r="H149" s="5"/>
+      <c r="I149" s="5"/>
+      <c r="J149" s="5"/>
+      <c r="K149" s="5"/>
+      <c r="L149" s="5"/>
+      <c r="M149" s="5"/>
+      <c r="N149" s="5"/>
+      <c r="O149" s="5"/>
+      <c r="P149" s="6"/>
+      <c r="Q149" s="5"/>
+      <c r="R149" s="5"/>
+    </row>
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A150" s="5"/>
+      <c r="B150" s="5"/>
+      <c r="C150" s="5"/>
+      <c r="D150" s="5"/>
+      <c r="E150" s="5"/>
+      <c r="F150" s="5"/>
+      <c r="G150" s="5"/>
+      <c r="H150" s="5"/>
+      <c r="I150" s="5"/>
+      <c r="J150" s="5"/>
+      <c r="K150" s="5"/>
+      <c r="L150" s="5"/>
+      <c r="M150" s="5"/>
+      <c r="N150" s="5"/>
+      <c r="O150" s="5"/>
+      <c r="P150" s="6"/>
+      <c r="Q150" s="5"/>
+      <c r="R150" s="5"/>
+    </row>
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A151" s="5"/>
+      <c r="B151" s="5"/>
+      <c r="C151" s="5"/>
+      <c r="D151" s="5"/>
+      <c r="E151" s="5"/>
+      <c r="F151" s="5"/>
+      <c r="G151" s="5"/>
+      <c r="H151" s="5"/>
+      <c r="I151" s="5"/>
+      <c r="J151" s="5"/>
+      <c r="K151" s="5"/>
+      <c r="L151" s="5"/>
+      <c r="M151" s="5"/>
+      <c r="N151" s="5"/>
+      <c r="O151" s="5"/>
+      <c r="P151" s="6"/>
+      <c r="Q151" s="5"/>
+      <c r="R151" s="5"/>
+    </row>
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A152" s="5"/>
+      <c r="B152" s="5"/>
+      <c r="C152" s="5"/>
+      <c r="D152" s="5"/>
+      <c r="E152" s="5"/>
+      <c r="F152" s="5"/>
+      <c r="G152" s="5"/>
+      <c r="H152" s="5"/>
+      <c r="I152" s="5"/>
+      <c r="J152" s="5"/>
+      <c r="K152" s="5"/>
+      <c r="L152" s="5"/>
+      <c r="M152" s="5"/>
+      <c r="N152" s="5"/>
+      <c r="O152" s="5"/>
+      <c r="P152" s="6"/>
+      <c r="Q152" s="5"/>
+      <c r="R152" s="5"/>
+    </row>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A153" s="5"/>
+      <c r="B153" s="5"/>
+      <c r="C153" s="5"/>
+      <c r="D153" s="5"/>
+      <c r="E153" s="5"/>
+      <c r="F153" s="5"/>
+      <c r="G153" s="5"/>
+      <c r="H153" s="5"/>
+      <c r="I153" s="5"/>
+      <c r="J153" s="5"/>
+      <c r="K153" s="5"/>
+      <c r="L153" s="5"/>
+      <c r="M153" s="5"/>
+      <c r="N153" s="5"/>
+      <c r="O153" s="5"/>
+      <c r="P153" s="6"/>
+      <c r="Q153" s="5"/>
+      <c r="R153" s="5"/>
+    </row>
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A154" s="5"/>
+      <c r="B154" s="5"/>
+      <c r="C154" s="5"/>
+      <c r="D154" s="5"/>
+      <c r="E154" s="5"/>
+      <c r="F154" s="5"/>
+      <c r="G154" s="5"/>
+      <c r="H154" s="5"/>
+      <c r="I154" s="5"/>
+      <c r="J154" s="5"/>
+      <c r="K154" s="5"/>
+      <c r="L154" s="5"/>
+      <c r="M154" s="5"/>
+      <c r="N154" s="5"/>
+      <c r="O154" s="5"/>
+      <c r="P154" s="6"/>
+      <c r="Q154" s="5"/>
+      <c r="R154" s="5"/>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A155" s="5"/>
+      <c r="B155" s="5"/>
+      <c r="C155" s="5"/>
+      <c r="D155" s="5"/>
+      <c r="E155" s="5"/>
+      <c r="F155" s="5"/>
+      <c r="G155" s="5"/>
+      <c r="H155" s="5"/>
+      <c r="I155" s="5"/>
+      <c r="J155" s="5"/>
+      <c r="K155" s="5"/>
+      <c r="L155" s="5"/>
+      <c r="M155" s="5"/>
+      <c r="N155" s="5"/>
+      <c r="O155" s="5"/>
+      <c r="P155" s="6"/>
+      <c r="Q155" s="5"/>
+      <c r="R155" s="5"/>
+    </row>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A156" s="5"/>
+      <c r="B156" s="5"/>
+      <c r="C156" s="5"/>
+      <c r="D156" s="5"/>
+      <c r="E156" s="5"/>
+      <c r="F156" s="5"/>
+      <c r="G156" s="5"/>
+      <c r="H156" s="5"/>
+      <c r="I156" s="5"/>
+      <c r="J156" s="5"/>
+      <c r="K156" s="5"/>
+      <c r="L156" s="5"/>
+      <c r="M156" s="5"/>
+      <c r="N156" s="5"/>
+      <c r="O156" s="5"/>
+      <c r="P156" s="6"/>
+      <c r="Q156" s="5"/>
+      <c r="R156" s="5"/>
+    </row>
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A157" s="5"/>
+      <c r="B157" s="5"/>
+      <c r="C157" s="5"/>
+      <c r="D157" s="5"/>
+      <c r="E157" s="5"/>
+      <c r="F157" s="5"/>
+      <c r="G157" s="5"/>
+      <c r="H157" s="5"/>
+      <c r="I157" s="5"/>
+      <c r="J157" s="5"/>
+      <c r="K157" s="5"/>
+      <c r="L157" s="5"/>
+      <c r="M157" s="5"/>
+      <c r="N157" s="5"/>
+      <c r="O157" s="5"/>
+      <c r="P157" s="6"/>
+      <c r="Q157" s="5"/>
+      <c r="R157" s="5"/>
+    </row>
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A158" s="5"/>
+      <c r="B158" s="5"/>
+      <c r="C158" s="5"/>
+      <c r="D158" s="5"/>
+      <c r="E158" s="5"/>
+      <c r="F158" s="5"/>
+      <c r="G158" s="5"/>
+      <c r="H158" s="5"/>
+      <c r="I158" s="5"/>
+      <c r="J158" s="5"/>
+      <c r="K158" s="5"/>
+      <c r="L158" s="5"/>
+      <c r="M158" s="5"/>
+      <c r="N158" s="5"/>
+      <c r="O158" s="5"/>
+      <c r="P158" s="6"/>
+      <c r="Q158" s="5"/>
+      <c r="R158" s="5"/>
+    </row>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A159" s="5"/>
+      <c r="B159" s="5"/>
+      <c r="C159" s="5"/>
+      <c r="D159" s="5"/>
+      <c r="E159" s="5"/>
+      <c r="F159" s="5"/>
+      <c r="G159" s="5"/>
+      <c r="H159" s="5"/>
+      <c r="I159" s="5"/>
+      <c r="J159" s="5"/>
+      <c r="K159" s="5"/>
+      <c r="L159" s="5"/>
+      <c r="M159" s="5"/>
+      <c r="N159" s="5"/>
+      <c r="O159" s="5"/>
+      <c r="P159" s="6"/>
+      <c r="Q159" s="5"/>
+      <c r="R159" s="5"/>
+    </row>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A160" s="5"/>
+      <c r="B160" s="5"/>
+      <c r="C160" s="5"/>
+      <c r="D160" s="5"/>
+      <c r="E160" s="5"/>
+      <c r="F160" s="5"/>
+      <c r="G160" s="5"/>
+      <c r="H160" s="5"/>
+      <c r="I160" s="5"/>
+      <c r="J160" s="5"/>
+      <c r="K160" s="5"/>
+      <c r="L160" s="5"/>
+      <c r="M160" s="5"/>
+      <c r="N160" s="5"/>
+      <c r="O160" s="5"/>
+      <c r="P160" s="6"/>
+      <c r="Q160" s="5"/>
+      <c r="R160" s="5"/>
+    </row>
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A161" s="5"/>
+      <c r="B161" s="5"/>
+      <c r="C161" s="5"/>
+      <c r="D161" s="5"/>
+      <c r="E161" s="5"/>
+      <c r="F161" s="5"/>
+      <c r="G161" s="5"/>
+      <c r="H161" s="5"/>
+      <c r="I161" s="5"/>
+      <c r="J161" s="5"/>
+      <c r="K161" s="5"/>
+      <c r="L161" s="5"/>
+      <c r="M161" s="5"/>
+      <c r="N161" s="5"/>
+      <c r="O161" s="5"/>
+      <c r="P161" s="6"/>
+      <c r="Q161" s="5"/>
+      <c r="R161" s="5"/>
+    </row>
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A162" s="5"/>
+      <c r="B162" s="5"/>
+      <c r="C162" s="5"/>
+      <c r="D162" s="5"/>
+      <c r="E162" s="5"/>
+      <c r="F162" s="5"/>
+      <c r="G162" s="5"/>
+      <c r="H162" s="5"/>
+      <c r="I162" s="5"/>
+      <c r="J162" s="5"/>
+      <c r="K162" s="5"/>
+      <c r="L162" s="5"/>
+      <c r="M162" s="5"/>
+      <c r="N162" s="5"/>
+      <c r="O162" s="5"/>
+      <c r="P162" s="6"/>
+      <c r="Q162" s="5"/>
+      <c r="R162" s="5"/>
+    </row>
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A163" s="5"/>
+      <c r="B163" s="5"/>
+      <c r="C163" s="5"/>
+      <c r="D163" s="5"/>
+      <c r="E163" s="5"/>
+      <c r="F163" s="5"/>
+      <c r="G163" s="5"/>
+      <c r="H163" s="5"/>
+      <c r="I163" s="5"/>
+      <c r="J163" s="5"/>
+      <c r="K163" s="5"/>
+      <c r="L163" s="5"/>
+      <c r="M163" s="5"/>
+      <c r="N163" s="5"/>
+      <c r="O163" s="5"/>
+      <c r="P163" s="6"/>
+      <c r="Q163" s="5"/>
+      <c r="R163" s="5"/>
+    </row>
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A164" s="5"/>
+      <c r="B164" s="5"/>
+      <c r="C164" s="5"/>
+      <c r="D164" s="5"/>
+      <c r="E164" s="5"/>
+      <c r="F164" s="5"/>
+      <c r="G164" s="5"/>
+      <c r="H164" s="5"/>
+      <c r="I164" s="5"/>
+      <c r="J164" s="5"/>
+      <c r="K164" s="5"/>
+      <c r="L164" s="5"/>
+      <c r="M164" s="5"/>
+      <c r="N164" s="5"/>
+      <c r="O164" s="5"/>
+      <c r="P164" s="6"/>
+      <c r="Q164" s="5"/>
+      <c r="R164" s="5"/>
+    </row>
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A165" s="5"/>
+      <c r="B165" s="5"/>
+      <c r="C165" s="5"/>
+      <c r="D165" s="5"/>
+      <c r="E165" s="5"/>
+      <c r="F165" s="5"/>
+      <c r="G165" s="5"/>
+      <c r="H165" s="5"/>
+      <c r="I165" s="5"/>
+      <c r="J165" s="5"/>
+      <c r="K165" s="5"/>
+      <c r="L165" s="5"/>
+      <c r="M165" s="5"/>
+      <c r="N165" s="5"/>
+      <c r="O165" s="5"/>
+      <c r="P165" s="6"/>
+      <c r="Q165" s="5"/>
+      <c r="R165" s="5"/>
+    </row>
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A166" s="5"/>
+      <c r="B166" s="5"/>
+      <c r="C166" s="5"/>
+      <c r="D166" s="5"/>
+      <c r="E166" s="5"/>
+      <c r="F166" s="5"/>
+      <c r="G166" s="5"/>
+      <c r="H166" s="5"/>
+      <c r="I166" s="5"/>
+      <c r="J166" s="5"/>
+      <c r="K166" s="5"/>
+      <c r="L166" s="5"/>
+      <c r="M166" s="5"/>
+      <c r="N166" s="5"/>
+      <c r="O166" s="5"/>
+      <c r="P166" s="6"/>
+      <c r="Q166" s="5"/>
+      <c r="R166" s="5"/>
+    </row>
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A167" s="5"/>
+      <c r="B167" s="5"/>
+      <c r="C167" s="5"/>
+      <c r="D167" s="5"/>
+      <c r="E167" s="5"/>
+      <c r="F167" s="5"/>
+      <c r="G167" s="5"/>
+      <c r="H167" s="5"/>
+      <c r="I167" s="5"/>
+      <c r="J167" s="5"/>
+      <c r="K167" s="5"/>
+      <c r="L167" s="5"/>
+      <c r="M167" s="5"/>
+      <c r="N167" s="5"/>
+      <c r="O167" s="5"/>
+      <c r="P167" s="6"/>
+      <c r="Q167" s="5"/>
+      <c r="R167" s="5"/>
+    </row>
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A168" s="5"/>
+      <c r="B168" s="5"/>
+      <c r="C168" s="5"/>
+      <c r="D168" s="5"/>
+      <c r="E168" s="5"/>
+      <c r="F168" s="5"/>
+      <c r="G168" s="5"/>
+      <c r="H168" s="5"/>
+      <c r="I168" s="5"/>
+      <c r="J168" s="5"/>
+      <c r="K168" s="5"/>
+      <c r="L168" s="5"/>
+      <c r="M168" s="5"/>
+      <c r="N168" s="5"/>
+      <c r="O168" s="5"/>
+      <c r="P168" s="6"/>
+      <c r="Q168" s="5"/>
+      <c r="R168" s="5"/>
+    </row>
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A169" s="5"/>
+      <c r="B169" s="5"/>
+      <c r="C169" s="5"/>
+      <c r="D169" s="5"/>
+      <c r="E169" s="5"/>
+      <c r="F169" s="5"/>
+      <c r="G169" s="5"/>
+      <c r="H169" s="5"/>
+      <c r="I169" s="5"/>
+      <c r="J169" s="5"/>
+      <c r="K169" s="5"/>
+      <c r="L169" s="5"/>
+      <c r="M169" s="5"/>
+      <c r="N169" s="5"/>
+      <c r="O169" s="5"/>
+      <c r="P169" s="6"/>
+      <c r="Q169" s="5"/>
+      <c r="R169" s="5"/>
+    </row>
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A170" s="5"/>
+      <c r="B170" s="5"/>
+      <c r="C170" s="5"/>
+      <c r="D170" s="5"/>
+      <c r="E170" s="5"/>
+      <c r="F170" s="5"/>
+      <c r="G170" s="5"/>
+      <c r="H170" s="5"/>
+      <c r="I170" s="5"/>
+      <c r="J170" s="5"/>
+      <c r="K170" s="5"/>
+      <c r="L170" s="5"/>
+      <c r="M170" s="5"/>
+      <c r="N170" s="5"/>
+      <c r="O170" s="5"/>
+      <c r="P170" s="6"/>
+      <c r="Q170" s="5"/>
+      <c r="R170" s="5"/>
+    </row>
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A171" s="5"/>
+      <c r="B171" s="5"/>
+      <c r="C171" s="5"/>
+      <c r="D171" s="5"/>
+      <c r="E171" s="5"/>
+      <c r="F171" s="5"/>
+      <c r="G171" s="5"/>
+      <c r="H171" s="5"/>
+      <c r="I171" s="5"/>
+      <c r="J171" s="5"/>
+      <c r="K171" s="5"/>
+      <c r="L171" s="5"/>
+      <c r="M171" s="5"/>
+      <c r="N171" s="5"/>
+      <c r="O171" s="5"/>
+      <c r="P171" s="6"/>
+      <c r="Q171" s="5"/>
+      <c r="R171" s="5"/>
+    </row>
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A172" s="5"/>
+      <c r="B172" s="5"/>
+      <c r="C172" s="5"/>
+      <c r="D172" s="5"/>
+      <c r="E172" s="5"/>
+      <c r="F172" s="5"/>
+      <c r="G172" s="5"/>
+      <c r="H172" s="5"/>
+      <c r="I172" s="5"/>
+      <c r="J172" s="5"/>
+      <c r="K172" s="5"/>
+      <c r="L172" s="5"/>
+      <c r="M172" s="5"/>
+      <c r="N172" s="5"/>
+      <c r="O172" s="5"/>
+      <c r="P172" s="6"/>
+      <c r="Q172" s="5"/>
+      <c r="R172" s="5"/>
+    </row>
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A173" s="5"/>
+      <c r="B173" s="5"/>
+      <c r="C173" s="5"/>
+      <c r="D173" s="5"/>
+      <c r="E173" s="5"/>
+      <c r="F173" s="5"/>
+      <c r="G173" s="5"/>
+      <c r="H173" s="5"/>
+      <c r="I173" s="5"/>
+      <c r="J173" s="5"/>
+      <c r="K173" s="5"/>
+      <c r="L173" s="5"/>
+      <c r="M173" s="5"/>
+      <c r="N173" s="5"/>
+      <c r="O173" s="5"/>
+      <c r="P173" s="6"/>
+      <c r="Q173" s="5"/>
+      <c r="R173" s="5"/>
+    </row>
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A174" s="5"/>
+      <c r="B174" s="5"/>
+      <c r="C174" s="5"/>
+      <c r="D174" s="5"/>
+      <c r="E174" s="5"/>
+      <c r="F174" s="5"/>
+      <c r="G174" s="5"/>
+      <c r="H174" s="5"/>
+      <c r="I174" s="5"/>
+      <c r="J174" s="5"/>
+      <c r="K174" s="5"/>
+      <c r="L174" s="5"/>
+      <c r="M174" s="5"/>
+      <c r="N174" s="5"/>
+      <c r="O174" s="5"/>
+      <c r="P174" s="6"/>
+      <c r="Q174" s="5"/>
+      <c r="R174" s="5"/>
+    </row>
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A175" s="5"/>
+      <c r="B175" s="5"/>
+      <c r="C175" s="5"/>
+      <c r="D175" s="5"/>
+      <c r="E175" s="5"/>
+      <c r="F175" s="5"/>
+      <c r="G175" s="5"/>
+      <c r="H175" s="5"/>
+      <c r="I175" s="5"/>
+      <c r="J175" s="5"/>
+      <c r="K175" s="5"/>
+      <c r="L175" s="5"/>
+      <c r="M175" s="5"/>
+      <c r="N175" s="5"/>
+      <c r="O175" s="5"/>
+      <c r="P175" s="6"/>
+      <c r="Q175" s="5"/>
+      <c r="R175" s="5"/>
+    </row>
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A176" s="5"/>
+      <c r="B176" s="5"/>
+      <c r="C176" s="5"/>
+      <c r="D176" s="5"/>
+      <c r="E176" s="5"/>
+      <c r="F176" s="5"/>
+      <c r="G176" s="5"/>
+      <c r="H176" s="5"/>
+      <c r="I176" s="5"/>
+      <c r="J176" s="5"/>
+      <c r="K176" s="5"/>
+      <c r="L176" s="5"/>
+      <c r="M176" s="5"/>
+      <c r="N176" s="5"/>
+      <c r="O176" s="5"/>
+      <c r="P176" s="6"/>
+      <c r="Q176" s="5"/>
+      <c r="R176" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -13883,6 +19655,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B96036E30F13644F923D207E371C305D" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d197ceb99055fd1a93a3a14aec1bdd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f76aa77c-8923-4724-9a6d-d588cc513697" xmlns:ns3="89c54d5b-05ac-45d5-9242-aabb385cc5ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b86266bfd619f312673123d0bd20d23" ns2:_="" ns3:_="">
     <xsd:import namespace="f76aa77c-8923-4724-9a6d-d588cc513697"/>
@@ -14077,17 +19860,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
   <ds:schemaRefs>
@@ -14097,6 +19869,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BDC8EFC-C946-4B3C-B84E-1270F018751C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14113,21 +19902,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/dados/metas.xlsx
+++ b/dados/metas.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.sa\Documents\dashboard-oportunidades\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DE449A-755E-477D-985A-0F21147DD0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6F0D15-0D99-4E6B-B61C-EE6A713768C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONSULTOR" sheetId="1" r:id="rId1"/>
     <sheet name="LOJA" sheetId="2" r:id="rId2"/>
+    <sheet name="ORÇAMENTO" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CONSULTOR!$A$1:$R$236</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="92">
   <si>
     <t>CÓD</t>
   </si>
@@ -363,12 +364,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -435,10 +442,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -16033,562 +16040,562 @@
       </c>
     </row>
     <row r="38" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A38" s="9">
+      <c r="A38" s="5">
         <v>17</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="5">
         <v>6</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="5">
         <v>8</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F38" s="5">
         <v>8</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="5">
         <v>7</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="5">
         <v>7</v>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="5">
         <v>8</v>
       </c>
-      <c r="J38" s="9">
+      <c r="J38" s="5">
         <v>8</v>
       </c>
-      <c r="K38" s="9">
+      <c r="K38" s="5">
         <v>10</v>
       </c>
-      <c r="L38" s="9">
+      <c r="L38" s="5">
         <v>10</v>
       </c>
-      <c r="M38" s="9">
+      <c r="M38" s="5">
         <v>11</v>
       </c>
-      <c r="N38" s="9">
+      <c r="N38" s="5">
         <v>7</v>
       </c>
-      <c r="O38" s="9">
+      <c r="O38" s="5">
         <v>7</v>
       </c>
-      <c r="P38" s="10">
+      <c r="P38" s="6">
         <v>97</v>
       </c>
-      <c r="Q38" s="9" t="s">
+      <c r="Q38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="R38" s="9" t="s">
+      <c r="R38" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A39" s="9">
+      <c r="A39" s="5">
         <v>17</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D39" s="9">
-        <v>0</v>
-      </c>
-      <c r="E39" s="9">
-        <v>1</v>
-      </c>
-      <c r="F39" s="9">
+      <c r="D39" s="5">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5">
+        <v>1</v>
+      </c>
+      <c r="F39" s="5">
         <v>2</v>
       </c>
-      <c r="G39" s="9">
-        <v>0</v>
-      </c>
-      <c r="H39" s="9">
+      <c r="G39" s="5">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5">
         <v>2</v>
       </c>
-      <c r="I39" s="9">
-        <v>0</v>
-      </c>
-      <c r="J39" s="9">
-        <v>0</v>
-      </c>
-      <c r="K39" s="9">
+      <c r="I39" s="5">
+        <v>0</v>
+      </c>
+      <c r="J39" s="5">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5">
         <v>4</v>
       </c>
-      <c r="L39" s="9">
-        <v>0</v>
-      </c>
-      <c r="M39" s="9">
-        <v>0</v>
-      </c>
-      <c r="N39" s="9">
-        <v>1</v>
-      </c>
-      <c r="O39" s="9">
-        <v>0</v>
-      </c>
-      <c r="P39" s="10">
+      <c r="L39" s="5">
+        <v>0</v>
+      </c>
+      <c r="M39" s="5">
+        <v>0</v>
+      </c>
+      <c r="N39" s="5">
+        <v>1</v>
+      </c>
+      <c r="O39" s="5">
+        <v>0</v>
+      </c>
+      <c r="P39" s="6">
         <v>9</v>
       </c>
-      <c r="Q39" s="9" t="s">
+      <c r="Q39" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="R39" s="9" t="s">
+      <c r="R39" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A40" s="9">
+      <c r="A40" s="5">
         <v>17</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="5">
         <v>2</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="5">
         <v>6</v>
       </c>
-      <c r="F40" s="9">
-        <v>1</v>
-      </c>
-      <c r="G40" s="9">
-        <v>0</v>
-      </c>
-      <c r="H40" s="9">
-        <v>0</v>
-      </c>
-      <c r="I40" s="9">
+      <c r="F40" s="5">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5">
+        <v>0</v>
+      </c>
+      <c r="H40" s="5">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5">
         <v>2</v>
       </c>
-      <c r="J40" s="9">
-        <v>0</v>
-      </c>
-      <c r="K40" s="9">
+      <c r="J40" s="5">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5">
         <v>3</v>
       </c>
-      <c r="L40" s="9">
+      <c r="L40" s="5">
         <v>4</v>
       </c>
-      <c r="M40" s="9">
+      <c r="M40" s="5">
         <v>4</v>
       </c>
-      <c r="N40" s="9">
+      <c r="N40" s="5">
         <v>2</v>
       </c>
-      <c r="O40" s="9">
+      <c r="O40" s="5">
         <v>2</v>
       </c>
-      <c r="P40" s="10">
+      <c r="P40" s="6">
         <v>29</v>
       </c>
-      <c r="Q40" s="9" t="s">
+      <c r="Q40" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="R40" s="9" t="s">
+      <c r="R40" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A41" s="9">
+      <c r="A41" s="5">
         <v>17</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D41" s="9">
-        <v>0</v>
-      </c>
-      <c r="E41" s="9">
+      <c r="D41" s="5">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5">
         <v>2</v>
       </c>
-      <c r="F41" s="9">
-        <v>0</v>
-      </c>
-      <c r="G41" s="9">
-        <v>0</v>
-      </c>
-      <c r="H41" s="9">
-        <v>0</v>
-      </c>
-      <c r="I41" s="9">
-        <v>0</v>
-      </c>
-      <c r="J41" s="9">
-        <v>0</v>
-      </c>
-      <c r="K41" s="9">
+      <c r="F41" s="5">
+        <v>0</v>
+      </c>
+      <c r="G41" s="5">
+        <v>0</v>
+      </c>
+      <c r="H41" s="5">
+        <v>0</v>
+      </c>
+      <c r="I41" s="5">
+        <v>0</v>
+      </c>
+      <c r="J41" s="5">
+        <v>0</v>
+      </c>
+      <c r="K41" s="5">
         <v>3</v>
       </c>
-      <c r="L41" s="9">
-        <v>1</v>
-      </c>
-      <c r="M41" s="9">
+      <c r="L41" s="5">
+        <v>1</v>
+      </c>
+      <c r="M41" s="5">
         <v>5</v>
       </c>
-      <c r="N41" s="9">
-        <v>0</v>
-      </c>
-      <c r="O41" s="9">
-        <v>0</v>
-      </c>
-      <c r="P41" s="10">
+      <c r="N41" s="5">
+        <v>0</v>
+      </c>
+      <c r="O41" s="5">
+        <v>0</v>
+      </c>
+      <c r="P41" s="6">
         <v>11</v>
       </c>
-      <c r="Q41" s="9" t="s">
+      <c r="Q41" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="R41" s="9" t="s">
+      <c r="R41" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A42" s="9">
+      <c r="A42" s="5">
         <v>17</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="5">
         <v>2</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="5">
         <v>5</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F42" s="5">
         <v>2</v>
       </c>
-      <c r="G42" s="9">
-        <v>0</v>
-      </c>
-      <c r="H42" s="9">
-        <v>0</v>
-      </c>
-      <c r="I42" s="9">
+      <c r="G42" s="5">
+        <v>0</v>
+      </c>
+      <c r="H42" s="5">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5">
         <v>2</v>
       </c>
-      <c r="J42" s="9">
-        <v>0</v>
-      </c>
-      <c r="K42" s="9">
+      <c r="J42" s="5">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5">
         <v>3</v>
       </c>
-      <c r="L42" s="9">
+      <c r="L42" s="5">
         <v>4</v>
       </c>
-      <c r="M42" s="9">
+      <c r="M42" s="5">
         <v>5</v>
       </c>
-      <c r="N42" s="9">
+      <c r="N42" s="5">
         <v>2</v>
       </c>
-      <c r="O42" s="9">
+      <c r="O42" s="5">
         <v>2</v>
       </c>
-      <c r="P42" s="10">
+      <c r="P42" s="6">
         <v>29</v>
       </c>
-      <c r="Q42" s="9" t="s">
+      <c r="Q42" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="R42" s="9" t="s">
+      <c r="R42" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A43" s="9">
+      <c r="A43" s="5">
         <v>17</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D43" s="9">
-        <v>0</v>
-      </c>
-      <c r="E43" s="9">
+      <c r="D43" s="5">
+        <v>0</v>
+      </c>
+      <c r="E43" s="5">
         <v>6</v>
       </c>
-      <c r="F43" s="9">
-        <v>1</v>
-      </c>
-      <c r="G43" s="9">
-        <v>0</v>
-      </c>
-      <c r="H43" s="9">
+      <c r="F43" s="5">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5">
+        <v>0</v>
+      </c>
+      <c r="H43" s="5">
         <v>4</v>
       </c>
-      <c r="I43" s="9">
-        <v>0</v>
-      </c>
-      <c r="J43" s="9">
+      <c r="I43" s="5">
+        <v>0</v>
+      </c>
+      <c r="J43" s="5">
         <v>4</v>
       </c>
-      <c r="K43" s="9">
+      <c r="K43" s="5">
         <v>5</v>
       </c>
-      <c r="L43" s="9">
-        <v>0</v>
-      </c>
-      <c r="M43" s="9">
-        <v>0</v>
-      </c>
-      <c r="N43" s="9">
-        <v>1</v>
-      </c>
-      <c r="O43" s="9">
-        <v>0</v>
-      </c>
-      <c r="P43" s="10">
+      <c r="L43" s="5">
+        <v>0</v>
+      </c>
+      <c r="M43" s="5">
+        <v>0</v>
+      </c>
+      <c r="N43" s="5">
+        <v>1</v>
+      </c>
+      <c r="O43" s="5">
+        <v>0</v>
+      </c>
+      <c r="P43" s="6">
         <v>24</v>
       </c>
-      <c r="Q43" s="9" t="s">
+      <c r="Q43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="R43" s="9" t="s">
+      <c r="R43" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A44" s="9">
+      <c r="A44" s="5">
         <v>17</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="5">
         <v>891473</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="5">
         <v>1472867</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F44" s="5">
         <v>1395350</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="5">
         <v>838501</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="5">
         <v>740051</v>
       </c>
-      <c r="I44" s="9">
+      <c r="I44" s="5">
         <v>1023256</v>
       </c>
-      <c r="J44" s="9">
+      <c r="J44" s="5">
         <v>1380620</v>
       </c>
-      <c r="K44" s="9">
+      <c r="K44" s="5">
         <v>1321706</v>
       </c>
-      <c r="L44" s="9">
+      <c r="L44" s="5">
         <v>1294315</v>
       </c>
-      <c r="M44" s="9">
+      <c r="M44" s="5">
         <v>1136951</v>
       </c>
-      <c r="N44" s="9">
+      <c r="N44" s="5">
         <v>1125323</v>
       </c>
-      <c r="O44" s="9">
+      <c r="O44" s="5">
         <v>882171</v>
       </c>
-      <c r="P44" s="10">
+      <c r="P44" s="6">
         <v>15000000</v>
       </c>
-      <c r="Q44" s="9" t="s">
+      <c r="Q44" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="R44" s="9" t="s">
+      <c r="R44" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A45" s="9">
+      <c r="A45" s="5">
         <v>17</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="5">
         <v>576486</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="5">
         <v>952455</v>
       </c>
-      <c r="F45" s="9">
+      <c r="F45" s="5">
         <v>902326</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="5">
         <v>656952</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="5">
         <v>448036</v>
       </c>
-      <c r="I45" s="9">
+      <c r="I45" s="5">
         <v>806280</v>
       </c>
-      <c r="J45" s="9">
+      <c r="J45" s="5">
         <v>776434</v>
       </c>
-      <c r="K45" s="9">
+      <c r="K45" s="5">
         <v>1045195</v>
       </c>
-      <c r="L45" s="9">
+      <c r="L45" s="5">
         <v>866021</v>
       </c>
-      <c r="M45" s="9">
+      <c r="M45" s="5">
         <v>915865</v>
       </c>
-      <c r="N45" s="9">
+      <c r="N45" s="5">
         <v>507726</v>
       </c>
-      <c r="O45" s="9">
+      <c r="O45" s="5">
         <v>547520</v>
       </c>
-      <c r="P45" s="10">
+      <c r="P45" s="6">
         <v>9700004</v>
       </c>
-      <c r="Q45" s="9" t="s">
+      <c r="Q45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="R45" s="9" t="s">
+      <c r="R45" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A46" s="9">
+      <c r="A46" s="5">
         <v>17</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="9">
-        <v>0</v>
-      </c>
-      <c r="E46" s="9">
+      <c r="D46" s="5">
+        <v>0</v>
+      </c>
+      <c r="E46" s="5">
         <v>6</v>
       </c>
-      <c r="F46" s="9">
-        <v>0</v>
-      </c>
-      <c r="G46" s="9">
-        <v>0</v>
-      </c>
-      <c r="H46" s="9">
+      <c r="F46" s="5">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5">
+        <v>0</v>
+      </c>
+      <c r="H46" s="5">
         <v>5</v>
       </c>
-      <c r="I46" s="9">
+      <c r="I46" s="5">
         <v>4</v>
       </c>
-      <c r="J46" s="9">
+      <c r="J46" s="5">
         <v>5</v>
       </c>
-      <c r="K46" s="9">
-        <v>0</v>
-      </c>
-      <c r="L46" s="9">
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5">
         <v>3</v>
       </c>
-      <c r="M46" s="9">
+      <c r="M46" s="5">
         <v>2</v>
       </c>
-      <c r="N46" s="9">
-        <v>0</v>
-      </c>
-      <c r="O46" s="9">
-        <v>0</v>
-      </c>
-      <c r="P46" s="10">
+      <c r="N46" s="5">
+        <v>0</v>
+      </c>
+      <c r="O46" s="5">
+        <v>0</v>
+      </c>
+      <c r="P46" s="6">
         <v>28</v>
       </c>
-      <c r="Q46" s="9" t="s">
+      <c r="Q46" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="R46" s="9" t="s">
+      <c r="R46" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A47" s="9">
+      <c r="A47" s="5">
         <v>17</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="5">
         <v>6</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="5">
         <v>6</v>
       </c>
-      <c r="F47" s="9">
+      <c r="F47" s="5">
         <v>6</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G47" s="5">
         <v>5</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H47" s="5">
         <v>5</v>
       </c>
-      <c r="I47" s="9">
+      <c r="I47" s="5">
         <v>5</v>
       </c>
-      <c r="J47" s="9">
+      <c r="J47" s="5">
         <v>5</v>
       </c>
-      <c r="K47" s="9">
+      <c r="K47" s="5">
         <v>5</v>
       </c>
-      <c r="L47" s="9">
+      <c r="L47" s="5">
         <v>5</v>
       </c>
-      <c r="M47" s="9">
+      <c r="M47" s="5">
         <v>5</v>
       </c>
-      <c r="N47" s="9">
+      <c r="N47" s="5">
         <v>5</v>
       </c>
-      <c r="O47" s="9">
+      <c r="O47" s="5">
         <v>5</v>
       </c>
-      <c r="P47" s="10">
+      <c r="P47" s="6">
         <v>72</v>
       </c>
-      <c r="Q47" s="9" t="s">
+      <c r="Q47" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="R47" s="9" t="s">
+      <c r="R47" s="5" t="s">
         <v>88</v>
       </c>
     </row>
@@ -19645,16 +19652,1848 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A764B28F-457A-4F3D-AEF6-E9832275A92C}">
+  <dimension ref="A1:R60"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="9">
+        <v>18</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>18</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
+        <v>18</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>18</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>18</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>16</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R12" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="9">
+        <v>16</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="9">
+        <v>16</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="9">
+        <v>16</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R15" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>34</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>34</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>34</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>34</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
+        <v>9</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R20" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>9</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R21" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="9">
+        <v>9</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R22" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="9">
+        <v>9</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R23" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="9">
+        <v>9</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R24" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A25" s="9">
+        <v>9</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R25" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
+        <v>9</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R26" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
+        <v>9</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R27" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>19</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R28" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>19</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R29" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>19</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R30" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>19</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R31" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>19</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R32" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>19</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R33" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>19</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R34" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>19</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R35" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>19</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R36" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>19</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R37" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" s="9">
+        <v>17</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R38" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" s="9">
+        <v>17</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R39" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" s="9">
+        <v>17</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R40" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A41" s="9">
+        <v>17</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R41" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" s="9">
+        <v>17</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R42" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" s="9">
+        <v>17</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R43" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" s="9">
+        <v>17</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
+      <c r="O44" s="9"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R44" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45" s="9">
+        <v>17</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+      <c r="O45" s="9"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R45" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A46" s="9">
+        <v>17</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="9"/>
+      <c r="O46" s="9"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R46" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" s="9">
+        <v>17</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9"/>
+      <c r="O47" s="9"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R47" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>30</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="6"/>
+      <c r="Q48" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R48" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>30</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="7"/>
+      <c r="O49" s="7"/>
+      <c r="P49" s="6"/>
+      <c r="Q49" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R49" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <v>30</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="6"/>
+      <c r="Q50" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R50" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>30</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="6"/>
+      <c r="Q51" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R51" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <v>30</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="6"/>
+      <c r="Q52" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R52" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <v>30</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="7"/>
+      <c r="K53" s="7"/>
+      <c r="L53" s="7"/>
+      <c r="M53" s="7"/>
+      <c r="N53" s="7"/>
+      <c r="O53" s="7"/>
+      <c r="P53" s="6"/>
+      <c r="Q53" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R53" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
+        <v>30</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="6"/>
+      <c r="Q54" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R54" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
+        <v>30</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="6"/>
+      <c r="Q55" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R55" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
+        <v>30</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="5"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="6"/>
+      <c r="Q56" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R56" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A57" s="5">
+        <v>30</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="5"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="6"/>
+      <c r="Q57" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R57" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" s="9">
+        <v>11</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+      <c r="M58" s="9"/>
+      <c r="N58" s="9"/>
+      <c r="O58" s="9"/>
+      <c r="P58" s="10"/>
+      <c r="Q58" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="R58" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59" s="9">
+        <v>11</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9"/>
+      <c r="K59" s="9"/>
+      <c r="L59" s="9"/>
+      <c r="M59" s="9"/>
+      <c r="N59" s="9"/>
+      <c r="O59" s="9"/>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="R59" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" s="9">
+        <v>11</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="9"/>
+      <c r="K60" s="9"/>
+      <c r="L60" s="9"/>
+      <c r="M60" s="9"/>
+      <c r="N60" s="9"/>
+      <c r="O60" s="9"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="R60" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
@@ -19663,6 +21502,15 @@
     <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19861,14 +21709,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -19881,6 +21721,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/dados/metas.xlsx
+++ b/dados/metas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.sa\Documents\dashboard-oportunidades\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6F0D15-0D99-4E6B-B61C-EE6A713768C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1658C36-6461-4CA6-9339-F5A281824532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONSULTOR" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="94">
   <si>
     <t>CÓD</t>
   </si>
@@ -317,6 +317,12 @@
   </si>
   <si>
     <t>PME - TANGUÁ</t>
+  </si>
+  <si>
+    <t>MECANIZAÇÃO DO CAFÉ</t>
+  </si>
+  <si>
+    <t>NATALIA.MORAES</t>
   </si>
 </sst>
 </file>
@@ -728,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R236"/>
+  <dimension ref="A1:R250"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
@@ -1809,46 +1815,46 @@
         <v>31</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D20" s="4">
         <v>0</v>
       </c>
       <c r="E20" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="F20" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G20" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="H20" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="I20" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="K20" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="L20" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="M20" s="4">
-        <v>150000</v>
+        <v>1</v>
       </c>
       <c r="N20" s="4">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="O20" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="P20" s="4">
-        <v>1200000</v>
+        <v>5</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>32</v>
@@ -1859,10 +1865,10 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>240053</v>
+        <v>40007</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>23</v>
@@ -1910,18 +1916,18 @@
         <v>32</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>240053</v>
+        <v>40006</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D22" s="4">
         <v>0</v>
@@ -1945,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="4">
         <v>0</v>
@@ -1960,48 +1966,48 @@
         <v>1</v>
       </c>
       <c r="P22" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q22" s="4" t="s">
         <v>32</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>240053</v>
+        <v>240045</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D23" s="4">
         <v>0</v>
       </c>
       <c r="E23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="4">
         <v>1</v>
       </c>
       <c r="H23" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="4">
         <v>0</v>
@@ -2010,13 +2016,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q23" s="4" t="s">
         <v>32</v>
@@ -2027,58 +2033,58 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>40007</v>
+        <v>240053</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D24" s="4">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="E24" s="4">
-        <v>80000</v>
+        <v>1</v>
       </c>
       <c r="F24" s="4">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="G24" s="4">
-        <v>70000</v>
+        <v>1</v>
       </c>
       <c r="H24" s="4">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="I24" s="4">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4">
-        <v>120000</v>
+        <v>1</v>
       </c>
       <c r="K24" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="L24" s="4">
-        <v>150000</v>
+        <v>1</v>
       </c>
       <c r="M24" s="4">
-        <v>140000</v>
+        <v>0</v>
       </c>
       <c r="N24" s="4">
-        <v>120000</v>
+        <v>1</v>
       </c>
       <c r="O24" s="4">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="P24" s="4">
-        <v>1000000</v>
+        <v>5</v>
       </c>
       <c r="Q24" s="4" t="s">
         <v>32</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2089,7 +2095,7 @@
         <v>33</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D25" s="4">
         <v>0</v>
@@ -2113,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="4">
         <v>0</v>
@@ -2128,7 +2134,7 @@
         <v>1</v>
       </c>
       <c r="P25" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q25" s="4" t="s">
         <v>32</v>
@@ -2139,10 +2145,10 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>40007</v>
+        <v>40006</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>24</v>
@@ -2195,13 +2201,13 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <v>40007</v>
+        <v>240045</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D27" s="4">
         <v>0</v>
@@ -2210,7 +2216,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="4">
         <v>1</v>
@@ -2222,81 +2228,81 @@
         <v>0</v>
       </c>
       <c r="J27" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="4">
         <v>1</v>
       </c>
       <c r="L27" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" s="4">
         <v>1</v>
       </c>
       <c r="N27" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" s="4">
         <v>1</v>
       </c>
       <c r="P27" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q27" s="4" t="s">
         <v>32</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <v>40006</v>
+        <v>240053</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D28" s="4">
-        <v>30000</v>
+        <v>106352</v>
       </c>
       <c r="E28" s="4">
-        <v>80000</v>
+        <v>113442</v>
       </c>
       <c r="F28" s="4">
-        <v>50000</v>
+        <v>158346</v>
       </c>
       <c r="G28" s="4">
-        <v>70000</v>
+        <v>163072</v>
       </c>
       <c r="H28" s="4">
-        <v>30000</v>
+        <v>144165</v>
       </c>
       <c r="I28" s="4">
-        <v>30000</v>
+        <v>155982</v>
       </c>
       <c r="J28" s="4">
-        <v>120000</v>
+        <v>139439</v>
       </c>
       <c r="K28" s="4">
-        <v>100000</v>
+        <v>155982</v>
       </c>
       <c r="L28" s="4">
-        <v>150000</v>
+        <v>141802</v>
       </c>
       <c r="M28" s="4">
-        <v>140000</v>
+        <v>89808</v>
       </c>
       <c r="N28" s="4">
-        <v>120000</v>
+        <v>75628</v>
       </c>
       <c r="O28" s="4">
-        <v>80000</v>
+        <v>155982</v>
       </c>
       <c r="P28" s="4">
-        <v>1000000</v>
+        <v>1600000</v>
       </c>
       <c r="Q28" s="4" t="s">
         <v>32</v>
@@ -2307,58 +2313,58 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <v>40006</v>
+        <v>40007</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D29" s="4">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="E29" s="4">
-        <v>1</v>
+        <v>80000</v>
       </c>
       <c r="F29" s="4">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G29" s="4">
-        <v>1</v>
+        <v>70000</v>
       </c>
       <c r="H29" s="4">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="I29" s="4">
-        <v>1</v>
+        <v>30000</v>
       </c>
       <c r="J29" s="4">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="K29" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="L29" s="4">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M29" s="4">
-        <v>1</v>
+        <v>140000</v>
       </c>
       <c r="N29" s="4">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="O29" s="4">
-        <v>1</v>
+        <v>80000</v>
       </c>
       <c r="P29" s="4">
-        <v>5</v>
+        <v>1000000</v>
       </c>
       <c r="Q29" s="4" t="s">
         <v>32</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -2369,102 +2375,102 @@
         <v>35</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D30" s="4">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="E30" s="4">
-        <v>1</v>
+        <v>80000</v>
       </c>
       <c r="F30" s="4">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G30" s="4">
-        <v>1</v>
+        <v>70000</v>
       </c>
       <c r="H30" s="4">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="I30" s="4">
-        <v>1</v>
+        <v>30000</v>
       </c>
       <c r="J30" s="4">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="K30" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="L30" s="4">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M30" s="4">
-        <v>1</v>
+        <v>140000</v>
       </c>
       <c r="N30" s="4">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="O30" s="4">
-        <v>1</v>
+        <v>80000</v>
       </c>
       <c r="P30" s="4">
-        <v>6</v>
+        <v>1000000</v>
       </c>
       <c r="Q30" s="4" t="s">
         <v>32</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <v>40006</v>
+        <v>240045</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D31" s="4">
-        <v>0</v>
+        <v>106352</v>
       </c>
       <c r="E31" s="4">
-        <v>1</v>
+        <v>113442</v>
       </c>
       <c r="F31" s="4">
-        <v>1</v>
+        <v>158346</v>
       </c>
       <c r="G31" s="4">
-        <v>1</v>
+        <v>163072</v>
       </c>
       <c r="H31" s="4">
-        <v>0</v>
+        <v>144165</v>
       </c>
       <c r="I31" s="4">
-        <v>0</v>
+        <v>155982</v>
       </c>
       <c r="J31" s="4">
-        <v>1</v>
+        <v>139439</v>
       </c>
       <c r="K31" s="4">
-        <v>1</v>
+        <v>155982</v>
       </c>
       <c r="L31" s="4">
-        <v>2</v>
+        <v>141802</v>
       </c>
       <c r="M31" s="4">
-        <v>1</v>
+        <v>89808</v>
       </c>
       <c r="N31" s="4">
-        <v>1</v>
+        <v>75628</v>
       </c>
       <c r="O31" s="4">
-        <v>1</v>
+        <v>155982</v>
       </c>
       <c r="P31" s="4">
-        <v>10</v>
+        <v>1600000</v>
       </c>
       <c r="Q31" s="4" t="s">
         <v>32</v>
@@ -2475,52 +2481,52 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <v>240045</v>
+        <v>240053</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D32" s="4">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="E32" s="4">
-        <v>190000</v>
+        <v>1</v>
       </c>
       <c r="F32" s="4">
-        <v>60000</v>
+        <v>1</v>
       </c>
       <c r="G32" s="4">
-        <v>140000</v>
+        <v>1</v>
       </c>
       <c r="H32" s="4">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="I32" s="4">
-        <v>50000</v>
+        <v>1</v>
       </c>
       <c r="J32" s="4">
-        <v>90000</v>
+        <v>1</v>
       </c>
       <c r="K32" s="4">
-        <v>90000</v>
+        <v>1</v>
       </c>
       <c r="L32" s="4">
-        <v>190000</v>
+        <v>1</v>
       </c>
       <c r="M32" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="N32" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="O32" s="4">
-        <v>90000</v>
+        <v>1</v>
       </c>
       <c r="P32" s="4">
-        <v>1300000</v>
+        <v>12</v>
       </c>
       <c r="Q32" s="4" t="s">
         <v>32</v>
@@ -2531,13 +2537,13 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
-        <v>240045</v>
+        <v>40007</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D33" s="4">
         <v>0</v>
@@ -2546,7 +2552,7 @@
         <v>1</v>
       </c>
       <c r="F33" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="4">
         <v>1</v>
@@ -2555,45 +2561,45 @@
         <v>0</v>
       </c>
       <c r="I33" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33" s="4">
         <v>1</v>
       </c>
       <c r="N33" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" s="4">
         <v>1</v>
       </c>
       <c r="P33" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q33" s="4" t="s">
         <v>32</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
-        <v>240045</v>
+        <v>40006</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D34" s="4">
         <v>0</v>
@@ -2602,7 +2608,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" s="4">
         <v>1</v>
@@ -2611,34 +2617,34 @@
         <v>0</v>
       </c>
       <c r="I34" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" s="4">
         <v>1</v>
       </c>
       <c r="L34" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" s="4">
         <v>1</v>
       </c>
       <c r="N34" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="4">
         <v>1</v>
       </c>
       <c r="P34" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q34" s="4" t="s">
         <v>32</v>
       </c>
       <c r="R34" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -2652,7 +2658,7 @@
         <v>28</v>
       </c>
       <c r="D35" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="4">
         <v>2</v>
@@ -2667,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="4">
         <v>1</v>
@@ -2688,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="P35" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q35" s="4" t="s">
         <v>32</v>
@@ -8641,46 +8647,10 @@
         <v>46</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D142" s="4">
-        <v>2</v>
-      </c>
-      <c r="E142" s="4">
-        <v>2</v>
-      </c>
-      <c r="F142" s="4">
-        <v>3</v>
-      </c>
-      <c r="G142" s="4">
-        <v>3</v>
-      </c>
-      <c r="H142" s="4">
-        <v>2</v>
-      </c>
-      <c r="I142" s="4">
-        <v>3</v>
-      </c>
-      <c r="J142" s="4">
-        <v>2</v>
-      </c>
-      <c r="K142" s="4">
-        <v>3</v>
-      </c>
-      <c r="L142" s="4">
-        <v>3</v>
-      </c>
-      <c r="M142" s="4">
-        <v>2</v>
-      </c>
-      <c r="N142" s="4">
-        <v>2</v>
-      </c>
-      <c r="O142" s="4">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="P142" s="4">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q142" s="4" t="s">
         <v>48</v>
@@ -8697,46 +8667,10 @@
         <v>49</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D143" s="4">
-        <v>5</v>
-      </c>
-      <c r="E143" s="4">
-        <v>5</v>
-      </c>
-      <c r="F143" s="4">
-        <v>6</v>
-      </c>
-      <c r="G143" s="4">
-        <v>7</v>
-      </c>
-      <c r="H143" s="4">
-        <v>6</v>
-      </c>
-      <c r="I143" s="4">
-        <v>7</v>
-      </c>
-      <c r="J143" s="4">
-        <v>5</v>
-      </c>
-      <c r="K143" s="4">
-        <v>8</v>
-      </c>
-      <c r="L143" s="4">
-        <v>7</v>
-      </c>
-      <c r="M143" s="4">
-        <v>5</v>
-      </c>
-      <c r="N143" s="4">
-        <v>4</v>
-      </c>
-      <c r="O143" s="4">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="P143" s="4">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="Q143" s="4" t="s">
         <v>48</v>
@@ -8753,46 +8687,10 @@
         <v>50</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D144" s="4">
-        <v>0</v>
-      </c>
-      <c r="E144" s="4">
-        <v>0</v>
-      </c>
-      <c r="F144" s="4">
-        <v>2</v>
-      </c>
-      <c r="G144" s="4">
-        <v>3</v>
-      </c>
-      <c r="H144" s="4">
-        <v>3</v>
-      </c>
-      <c r="I144" s="4">
-        <v>4</v>
-      </c>
-      <c r="J144" s="4">
-        <v>4</v>
-      </c>
-      <c r="K144" s="4">
-        <v>4</v>
-      </c>
-      <c r="L144" s="4">
-        <v>4</v>
-      </c>
-      <c r="M144" s="4">
-        <v>4</v>
-      </c>
-      <c r="N144" s="4">
-        <v>4</v>
-      </c>
-      <c r="O144" s="4">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="P144" s="4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Q144" s="4" t="s">
         <v>48</v>
@@ -8809,46 +8707,10 @@
         <v>51</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D145" s="4">
-        <v>3</v>
-      </c>
-      <c r="E145" s="4">
-        <v>3</v>
-      </c>
-      <c r="F145" s="4">
-        <v>4</v>
-      </c>
-      <c r="G145" s="4">
-        <v>4</v>
-      </c>
-      <c r="H145" s="4">
-        <v>3</v>
-      </c>
-      <c r="I145" s="4">
-        <v>4</v>
-      </c>
-      <c r="J145" s="4">
-        <v>3</v>
-      </c>
-      <c r="K145" s="4">
-        <v>4</v>
-      </c>
-      <c r="L145" s="4">
-        <v>4</v>
-      </c>
-      <c r="M145" s="4">
-        <v>3</v>
-      </c>
-      <c r="N145" s="4">
-        <v>2</v>
-      </c>
-      <c r="O145" s="4">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="P145" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q145" s="4" t="s">
         <v>48</v>
@@ -8865,46 +8727,10 @@
         <v>52</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D146" s="4">
-        <v>5</v>
-      </c>
-      <c r="E146" s="4">
-        <v>5</v>
-      </c>
-      <c r="F146" s="4">
-        <v>6</v>
-      </c>
-      <c r="G146" s="4">
-        <v>7</v>
-      </c>
-      <c r="H146" s="4">
-        <v>6</v>
-      </c>
-      <c r="I146" s="4">
-        <v>7</v>
-      </c>
-      <c r="J146" s="4">
-        <v>5</v>
-      </c>
-      <c r="K146" s="4">
-        <v>8</v>
-      </c>
-      <c r="L146" s="4">
-        <v>7</v>
-      </c>
-      <c r="M146" s="4">
-        <v>5</v>
-      </c>
-      <c r="N146" s="4">
-        <v>4</v>
-      </c>
-      <c r="O146" s="4">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="P146" s="4">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="Q146" s="4" t="s">
         <v>48</v>
@@ -8921,46 +8747,10 @@
         <v>53</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D147" s="4">
-        <v>0</v>
-      </c>
-      <c r="E147" s="4">
-        <v>0</v>
-      </c>
-      <c r="F147" s="4">
-        <v>1</v>
-      </c>
-      <c r="G147" s="4">
-        <v>2</v>
-      </c>
-      <c r="H147" s="4">
-        <v>3</v>
-      </c>
-      <c r="I147" s="4">
-        <v>2</v>
-      </c>
-      <c r="J147" s="4">
-        <v>3</v>
-      </c>
-      <c r="K147" s="4">
-        <v>3</v>
-      </c>
-      <c r="L147" s="4">
-        <v>3</v>
-      </c>
-      <c r="M147" s="4">
-        <v>3</v>
-      </c>
-      <c r="N147" s="4">
-        <v>3</v>
-      </c>
-      <c r="O147" s="4">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="P147" s="4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q147" s="4" t="s">
         <v>48</v>
@@ -8977,46 +8767,46 @@
         <v>46</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D148" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E148" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G148" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H148" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I148" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J148" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K148" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L148" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M148" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N148" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O148" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P148" s="4">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="Q148" s="4" t="s">
         <v>48</v>
@@ -9033,46 +8823,46 @@
         <v>49</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D149" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E149" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F149" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G149" s="4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H149" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I149" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J149" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K149" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L149" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M149" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N149" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O149" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P149" s="4">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="Q149" s="4" t="s">
         <v>48</v>
@@ -9089,7 +8879,7 @@
         <v>50</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D150" s="4">
         <v>0</v>
@@ -9098,37 +8888,37 @@
         <v>0</v>
       </c>
       <c r="F150" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G150" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H150" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I150" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J150" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K150" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L150" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M150" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N150" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O150" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P150" s="4">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="Q150" s="4" t="s">
         <v>48</v>
@@ -9145,46 +8935,46 @@
         <v>51</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D151" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E151" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F151" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G151" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H151" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I151" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J151" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K151" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L151" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M151" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N151" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O151" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P151" s="4">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="Q151" s="4" t="s">
         <v>48</v>
@@ -9201,46 +8991,46 @@
         <v>52</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D152" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E152" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F152" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G152" s="4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H152" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I152" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J152" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K152" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L152" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M152" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N152" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O152" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P152" s="4">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="Q152" s="4" t="s">
         <v>48</v>
@@ -9257,7 +9047,7 @@
         <v>53</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D153" s="4">
         <v>0</v>
@@ -9269,34 +9059,34 @@
         <v>1</v>
       </c>
       <c r="G153" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H153" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I153" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J153" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K153" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L153" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M153" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N153" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O153" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P153" s="4">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="Q153" s="4" t="s">
         <v>48</v>
@@ -9307,55 +9097,55 @@
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
-        <v>240035</v>
+        <v>221003</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D154" s="4">
-        <v>440120</v>
+        <v>0</v>
       </c>
       <c r="E154" s="4">
-        <v>408683</v>
+        <v>1</v>
       </c>
       <c r="F154" s="4">
-        <v>458084</v>
+        <v>0</v>
       </c>
       <c r="G154" s="4">
-        <v>395210</v>
+        <v>0</v>
       </c>
       <c r="H154" s="4">
-        <v>619760</v>
+        <v>1</v>
       </c>
       <c r="I154" s="4">
-        <v>574850</v>
+        <v>1</v>
       </c>
       <c r="J154" s="4">
-        <v>440120</v>
+        <v>1</v>
       </c>
       <c r="K154" s="4">
-        <v>633234</v>
+        <v>0</v>
       </c>
       <c r="L154" s="4">
-        <v>642216</v>
+        <v>1</v>
       </c>
       <c r="M154" s="4">
-        <v>588323</v>
+        <v>0</v>
       </c>
       <c r="N154" s="4">
-        <v>386228</v>
+        <v>1</v>
       </c>
       <c r="O154" s="4">
-        <v>413174</v>
+        <v>0</v>
       </c>
       <c r="P154" s="4">
-        <v>6000002</v>
+        <v>6</v>
       </c>
       <c r="Q154" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="R154" s="4" t="s">
         <v>21</v>
@@ -9363,13 +9153,13 @@
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
-        <v>240035</v>
+        <v>220939</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D155" s="4">
         <v>0</v>
@@ -9381,37 +9171,37 @@
         <v>0</v>
       </c>
       <c r="G155" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H155" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I155" s="4">
         <v>1</v>
       </c>
       <c r="J155" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K155" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L155" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N155" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O155" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P155" s="4">
         <v>6</v>
       </c>
       <c r="Q155" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="R155" s="4" t="s">
         <v>21</v>
@@ -9419,55 +9209,55 @@
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
-        <v>240035</v>
+        <v>221035</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D156" s="4">
         <v>0</v>
       </c>
       <c r="E156" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F156" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I156" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J156" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K156" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L156" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M156" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N156" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O156" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P156" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q156" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="R156" s="4" t="s">
         <v>21</v>
@@ -9475,55 +9265,55 @@
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
-        <v>240035</v>
+        <v>220973</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D157" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E157" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F157" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G157" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H157" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I157" s="4">
+        <v>1</v>
+      </c>
+      <c r="J157" s="4">
+        <v>1</v>
+      </c>
+      <c r="K157" s="4">
+        <v>0</v>
+      </c>
+      <c r="L157" s="4">
+        <v>1</v>
+      </c>
+      <c r="M157" s="4">
+        <v>0</v>
+      </c>
+      <c r="N157" s="4">
+        <v>1</v>
+      </c>
+      <c r="O157" s="4">
+        <v>0</v>
+      </c>
+      <c r="P157" s="4">
         <v>6</v>
       </c>
-      <c r="J157" s="4">
-        <v>4</v>
-      </c>
-      <c r="K157" s="4">
-        <v>7</v>
-      </c>
-      <c r="L157" s="4">
-        <v>9</v>
-      </c>
-      <c r="M157" s="4">
-        <v>6</v>
-      </c>
-      <c r="N157" s="4">
-        <v>5</v>
-      </c>
-      <c r="O157" s="4">
-        <v>3</v>
-      </c>
-      <c r="P157" s="4">
-        <v>60</v>
-      </c>
       <c r="Q157" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="R157" s="4" t="s">
         <v>21</v>
@@ -9531,81 +9321,81 @@
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
-        <v>2417</v>
+        <v>220904</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D158" s="4">
-        <v>330090</v>
+        <v>0</v>
       </c>
       <c r="E158" s="4">
-        <v>306512</v>
+        <v>1</v>
       </c>
       <c r="F158" s="4">
-        <v>343563</v>
+        <v>0</v>
       </c>
       <c r="G158" s="4">
-        <v>296407</v>
+        <v>0</v>
       </c>
       <c r="H158" s="4">
-        <v>464820</v>
+        <v>1</v>
       </c>
       <c r="I158" s="4">
-        <v>431138</v>
+        <v>1</v>
       </c>
       <c r="J158" s="4">
-        <v>330090</v>
+        <v>1</v>
       </c>
       <c r="K158" s="4">
-        <v>474925</v>
+        <v>0</v>
       </c>
       <c r="L158" s="4">
-        <v>481662</v>
+        <v>1</v>
       </c>
       <c r="M158" s="4">
-        <v>441243</v>
+        <v>0</v>
       </c>
       <c r="N158" s="4">
-        <v>289670</v>
+        <v>1</v>
       </c>
       <c r="O158" s="4">
-        <v>309880</v>
+        <v>0</v>
       </c>
       <c r="P158" s="4">
-        <v>4500000</v>
+        <v>6</v>
       </c>
       <c r="Q158" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="R158" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
-        <v>2417</v>
+        <v>220999</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D159" s="4">
         <v>0</v>
       </c>
       <c r="E159" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F159" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G159" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H159" s="4">
         <v>0</v>
@@ -9617,25 +9407,25 @@
         <v>0</v>
       </c>
       <c r="K159" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L159" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M159" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N159" s="4">
         <v>0</v>
       </c>
       <c r="O159" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P159" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q159" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="R159" s="4" t="s">
         <v>21</v>
@@ -9643,13 +9433,13 @@
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
-        <v>2417</v>
+        <v>240035</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D160" s="4">
         <v>0</v>
@@ -9705,46 +9495,46 @@
         <v>58</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D161" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E161" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F161" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G161" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H161" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I161" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J161" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K161" s="4">
+        <v>1</v>
+      </c>
+      <c r="L161" s="4">
+        <v>0</v>
+      </c>
+      <c r="M161" s="4">
+        <v>1</v>
+      </c>
+      <c r="N161" s="4">
+        <v>0</v>
+      </c>
+      <c r="O161" s="4">
+        <v>1</v>
+      </c>
+      <c r="P161" s="4">
         <v>6</v>
-      </c>
-      <c r="L161" s="4">
-        <v>8</v>
-      </c>
-      <c r="M161" s="4">
-        <v>4</v>
-      </c>
-      <c r="N161" s="4">
-        <v>3</v>
-      </c>
-      <c r="O161" s="4">
-        <v>3</v>
-      </c>
-      <c r="P161" s="4">
-        <v>50</v>
       </c>
       <c r="Q161" s="4" t="s">
         <v>57</v>
@@ -9761,46 +9551,46 @@
         <v>59</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D162" s="4">
-        <v>330090</v>
+        <v>0</v>
       </c>
       <c r="E162" s="4">
-        <v>306512</v>
+        <v>1</v>
       </c>
       <c r="F162" s="4">
-        <v>343563</v>
+        <v>0</v>
       </c>
       <c r="G162" s="4">
-        <v>296407</v>
+        <v>1</v>
       </c>
       <c r="H162" s="4">
-        <v>464820</v>
+        <v>0</v>
       </c>
       <c r="I162" s="4">
-        <v>431138</v>
+        <v>1</v>
       </c>
       <c r="J162" s="4">
-        <v>330090</v>
+        <v>0</v>
       </c>
       <c r="K162" s="4">
-        <v>474925</v>
+        <v>1</v>
       </c>
       <c r="L162" s="4">
-        <v>481662</v>
+        <v>0</v>
       </c>
       <c r="M162" s="4">
-        <v>441243</v>
+        <v>1</v>
       </c>
       <c r="N162" s="4">
-        <v>289670</v>
+        <v>0</v>
       </c>
       <c r="O162" s="4">
-        <v>309880</v>
+        <v>1</v>
       </c>
       <c r="P162" s="4">
-        <v>4500000</v>
+        <v>6</v>
       </c>
       <c r="Q162" s="4" t="s">
         <v>57</v>
@@ -9811,10 +9601,10 @@
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
-        <v>2425</v>
+        <v>240048</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>23</v>
@@ -9867,13 +9657,13 @@
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
-        <v>2425</v>
+        <v>240060</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D164" s="4">
         <v>0</v>
@@ -9918,57 +9708,57 @@
         <v>57</v>
       </c>
       <c r="R164" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
-        <v>2425</v>
+        <v>2419</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D165" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E165" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F165" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G165" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H165" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I165" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J165" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K165" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L165" s="4">
+        <v>0</v>
+      </c>
+      <c r="M165" s="4">
+        <v>1</v>
+      </c>
+      <c r="N165" s="4">
+        <v>0</v>
+      </c>
+      <c r="O165" s="4">
+        <v>1</v>
+      </c>
+      <c r="P165" s="4">
         <v>6</v>
-      </c>
-      <c r="M165" s="4">
-        <v>3</v>
-      </c>
-      <c r="N165" s="4">
-        <v>3</v>
-      </c>
-      <c r="O165" s="4">
-        <v>2</v>
-      </c>
-      <c r="P165" s="4">
-        <v>40</v>
       </c>
       <c r="Q165" s="4" t="s">
         <v>57</v>
@@ -9979,52 +9769,52 @@
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
-        <v>240048</v>
+        <v>240058</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D166" s="4">
-        <v>183383</v>
+        <v>0</v>
       </c>
       <c r="E166" s="4">
-        <v>170284</v>
+        <v>1</v>
       </c>
       <c r="F166" s="4">
-        <v>190868</v>
+        <v>0</v>
       </c>
       <c r="G166" s="4">
-        <v>164671</v>
+        <v>1</v>
       </c>
       <c r="H166" s="4">
-        <v>258234</v>
+        <v>0</v>
       </c>
       <c r="I166" s="4">
-        <v>239521</v>
+        <v>1</v>
       </c>
       <c r="J166" s="4">
-        <v>183383</v>
+        <v>0</v>
       </c>
       <c r="K166" s="4">
-        <v>263847</v>
+        <v>1</v>
       </c>
       <c r="L166" s="4">
-        <v>267590</v>
+        <v>0</v>
       </c>
       <c r="M166" s="4">
-        <v>245135</v>
+        <v>1</v>
       </c>
       <c r="N166" s="4">
-        <v>160928</v>
+        <v>0</v>
       </c>
       <c r="O166" s="4">
-        <v>172156</v>
+        <v>1</v>
       </c>
       <c r="P166" s="4">
-        <v>2500000</v>
+        <v>6</v>
       </c>
       <c r="Q166" s="4" t="s">
         <v>57</v>
@@ -10035,29 +9825,14 @@
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
-        <v>240048</v>
+        <v>289821</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D167" s="4">
-        <v>0</v>
-      </c>
-      <c r="E167" s="4">
-        <v>1</v>
-      </c>
-      <c r="F167" s="4">
-        <v>0</v>
-      </c>
-      <c r="G167" s="4">
-        <v>1</v>
-      </c>
-      <c r="H167" s="4">
-        <v>0</v>
-      </c>
       <c r="I167" s="4">
         <v>1</v>
       </c>
@@ -10080,7 +9855,7 @@
         <v>1</v>
       </c>
       <c r="P167" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q167" s="4" t="s">
         <v>57</v>
@@ -10091,10 +9866,10 @@
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
-        <v>240048</v>
+        <v>240035</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>24</v>
@@ -10147,52 +9922,52 @@
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
-        <v>240048</v>
+        <v>2417</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D169" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E169" s="4">
         <v>1</v>
       </c>
       <c r="F169" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G169" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H169" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I169" s="4">
         <v>1</v>
       </c>
       <c r="J169" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K169" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L169" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M169" s="4">
         <v>1</v>
       </c>
       <c r="N169" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O169" s="4">
         <v>1</v>
       </c>
       <c r="P169" s="4">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q169" s="4" t="s">
         <v>57</v>
@@ -10203,69 +9978,69 @@
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
-        <v>240060</v>
+        <v>2425</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D170" s="4">
-        <v>88024</v>
+        <v>0</v>
       </c>
       <c r="E170" s="4">
-        <v>81737</v>
+        <v>1</v>
       </c>
       <c r="F170" s="4">
-        <v>91617</v>
+        <v>0</v>
       </c>
       <c r="G170" s="4">
-        <v>79042</v>
+        <v>1</v>
       </c>
       <c r="H170" s="4">
-        <v>123952</v>
+        <v>0</v>
       </c>
       <c r="I170" s="4">
-        <v>114970</v>
+        <v>1</v>
       </c>
       <c r="J170" s="4">
-        <v>88024</v>
+        <v>0</v>
       </c>
       <c r="K170" s="4">
-        <v>126647</v>
+        <v>1</v>
       </c>
       <c r="L170" s="4">
-        <v>128443</v>
+        <v>0</v>
       </c>
       <c r="M170" s="4">
-        <v>117665</v>
+        <v>1</v>
       </c>
       <c r="N170" s="4">
-        <v>77246</v>
+        <v>0</v>
       </c>
       <c r="O170" s="4">
-        <v>82635</v>
+        <v>1</v>
       </c>
       <c r="P170" s="4">
-        <v>1200002</v>
+        <v>6</v>
       </c>
       <c r="Q170" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R170" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
-        <v>240060</v>
+        <v>240048</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D171" s="4">
         <v>0</v>
@@ -10310,7 +10085,7 @@
         <v>57</v>
       </c>
       <c r="R171" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.25">
@@ -10371,108 +10146,108 @@
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
-        <v>240060</v>
+        <v>2419</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D173" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E173" s="4">
         <v>1</v>
       </c>
       <c r="F173" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G173" s="4">
         <v>1</v>
       </c>
       <c r="H173" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I173" s="4">
         <v>1</v>
       </c>
       <c r="J173" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K173" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L173" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M173" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N173" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O173" s="4">
         <v>1</v>
       </c>
       <c r="P173" s="4">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q173" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R173" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
-        <v>2419</v>
+        <v>240058</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D174" s="4">
-        <v>256737</v>
+        <v>0</v>
       </c>
       <c r="E174" s="4">
-        <v>238398</v>
+        <v>1</v>
       </c>
       <c r="F174" s="4">
-        <v>267216</v>
+        <v>0</v>
       </c>
       <c r="G174" s="4">
-        <v>230539</v>
+        <v>1</v>
       </c>
       <c r="H174" s="4">
-        <v>361527</v>
+        <v>0</v>
       </c>
       <c r="I174" s="4">
-        <v>335329</v>
+        <v>1</v>
       </c>
       <c r="J174" s="4">
-        <v>256737</v>
+        <v>0</v>
       </c>
       <c r="K174" s="4">
-        <v>369386</v>
+        <v>1</v>
       </c>
       <c r="L174" s="4">
-        <v>374626</v>
+        <v>0</v>
       </c>
       <c r="M174" s="4">
-        <v>343189</v>
+        <v>1</v>
       </c>
       <c r="N174" s="4">
-        <v>225299</v>
+        <v>0</v>
       </c>
       <c r="O174" s="4">
-        <v>241018</v>
+        <v>1</v>
       </c>
       <c r="P174" s="4">
-        <v>3500001</v>
+        <v>6</v>
       </c>
       <c r="Q174" s="4" t="s">
         <v>57</v>
@@ -10483,28 +10258,13 @@
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
-        <v>2419</v>
+        <v>289821</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D175" s="4">
-        <v>0</v>
-      </c>
-      <c r="E175" s="4">
-        <v>1</v>
-      </c>
-      <c r="F175" s="4">
-        <v>0</v>
-      </c>
-      <c r="G175" s="4">
-        <v>1</v>
-      </c>
-      <c r="H175" s="4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I175" s="4">
         <v>1</v>
@@ -10528,7 +10288,7 @@
         <v>1</v>
       </c>
       <c r="P175" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q175" s="4" t="s">
         <v>57</v>
@@ -10539,52 +10299,52 @@
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
-        <v>2419</v>
+        <v>240035</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D176" s="4">
-        <v>0</v>
+        <v>440120</v>
       </c>
       <c r="E176" s="4">
-        <v>1</v>
+        <v>408683</v>
       </c>
       <c r="F176" s="4">
-        <v>0</v>
+        <v>458084</v>
       </c>
       <c r="G176" s="4">
-        <v>1</v>
+        <v>395210</v>
       </c>
       <c r="H176" s="4">
-        <v>0</v>
+        <v>619760</v>
       </c>
       <c r="I176" s="4">
-        <v>1</v>
+        <v>574850</v>
       </c>
       <c r="J176" s="4">
-        <v>0</v>
+        <v>440120</v>
       </c>
       <c r="K176" s="4">
-        <v>1</v>
+        <v>633234</v>
       </c>
       <c r="L176" s="4">
-        <v>0</v>
+        <v>642216</v>
       </c>
       <c r="M176" s="4">
-        <v>1</v>
+        <v>588323</v>
       </c>
       <c r="N176" s="4">
-        <v>0</v>
+        <v>386228</v>
       </c>
       <c r="O176" s="4">
-        <v>1</v>
+        <v>413174</v>
       </c>
       <c r="P176" s="4">
-        <v>6</v>
+        <v>6000002</v>
       </c>
       <c r="Q176" s="4" t="s">
         <v>57</v>
@@ -10595,52 +10355,52 @@
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D177" s="4">
-        <v>2</v>
+        <v>330090</v>
       </c>
       <c r="E177" s="4">
-        <v>3</v>
+        <v>306512</v>
       </c>
       <c r="F177" s="4">
-        <v>2</v>
+        <v>343563</v>
       </c>
       <c r="G177" s="4">
-        <v>3</v>
+        <v>296407</v>
       </c>
       <c r="H177" s="4">
-        <v>4</v>
+        <v>464820</v>
       </c>
       <c r="I177" s="4">
-        <v>4</v>
+        <v>431138</v>
       </c>
       <c r="J177" s="4">
-        <v>3</v>
+        <v>330090</v>
       </c>
       <c r="K177" s="4">
-        <v>5</v>
+        <v>474925</v>
       </c>
       <c r="L177" s="4">
-        <v>6</v>
+        <v>481662</v>
       </c>
       <c r="M177" s="4">
-        <v>3</v>
+        <v>441243</v>
       </c>
       <c r="N177" s="4">
-        <v>3</v>
+        <v>289670</v>
       </c>
       <c r="O177" s="4">
-        <v>2</v>
+        <v>309880</v>
       </c>
       <c r="P177" s="4">
-        <v>40</v>
+        <v>4500000</v>
       </c>
       <c r="Q177" s="4" t="s">
         <v>57</v>
@@ -10651,52 +10411,52 @@
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
-        <v>240058</v>
+        <v>2425</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D178" s="4">
-        <v>176048</v>
+        <v>330090</v>
       </c>
       <c r="E178" s="4">
-        <v>163473</v>
+        <v>306512</v>
       </c>
       <c r="F178" s="4">
-        <v>183234</v>
+        <v>343563</v>
       </c>
       <c r="G178" s="4">
-        <v>158084</v>
+        <v>296407</v>
       </c>
       <c r="H178" s="4">
-        <v>247904</v>
+        <v>464820</v>
       </c>
       <c r="I178" s="4">
-        <v>229940</v>
+        <v>431138</v>
       </c>
       <c r="J178" s="4">
-        <v>176048</v>
+        <v>330090</v>
       </c>
       <c r="K178" s="4">
-        <v>253293</v>
+        <v>474925</v>
       </c>
       <c r="L178" s="4">
-        <v>256886</v>
+        <v>481662</v>
       </c>
       <c r="M178" s="4">
-        <v>235329</v>
+        <v>441243</v>
       </c>
       <c r="N178" s="4">
-        <v>154491</v>
+        <v>289670</v>
       </c>
       <c r="O178" s="4">
-        <v>165269</v>
+        <v>309880</v>
       </c>
       <c r="P178" s="4">
-        <v>2399999</v>
+        <v>4500000</v>
       </c>
       <c r="Q178" s="4" t="s">
         <v>57</v>
@@ -10707,52 +10467,52 @@
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
-        <v>240058</v>
+        <v>240048</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D179" s="4">
-        <v>0</v>
+        <v>183383</v>
       </c>
       <c r="E179" s="4">
-        <v>1</v>
+        <v>170284</v>
       </c>
       <c r="F179" s="4">
-        <v>0</v>
+        <v>190868</v>
       </c>
       <c r="G179" s="4">
-        <v>1</v>
+        <v>164671</v>
       </c>
       <c r="H179" s="4">
-        <v>0</v>
+        <v>258234</v>
       </c>
       <c r="I179" s="4">
-        <v>1</v>
+        <v>239521</v>
       </c>
       <c r="J179" s="4">
-        <v>0</v>
+        <v>183383</v>
       </c>
       <c r="K179" s="4">
-        <v>1</v>
+        <v>263847</v>
       </c>
       <c r="L179" s="4">
-        <v>0</v>
+        <v>267590</v>
       </c>
       <c r="M179" s="4">
-        <v>1</v>
+        <v>245135</v>
       </c>
       <c r="N179" s="4">
-        <v>0</v>
+        <v>160928</v>
       </c>
       <c r="O179" s="4">
-        <v>1</v>
+        <v>172156</v>
       </c>
       <c r="P179" s="4">
-        <v>6</v>
+        <v>2500000</v>
       </c>
       <c r="Q179" s="4" t="s">
         <v>57</v>
@@ -10763,108 +10523,108 @@
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
-        <v>240058</v>
+        <v>240060</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D180" s="4">
-        <v>0</v>
+        <v>88024</v>
       </c>
       <c r="E180" s="4">
-        <v>1</v>
+        <v>81737</v>
       </c>
       <c r="F180" s="4">
-        <v>0</v>
+        <v>91617</v>
       </c>
       <c r="G180" s="4">
-        <v>1</v>
+        <v>79042</v>
       </c>
       <c r="H180" s="4">
-        <v>0</v>
+        <v>123952</v>
       </c>
       <c r="I180" s="4">
-        <v>1</v>
+        <v>114970</v>
       </c>
       <c r="J180" s="4">
-        <v>0</v>
+        <v>88024</v>
       </c>
       <c r="K180" s="4">
-        <v>1</v>
+        <v>126647</v>
       </c>
       <c r="L180" s="4">
-        <v>0</v>
+        <v>128443</v>
       </c>
       <c r="M180" s="4">
-        <v>1</v>
+        <v>117665</v>
       </c>
       <c r="N180" s="4">
-        <v>0</v>
+        <v>77246</v>
       </c>
       <c r="O180" s="4">
-        <v>1</v>
+        <v>82635</v>
       </c>
       <c r="P180" s="4">
-        <v>6</v>
+        <v>1200002</v>
       </c>
       <c r="Q180" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R180" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
-        <v>240058</v>
+        <v>2419</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D181" s="4">
-        <v>2</v>
+        <v>256737</v>
       </c>
       <c r="E181" s="4">
-        <v>2</v>
+        <v>238398</v>
       </c>
       <c r="F181" s="4">
-        <v>2</v>
+        <v>267216</v>
       </c>
       <c r="G181" s="4">
-        <v>2</v>
+        <v>230539</v>
       </c>
       <c r="H181" s="4">
-        <v>3</v>
+        <v>361527</v>
       </c>
       <c r="I181" s="4">
-        <v>3</v>
+        <v>335329</v>
       </c>
       <c r="J181" s="4">
-        <v>2</v>
+        <v>256737</v>
       </c>
       <c r="K181" s="4">
-        <v>4</v>
+        <v>369386</v>
       </c>
       <c r="L181" s="4">
-        <v>4</v>
+        <v>374626</v>
       </c>
       <c r="M181" s="4">
-        <v>2</v>
+        <v>343189</v>
       </c>
       <c r="N181" s="4">
-        <v>2</v>
+        <v>225299</v>
       </c>
       <c r="O181" s="4">
-        <v>2</v>
+        <v>241018</v>
       </c>
       <c r="P181" s="4">
-        <v>30</v>
+        <v>3500001</v>
       </c>
       <c r="Q181" s="4" t="s">
         <v>57</v>
@@ -10875,55 +10635,55 @@
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
-        <v>230305</v>
+        <v>240058</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D182" s="4">
-        <v>299114</v>
+        <v>176048</v>
       </c>
       <c r="E182" s="4">
-        <v>319055</v>
+        <v>163473</v>
       </c>
       <c r="F182" s="4">
-        <v>445347</v>
+        <v>183234</v>
       </c>
       <c r="G182" s="4">
-        <v>458641</v>
+        <v>158084</v>
       </c>
       <c r="H182" s="4">
-        <v>405465</v>
+        <v>247904</v>
       </c>
       <c r="I182" s="4">
-        <v>438700</v>
+        <v>229940</v>
       </c>
       <c r="J182" s="4">
-        <v>392171</v>
+        <v>176048</v>
       </c>
       <c r="K182" s="4">
-        <v>438700</v>
+        <v>253293</v>
       </c>
       <c r="L182" s="4">
-        <v>398818</v>
+        <v>256886</v>
       </c>
       <c r="M182" s="4">
-        <v>252585</v>
+        <v>235329</v>
       </c>
       <c r="N182" s="4">
-        <v>212703</v>
+        <v>154491</v>
       </c>
       <c r="O182" s="4">
-        <v>438700</v>
+        <v>165269</v>
       </c>
       <c r="P182" s="4">
-        <v>4499999</v>
+        <v>2399999</v>
       </c>
       <c r="Q182" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="R182" s="4" t="s">
         <v>21</v>
@@ -10931,55 +10691,40 @@
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
-        <v>230305</v>
+        <v>289821</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D183" s="4">
-        <v>1</v>
-      </c>
-      <c r="E183" s="4">
-        <v>1</v>
-      </c>
-      <c r="F183" s="4">
-        <v>1</v>
-      </c>
-      <c r="G183" s="4">
-        <v>1</v>
-      </c>
-      <c r="H183" s="4">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I183" s="4">
-        <v>1</v>
+        <v>114970</v>
       </c>
       <c r="J183" s="4">
-        <v>1</v>
+        <v>88024</v>
       </c>
       <c r="K183" s="4">
-        <v>1</v>
+        <v>126647</v>
       </c>
       <c r="L183" s="4">
-        <v>1</v>
+        <v>128443</v>
       </c>
       <c r="M183" s="4">
-        <v>1</v>
+        <v>117665</v>
       </c>
       <c r="N183" s="4">
-        <v>1</v>
+        <v>77246</v>
       </c>
       <c r="O183" s="4">
-        <v>1</v>
+        <v>82635</v>
       </c>
       <c r="P183" s="4">
-        <v>12</v>
+        <v>735630</v>
       </c>
       <c r="Q183" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="R183" s="4" t="s">
         <v>21</v>
@@ -10987,55 +10732,55 @@
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
-        <v>230305</v>
+        <v>240035</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D184" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E184" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F184" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G184" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H184" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I184" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J184" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K184" s="4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L184" s="4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M184" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N184" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O184" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P184" s="4">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="Q184" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="R184" s="4" t="s">
         <v>21</v>
@@ -11043,55 +10788,55 @@
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
-        <v>230305</v>
+        <v>2417</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D185" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E185" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F185" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G185" s="4">
+        <v>4</v>
+      </c>
+      <c r="H185" s="4">
+        <v>4</v>
+      </c>
+      <c r="I185" s="4">
+        <v>4</v>
+      </c>
+      <c r="J185" s="4">
+        <v>4</v>
+      </c>
+      <c r="K185" s="4">
+        <v>6</v>
+      </c>
+      <c r="L185" s="4">
+        <v>8</v>
+      </c>
+      <c r="M185" s="4">
+        <v>4</v>
+      </c>
+      <c r="N185" s="4">
         <v>3</v>
-      </c>
-      <c r="H185" s="4">
-        <v>2</v>
-      </c>
-      <c r="I185" s="4">
-        <v>2</v>
-      </c>
-      <c r="J185" s="4">
-        <v>2</v>
-      </c>
-      <c r="K185" s="4">
-        <v>3</v>
-      </c>
-      <c r="L185" s="4">
-        <v>2</v>
-      </c>
-      <c r="M185" s="4">
-        <v>3</v>
-      </c>
-      <c r="N185" s="4">
-        <v>2</v>
       </c>
       <c r="O185" s="4">
         <v>3</v>
       </c>
       <c r="P185" s="4">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="Q185" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="R185" s="4" t="s">
         <v>21</v>
@@ -11099,55 +10844,55 @@
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
-        <v>230305</v>
+        <v>2425</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D186" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E186" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F186" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G186" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H186" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I186" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J186" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K186" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L186" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M186" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N186" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O186" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P186" s="4">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="Q186" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="R186" s="4" t="s">
         <v>21</v>
@@ -11155,55 +10900,55 @@
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
-        <v>230307</v>
+        <v>240048</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D187" s="4">
-        <v>299114</v>
+        <v>1</v>
       </c>
       <c r="E187" s="4">
-        <v>319055</v>
+        <v>1</v>
       </c>
       <c r="F187" s="4">
-        <v>445347</v>
+        <v>1</v>
       </c>
       <c r="G187" s="4">
-        <v>458641</v>
+        <v>2</v>
       </c>
       <c r="H187" s="4">
-        <v>405465</v>
+        <v>1</v>
       </c>
       <c r="I187" s="4">
-        <v>438700</v>
+        <v>1</v>
       </c>
       <c r="J187" s="4">
-        <v>392171</v>
+        <v>1</v>
       </c>
       <c r="K187" s="4">
-        <v>438700</v>
+        <v>2</v>
       </c>
       <c r="L187" s="4">
-        <v>398818</v>
+        <v>2</v>
       </c>
       <c r="M187" s="4">
-        <v>252585</v>
+        <v>1</v>
       </c>
       <c r="N187" s="4">
-        <v>212703</v>
+        <v>1</v>
       </c>
       <c r="O187" s="4">
-        <v>438700</v>
+        <v>1</v>
       </c>
       <c r="P187" s="4">
-        <v>4499999</v>
+        <v>15</v>
       </c>
       <c r="Q187" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="R187" s="4" t="s">
         <v>21</v>
@@ -11211,10 +10956,10 @@
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
-        <v>230307</v>
+        <v>230305</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>23</v>
@@ -11273,46 +11018,46 @@
         <v>66</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D189" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E189" s="4">
         <v>1</v>
       </c>
       <c r="F189" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G189" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H189" s="4">
         <v>1</v>
       </c>
       <c r="I189" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J189" s="4">
         <v>1</v>
       </c>
       <c r="K189" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L189" s="4">
         <v>1</v>
       </c>
       <c r="M189" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N189" s="4">
         <v>1</v>
       </c>
       <c r="O189" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P189" s="4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q189" s="4" t="s">
         <v>65</v>
@@ -11323,52 +11068,52 @@
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
-        <v>230307</v>
+        <v>230306</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D190" s="4">
         <v>1</v>
       </c>
       <c r="E190" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F190" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G190" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H190" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I190" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J190" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K190" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L190" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M190" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N190" s="4">
         <v>1</v>
       </c>
       <c r="O190" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P190" s="4">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="Q190" s="4" t="s">
         <v>65</v>
@@ -11379,52 +11124,52 @@
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
-        <v>230307</v>
+        <v>230301</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D191" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E191" s="4">
         <v>1</v>
       </c>
       <c r="F191" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G191" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H191" s="4">
         <v>1</v>
       </c>
       <c r="I191" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J191" s="4">
         <v>1</v>
       </c>
       <c r="K191" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L191" s="4">
         <v>1</v>
       </c>
       <c r="M191" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N191" s="4">
         <v>1</v>
       </c>
       <c r="O191" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P191" s="4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q191" s="4" t="s">
         <v>65</v>
@@ -11435,52 +11180,52 @@
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
-        <v>230306</v>
+        <v>230305</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D192" s="4">
-        <v>299114</v>
+        <v>0</v>
       </c>
       <c r="E192" s="4">
-        <v>319055</v>
+        <v>1</v>
       </c>
       <c r="F192" s="4">
-        <v>445347</v>
+        <v>0</v>
       </c>
       <c r="G192" s="4">
-        <v>458641</v>
+        <v>0</v>
       </c>
       <c r="H192" s="4">
-        <v>405465</v>
+        <v>1</v>
       </c>
       <c r="I192" s="4">
-        <v>438700</v>
+        <v>0</v>
       </c>
       <c r="J192" s="4">
-        <v>392171</v>
+        <v>1</v>
       </c>
       <c r="K192" s="4">
-        <v>438700</v>
+        <v>0</v>
       </c>
       <c r="L192" s="4">
-        <v>398818</v>
+        <v>1</v>
       </c>
       <c r="M192" s="4">
-        <v>252585</v>
+        <v>0</v>
       </c>
       <c r="N192" s="4">
-        <v>212703</v>
+        <v>1</v>
       </c>
       <c r="O192" s="4">
-        <v>438700</v>
+        <v>0</v>
       </c>
       <c r="P192" s="4">
-        <v>4499999</v>
+        <v>5</v>
       </c>
       <c r="Q192" s="4" t="s">
         <v>65</v>
@@ -11491,52 +11236,52 @@
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
-        <v>230306</v>
+        <v>230307</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D193" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E193" s="4">
         <v>1</v>
       </c>
       <c r="F193" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G193" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H193" s="4">
         <v>1</v>
       </c>
       <c r="I193" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J193" s="4">
         <v>1</v>
       </c>
       <c r="K193" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L193" s="4">
         <v>1</v>
       </c>
       <c r="M193" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N193" s="4">
         <v>1</v>
       </c>
       <c r="O193" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P193" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q193" s="4" t="s">
         <v>65</v>
@@ -11603,52 +11348,52 @@
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
-        <v>230306</v>
+        <v>230301</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D195" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E195" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F195" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G195" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H195" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I195" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J195" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K195" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L195" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M195" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N195" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O195" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P195" s="4">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="Q195" s="4" t="s">
         <v>65</v>
@@ -11659,52 +11404,52 @@
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
-        <v>230306</v>
+        <v>230305</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D196" s="4">
-        <v>0</v>
+        <v>299114</v>
       </c>
       <c r="E196" s="4">
-        <v>1</v>
+        <v>319055</v>
       </c>
       <c r="F196" s="4">
-        <v>0</v>
+        <v>445347</v>
       </c>
       <c r="G196" s="4">
-        <v>0</v>
+        <v>458641</v>
       </c>
       <c r="H196" s="4">
-        <v>1</v>
+        <v>405465</v>
       </c>
       <c r="I196" s="4">
-        <v>0</v>
+        <v>438700</v>
       </c>
       <c r="J196" s="4">
-        <v>1</v>
+        <v>392171</v>
       </c>
       <c r="K196" s="4">
-        <v>0</v>
+        <v>438700</v>
       </c>
       <c r="L196" s="4">
-        <v>1</v>
+        <v>398818</v>
       </c>
       <c r="M196" s="4">
-        <v>0</v>
+        <v>252585</v>
       </c>
       <c r="N196" s="4">
-        <v>1</v>
+        <v>212703</v>
       </c>
       <c r="O196" s="4">
-        <v>0</v>
+        <v>438700</v>
       </c>
       <c r="P196" s="4">
-        <v>5</v>
+        <v>4499999</v>
       </c>
       <c r="Q196" s="4" t="s">
         <v>65</v>
@@ -11715,10 +11460,10 @@
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
-        <v>230301</v>
+        <v>230307</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>19</v>
@@ -11771,52 +11516,52 @@
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
-        <v>230301</v>
+        <v>230306</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D198" s="4">
-        <v>1</v>
+        <v>299114</v>
       </c>
       <c r="E198" s="4">
-        <v>1</v>
+        <v>319055</v>
       </c>
       <c r="F198" s="4">
-        <v>1</v>
+        <v>445347</v>
       </c>
       <c r="G198" s="4">
-        <v>1</v>
+        <v>458641</v>
       </c>
       <c r="H198" s="4">
-        <v>1</v>
+        <v>405465</v>
       </c>
       <c r="I198" s="4">
-        <v>1</v>
+        <v>438700</v>
       </c>
       <c r="J198" s="4">
-        <v>1</v>
+        <v>392171</v>
       </c>
       <c r="K198" s="4">
-        <v>1</v>
+        <v>438700</v>
       </c>
       <c r="L198" s="4">
-        <v>1</v>
+        <v>398818</v>
       </c>
       <c r="M198" s="4">
-        <v>1</v>
+        <v>252585</v>
       </c>
       <c r="N198" s="4">
-        <v>1</v>
+        <v>212703</v>
       </c>
       <c r="O198" s="4">
-        <v>1</v>
+        <v>438700</v>
       </c>
       <c r="P198" s="4">
-        <v>12</v>
+        <v>4499999</v>
       </c>
       <c r="Q198" s="4" t="s">
         <v>65</v>
@@ -11833,46 +11578,46 @@
         <v>68</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D199" s="4">
-        <v>0</v>
+        <v>299114</v>
       </c>
       <c r="E199" s="4">
-        <v>1</v>
+        <v>319055</v>
       </c>
       <c r="F199" s="4">
-        <v>0</v>
+        <v>445347</v>
       </c>
       <c r="G199" s="4">
-        <v>0</v>
+        <v>458641</v>
       </c>
       <c r="H199" s="4">
-        <v>1</v>
+        <v>405465</v>
       </c>
       <c r="I199" s="4">
-        <v>0</v>
+        <v>438700</v>
       </c>
       <c r="J199" s="4">
-        <v>1</v>
+        <v>392171</v>
       </c>
       <c r="K199" s="4">
-        <v>0</v>
+        <v>438700</v>
       </c>
       <c r="L199" s="4">
-        <v>1</v>
+        <v>398818</v>
       </c>
       <c r="M199" s="4">
-        <v>0</v>
+        <v>252585</v>
       </c>
       <c r="N199" s="4">
-        <v>1</v>
+        <v>212703</v>
       </c>
       <c r="O199" s="4">
-        <v>0</v>
+        <v>438700</v>
       </c>
       <c r="P199" s="4">
-        <v>5</v>
+        <v>4499999</v>
       </c>
       <c r="Q199" s="4" t="s">
         <v>65</v>
@@ -11883,52 +11628,16 @@
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" s="4">
-        <v>230301</v>
+        <v>230305</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D200" s="4">
-        <v>1</v>
-      </c>
-      <c r="E200" s="4">
-        <v>2</v>
-      </c>
-      <c r="F200" s="4">
-        <v>2</v>
-      </c>
-      <c r="G200" s="4">
-        <v>3</v>
-      </c>
-      <c r="H200" s="4">
-        <v>2</v>
-      </c>
-      <c r="I200" s="4">
-        <v>2</v>
-      </c>
-      <c r="J200" s="4">
-        <v>2</v>
-      </c>
-      <c r="K200" s="4">
-        <v>3</v>
-      </c>
-      <c r="L200" s="4">
-        <v>2</v>
-      </c>
-      <c r="M200" s="4">
-        <v>3</v>
-      </c>
-      <c r="N200" s="4">
-        <v>2</v>
-      </c>
-      <c r="O200" s="4">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="P200" s="4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q200" s="4" t="s">
         <v>65</v>
@@ -11939,52 +11648,16 @@
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
-        <v>230301</v>
+        <v>230307</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D201" s="4">
-        <v>0</v>
-      </c>
-      <c r="E201" s="4">
-        <v>1</v>
-      </c>
-      <c r="F201" s="4">
-        <v>0</v>
-      </c>
-      <c r="G201" s="4">
-        <v>0</v>
-      </c>
-      <c r="H201" s="4">
-        <v>1</v>
-      </c>
-      <c r="I201" s="4">
-        <v>0</v>
-      </c>
-      <c r="J201" s="4">
-        <v>1</v>
-      </c>
-      <c r="K201" s="4">
-        <v>0</v>
-      </c>
-      <c r="L201" s="4">
-        <v>1</v>
-      </c>
-      <c r="M201" s="4">
-        <v>0</v>
-      </c>
-      <c r="N201" s="4">
-        <v>1</v>
-      </c>
-      <c r="O201" s="4">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="P201" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q201" s="4" t="s">
         <v>65</v>
@@ -11995,55 +11668,19 @@
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
-        <v>280037</v>
+        <v>230306</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D202" s="4">
-        <v>80233</v>
-      </c>
-      <c r="E202" s="4">
-        <v>132558</v>
-      </c>
-      <c r="F202" s="4">
-        <v>125581</v>
-      </c>
-      <c r="G202" s="4">
-        <v>102907</v>
-      </c>
-      <c r="H202" s="4">
-        <v>66279</v>
-      </c>
-      <c r="I202" s="4">
-        <v>125581</v>
-      </c>
-      <c r="J202" s="4">
-        <v>120349</v>
-      </c>
-      <c r="K202" s="4">
-        <v>162209</v>
-      </c>
-      <c r="L202" s="4">
-        <v>134302</v>
-      </c>
-      <c r="M202" s="4">
-        <v>139535</v>
-      </c>
-      <c r="N202" s="4">
-        <v>76745</v>
-      </c>
-      <c r="O202" s="4">
-        <v>83721</v>
+        <v>92</v>
       </c>
       <c r="P202" s="4">
-        <v>1350000</v>
+        <v>0</v>
       </c>
       <c r="Q202" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R202" s="4" t="s">
         <v>21</v>
@@ -12051,55 +11688,19 @@
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
-        <v>280037</v>
+        <v>230301</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D203" s="4">
-        <v>0</v>
-      </c>
-      <c r="E203" s="4">
-        <v>1</v>
-      </c>
-      <c r="F203" s="4">
-        <v>0</v>
-      </c>
-      <c r="G203" s="4">
-        <v>0</v>
-      </c>
-      <c r="H203" s="4">
-        <v>0</v>
-      </c>
-      <c r="I203" s="4">
-        <v>0</v>
-      </c>
-      <c r="J203" s="4">
-        <v>0</v>
-      </c>
-      <c r="K203" s="4">
-        <v>0</v>
-      </c>
-      <c r="L203" s="4">
-        <v>0</v>
-      </c>
-      <c r="M203" s="4">
-        <v>0</v>
-      </c>
-      <c r="N203" s="4">
-        <v>0</v>
-      </c>
-      <c r="O203" s="4">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="P203" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q203" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R203" s="4" t="s">
         <v>21</v>
@@ -12107,55 +11708,55 @@
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
-        <v>280037</v>
+        <v>230305</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D204" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E204" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F204" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G204" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H204" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I204" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J204" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K204" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L204" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M204" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N204" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O204" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P204" s="4">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="Q204" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R204" s="4" t="s">
         <v>21</v>
@@ -12163,55 +11764,55 @@
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
-        <v>280037</v>
+        <v>230307</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D205" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E205" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F205" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G205" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H205" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I205" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J205" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K205" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L205" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M205" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N205" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O205" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P205" s="4">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="Q205" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R205" s="4" t="s">
         <v>21</v>
@@ -12219,55 +11820,55 @@
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" s="4">
-        <v>280037</v>
+        <v>230306</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D206" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E206" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F206" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G206" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H206" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I206" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J206" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K206" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L206" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M206" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N206" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O206" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P206" s="4">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Q206" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R206" s="4" t="s">
         <v>21</v>
@@ -12275,55 +11876,55 @@
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
-        <v>280037</v>
+        <v>230301</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D207" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E207" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F207" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G207" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H207" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I207" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J207" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K207" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L207" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M207" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N207" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O207" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P207" s="4">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="Q207" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R207" s="4" t="s">
         <v>21</v>
@@ -12331,19 +11932,19 @@
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" s="4">
-        <v>280037</v>
+        <v>230305</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D208" s="4">
         <v>0</v>
       </c>
       <c r="E208" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F208" s="4">
         <v>0</v>
@@ -12352,13 +11953,13 @@
         <v>0</v>
       </c>
       <c r="H208" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I208" s="4">
         <v>0</v>
       </c>
       <c r="J208" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K208" s="4">
         <v>0</v>
@@ -12370,16 +11971,16 @@
         <v>0</v>
       </c>
       <c r="N208" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O208" s="4">
         <v>0</v>
       </c>
       <c r="P208" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q208" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R208" s="4" t="s">
         <v>21</v>
@@ -12387,55 +11988,55 @@
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
-        <v>280037</v>
+        <v>230307</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D209" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E209" s="4">
         <v>1</v>
       </c>
       <c r="F209" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G209" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H209" s="4">
         <v>1</v>
       </c>
       <c r="I209" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J209" s="4">
         <v>1</v>
       </c>
       <c r="K209" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L209" s="4">
         <v>1</v>
       </c>
       <c r="M209" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N209" s="4">
         <v>1</v>
       </c>
       <c r="O209" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P209" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q209" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R209" s="4" t="s">
         <v>21</v>
@@ -12443,55 +12044,55 @@
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" s="4">
-        <v>280037</v>
+        <v>230306</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D210" s="4">
-        <v>95090</v>
+        <v>0</v>
       </c>
       <c r="E210" s="4">
-        <v>157106</v>
+        <v>1</v>
       </c>
       <c r="F210" s="4">
-        <v>148837</v>
+        <v>0</v>
       </c>
       <c r="G210" s="4">
-        <v>121964</v>
+        <v>0</v>
       </c>
       <c r="H210" s="4">
-        <v>78553</v>
+        <v>1</v>
       </c>
       <c r="I210" s="4">
-        <v>148837</v>
+        <v>0</v>
       </c>
       <c r="J210" s="4">
-        <v>142636</v>
+        <v>1</v>
       </c>
       <c r="K210" s="4">
-        <v>192248</v>
+        <v>0</v>
       </c>
       <c r="L210" s="4">
-        <v>159173</v>
+        <v>1</v>
       </c>
       <c r="M210" s="4">
-        <v>165375</v>
+        <v>0</v>
       </c>
       <c r="N210" s="4">
-        <v>90956</v>
+        <v>1</v>
       </c>
       <c r="O210" s="4">
-        <v>99225</v>
+        <v>0</v>
       </c>
       <c r="P210" s="4">
-        <v>1600000</v>
+        <v>5</v>
       </c>
       <c r="Q210" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R210" s="4" t="s">
         <v>21</v>
@@ -12499,55 +12100,55 @@
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
-        <v>2712</v>
+        <v>230301</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D211" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="E211" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="F211" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G211" s="4">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="H211" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="I211" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="J211" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="K211" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="L211" s="4">
-        <v>300000</v>
+        <v>1</v>
       </c>
       <c r="M211" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="N211" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="O211" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="P211" s="4">
-        <v>2200000</v>
+        <v>5</v>
       </c>
       <c r="Q211" s="4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="R211" s="4" t="s">
         <v>21</v>
@@ -12555,55 +12156,55 @@
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
-        <v>2712</v>
+        <v>280037</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D212" s="4">
-        <v>0</v>
+        <v>80233</v>
       </c>
       <c r="E212" s="4">
-        <v>1</v>
+        <v>132558</v>
       </c>
       <c r="F212" s="4">
-        <v>0</v>
+        <v>125581</v>
       </c>
       <c r="G212" s="4">
-        <v>1</v>
+        <v>102907</v>
       </c>
       <c r="H212" s="4">
-        <v>0</v>
+        <v>66279</v>
       </c>
       <c r="I212" s="4">
-        <v>1</v>
+        <v>125581</v>
       </c>
       <c r="J212" s="4">
-        <v>0</v>
+        <v>120349</v>
       </c>
       <c r="K212" s="4">
-        <v>1</v>
+        <v>162209</v>
       </c>
       <c r="L212" s="4">
-        <v>0</v>
+        <v>134302</v>
       </c>
       <c r="M212" s="4">
-        <v>1</v>
+        <v>139535</v>
       </c>
       <c r="N212" s="4">
-        <v>0</v>
+        <v>76745</v>
       </c>
       <c r="O212" s="4">
-        <v>1</v>
+        <v>83721</v>
       </c>
       <c r="P212" s="4">
-        <v>6</v>
+        <v>1350000</v>
       </c>
       <c r="Q212" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R212" s="4" t="s">
         <v>21</v>
@@ -12611,13 +12212,13 @@
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
-        <v>2712</v>
+        <v>280037</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D213" s="4">
         <v>0</v>
@@ -12629,37 +12230,37 @@
         <v>0</v>
       </c>
       <c r="G213" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H213" s="4">
         <v>0</v>
       </c>
       <c r="I213" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J213" s="4">
         <v>0</v>
       </c>
       <c r="K213" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L213" s="4">
         <v>0</v>
       </c>
       <c r="M213" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N213" s="4">
         <v>0</v>
       </c>
       <c r="O213" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P213" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q213" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R213" s="4" t="s">
         <v>21</v>
@@ -12667,25 +12268,25 @@
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
-        <v>2712</v>
+        <v>280037</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D214" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E214" s="4">
         <v>1</v>
       </c>
       <c r="F214" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G214" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H214" s="4">
         <v>1</v>
@@ -12697,25 +12298,25 @@
         <v>1</v>
       </c>
       <c r="K214" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L214" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M214" s="4">
         <v>1</v>
       </c>
       <c r="N214" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O214" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P214" s="4">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="Q214" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R214" s="4" t="s">
         <v>21</v>
@@ -12723,22 +12324,22 @@
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
-        <v>2712</v>
+        <v>280037</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D215" s="4">
         <v>0</v>
       </c>
       <c r="E215" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F215" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G215" s="4">
         <v>0</v>
@@ -12771,7 +12372,7 @@
         <v>4</v>
       </c>
       <c r="Q215" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R215" s="4" t="s">
         <v>21</v>
@@ -12779,13 +12380,13 @@
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
-        <v>270018</v>
+        <v>280037</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D216" s="4">
         <v>0</v>
@@ -12794,40 +12395,40 @@
         <v>0</v>
       </c>
       <c r="F216" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G216" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H216" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="I216" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="J216" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="K216" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="L216" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="M216" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="N216" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="O216" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="P216" s="4">
-        <v>1500000</v>
+        <v>1</v>
       </c>
       <c r="Q216" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R216" s="4" t="s">
         <v>21</v>
@@ -12835,55 +12436,55 @@
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
-        <v>270018</v>
+        <v>280037</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D217" s="4">
         <v>0</v>
       </c>
       <c r="E217" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F217" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G217" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H217" s="4">
         <v>0</v>
       </c>
       <c r="I217" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J217" s="4">
         <v>0</v>
       </c>
       <c r="K217" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L217" s="4">
         <v>0</v>
       </c>
       <c r="M217" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N217" s="4">
         <v>0</v>
       </c>
       <c r="O217" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P217" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q217" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R217" s="4" t="s">
         <v>21</v>
@@ -12891,13 +12492,13 @@
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
-        <v>270018</v>
+        <v>280037</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D218" s="4">
         <v>0</v>
@@ -12909,13 +12510,13 @@
         <v>0</v>
       </c>
       <c r="G218" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H218" s="4">
         <v>0</v>
       </c>
       <c r="I218" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J218" s="4">
         <v>0</v>
@@ -12924,22 +12525,22 @@
         <v>0</v>
       </c>
       <c r="L218" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M218" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N218" s="4">
         <v>0</v>
       </c>
       <c r="O218" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P218" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q218" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R218" s="4" t="s">
         <v>21</v>
@@ -12947,19 +12548,19 @@
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
-        <v>270018</v>
+        <v>280037</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C219" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D219" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E219" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F219" s="4">
         <v>1</v>
@@ -12992,10 +12593,10 @@
         <v>1</v>
       </c>
       <c r="P219" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q219" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R219" s="4" t="s">
         <v>21</v>
@@ -13003,55 +12604,55 @@
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
-        <v>270018</v>
+        <v>280037</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D220" s="4">
-        <v>0</v>
+        <v>95090</v>
       </c>
       <c r="E220" s="4">
-        <v>0</v>
+        <v>157106</v>
       </c>
       <c r="F220" s="4">
-        <v>1</v>
+        <v>148837</v>
       </c>
       <c r="G220" s="4">
-        <v>0</v>
+        <v>121964</v>
       </c>
       <c r="H220" s="4">
-        <v>0</v>
+        <v>78553</v>
       </c>
       <c r="I220" s="4">
-        <v>1</v>
+        <v>148837</v>
       </c>
       <c r="J220" s="4">
-        <v>0</v>
+        <v>142636</v>
       </c>
       <c r="K220" s="4">
-        <v>0</v>
+        <v>192248</v>
       </c>
       <c r="L220" s="4">
-        <v>1</v>
+        <v>159173</v>
       </c>
       <c r="M220" s="4">
-        <v>0</v>
+        <v>165375</v>
       </c>
       <c r="N220" s="4">
-        <v>0</v>
+        <v>90956</v>
       </c>
       <c r="O220" s="4">
-        <v>1</v>
+        <v>99225</v>
       </c>
       <c r="P220" s="4">
-        <v>4</v>
+        <v>1600000</v>
       </c>
       <c r="Q220" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R220" s="4" t="s">
         <v>21</v>
@@ -13059,52 +12660,52 @@
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
-        <v>270035</v>
+        <v>2712</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D221" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="E221" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="F221" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G221" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="H221" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="I221" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="J221" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="K221" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="L221" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="M221" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="N221" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="O221" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="P221" s="4">
-        <v>1700000</v>
+        <v>6</v>
       </c>
       <c r="Q221" s="4" t="s">
         <v>72</v>
@@ -13115,10 +12716,10 @@
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
-        <v>270035</v>
+        <v>270018</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>23</v>
@@ -13127,7 +12728,7 @@
         <v>0</v>
       </c>
       <c r="E222" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F222" s="4">
         <v>0</v>
@@ -13160,7 +12761,7 @@
         <v>1</v>
       </c>
       <c r="P222" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q222" s="4" t="s">
         <v>72</v>
@@ -13177,7 +12778,7 @@
         <v>74</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D223" s="4">
         <v>0</v>
@@ -13227,52 +12828,52 @@
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
-        <v>270035</v>
+        <v>270029</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D224" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E224" s="4">
         <v>1</v>
       </c>
       <c r="F224" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G224" s="4">
         <v>1</v>
       </c>
       <c r="H224" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I224" s="4">
         <v>1</v>
       </c>
       <c r="J224" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K224" s="4">
         <v>1</v>
       </c>
       <c r="L224" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M224" s="4">
         <v>1</v>
       </c>
       <c r="N224" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O224" s="4">
         <v>1</v>
       </c>
       <c r="P224" s="4">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q224" s="4" t="s">
         <v>72</v>
@@ -13283,25 +12884,25 @@
     </row>
     <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
-        <v>270035</v>
+        <v>2712</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D225" s="4">
         <v>0</v>
       </c>
       <c r="E225" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F225" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G225" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H225" s="4">
         <v>0</v>
@@ -13313,13 +12914,13 @@
         <v>0</v>
       </c>
       <c r="K225" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L225" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M225" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N225" s="4">
         <v>0</v>
@@ -13328,7 +12929,7 @@
         <v>1</v>
       </c>
       <c r="P225" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q225" s="4" t="s">
         <v>72</v>
@@ -13339,52 +12940,52 @@
     </row>
     <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
-        <v>270029</v>
+        <v>270018</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D226" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="E226" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="F226" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G226" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="H226" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="I226" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="J226" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="K226" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="L226" s="4">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="M226" s="4">
-        <v>200000</v>
+        <v>1</v>
       </c>
       <c r="N226" s="4">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="O226" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="P226" s="4">
-        <v>1700000</v>
+        <v>4</v>
       </c>
       <c r="Q226" s="4" t="s">
         <v>72</v>
@@ -13395,13 +12996,13 @@
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
-        <v>270029</v>
+        <v>270035</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D227" s="4">
         <v>0</v>
@@ -13507,52 +13108,52 @@
     </row>
     <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
-        <v>270029</v>
+        <v>2712</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D229" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="E229" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="F229" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="G229" s="4">
-        <v>1</v>
+        <v>300000</v>
       </c>
       <c r="H229" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="I229" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="J229" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="K229" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="L229" s="4">
-        <v>2</v>
+        <v>300000</v>
       </c>
       <c r="M229" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="N229" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="O229" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="P229" s="4">
-        <v>13</v>
+        <v>2200000</v>
       </c>
       <c r="Q229" s="4" t="s">
         <v>72</v>
@@ -13563,13 +13164,13 @@
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
-        <v>270029</v>
+        <v>270018</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D230" s="4">
         <v>0</v>
@@ -13578,37 +13179,37 @@
         <v>0</v>
       </c>
       <c r="F230" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="G230" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H230" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="I230" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="J230" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="K230" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="L230" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="M230" s="4">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="N230" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="O230" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="P230" s="4">
-        <v>4</v>
+        <v>1500000</v>
       </c>
       <c r="Q230" s="4" t="s">
         <v>72</v>
@@ -13619,55 +13220,55 @@
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
-        <v>212910</v>
+        <v>270035</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D231" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="E231" s="4">
-        <v>5</v>
+        <v>100000</v>
       </c>
       <c r="F231" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="G231" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="H231" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="I231" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="J231" s="4">
-        <v>2</v>
+        <v>200000</v>
       </c>
       <c r="K231" s="4">
-        <v>2</v>
+        <v>200000</v>
       </c>
       <c r="L231" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="M231" s="4">
-        <v>2</v>
+        <v>200000</v>
       </c>
       <c r="N231" s="4">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="O231" s="4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="P231" s="4">
-        <v>17</v>
+        <v>1700000</v>
       </c>
       <c r="Q231" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="R231" s="4" t="s">
         <v>21</v>
@@ -13675,55 +13276,55 @@
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
-        <v>212910</v>
+        <v>270029</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D232" s="4">
-        <v>133333</v>
+        <v>100000</v>
       </c>
       <c r="E232" s="4">
-        <v>315152</v>
+        <v>100000</v>
       </c>
       <c r="F232" s="4">
-        <v>60606</v>
+        <v>200000</v>
       </c>
       <c r="G232" s="4">
-        <v>109091</v>
+        <v>100000</v>
       </c>
       <c r="H232" s="4">
-        <v>169697</v>
+        <v>100000</v>
       </c>
       <c r="I232" s="4">
-        <v>157576</v>
+        <v>100000</v>
       </c>
       <c r="J232" s="4">
-        <v>181818</v>
+        <v>200000</v>
       </c>
       <c r="K232" s="4">
-        <v>254545</v>
+        <v>200000</v>
       </c>
       <c r="L232" s="4">
-        <v>230303</v>
+        <v>200000</v>
       </c>
       <c r="M232" s="4">
-        <v>193939</v>
+        <v>200000</v>
       </c>
       <c r="N232" s="4">
-        <v>121213</v>
+        <v>100000</v>
       </c>
       <c r="O232" s="4">
-        <v>72727</v>
+        <v>100000</v>
       </c>
       <c r="P232" s="4">
-        <v>2000000</v>
+        <v>1700000</v>
       </c>
       <c r="Q232" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="R232" s="4" t="s">
         <v>21</v>
@@ -13731,55 +13332,55 @@
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
-        <v>212910</v>
+        <v>2712</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D233" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E233" s="4">
         <v>1</v>
       </c>
       <c r="F233" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G233" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H233" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I233" s="4">
         <v>1</v>
       </c>
       <c r="J233" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K233" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L233" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M233" s="4">
         <v>1</v>
       </c>
       <c r="N233" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O233" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P233" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Q233" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="R233" s="4" t="s">
         <v>21</v>
@@ -13787,55 +13388,55 @@
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
-        <v>212876</v>
+        <v>270018</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D234" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E234" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F234" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G234" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H234" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I234" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J234" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K234" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L234" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M234" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N234" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O234" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P234" s="4">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="Q234" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="R234" s="4" t="s">
         <v>21</v>
@@ -13843,55 +13444,55 @@
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
-        <v>212876</v>
+        <v>270035</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D235" s="4">
-        <v>222222</v>
+        <v>1</v>
       </c>
       <c r="E235" s="4">
-        <v>130719</v>
+        <v>1</v>
       </c>
       <c r="F235" s="4">
-        <v>222222</v>
+        <v>1</v>
       </c>
       <c r="G235" s="4">
-        <v>156863</v>
+        <v>1</v>
       </c>
       <c r="H235" s="4">
-        <v>222222</v>
+        <v>1</v>
       </c>
       <c r="I235" s="4">
-        <v>91503</v>
+        <v>1</v>
       </c>
       <c r="J235" s="4">
-        <v>209150</v>
+        <v>1</v>
       </c>
       <c r="K235" s="4">
-        <v>261438</v>
+        <v>1</v>
       </c>
       <c r="L235" s="4">
-        <v>143791</v>
+        <v>2</v>
       </c>
       <c r="M235" s="4">
-        <v>91504</v>
+        <v>1</v>
       </c>
       <c r="N235" s="4">
-        <v>143791</v>
+        <v>1</v>
       </c>
       <c r="O235" s="4">
-        <v>104575</v>
+        <v>1</v>
       </c>
       <c r="P235" s="4">
-        <v>2000000</v>
+        <v>13</v>
       </c>
       <c r="Q235" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="R235" s="4" t="s">
         <v>21</v>
@@ -13899,57 +13500,826 @@
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
+        <v>270029</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D236" s="4">
+        <v>1</v>
+      </c>
+      <c r="E236" s="4">
+        <v>1</v>
+      </c>
+      <c r="F236" s="4">
+        <v>1</v>
+      </c>
+      <c r="G236" s="4">
+        <v>1</v>
+      </c>
+      <c r="H236" s="4">
+        <v>1</v>
+      </c>
+      <c r="I236" s="4">
+        <v>1</v>
+      </c>
+      <c r="J236" s="4">
+        <v>1</v>
+      </c>
+      <c r="K236" s="4">
+        <v>1</v>
+      </c>
+      <c r="L236" s="4">
+        <v>2</v>
+      </c>
+      <c r="M236" s="4">
+        <v>1</v>
+      </c>
+      <c r="N236" s="4">
+        <v>1</v>
+      </c>
+      <c r="O236" s="4">
+        <v>1</v>
+      </c>
+      <c r="P236" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q236" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="R236" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A237" s="4">
+        <v>2712</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D237" s="4">
+        <v>0</v>
+      </c>
+      <c r="E237" s="4">
+        <v>0</v>
+      </c>
+      <c r="F237" s="4">
+        <v>1</v>
+      </c>
+      <c r="G237" s="4">
+        <v>0</v>
+      </c>
+      <c r="H237" s="4">
+        <v>0</v>
+      </c>
+      <c r="I237" s="4">
+        <v>1</v>
+      </c>
+      <c r="J237" s="4">
+        <v>0</v>
+      </c>
+      <c r="K237" s="4">
+        <v>0</v>
+      </c>
+      <c r="L237" s="4">
+        <v>1</v>
+      </c>
+      <c r="M237" s="4">
+        <v>0</v>
+      </c>
+      <c r="N237" s="4">
+        <v>0</v>
+      </c>
+      <c r="O237" s="4">
+        <v>1</v>
+      </c>
+      <c r="P237" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q237" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="R237" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A238" s="4">
+        <v>270018</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D238" s="4">
+        <v>0</v>
+      </c>
+      <c r="E238" s="4">
+        <v>0</v>
+      </c>
+      <c r="F238" s="4">
+        <v>1</v>
+      </c>
+      <c r="G238" s="4">
+        <v>0</v>
+      </c>
+      <c r="H238" s="4">
+        <v>0</v>
+      </c>
+      <c r="I238" s="4">
+        <v>1</v>
+      </c>
+      <c r="J238" s="4">
+        <v>0</v>
+      </c>
+      <c r="K238" s="4">
+        <v>0</v>
+      </c>
+      <c r="L238" s="4">
+        <v>1</v>
+      </c>
+      <c r="M238" s="4">
+        <v>0</v>
+      </c>
+      <c r="N238" s="4">
+        <v>0</v>
+      </c>
+      <c r="O238" s="4">
+        <v>1</v>
+      </c>
+      <c r="P238" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q238" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="R238" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A239" s="4">
+        <v>270035</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D239" s="4">
+        <v>0</v>
+      </c>
+      <c r="E239" s="4">
+        <v>0</v>
+      </c>
+      <c r="F239" s="4">
+        <v>1</v>
+      </c>
+      <c r="G239" s="4">
+        <v>0</v>
+      </c>
+      <c r="H239" s="4">
+        <v>0</v>
+      </c>
+      <c r="I239" s="4">
+        <v>1</v>
+      </c>
+      <c r="J239" s="4">
+        <v>0</v>
+      </c>
+      <c r="K239" s="4">
+        <v>0</v>
+      </c>
+      <c r="L239" s="4">
+        <v>1</v>
+      </c>
+      <c r="M239" s="4">
+        <v>0</v>
+      </c>
+      <c r="N239" s="4">
+        <v>0</v>
+      </c>
+      <c r="O239" s="4">
+        <v>1</v>
+      </c>
+      <c r="P239" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q239" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="R239" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A240" s="4">
+        <v>270029</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D240" s="4">
+        <v>0</v>
+      </c>
+      <c r="E240" s="4">
+        <v>0</v>
+      </c>
+      <c r="F240" s="4">
+        <v>1</v>
+      </c>
+      <c r="G240" s="4">
+        <v>0</v>
+      </c>
+      <c r="H240" s="4">
+        <v>0</v>
+      </c>
+      <c r="I240" s="4">
+        <v>1</v>
+      </c>
+      <c r="J240" s="4">
+        <v>0</v>
+      </c>
+      <c r="K240" s="4">
+        <v>0</v>
+      </c>
+      <c r="L240" s="4">
+        <v>1</v>
+      </c>
+      <c r="M240" s="4">
+        <v>0</v>
+      </c>
+      <c r="N240" s="4">
+        <v>0</v>
+      </c>
+      <c r="O240" s="4">
+        <v>1</v>
+      </c>
+      <c r="P240" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q240" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="R240" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A241" s="4">
+        <v>212910</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D241" s="4">
+        <v>1</v>
+      </c>
+      <c r="E241" s="4">
+        <v>5</v>
+      </c>
+      <c r="F241" s="4">
+        <v>1</v>
+      </c>
+      <c r="G241" s="4">
+        <v>1</v>
+      </c>
+      <c r="H241" s="4">
+        <v>0</v>
+      </c>
+      <c r="I241" s="4">
+        <v>1</v>
+      </c>
+      <c r="J241" s="4">
+        <v>2</v>
+      </c>
+      <c r="K241" s="4">
+        <v>2</v>
+      </c>
+      <c r="L241" s="4">
+        <v>1</v>
+      </c>
+      <c r="M241" s="4">
+        <v>2</v>
+      </c>
+      <c r="N241" s="4">
+        <v>1</v>
+      </c>
+      <c r="O241" s="4">
+        <v>0</v>
+      </c>
+      <c r="P241" s="4">
+        <v>17</v>
+      </c>
+      <c r="Q241" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R241" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A242" s="4">
+        <v>212910</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D242" s="4">
+        <v>133333</v>
+      </c>
+      <c r="E242" s="4">
+        <v>315152</v>
+      </c>
+      <c r="F242" s="4">
+        <v>60606</v>
+      </c>
+      <c r="G242" s="4">
+        <v>109091</v>
+      </c>
+      <c r="H242" s="4">
+        <v>169697</v>
+      </c>
+      <c r="I242" s="4">
+        <v>157576</v>
+      </c>
+      <c r="J242" s="4">
+        <v>181818</v>
+      </c>
+      <c r="K242" s="4">
+        <v>254545</v>
+      </c>
+      <c r="L242" s="4">
+        <v>230303</v>
+      </c>
+      <c r="M242" s="4">
+        <v>193939</v>
+      </c>
+      <c r="N242" s="4">
+        <v>121213</v>
+      </c>
+      <c r="O242" s="4">
+        <v>72727</v>
+      </c>
+      <c r="P242" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="Q242" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R242" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A243" s="4">
+        <v>212910</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D243" s="4">
+        <v>0</v>
+      </c>
+      <c r="E243" s="4">
+        <v>1</v>
+      </c>
+      <c r="F243" s="4">
+        <v>0</v>
+      </c>
+      <c r="G243" s="4">
+        <v>1</v>
+      </c>
+      <c r="H243" s="4">
+        <v>0</v>
+      </c>
+      <c r="I243" s="4">
+        <v>1</v>
+      </c>
+      <c r="J243" s="4">
+        <v>0</v>
+      </c>
+      <c r="K243" s="4">
+        <v>0</v>
+      </c>
+      <c r="L243" s="4">
+        <v>0</v>
+      </c>
+      <c r="M243" s="4">
+        <v>1</v>
+      </c>
+      <c r="N243" s="4">
+        <v>0</v>
+      </c>
+      <c r="O243" s="4">
+        <v>1</v>
+      </c>
+      <c r="P243" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q243" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R243" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A244" s="4">
         <v>212876</v>
       </c>
-      <c r="B236" s="4" t="s">
+      <c r="B244" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C236" s="4" t="s">
+      <c r="C244" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D244" s="4">
+        <v>4</v>
+      </c>
+      <c r="E244" s="4">
+        <v>3</v>
+      </c>
+      <c r="F244" s="4">
+        <v>3</v>
+      </c>
+      <c r="G244" s="4">
+        <v>3</v>
+      </c>
+      <c r="H244" s="4">
+        <v>2</v>
+      </c>
+      <c r="I244" s="4">
+        <v>4</v>
+      </c>
+      <c r="J244" s="4">
+        <v>4</v>
+      </c>
+      <c r="K244" s="4">
+        <v>4</v>
+      </c>
+      <c r="L244" s="4">
+        <v>2</v>
+      </c>
+      <c r="M244" s="4">
+        <v>3</v>
+      </c>
+      <c r="N244" s="4">
+        <v>3</v>
+      </c>
+      <c r="O244" s="4">
+        <v>3</v>
+      </c>
+      <c r="P244" s="4">
+        <v>38</v>
+      </c>
+      <c r="Q244" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R244" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A245" s="4">
+        <v>212876</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D245" s="4">
+        <v>222222</v>
+      </c>
+      <c r="E245" s="4">
+        <v>130719</v>
+      </c>
+      <c r="F245" s="4">
+        <v>222222</v>
+      </c>
+      <c r="G245" s="4">
+        <v>156863</v>
+      </c>
+      <c r="H245" s="4">
+        <v>222222</v>
+      </c>
+      <c r="I245" s="4">
+        <v>91503</v>
+      </c>
+      <c r="J245" s="4">
+        <v>209150</v>
+      </c>
+      <c r="K245" s="4">
+        <v>261438</v>
+      </c>
+      <c r="L245" s="4">
+        <v>143791</v>
+      </c>
+      <c r="M245" s="4">
+        <v>91504</v>
+      </c>
+      <c r="N245" s="4">
+        <v>143791</v>
+      </c>
+      <c r="O245" s="4">
+        <v>104575</v>
+      </c>
+      <c r="P245" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="Q245" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R245" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A246" s="4">
+        <v>212876</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C246" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D236" s="4">
-        <v>0</v>
-      </c>
-      <c r="E236" s="4">
-        <v>1</v>
-      </c>
-      <c r="F236" s="4">
-        <v>0</v>
-      </c>
-      <c r="G236" s="4">
-        <v>1</v>
-      </c>
-      <c r="H236" s="4">
-        <v>0</v>
-      </c>
-      <c r="I236" s="4">
-        <v>1</v>
-      </c>
-      <c r="J236" s="4">
-        <v>0</v>
-      </c>
-      <c r="K236" s="4">
-        <v>0</v>
-      </c>
-      <c r="L236" s="4">
-        <v>0</v>
-      </c>
-      <c r="M236" s="4">
-        <v>1</v>
-      </c>
-      <c r="N236" s="4">
-        <v>0</v>
-      </c>
-      <c r="O236" s="4">
-        <v>1</v>
-      </c>
-      <c r="P236" s="4">
+      <c r="D246" s="4">
+        <v>0</v>
+      </c>
+      <c r="E246" s="4">
+        <v>1</v>
+      </c>
+      <c r="F246" s="4">
+        <v>0</v>
+      </c>
+      <c r="G246" s="4">
+        <v>1</v>
+      </c>
+      <c r="H246" s="4">
+        <v>0</v>
+      </c>
+      <c r="I246" s="4">
+        <v>1</v>
+      </c>
+      <c r="J246" s="4">
+        <v>0</v>
+      </c>
+      <c r="K246" s="4">
+        <v>0</v>
+      </c>
+      <c r="L246" s="4">
+        <v>0</v>
+      </c>
+      <c r="M246" s="4">
+        <v>1</v>
+      </c>
+      <c r="N246" s="4">
+        <v>0</v>
+      </c>
+      <c r="O246" s="4">
+        <v>1</v>
+      </c>
+      <c r="P246" s="4">
         <v>5</v>
       </c>
-      <c r="Q236" s="4" t="s">
+      <c r="Q246" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="R236" s="4" t="s">
+      <c r="R246" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A247" s="4">
+        <v>240060</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D247" s="4">
+        <v>1</v>
+      </c>
+      <c r="E247" s="4">
+        <v>1</v>
+      </c>
+      <c r="F247" s="4">
+        <v>1</v>
+      </c>
+      <c r="G247" s="4">
+        <v>1</v>
+      </c>
+      <c r="H247" s="4">
+        <v>1</v>
+      </c>
+      <c r="I247" s="4">
+        <v>1</v>
+      </c>
+      <c r="J247" s="4">
+        <v>1</v>
+      </c>
+      <c r="K247" s="4">
+        <v>2</v>
+      </c>
+      <c r="L247" s="4">
+        <v>2</v>
+      </c>
+      <c r="M247" s="4">
+        <v>2</v>
+      </c>
+      <c r="N247" s="4">
+        <v>1</v>
+      </c>
+      <c r="O247" s="4">
+        <v>1</v>
+      </c>
+      <c r="P247" s="4">
+        <v>15</v>
+      </c>
+      <c r="Q247" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R247" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A248" s="4">
+        <v>2419</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D248" s="4">
+        <v>2</v>
+      </c>
+      <c r="E248" s="4">
+        <v>3</v>
+      </c>
+      <c r="F248" s="4">
+        <v>2</v>
+      </c>
+      <c r="G248" s="4">
+        <v>3</v>
+      </c>
+      <c r="H248" s="4">
+        <v>4</v>
+      </c>
+      <c r="I248" s="4">
+        <v>4</v>
+      </c>
+      <c r="J248" s="4">
+        <v>3</v>
+      </c>
+      <c r="K248" s="4">
+        <v>5</v>
+      </c>
+      <c r="L248" s="4">
+        <v>6</v>
+      </c>
+      <c r="M248" s="4">
+        <v>3</v>
+      </c>
+      <c r="N248" s="4">
+        <v>3</v>
+      </c>
+      <c r="O248" s="4">
+        <v>2</v>
+      </c>
+      <c r="P248" s="4">
+        <v>40</v>
+      </c>
+      <c r="Q248" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R248" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A249" s="4">
+        <v>240058</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D249" s="4">
+        <v>2</v>
+      </c>
+      <c r="E249" s="4">
+        <v>2</v>
+      </c>
+      <c r="F249" s="4">
+        <v>2</v>
+      </c>
+      <c r="G249" s="4">
+        <v>2</v>
+      </c>
+      <c r="H249" s="4">
+        <v>3</v>
+      </c>
+      <c r="I249" s="4">
+        <v>3</v>
+      </c>
+      <c r="J249" s="4">
+        <v>2</v>
+      </c>
+      <c r="K249" s="4">
+        <v>4</v>
+      </c>
+      <c r="L249" s="4">
+        <v>4</v>
+      </c>
+      <c r="M249" s="4">
+        <v>2</v>
+      </c>
+      <c r="N249" s="4">
+        <v>2</v>
+      </c>
+      <c r="O249" s="4">
+        <v>2</v>
+      </c>
+      <c r="P249" s="4">
+        <v>30</v>
+      </c>
+      <c r="Q249" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R249" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A250" s="4">
+        <v>289821</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I250" s="4">
+        <v>1</v>
+      </c>
+      <c r="J250" s="4">
+        <v>1</v>
+      </c>
+      <c r="K250" s="4">
+        <v>2</v>
+      </c>
+      <c r="L250" s="4">
+        <v>2</v>
+      </c>
+      <c r="M250" s="4">
+        <v>2</v>
+      </c>
+      <c r="N250" s="4">
+        <v>1</v>
+      </c>
+      <c r="O250" s="4">
+        <v>1</v>
+      </c>
+      <c r="P250" s="4">
+        <v>10</v>
+      </c>
+      <c r="Q250" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R250" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -21494,26 +21864,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B96036E30F13644F923D207E371C305D" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d197ceb99055fd1a93a3a14aec1bdd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f76aa77c-8923-4724-9a6d-d588cc513697" xmlns:ns3="89c54d5b-05ac-45d5-9242-aabb385cc5ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b86266bfd619f312673123d0bd20d23" ns2:_="" ns3:_="">
     <xsd:import namespace="f76aa77c-8923-4724-9a6d-d588cc513697"/>
@@ -21708,32 +22058,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BDC8EFC-C946-4B3C-B84E-1270F018751C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21750,4 +22095,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/dados/metas.xlsx
+++ b/dados/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.sa\Documents\dashboard-oportunidades\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D23C76-5B77-4A93-9150-AB49C028919D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC705B24-26E3-4CF9-9434-7D0343B6C216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -178,9 +178,6 @@
     <t>SIMAO.CASTRO</t>
   </si>
   <si>
-    <t>WESLEY</t>
-  </si>
-  <si>
     <t>ADNU.SILVA</t>
   </si>
   <si>
@@ -320,6 +317,9 @@
   </si>
   <si>
     <t>NATALIA.MORAES</t>
+  </si>
+  <si>
+    <t>WESLEY.LIMA</t>
   </si>
 </sst>
 </file>
@@ -801,10 +801,10 @@
         <v>221003</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
@@ -846,7 +846,7 @@
         <v>7</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R2" s="4" t="s">
         <v>21</v>
@@ -857,10 +857,10 @@
         <v>220939</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" s="4">
         <v>4</v>
@@ -902,7 +902,7 @@
         <v>36</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>21</v>
@@ -913,10 +913,10 @@
         <v>221035</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="4">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>20</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R4" s="4" t="s">
         <v>21</v>
@@ -969,10 +969,10 @@
         <v>220973</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="4">
         <v>2</v>
@@ -1014,7 +1014,7 @@
         <v>18</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R5" s="4" t="s">
         <v>21</v>
@@ -1025,10 +1025,10 @@
         <v>220904</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="4">
         <v>4</v>
@@ -1070,7 +1070,7 @@
         <v>36</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R6" s="4" t="s">
         <v>34</v>
@@ -1081,10 +1081,10 @@
         <v>220999</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
@@ -1126,7 +1126,7 @@
         <v>6</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R7" s="4" t="s">
         <v>21</v>
@@ -1585,19 +1585,10 @@
         <v>250111</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4">
-        <v>0</v>
       </c>
       <c r="G16" s="4">
         <v>0</v>
@@ -1641,7 +1632,7 @@
         <v>280037</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>22</v>
@@ -1686,7 +1677,7 @@
         <v>1</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R17" s="4" t="s">
         <v>21</v>
@@ -2369,19 +2360,10 @@
         <v>250111</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="4">
-        <v>0</v>
-      </c>
-      <c r="F30" s="4">
-        <v>0</v>
       </c>
       <c r="G30" s="4">
         <v>1</v>
@@ -2425,7 +2407,7 @@
         <v>221003</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>23</v>
@@ -2470,7 +2452,7 @@
         <v>6</v>
       </c>
       <c r="Q31" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R31" s="4" t="s">
         <v>21</v>
@@ -2481,7 +2463,7 @@
         <v>220939</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>23</v>
@@ -2526,7 +2508,7 @@
         <v>6</v>
       </c>
       <c r="Q32" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R32" s="4" t="s">
         <v>21</v>
@@ -2537,7 +2519,7 @@
         <v>221035</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>23</v>
@@ -2582,7 +2564,7 @@
         <v>6</v>
       </c>
       <c r="Q33" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R33" s="4" t="s">
         <v>21</v>
@@ -2593,7 +2575,7 @@
         <v>220973</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>23</v>
@@ -2638,7 +2620,7 @@
         <v>6</v>
       </c>
       <c r="Q34" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R34" s="4" t="s">
         <v>21</v>
@@ -2649,7 +2631,7 @@
         <v>220904</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>23</v>
@@ -2694,7 +2676,7 @@
         <v>6</v>
       </c>
       <c r="Q35" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R35" s="4" t="s">
         <v>34</v>
@@ -2705,7 +2687,7 @@
         <v>220999</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>23</v>
@@ -2750,7 +2732,7 @@
         <v>6</v>
       </c>
       <c r="Q36" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R36" s="4" t="s">
         <v>21</v>
@@ -2761,7 +2743,7 @@
         <v>240035</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>23</v>
@@ -2806,7 +2788,7 @@
         <v>6</v>
       </c>
       <c r="Q37" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R37" s="4" t="s">
         <v>21</v>
@@ -2817,7 +2799,7 @@
         <v>2417</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>23</v>
@@ -2862,7 +2844,7 @@
         <v>6</v>
       </c>
       <c r="Q38" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R38" s="4" t="s">
         <v>21</v>
@@ -2873,7 +2855,7 @@
         <v>2425</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>23</v>
@@ -2918,7 +2900,7 @@
         <v>6</v>
       </c>
       <c r="Q39" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R39" s="4" t="s">
         <v>21</v>
@@ -2929,7 +2911,7 @@
         <v>240048</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>23</v>
@@ -2974,7 +2956,7 @@
         <v>6</v>
       </c>
       <c r="Q40" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R40" s="4" t="s">
         <v>21</v>
@@ -2985,7 +2967,7 @@
         <v>240060</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>23</v>
@@ -3030,7 +3012,7 @@
         <v>6</v>
       </c>
       <c r="Q41" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R41" s="4" t="s">
         <v>34</v>
@@ -3041,7 +3023,7 @@
         <v>2419</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>23</v>
@@ -3086,7 +3068,7 @@
         <v>6</v>
       </c>
       <c r="Q42" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R42" s="4" t="s">
         <v>21</v>
@@ -3097,7 +3079,7 @@
         <v>240058</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>23</v>
@@ -3142,7 +3124,7 @@
         <v>6</v>
       </c>
       <c r="Q43" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R43" s="4" t="s">
         <v>21</v>
@@ -3153,7 +3135,7 @@
         <v>289821</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>23</v>
@@ -3183,7 +3165,7 @@
         <v>4</v>
       </c>
       <c r="Q44" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R44" s="4" t="s">
         <v>21</v>
@@ -3194,7 +3176,7 @@
         <v>230305</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>23</v>
@@ -3239,7 +3221,7 @@
         <v>12</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R45" s="4" t="s">
         <v>21</v>
@@ -3250,7 +3232,7 @@
         <v>230307</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>23</v>
@@ -3295,7 +3277,7 @@
         <v>12</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R46" s="4" t="s">
         <v>21</v>
@@ -3306,7 +3288,7 @@
         <v>230306</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>23</v>
@@ -3351,7 +3333,7 @@
         <v>12</v>
       </c>
       <c r="Q47" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R47" s="4" t="s">
         <v>21</v>
@@ -3362,7 +3344,7 @@
         <v>230301</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>23</v>
@@ -3407,7 +3389,7 @@
         <v>12</v>
       </c>
       <c r="Q48" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R48" s="4" t="s">
         <v>21</v>
@@ -3418,7 +3400,7 @@
         <v>280037</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>23</v>
@@ -3463,7 +3445,7 @@
         <v>8</v>
       </c>
       <c r="Q49" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R49" s="4" t="s">
         <v>21</v>
@@ -3474,7 +3456,7 @@
         <v>2712</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>23</v>
@@ -3519,7 +3501,7 @@
         <v>6</v>
       </c>
       <c r="Q50" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R50" s="4" t="s">
         <v>21</v>
@@ -3530,7 +3512,7 @@
         <v>270018</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>23</v>
@@ -3575,7 +3557,7 @@
         <v>5</v>
       </c>
       <c r="Q51" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R51" s="4" t="s">
         <v>21</v>
@@ -3586,7 +3568,7 @@
         <v>270035</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>23</v>
@@ -3631,7 +3613,7 @@
         <v>6</v>
       </c>
       <c r="Q52" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R52" s="4" t="s">
         <v>21</v>
@@ -3642,7 +3624,7 @@
         <v>270029</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>23</v>
@@ -3687,7 +3669,7 @@
         <v>6</v>
       </c>
       <c r="Q53" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R53" s="4" t="s">
         <v>21</v>
@@ -3698,7 +3680,7 @@
         <v>212910</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>23</v>
@@ -3743,7 +3725,7 @@
         <v>5</v>
       </c>
       <c r="Q54" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R54" s="4" t="s">
         <v>21</v>
@@ -3754,7 +3736,7 @@
         <v>212876</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>23</v>
@@ -3799,7 +3781,7 @@
         <v>5</v>
       </c>
       <c r="Q55" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R55" s="4" t="s">
         <v>21</v>
@@ -3810,10 +3792,10 @@
         <v>221003</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D56" s="4">
         <v>0</v>
@@ -3855,7 +3837,7 @@
         <v>2</v>
       </c>
       <c r="Q56" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R56" s="4" t="s">
         <v>21</v>
@@ -3866,10 +3848,10 @@
         <v>220939</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D57" s="4">
         <v>1</v>
@@ -3911,7 +3893,7 @@
         <v>6</v>
       </c>
       <c r="Q57" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R57" s="4" t="s">
         <v>21</v>
@@ -3922,10 +3904,10 @@
         <v>221035</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D58" s="4">
         <v>0</v>
@@ -3967,7 +3949,7 @@
         <v>3</v>
       </c>
       <c r="Q58" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R58" s="4" t="s">
         <v>21</v>
@@ -3978,10 +3960,10 @@
         <v>220973</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D59" s="4">
         <v>0</v>
@@ -4023,7 +4005,7 @@
         <v>3</v>
       </c>
       <c r="Q59" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R59" s="4" t="s">
         <v>21</v>
@@ -4034,10 +4016,10 @@
         <v>220904</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D60" s="4">
         <v>1</v>
@@ -4079,7 +4061,7 @@
         <v>5</v>
       </c>
       <c r="Q60" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R60" s="4" t="s">
         <v>34</v>
@@ -4090,10 +4072,10 @@
         <v>220999</v>
       </c>
       <c r="B61" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="D61" s="4">
         <v>0</v>
@@ -4135,7 +4117,7 @@
         <v>2</v>
       </c>
       <c r="Q61" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R61" s="4" t="s">
         <v>21</v>
@@ -4818,19 +4800,10 @@
         <v>250111</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="D74" s="4">
-        <v>0</v>
-      </c>
-      <c r="E74" s="4">
-        <v>0</v>
-      </c>
-      <c r="F74" s="4">
-        <v>0</v>
       </c>
       <c r="G74" s="4">
         <v>0</v>
@@ -4874,7 +4847,7 @@
         <v>221003</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>24</v>
@@ -4919,7 +4892,7 @@
         <v>6</v>
       </c>
       <c r="Q75" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R75" s="4" t="s">
         <v>21</v>
@@ -4930,7 +4903,7 @@
         <v>220939</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>24</v>
@@ -4975,7 +4948,7 @@
         <v>6</v>
       </c>
       <c r="Q76" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R76" s="4" t="s">
         <v>21</v>
@@ -4986,7 +4959,7 @@
         <v>221035</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>24</v>
@@ -5031,7 +5004,7 @@
         <v>4</v>
       </c>
       <c r="Q77" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R77" s="4" t="s">
         <v>21</v>
@@ -5042,7 +5015,7 @@
         <v>220973</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>24</v>
@@ -5087,7 +5060,7 @@
         <v>6</v>
       </c>
       <c r="Q78" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R78" s="4" t="s">
         <v>21</v>
@@ -5098,7 +5071,7 @@
         <v>220904</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>24</v>
@@ -5143,7 +5116,7 @@
         <v>6</v>
       </c>
       <c r="Q79" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R79" s="4" t="s">
         <v>34</v>
@@ -5154,7 +5127,7 @@
         <v>220999</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>24</v>
@@ -5199,7 +5172,7 @@
         <v>4</v>
       </c>
       <c r="Q80" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R80" s="4" t="s">
         <v>21</v>
@@ -5210,7 +5183,7 @@
         <v>240035</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>24</v>
@@ -5255,7 +5228,7 @@
         <v>6</v>
       </c>
       <c r="Q81" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R81" s="4" t="s">
         <v>21</v>
@@ -5266,7 +5239,7 @@
         <v>2417</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>24</v>
@@ -5311,7 +5284,7 @@
         <v>6</v>
       </c>
       <c r="Q82" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R82" s="4" t="s">
         <v>21</v>
@@ -5322,7 +5295,7 @@
         <v>2425</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>24</v>
@@ -5367,7 +5340,7 @@
         <v>6</v>
       </c>
       <c r="Q83" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R83" s="4" t="s">
         <v>21</v>
@@ -5378,7 +5351,7 @@
         <v>240048</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>24</v>
@@ -5423,7 +5396,7 @@
         <v>6</v>
       </c>
       <c r="Q84" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R84" s="4" t="s">
         <v>21</v>
@@ -5434,7 +5407,7 @@
         <v>240060</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>24</v>
@@ -5479,7 +5452,7 @@
         <v>6</v>
       </c>
       <c r="Q85" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R85" s="4" t="s">
         <v>34</v>
@@ -5490,7 +5463,7 @@
         <v>2419</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>24</v>
@@ -5535,7 +5508,7 @@
         <v>6</v>
       </c>
       <c r="Q86" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R86" s="4" t="s">
         <v>21</v>
@@ -5546,7 +5519,7 @@
         <v>240058</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>24</v>
@@ -5591,7 +5564,7 @@
         <v>6</v>
       </c>
       <c r="Q87" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R87" s="4" t="s">
         <v>21</v>
@@ -5602,7 +5575,7 @@
         <v>289821</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>24</v>
@@ -5632,7 +5605,7 @@
         <v>4</v>
       </c>
       <c r="Q88" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R88" s="4" t="s">
         <v>21</v>
@@ -5643,7 +5616,7 @@
         <v>230305</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>24</v>
@@ -5688,7 +5661,7 @@
         <v>5</v>
       </c>
       <c r="Q89" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R89" s="4" t="s">
         <v>21</v>
@@ -5699,7 +5672,7 @@
         <v>230307</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>24</v>
@@ -5744,7 +5717,7 @@
         <v>5</v>
       </c>
       <c r="Q90" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R90" s="4" t="s">
         <v>21</v>
@@ -5755,7 +5728,7 @@
         <v>230306</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>24</v>
@@ -5800,7 +5773,7 @@
         <v>5</v>
       </c>
       <c r="Q91" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R91" s="4" t="s">
         <v>21</v>
@@ -5811,7 +5784,7 @@
         <v>230301</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>24</v>
@@ -5856,7 +5829,7 @@
         <v>5</v>
       </c>
       <c r="Q92" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R92" s="4" t="s">
         <v>21</v>
@@ -5867,7 +5840,7 @@
         <v>280037</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>24</v>
@@ -5912,7 +5885,7 @@
         <v>4</v>
       </c>
       <c r="Q93" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R93" s="4" t="s">
         <v>21</v>
@@ -5923,7 +5896,7 @@
         <v>2712</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>24</v>
@@ -5968,7 +5941,7 @@
         <v>6</v>
       </c>
       <c r="Q94" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R94" s="4" t="s">
         <v>21</v>
@@ -5979,7 +5952,7 @@
         <v>270018</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>24</v>
@@ -6024,7 +5997,7 @@
         <v>4</v>
       </c>
       <c r="Q95" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R95" s="4" t="s">
         <v>21</v>
@@ -6035,7 +6008,7 @@
         <v>270035</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>24</v>
@@ -6080,7 +6053,7 @@
         <v>6</v>
       </c>
       <c r="Q96" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R96" s="4" t="s">
         <v>21</v>
@@ -6091,7 +6064,7 @@
         <v>270029</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>24</v>
@@ -6136,7 +6109,7 @@
         <v>6</v>
       </c>
       <c r="Q97" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R97" s="4" t="s">
         <v>21</v>
@@ -6819,19 +6792,10 @@
         <v>250111</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="D110" s="4">
-        <v>0</v>
-      </c>
-      <c r="E110" s="4">
-        <v>0</v>
-      </c>
-      <c r="F110" s="4">
-        <v>0</v>
       </c>
       <c r="G110" s="4">
         <v>70000</v>
@@ -6875,7 +6839,7 @@
         <v>221003</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>19</v>
@@ -6920,7 +6884,7 @@
         <v>4999999</v>
       </c>
       <c r="Q111" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R111" s="4" t="s">
         <v>21</v>
@@ -6931,7 +6895,7 @@
         <v>220939</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>19</v>
@@ -6976,7 +6940,7 @@
         <v>12000000</v>
       </c>
       <c r="Q112" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R112" s="4" t="s">
         <v>21</v>
@@ -6987,7 +6951,7 @@
         <v>221035</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>19</v>
@@ -7032,7 +6996,7 @@
         <v>6000000</v>
       </c>
       <c r="Q113" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R113" s="4" t="s">
         <v>21</v>
@@ -7043,7 +7007,7 @@
         <v>220973</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>19</v>
@@ -7088,7 +7052,7 @@
         <v>6000001</v>
       </c>
       <c r="Q114" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R114" s="4" t="s">
         <v>21</v>
@@ -7099,7 +7063,7 @@
         <v>220904</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>19</v>
@@ -7144,7 +7108,7 @@
         <v>12000000</v>
       </c>
       <c r="Q115" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R115" s="4" t="s">
         <v>34</v>
@@ -7155,7 +7119,7 @@
         <v>220999</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>19</v>
@@ -7200,7 +7164,7 @@
         <v>3999999.9999999995</v>
       </c>
       <c r="Q116" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R116" s="4" t="s">
         <v>21</v>
@@ -7211,7 +7175,7 @@
         <v>240035</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>19</v>
@@ -7256,7 +7220,7 @@
         <v>6000002</v>
       </c>
       <c r="Q117" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R117" s="4" t="s">
         <v>21</v>
@@ -7267,7 +7231,7 @@
         <v>2417</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>19</v>
@@ -7312,7 +7276,7 @@
         <v>4500000</v>
       </c>
       <c r="Q118" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R118" s="4" t="s">
         <v>21</v>
@@ -7323,7 +7287,7 @@
         <v>2425</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>19</v>
@@ -7368,7 +7332,7 @@
         <v>4500000</v>
       </c>
       <c r="Q119" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R119" s="4" t="s">
         <v>21</v>
@@ -7379,7 +7343,7 @@
         <v>240048</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>19</v>
@@ -7424,7 +7388,7 @@
         <v>2500000</v>
       </c>
       <c r="Q120" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R120" s="4" t="s">
         <v>21</v>
@@ -7435,7 +7399,7 @@
         <v>240060</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>19</v>
@@ -7480,7 +7444,7 @@
         <v>1200002</v>
       </c>
       <c r="Q121" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R121" s="4" t="s">
         <v>34</v>
@@ -7491,7 +7455,7 @@
         <v>2419</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>19</v>
@@ -7536,7 +7500,7 @@
         <v>3500001</v>
       </c>
       <c r="Q122" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R122" s="4" t="s">
         <v>21</v>
@@ -7547,7 +7511,7 @@
         <v>240058</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>19</v>
@@ -7592,7 +7556,7 @@
         <v>2399999</v>
       </c>
       <c r="Q123" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R123" s="4" t="s">
         <v>21</v>
@@ -7603,7 +7567,7 @@
         <v>289821</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>19</v>
@@ -7633,7 +7597,7 @@
         <v>735630</v>
       </c>
       <c r="Q124" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R124" s="4" t="s">
         <v>21</v>
@@ -7644,7 +7608,7 @@
         <v>230305</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>19</v>
@@ -7689,7 +7653,7 @@
         <v>4499999</v>
       </c>
       <c r="Q125" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R125" s="4" t="s">
         <v>21</v>
@@ -7700,7 +7664,7 @@
         <v>230307</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>19</v>
@@ -7745,7 +7709,7 @@
         <v>4499999</v>
       </c>
       <c r="Q126" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R126" s="4" t="s">
         <v>21</v>
@@ -7756,7 +7720,7 @@
         <v>230306</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>19</v>
@@ -7801,7 +7765,7 @@
         <v>4499999</v>
       </c>
       <c r="Q127" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R127" s="4" t="s">
         <v>21</v>
@@ -7812,7 +7776,7 @@
         <v>230301</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>19</v>
@@ -7857,7 +7821,7 @@
         <v>4499999</v>
       </c>
       <c r="Q128" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R128" s="4" t="s">
         <v>21</v>
@@ -7868,7 +7832,7 @@
         <v>280037</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>19</v>
@@ -7913,7 +7877,7 @@
         <v>1350000</v>
       </c>
       <c r="Q129" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R129" s="4" t="s">
         <v>21</v>
@@ -7924,7 +7888,7 @@
         <v>2712</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>19</v>
@@ -7969,7 +7933,7 @@
         <v>2200000</v>
       </c>
       <c r="Q130" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R130" s="4" t="s">
         <v>21</v>
@@ -7980,7 +7944,7 @@
         <v>270018</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>19</v>
@@ -8025,7 +7989,7 @@
         <v>1500000</v>
       </c>
       <c r="Q131" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R131" s="4" t="s">
         <v>21</v>
@@ -8036,7 +8000,7 @@
         <v>270035</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>19</v>
@@ -8081,7 +8045,7 @@
         <v>1700000</v>
       </c>
       <c r="Q132" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R132" s="4" t="s">
         <v>21</v>
@@ -8092,7 +8056,7 @@
         <v>270029</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>19</v>
@@ -8137,7 +8101,7 @@
         <v>1700000</v>
       </c>
       <c r="Q133" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R133" s="4" t="s">
         <v>21</v>
@@ -8148,7 +8112,7 @@
         <v>212910</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>19</v>
@@ -8193,7 +8157,7 @@
         <v>2000000</v>
       </c>
       <c r="Q134" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R134" s="4" t="s">
         <v>21</v>
@@ -8204,7 +8168,7 @@
         <v>212876</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>19</v>
@@ -8249,7 +8213,7 @@
         <v>2000000</v>
       </c>
       <c r="Q135" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R135" s="4" t="s">
         <v>21</v>
@@ -8260,10 +8224,10 @@
         <v>221003</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D136" s="4">
         <v>0</v>
@@ -8305,7 +8269,7 @@
         <v>1</v>
       </c>
       <c r="Q136" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R136" s="4" t="s">
         <v>21</v>
@@ -8316,10 +8280,10 @@
         <v>220939</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D137" s="4">
         <v>0</v>
@@ -8361,7 +8325,7 @@
         <v>3</v>
       </c>
       <c r="Q137" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R137" s="4" t="s">
         <v>21</v>
@@ -8372,10 +8336,10 @@
         <v>221035</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D138" s="4">
         <v>0</v>
@@ -8417,7 +8381,7 @@
         <v>2</v>
       </c>
       <c r="Q138" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R138" s="4" t="s">
         <v>21</v>
@@ -8428,10 +8392,10 @@
         <v>220973</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D139" s="4">
         <v>0</v>
@@ -8473,7 +8437,7 @@
         <v>2</v>
       </c>
       <c r="Q139" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R139" s="4" t="s">
         <v>21</v>
@@ -8484,10 +8448,10 @@
         <v>220904</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D140" s="4">
         <v>0</v>
@@ -8529,7 +8493,7 @@
         <v>3</v>
       </c>
       <c r="Q140" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R140" s="4" t="s">
         <v>34</v>
@@ -8540,10 +8504,10 @@
         <v>220999</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D141" s="4">
         <v>0</v>
@@ -8585,7 +8549,7 @@
         <v>1</v>
       </c>
       <c r="Q141" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R141" s="4" t="s">
         <v>21</v>
@@ -9044,19 +9008,10 @@
         <v>250111</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="D150" s="4">
-        <v>0</v>
-      </c>
-      <c r="E150" s="4">
-        <v>0</v>
-      </c>
-      <c r="F150" s="4">
-        <v>0</v>
       </c>
       <c r="G150" s="4">
         <v>0</v>
@@ -9100,7 +9055,7 @@
         <v>280037</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>25</v>
@@ -9145,7 +9100,7 @@
         <v>1</v>
       </c>
       <c r="Q151" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R151" s="4" t="s">
         <v>21</v>
@@ -9604,19 +9559,10 @@
         <v>250111</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="D160" s="4">
-        <v>0</v>
-      </c>
-      <c r="E160" s="4">
-        <v>0</v>
-      </c>
-      <c r="F160" s="4">
-        <v>0</v>
       </c>
       <c r="G160" s="4">
         <v>0</v>
@@ -9660,7 +9606,7 @@
         <v>280037</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>26</v>
@@ -9705,7 +9651,7 @@
         <v>2</v>
       </c>
       <c r="Q161" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R161" s="4" t="s">
         <v>21</v>
@@ -10164,19 +10110,10 @@
         <v>250111</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="D170" s="4">
-        <v>0</v>
-      </c>
-      <c r="E170" s="4">
-        <v>0</v>
-      </c>
-      <c r="F170" s="4">
-        <v>0</v>
       </c>
       <c r="G170" s="4">
         <v>0</v>
@@ -10220,7 +10157,7 @@
         <v>280037</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>27</v>
@@ -10265,7 +10202,7 @@
         <v>1</v>
       </c>
       <c r="Q171" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R171" s="4" t="s">
         <v>21</v>
@@ -10948,19 +10885,10 @@
         <v>250111</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="D184" s="4">
-        <v>0</v>
-      </c>
-      <c r="E184" s="4">
-        <v>0</v>
-      </c>
-      <c r="F184" s="4">
-        <v>0</v>
       </c>
       <c r="G184" s="4">
         <v>1</v>
@@ -11004,7 +10932,7 @@
         <v>221003</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>28</v>
@@ -11049,7 +10977,7 @@
         <v>29</v>
       </c>
       <c r="Q185" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R185" s="4" t="s">
         <v>21</v>
@@ -11060,7 +10988,7 @@
         <v>220939</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>28</v>
@@ -11105,7 +11033,7 @@
         <v>70</v>
       </c>
       <c r="Q186" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R186" s="4" t="s">
         <v>21</v>
@@ -11116,7 +11044,7 @@
         <v>221035</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>28</v>
@@ -11161,7 +11089,7 @@
         <v>35</v>
       </c>
       <c r="Q187" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R187" s="4" t="s">
         <v>21</v>
@@ -11172,7 +11100,7 @@
         <v>220973</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>28</v>
@@ -11217,7 +11145,7 @@
         <v>40</v>
       </c>
       <c r="Q188" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R188" s="4" t="s">
         <v>21</v>
@@ -11228,7 +11156,7 @@
         <v>220904</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>28</v>
@@ -11273,7 +11201,7 @@
         <v>70</v>
       </c>
       <c r="Q189" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R189" s="4" t="s">
         <v>34</v>
@@ -11284,7 +11212,7 @@
         <v>220999</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>28</v>
@@ -11329,7 +11257,7 @@
         <v>25</v>
       </c>
       <c r="Q190" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R190" s="4" t="s">
         <v>21</v>
@@ -11340,7 +11268,7 @@
         <v>240035</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>28</v>
@@ -11385,7 +11313,7 @@
         <v>60</v>
       </c>
       <c r="Q191" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R191" s="4" t="s">
         <v>21</v>
@@ -11396,7 +11324,7 @@
         <v>2417</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>28</v>
@@ -11441,7 +11369,7 @@
         <v>50</v>
       </c>
       <c r="Q192" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R192" s="4" t="s">
         <v>21</v>
@@ -11452,7 +11380,7 @@
         <v>2425</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>28</v>
@@ -11497,7 +11425,7 @@
         <v>40</v>
       </c>
       <c r="Q193" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R193" s="4" t="s">
         <v>21</v>
@@ -11508,7 +11436,7 @@
         <v>240048</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>28</v>
@@ -11553,7 +11481,7 @@
         <v>15</v>
       </c>
       <c r="Q194" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R194" s="4" t="s">
         <v>21</v>
@@ -11564,7 +11492,7 @@
         <v>230305</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>28</v>
@@ -11609,7 +11537,7 @@
         <v>27</v>
       </c>
       <c r="Q195" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R195" s="4" t="s">
         <v>21</v>
@@ -11620,7 +11548,7 @@
         <v>230307</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C196" s="4" t="s">
         <v>28</v>
@@ -11665,7 +11593,7 @@
         <v>23</v>
       </c>
       <c r="Q196" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R196" s="4" t="s">
         <v>21</v>
@@ -11676,7 +11604,7 @@
         <v>230306</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>28</v>
@@ -11721,7 +11649,7 @@
         <v>27</v>
       </c>
       <c r="Q197" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R197" s="4" t="s">
         <v>21</v>
@@ -11732,7 +11660,7 @@
         <v>230301</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>28</v>
@@ -11777,7 +11705,7 @@
         <v>27</v>
       </c>
       <c r="Q198" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R198" s="4" t="s">
         <v>21</v>
@@ -11788,7 +11716,7 @@
         <v>280037</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>28</v>
@@ -11833,7 +11761,7 @@
         <v>12</v>
       </c>
       <c r="Q199" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R199" s="4" t="s">
         <v>21</v>
@@ -11844,7 +11772,7 @@
         <v>2712</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>28</v>
@@ -11889,7 +11817,7 @@
         <v>20</v>
       </c>
       <c r="Q200" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R200" s="4" t="s">
         <v>21</v>
@@ -11900,7 +11828,7 @@
         <v>270018</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>28</v>
@@ -11945,7 +11873,7 @@
         <v>10</v>
       </c>
       <c r="Q201" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R201" s="4" t="s">
         <v>21</v>
@@ -11956,7 +11884,7 @@
         <v>270035</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C202" s="4" t="s">
         <v>28</v>
@@ -12001,7 +11929,7 @@
         <v>13</v>
       </c>
       <c r="Q202" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R202" s="4" t="s">
         <v>21</v>
@@ -12012,7 +11940,7 @@
         <v>270029</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C203" s="4" t="s">
         <v>28</v>
@@ -12057,7 +11985,7 @@
         <v>13</v>
       </c>
       <c r="Q203" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R203" s="4" t="s">
         <v>21</v>
@@ -12068,7 +11996,7 @@
         <v>212910</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>28</v>
@@ -12113,7 +12041,7 @@
         <v>17</v>
       </c>
       <c r="Q204" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R204" s="4" t="s">
         <v>21</v>
@@ -12124,7 +12052,7 @@
         <v>212876</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>28</v>
@@ -12169,7 +12097,7 @@
         <v>38</v>
       </c>
       <c r="Q205" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R205" s="4" t="s">
         <v>21</v>
@@ -12180,7 +12108,7 @@
         <v>240060</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>28</v>
@@ -12225,7 +12153,7 @@
         <v>15</v>
       </c>
       <c r="Q206" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R206" s="4" t="s">
         <v>34</v>
@@ -12236,7 +12164,7 @@
         <v>2419</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C207" s="4" t="s">
         <v>28</v>
@@ -12281,7 +12209,7 @@
         <v>40</v>
       </c>
       <c r="Q207" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R207" s="4" t="s">
         <v>21</v>
@@ -12292,7 +12220,7 @@
         <v>240058</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>28</v>
@@ -12337,7 +12265,7 @@
         <v>30</v>
       </c>
       <c r="Q208" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R208" s="4" t="s">
         <v>21</v>
@@ -12348,7 +12276,7 @@
         <v>289821</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>28</v>
@@ -12378,7 +12306,7 @@
         <v>10</v>
       </c>
       <c r="Q209" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R209" s="4" t="s">
         <v>21</v>
@@ -12837,19 +12765,10 @@
         <v>250111</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="D218" s="4">
-        <v>0</v>
-      </c>
-      <c r="E218" s="4">
-        <v>0</v>
-      </c>
-      <c r="F218" s="4">
-        <v>0</v>
       </c>
       <c r="G218" s="4">
         <v>0</v>
@@ -12893,7 +12812,7 @@
         <v>280037</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C219" s="4" t="s">
         <v>29</v>
@@ -12938,7 +12857,7 @@
         <v>1600000</v>
       </c>
       <c r="Q219" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R219" s="4" t="s">
         <v>21</v>
@@ -13285,19 +13204,10 @@
         <v>250111</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C226" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="D226" s="4">
-        <v>0</v>
-      </c>
-      <c r="E226" s="4">
-        <v>0</v>
-      </c>
-      <c r="F226" s="4">
-        <v>0</v>
       </c>
       <c r="G226" s="4">
         <v>0</v>
@@ -13341,7 +13251,7 @@
         <v>221003</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>39</v>
@@ -13386,7 +13296,7 @@
         <v>6</v>
       </c>
       <c r="Q227" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R227" s="4" t="s">
         <v>21</v>
@@ -13397,7 +13307,7 @@
         <v>220939</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C228" s="4" t="s">
         <v>39</v>
@@ -13442,7 +13352,7 @@
         <v>6</v>
       </c>
       <c r="Q228" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R228" s="4" t="s">
         <v>21</v>
@@ -13453,7 +13363,7 @@
         <v>221035</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C229" s="4" t="s">
         <v>39</v>
@@ -13498,7 +13408,7 @@
         <v>5</v>
       </c>
       <c r="Q229" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R229" s="4" t="s">
         <v>21</v>
@@ -13509,7 +13419,7 @@
         <v>220973</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>39</v>
@@ -13554,7 +13464,7 @@
         <v>6</v>
       </c>
       <c r="Q230" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R230" s="4" t="s">
         <v>21</v>
@@ -13565,7 +13475,7 @@
         <v>220904</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>39</v>
@@ -13610,7 +13520,7 @@
         <v>6</v>
       </c>
       <c r="Q231" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R231" s="4" t="s">
         <v>34</v>
@@ -13621,7 +13531,7 @@
         <v>220999</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>39</v>
@@ -13666,7 +13576,7 @@
         <v>3</v>
       </c>
       <c r="Q232" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R232" s="4" t="s">
         <v>21</v>
@@ -13677,7 +13587,7 @@
         <v>230305</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>39</v>
@@ -13722,7 +13632,7 @@
         <v>5</v>
       </c>
       <c r="Q233" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R233" s="4" t="s">
         <v>21</v>
@@ -13733,7 +13643,7 @@
         <v>230307</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>39</v>
@@ -13778,7 +13688,7 @@
         <v>5</v>
       </c>
       <c r="Q234" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R234" s="4" t="s">
         <v>21</v>
@@ -13789,7 +13699,7 @@
         <v>230306</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C235" s="4" t="s">
         <v>39</v>
@@ -13834,7 +13744,7 @@
         <v>5</v>
       </c>
       <c r="Q235" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R235" s="4" t="s">
         <v>21</v>
@@ -13845,7 +13755,7 @@
         <v>230301</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C236" s="4" t="s">
         <v>39</v>
@@ -13890,7 +13800,7 @@
         <v>5</v>
       </c>
       <c r="Q236" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R236" s="4" t="s">
         <v>21</v>
@@ -13901,7 +13811,7 @@
         <v>2712</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>39</v>
@@ -13946,7 +13856,7 @@
         <v>4</v>
       </c>
       <c r="Q237" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R237" s="4" t="s">
         <v>21</v>
@@ -13957,7 +13867,7 @@
         <v>270018</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>39</v>
@@ -14002,7 +13912,7 @@
         <v>4</v>
       </c>
       <c r="Q238" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R238" s="4" t="s">
         <v>21</v>
@@ -14013,7 +13923,7 @@
         <v>270035</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>39</v>
@@ -14058,7 +13968,7 @@
         <v>4</v>
       </c>
       <c r="Q239" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R239" s="4" t="s">
         <v>21</v>
@@ -14069,7 +13979,7 @@
         <v>270029</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C240" s="4" t="s">
         <v>39</v>
@@ -14114,18 +14024,14 @@
         <v>4</v>
       </c>
       <c r="Q240" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R240" s="4" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R240" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R240">
-      <sortCondition ref="C1:C240"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:R240" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14144,7 +14050,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -14192,7 +14098,7 @@
         <v>16</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -14200,7 +14106,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>28</v>
@@ -14245,10 +14151,10 @@
         <v>56</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -14256,7 +14162,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>19</v>
@@ -14301,10 +14207,10 @@
         <v>7100000</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -14312,7 +14218,7 @@
         <v>18</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>39</v>
@@ -14357,10 +14263,10 @@
         <v>16</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -14368,7 +14274,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>24</v>
@@ -14413,10 +14319,10 @@
         <v>22</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -14424,7 +14330,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>23</v>
@@ -14469,10 +14375,10 @@
         <v>23</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -14480,7 +14386,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>28</v>
@@ -14525,10 +14431,10 @@
         <v>104</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -14536,7 +14442,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>19</v>
@@ -14581,10 +14487,10 @@
         <v>17999996</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -14592,7 +14498,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>39</v>
@@ -14637,10 +14543,10 @@
         <v>20</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -14648,7 +14554,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>24</v>
@@ -14693,10 +14599,10 @@
         <v>20</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -14704,7 +14610,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>23</v>
@@ -14749,10 +14655,10 @@
         <v>48</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -14760,7 +14666,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>28</v>
@@ -14805,10 +14711,10 @@
         <v>250</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -14816,7 +14722,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>19</v>
@@ -14861,10 +14767,10 @@
         <v>24600004</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -14872,7 +14778,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>24</v>
@@ -14917,10 +14823,10 @@
         <v>42</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -14928,7 +14834,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>23</v>
@@ -14973,10 +14879,10 @@
         <v>42</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -14984,7 +14890,7 @@
         <v>34</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>28</v>
@@ -15032,7 +14938,7 @@
         <v>32</v>
       </c>
       <c r="R16" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -15040,7 +14946,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>19</v>
@@ -15088,7 +14994,7 @@
         <v>32</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -15096,7 +15002,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>24</v>
@@ -15144,7 +15050,7 @@
         <v>32</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -15152,7 +15058,7 @@
         <v>34</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>23</v>
@@ -15200,7 +15106,7 @@
         <v>32</v>
       </c>
       <c r="R19" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -15208,7 +15114,7 @@
         <v>9</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>28</v>
@@ -15253,10 +15159,10 @@
         <v>269</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R20" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -15264,10 +15170,10 @@
         <v>9</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="5">
         <v>2</v>
@@ -15309,10 +15215,10 @@
         <v>21</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R21" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -15320,10 +15226,10 @@
         <v>9</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22" s="5">
         <v>11</v>
@@ -15365,10 +15271,10 @@
         <v>123</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -15376,10 +15282,10 @@
         <v>9</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D23" s="5">
         <v>0</v>
@@ -15421,10 +15327,10 @@
         <v>12</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R23" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -15432,7 +15338,7 @@
         <v>9</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>19</v>
@@ -15477,10 +15383,10 @@
         <v>45000000</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R24" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -15488,7 +15394,7 @@
         <v>9</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>39</v>
@@ -15533,10 +15439,10 @@
         <v>32</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R25" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -15544,7 +15450,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>24</v>
@@ -15589,10 +15495,10 @@
         <v>32</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R26" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -15600,7 +15506,7 @@
         <v>9</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>23</v>
@@ -15645,10 +15551,10 @@
         <v>36</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R27" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -15656,7 +15562,7 @@
         <v>19</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>28</v>
@@ -15704,7 +15610,7 @@
         <v>20</v>
       </c>
       <c r="R28" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -15712,7 +15618,7 @@
         <v>19</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>25</v>
@@ -15760,7 +15666,7 @@
         <v>20</v>
       </c>
       <c r="R29" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -15768,7 +15674,7 @@
         <v>19</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>22</v>
@@ -15816,7 +15722,7 @@
         <v>20</v>
       </c>
       <c r="R30" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -15824,7 +15730,7 @@
         <v>19</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>27</v>
@@ -15872,7 +15778,7 @@
         <v>20</v>
       </c>
       <c r="R31" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -15880,7 +15786,7 @@
         <v>19</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>26</v>
@@ -15928,7 +15834,7 @@
         <v>20</v>
       </c>
       <c r="R32" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -15936,7 +15842,7 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>24</v>
@@ -15984,7 +15890,7 @@
         <v>20</v>
       </c>
       <c r="R33" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -15992,7 +15898,7 @@
         <v>19</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>29</v>
@@ -16040,7 +15946,7 @@
         <v>20</v>
       </c>
       <c r="R34" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -16048,7 +15954,7 @@
         <v>19</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>19</v>
@@ -16096,7 +16002,7 @@
         <v>20</v>
       </c>
       <c r="R35" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -16104,7 +16010,7 @@
         <v>19</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>23</v>
@@ -16152,7 +16058,7 @@
         <v>20</v>
       </c>
       <c r="R36" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -16160,7 +16066,7 @@
         <v>19</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>39</v>
@@ -16208,7 +16114,7 @@
         <v>20</v>
       </c>
       <c r="R37" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -16216,7 +16122,7 @@
         <v>17</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>28</v>
@@ -16264,7 +16170,7 @@
         <v>38</v>
       </c>
       <c r="R38" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -16272,7 +16178,7 @@
         <v>17</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>25</v>
@@ -16320,7 +16226,7 @@
         <v>38</v>
       </c>
       <c r="R39" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -16328,7 +16234,7 @@
         <v>17</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>22</v>
@@ -16376,7 +16282,7 @@
         <v>38</v>
       </c>
       <c r="R40" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -16384,7 +16290,7 @@
         <v>17</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>27</v>
@@ -16432,7 +16338,7 @@
         <v>38</v>
       </c>
       <c r="R41" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -16440,7 +16346,7 @@
         <v>17</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>26</v>
@@ -16488,7 +16394,7 @@
         <v>38</v>
       </c>
       <c r="R42" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -16496,7 +16402,7 @@
         <v>17</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>24</v>
@@ -16544,7 +16450,7 @@
         <v>38</v>
       </c>
       <c r="R43" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -16552,7 +16458,7 @@
         <v>17</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>29</v>
@@ -16600,7 +16506,7 @@
         <v>38</v>
       </c>
       <c r="R44" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -16608,7 +16514,7 @@
         <v>17</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>19</v>
@@ -16656,7 +16562,7 @@
         <v>38</v>
       </c>
       <c r="R45" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -16664,7 +16570,7 @@
         <v>17</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>39</v>
@@ -16712,7 +16618,7 @@
         <v>38</v>
       </c>
       <c r="R46" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -16720,7 +16626,7 @@
         <v>17</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>23</v>
@@ -16768,7 +16674,7 @@
         <v>38</v>
       </c>
       <c r="R47" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
@@ -16776,7 +16682,7 @@
         <v>30</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>28</v>
@@ -16821,10 +16727,10 @@
         <v>12</v>
       </c>
       <c r="Q48" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R48" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
@@ -16832,7 +16738,7 @@
         <v>30</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>25</v>
@@ -16877,10 +16783,10 @@
         <v>1</v>
       </c>
       <c r="Q49" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R49" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
@@ -16888,7 +16794,7 @@
         <v>30</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>22</v>
@@ -16933,10 +16839,10 @@
         <v>1</v>
       </c>
       <c r="Q50" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R50" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -16944,7 +16850,7 @@
         <v>30</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>27</v>
@@ -16989,10 +16895,10 @@
         <v>1</v>
       </c>
       <c r="Q51" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R51" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
@@ -17000,7 +16906,7 @@
         <v>30</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>26</v>
@@ -17045,10 +16951,10 @@
         <v>2</v>
       </c>
       <c r="Q52" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R52" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
@@ -17056,7 +16962,7 @@
         <v>30</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>24</v>
@@ -17101,10 +17007,10 @@
         <v>4</v>
       </c>
       <c r="Q53" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R53" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
@@ -17112,7 +17018,7 @@
         <v>30</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>29</v>
@@ -17157,10 +17063,10 @@
         <v>1600000</v>
       </c>
       <c r="Q54" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R54" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
@@ -17168,7 +17074,7 @@
         <v>30</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>19</v>
@@ -17213,10 +17119,10 @@
         <v>1350000</v>
       </c>
       <c r="Q55" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R55" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
@@ -17224,7 +17130,7 @@
         <v>30</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>23</v>
@@ -17269,10 +17175,10 @@
         <v>8</v>
       </c>
       <c r="Q56" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R56" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -17280,7 +17186,7 @@
         <v>30</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>39</v>
@@ -17325,10 +17231,10 @@
         <v>0</v>
       </c>
       <c r="Q57" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R57" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
@@ -17336,7 +17242,7 @@
         <v>11</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>28</v>
@@ -17381,10 +17287,10 @@
         <v>55</v>
       </c>
       <c r="Q58" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R58" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
@@ -17392,7 +17298,7 @@
         <v>11</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>19</v>
@@ -17437,10 +17343,10 @@
         <v>4000000</v>
       </c>
       <c r="Q59" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R59" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
@@ -17448,7 +17354,7 @@
         <v>11</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>23</v>
@@ -17493,10 +17399,10 @@
         <v>10</v>
       </c>
       <c r="Q60" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R60" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
@@ -19839,7 +19745,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -19887,7 +19793,7 @@
         <v>16</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -19895,7 +19801,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>28</v>
@@ -19914,10 +19820,10 @@
       <c r="O2" s="9"/>
       <c r="P2" s="10"/>
       <c r="Q2" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -19925,7 +19831,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>19</v>
@@ -19944,10 +19850,10 @@
       <c r="O3" s="9"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -19955,7 +19861,7 @@
         <v>18</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>39</v>
@@ -19974,10 +19880,10 @@
       <c r="O4" s="9"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R4" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -19985,7 +19891,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>24</v>
@@ -20004,10 +19910,10 @@
       <c r="O5" s="9"/>
       <c r="P5" s="10"/>
       <c r="Q5" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R5" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -20015,7 +19921,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>23</v>
@@ -20034,10 +19940,10 @@
       <c r="O6" s="9"/>
       <c r="P6" s="10"/>
       <c r="Q6" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R6" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -20045,7 +19951,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>28</v>
@@ -20064,10 +19970,10 @@
       <c r="O7" s="5"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -20075,7 +19981,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>19</v>
@@ -20094,10 +20000,10 @@
       <c r="O8" s="5"/>
       <c r="P8" s="6"/>
       <c r="Q8" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -20105,7 +20011,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>39</v>
@@ -20124,10 +20030,10 @@
       <c r="O9" s="5"/>
       <c r="P9" s="6"/>
       <c r="Q9" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -20135,7 +20041,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>24</v>
@@ -20154,10 +20060,10 @@
       <c r="O10" s="5"/>
       <c r="P10" s="6"/>
       <c r="Q10" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -20165,7 +20071,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>23</v>
@@ -20184,10 +20090,10 @@
       <c r="O11" s="5"/>
       <c r="P11" s="6"/>
       <c r="Q11" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -20195,7 +20101,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>28</v>
@@ -20214,10 +20120,10 @@
       <c r="O12" s="9"/>
       <c r="P12" s="10"/>
       <c r="Q12" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R12" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -20225,7 +20131,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>19</v>
@@ -20244,10 +20150,10 @@
       <c r="O13" s="9"/>
       <c r="P13" s="10"/>
       <c r="Q13" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R13" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -20255,7 +20161,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>24</v>
@@ -20274,10 +20180,10 @@
       <c r="O14" s="9"/>
       <c r="P14" s="10"/>
       <c r="Q14" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R14" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -20285,7 +20191,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>23</v>
@@ -20304,10 +20210,10 @@
       <c r="O15" s="9"/>
       <c r="P15" s="10"/>
       <c r="Q15" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R15" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -20315,7 +20221,7 @@
         <v>34</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>28</v>
@@ -20337,7 +20243,7 @@
         <v>32</v>
       </c>
       <c r="R16" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -20345,7 +20251,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>19</v>
@@ -20367,7 +20273,7 @@
         <v>32</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -20375,7 +20281,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>24</v>
@@ -20397,7 +20303,7 @@
         <v>32</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -20405,7 +20311,7 @@
         <v>34</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>23</v>
@@ -20427,7 +20333,7 @@
         <v>32</v>
       </c>
       <c r="R19" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -20435,7 +20341,7 @@
         <v>9</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>28</v>
@@ -20454,10 +20360,10 @@
       <c r="O20" s="9"/>
       <c r="P20" s="10"/>
       <c r="Q20" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R20" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -20465,10 +20371,10 @@
         <v>9</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
@@ -20484,10 +20390,10 @@
       <c r="O21" s="9"/>
       <c r="P21" s="10"/>
       <c r="Q21" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R21" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -20495,10 +20401,10 @@
         <v>9</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
@@ -20514,10 +20420,10 @@
       <c r="O22" s="9"/>
       <c r="P22" s="10"/>
       <c r="Q22" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R22" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -20525,10 +20431,10 @@
         <v>9</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
@@ -20544,10 +20450,10 @@
       <c r="O23" s="9"/>
       <c r="P23" s="10"/>
       <c r="Q23" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R23" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -20555,7 +20461,7 @@
         <v>9</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>19</v>
@@ -20574,10 +20480,10 @@
       <c r="O24" s="9"/>
       <c r="P24" s="10"/>
       <c r="Q24" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R24" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -20585,7 +20491,7 @@
         <v>9</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>39</v>
@@ -20604,10 +20510,10 @@
       <c r="O25" s="9"/>
       <c r="P25" s="10"/>
       <c r="Q25" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R25" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -20615,7 +20521,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>24</v>
@@ -20634,10 +20540,10 @@
       <c r="O26" s="9"/>
       <c r="P26" s="10"/>
       <c r="Q26" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R26" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -20645,7 +20551,7 @@
         <v>9</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>23</v>
@@ -20664,10 +20570,10 @@
       <c r="O27" s="9"/>
       <c r="P27" s="10"/>
       <c r="Q27" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R27" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -20675,7 +20581,7 @@
         <v>19</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>28</v>
@@ -20697,7 +20603,7 @@
         <v>20</v>
       </c>
       <c r="R28" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -20705,7 +20611,7 @@
         <v>19</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>25</v>
@@ -20727,7 +20633,7 @@
         <v>20</v>
       </c>
       <c r="R29" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -20735,7 +20641,7 @@
         <v>19</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>22</v>
@@ -20757,7 +20663,7 @@
         <v>20</v>
       </c>
       <c r="R30" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -20765,7 +20671,7 @@
         <v>19</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>27</v>
@@ -20787,7 +20693,7 @@
         <v>20</v>
       </c>
       <c r="R31" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -20795,7 +20701,7 @@
         <v>19</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>26</v>
@@ -20817,7 +20723,7 @@
         <v>20</v>
       </c>
       <c r="R32" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -20825,7 +20731,7 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>24</v>
@@ -20847,7 +20753,7 @@
         <v>20</v>
       </c>
       <c r="R33" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -20855,7 +20761,7 @@
         <v>19</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>29</v>
@@ -20877,7 +20783,7 @@
         <v>20</v>
       </c>
       <c r="R34" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -20885,7 +20791,7 @@
         <v>19</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>19</v>
@@ -20907,7 +20813,7 @@
         <v>20</v>
       </c>
       <c r="R35" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -20915,7 +20821,7 @@
         <v>19</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>23</v>
@@ -20937,7 +20843,7 @@
         <v>20</v>
       </c>
       <c r="R36" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -20945,7 +20851,7 @@
         <v>19</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>39</v>
@@ -20967,7 +20873,7 @@
         <v>20</v>
       </c>
       <c r="R37" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
@@ -20975,7 +20881,7 @@
         <v>17</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>28</v>
@@ -20997,7 +20903,7 @@
         <v>38</v>
       </c>
       <c r="R38" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
@@ -21005,7 +20911,7 @@
         <v>17</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>25</v>
@@ -21027,7 +20933,7 @@
         <v>38</v>
       </c>
       <c r="R39" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -21035,7 +20941,7 @@
         <v>17</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>22</v>
@@ -21057,7 +20963,7 @@
         <v>38</v>
       </c>
       <c r="R40" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -21065,7 +20971,7 @@
         <v>17</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>27</v>
@@ -21087,7 +20993,7 @@
         <v>38</v>
       </c>
       <c r="R41" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -21095,7 +21001,7 @@
         <v>17</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>26</v>
@@ -21117,7 +21023,7 @@
         <v>38</v>
       </c>
       <c r="R42" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
@@ -21125,7 +21031,7 @@
         <v>17</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>24</v>
@@ -21147,7 +21053,7 @@
         <v>38</v>
       </c>
       <c r="R43" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
@@ -21155,7 +21061,7 @@
         <v>17</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>29</v>
@@ -21177,7 +21083,7 @@
         <v>38</v>
       </c>
       <c r="R44" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -21185,7 +21091,7 @@
         <v>17</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>19</v>
@@ -21207,7 +21113,7 @@
         <v>38</v>
       </c>
       <c r="R45" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -21215,7 +21121,7 @@
         <v>17</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>39</v>
@@ -21237,7 +21143,7 @@
         <v>38</v>
       </c>
       <c r="R46" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -21245,7 +21151,7 @@
         <v>17</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>23</v>
@@ -21267,7 +21173,7 @@
         <v>38</v>
       </c>
       <c r="R47" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
@@ -21275,7 +21181,7 @@
         <v>30</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>28</v>
@@ -21294,10 +21200,10 @@
       <c r="O48" s="5"/>
       <c r="P48" s="6"/>
       <c r="Q48" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R48" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
@@ -21305,7 +21211,7 @@
         <v>30</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>25</v>
@@ -21324,10 +21230,10 @@
       <c r="O49" s="7"/>
       <c r="P49" s="6"/>
       <c r="Q49" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R49" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
@@ -21335,7 +21241,7 @@
         <v>30</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>22</v>
@@ -21354,10 +21260,10 @@
       <c r="O50" s="5"/>
       <c r="P50" s="6"/>
       <c r="Q50" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R50" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -21365,7 +21271,7 @@
         <v>30</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>27</v>
@@ -21384,10 +21290,10 @@
       <c r="O51" s="5"/>
       <c r="P51" s="6"/>
       <c r="Q51" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R51" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
@@ -21395,7 +21301,7 @@
         <v>30</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>26</v>
@@ -21414,10 +21320,10 @@
       <c r="O52" s="5"/>
       <c r="P52" s="6"/>
       <c r="Q52" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R52" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
@@ -21425,7 +21331,7 @@
         <v>30</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>24</v>
@@ -21444,10 +21350,10 @@
       <c r="O53" s="7"/>
       <c r="P53" s="6"/>
       <c r="Q53" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R53" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
@@ -21455,7 +21361,7 @@
         <v>30</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>29</v>
@@ -21474,10 +21380,10 @@
       <c r="O54" s="5"/>
       <c r="P54" s="6"/>
       <c r="Q54" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R54" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
@@ -21485,7 +21391,7 @@
         <v>30</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>19</v>
@@ -21504,10 +21410,10 @@
       <c r="O55" s="5"/>
       <c r="P55" s="6"/>
       <c r="Q55" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R55" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
@@ -21515,7 +21421,7 @@
         <v>30</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>23</v>
@@ -21534,10 +21440,10 @@
       <c r="O56" s="5"/>
       <c r="P56" s="6"/>
       <c r="Q56" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R56" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:18" ht="18" x14ac:dyDescent="0.25">
@@ -21545,7 +21451,7 @@
         <v>30</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>39</v>
@@ -21564,10 +21470,10 @@
       <c r="O57" s="5"/>
       <c r="P57" s="6"/>
       <c r="Q57" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R57" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
@@ -21575,7 +21481,7 @@
         <v>11</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C58" s="9" t="s">
         <v>28</v>
@@ -21594,10 +21500,10 @@
       <c r="O58" s="9"/>
       <c r="P58" s="10"/>
       <c r="Q58" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R58" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
@@ -21605,7 +21511,7 @@
         <v>11</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C59" s="9" t="s">
         <v>19</v>
@@ -21624,10 +21530,10 @@
       <c r="O59" s="9"/>
       <c r="P59" s="10"/>
       <c r="Q59" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R59" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
@@ -21635,7 +21541,7 @@
         <v>11</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>23</v>
@@ -21654,10 +21560,10 @@
       <c r="O60" s="9"/>
       <c r="P60" s="10"/>
       <c r="Q60" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R60" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -21666,26 +21572,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B96036E30F13644F923D207E371C305D" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d197ceb99055fd1a93a3a14aec1bdd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f76aa77c-8923-4724-9a6d-d588cc513697" xmlns:ns3="89c54d5b-05ac-45d5-9242-aabb385cc5ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b86266bfd619f312673123d0bd20d23" ns2:_="" ns3:_="">
     <xsd:import namespace="f76aa77c-8923-4724-9a6d-d588cc513697"/>
@@ -21880,32 +21766,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BDC8EFC-C946-4B3C-B84E-1270F018751C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21922,4 +21803,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/dados/metas.xlsx
+++ b/dados/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.sa\Documents\dashboard-oportunidades\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A8B9C1-ECF7-45B3-ADB9-1CA88A09E1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B755A52D-C568-49CC-A673-48E3C2CBDC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="94">
   <si>
     <t>CÓD</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>WESLEY.LIMA</t>
+  </si>
+  <si>
+    <t>HUGO.MOL</t>
   </si>
 </sst>
 </file>
@@ -731,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R240"/>
+  <dimension ref="A1:R244"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
@@ -849,7 +852,7 @@
         <v>32</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -905,7 +908,7 @@
         <v>32</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -961,7 +964,7 @@
         <v>32</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1017,7 +1020,7 @@
         <v>32</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -4545,7 +4548,7 @@
         <v>20</v>
       </c>
       <c r="R68" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
@@ -4601,7 +4604,7 @@
         <v>20</v>
       </c>
       <c r="R69" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -4657,7 +4660,7 @@
         <v>20</v>
       </c>
       <c r="R70" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
@@ -4713,7 +4716,7 @@
         <v>20</v>
       </c>
       <c r="R71" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
@@ -4769,7 +4772,7 @@
         <v>20</v>
       </c>
       <c r="R72" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
@@ -4825,7 +4828,7 @@
         <v>20</v>
       </c>
       <c r="R73" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
@@ -4881,7 +4884,7 @@
         <v>20</v>
       </c>
       <c r="R74" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
@@ -4937,7 +4940,7 @@
         <v>20</v>
       </c>
       <c r="R75" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
@@ -4993,7 +4996,7 @@
         <v>20</v>
       </c>
       <c r="R76" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
@@ -14030,12 +14033,148 @@
         <v>21</v>
       </c>
     </row>
+    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A241" s="4">
+        <v>40011</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K241" s="4">
+        <v>0</v>
+      </c>
+      <c r="L241" s="4">
+        <v>0</v>
+      </c>
+      <c r="M241" s="4">
+        <v>1</v>
+      </c>
+      <c r="N241" s="4">
+        <v>0</v>
+      </c>
+      <c r="O241" s="4">
+        <v>1</v>
+      </c>
+      <c r="P241" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q241" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R241" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A242" s="4">
+        <v>40011</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K242" s="4">
+        <v>1</v>
+      </c>
+      <c r="L242" s="4">
+        <v>0</v>
+      </c>
+      <c r="M242" s="4">
+        <v>1</v>
+      </c>
+      <c r="N242" s="4">
+        <v>0</v>
+      </c>
+      <c r="O242" s="4">
+        <v>1</v>
+      </c>
+      <c r="P242" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q242" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R242" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A243" s="4">
+        <v>40011</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K243" s="4">
+        <v>100000</v>
+      </c>
+      <c r="L243" s="4">
+        <v>150000</v>
+      </c>
+      <c r="M243" s="4">
+        <v>140000</v>
+      </c>
+      <c r="N243" s="4">
+        <v>120000</v>
+      </c>
+      <c r="O243" s="4">
+        <v>80000</v>
+      </c>
+      <c r="P243" s="4">
+        <v>590000</v>
+      </c>
+      <c r="Q243" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R243" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A244" s="4">
+        <v>40011</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K244" s="4">
+        <v>1</v>
+      </c>
+      <c r="L244" s="4">
+        <v>2</v>
+      </c>
+      <c r="M244" s="4">
+        <v>1</v>
+      </c>
+      <c r="N244" s="4">
+        <v>1</v>
+      </c>
+      <c r="O244" s="4">
+        <v>1</v>
+      </c>
+      <c r="P244" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q244" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R244" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R240" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R240">
-      <sortCondition ref="B1:B240"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:R240" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21576,26 +21715,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B96036E30F13644F923D207E371C305D" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d197ceb99055fd1a93a3a14aec1bdd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f76aa77c-8923-4724-9a6d-d588cc513697" xmlns:ns3="89c54d5b-05ac-45d5-9242-aabb385cc5ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b86266bfd619f312673123d0bd20d23" ns2:_="" ns3:_="">
     <xsd:import namespace="f76aa77c-8923-4724-9a6d-d588cc513697"/>
@@ -21790,32 +21909,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BDC8EFC-C946-4B3C-B84E-1270F018751C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21832,4 +21946,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/dados/metas.xlsx
+++ b/dados/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.sa\Documents\dashboard-oportunidades\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CE5EEB-0940-4C12-95B5-6FAEAE4AACCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BBD786-9CBC-4E49-8D77-5E5D27E6DDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5003,6 +5003,9 @@
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A77" s="4">
+        <v>260044</v>
+      </c>
       <c r="B77" s="4" t="s">
         <v>94</v>
       </c>
@@ -5032,6 +5035,9 @@
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A78" s="4">
+        <v>260044</v>
+      </c>
       <c r="B78" s="4" t="s">
         <v>94</v>
       </c>
@@ -5061,6 +5067,9 @@
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A79" s="4">
+        <v>260044</v>
+      </c>
       <c r="B79" s="4" t="s">
         <v>94</v>
       </c>
@@ -5090,6 +5099,9 @@
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A80" s="4">
+        <v>260044</v>
+      </c>
       <c r="B80" s="4" t="s">
         <v>94</v>
       </c>
@@ -5119,6 +5131,9 @@
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A81" s="4">
+        <v>260044</v>
+      </c>
       <c r="B81" s="4" t="s">
         <v>94</v>
       </c>
@@ -5148,6 +5163,9 @@
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A82" s="4">
+        <v>260044</v>
+      </c>
       <c r="B82" s="4" t="s">
         <v>94</v>
       </c>
@@ -5177,6 +5195,9 @@
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A83" s="4">
+        <v>260044</v>
+      </c>
       <c r="B83" s="4" t="s">
         <v>94</v>
       </c>
@@ -5206,6 +5227,9 @@
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A84" s="4">
+        <v>260044</v>
+      </c>
       <c r="B84" s="4" t="s">
         <v>94</v>
       </c>
@@ -5235,6 +5259,9 @@
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A85" s="4">
+        <v>260044</v>
+      </c>
       <c r="B85" s="4" t="s">
         <v>94</v>
       </c>

--- a/dados/metas.xlsx
+++ b/dados/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.sa\Documents\dashboard-oportunidades\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BBD786-9CBC-4E49-8D77-5E5D27E6DDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F1C0CF-59CA-4E66-A1C7-1C85BAE78261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11275,7 +11275,7 @@
         <v>38</v>
       </c>
       <c r="R193" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.25">
@@ -22006,26 +22006,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B96036E30F13644F923D207E371C305D" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d197ceb99055fd1a93a3a14aec1bdd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f76aa77c-8923-4724-9a6d-d588cc513697" xmlns:ns3="89c54d5b-05ac-45d5-9242-aabb385cc5ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b86266bfd619f312673123d0bd20d23" ns2:_="" ns3:_="">
     <xsd:import namespace="f76aa77c-8923-4724-9a6d-d588cc513697"/>
@@ -22220,32 +22200,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BDC8EFC-C946-4B3C-B84E-1270F018751C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22262,4 +22237,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/dados/metas.xlsx
+++ b/dados/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.sa\Documents\dashboard-oportunidades\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F1C0CF-59CA-4E66-A1C7-1C85BAE78261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED88F9D-4825-4696-B598-D9528DCAD3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="ORÇAMENTO" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CONSULTOR!$A$1:$R$249</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CONSULTOR!$A$1:$R$254</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="96">
   <si>
     <t>CÓD</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>RAFAEL.CAETANO</t>
+  </si>
+  <si>
+    <t>TAYRONE.SEPULCRO</t>
   </si>
 </sst>
 </file>
@@ -737,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R253"/>
+  <dimension ref="A1:R258"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
@@ -13459,7 +13462,7 @@
         <v>47</v>
       </c>
       <c r="R232" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.25">
@@ -13515,7 +13518,7 @@
         <v>47</v>
       </c>
       <c r="R233" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.25">
@@ -13571,7 +13574,7 @@
         <v>47</v>
       </c>
       <c r="R234" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.25">
@@ -13627,7 +13630,7 @@
         <v>47</v>
       </c>
       <c r="R235" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.25">
@@ -13683,7 +13686,7 @@
         <v>47</v>
       </c>
       <c r="R236" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="237" spans="1:18" x14ac:dyDescent="0.25">
@@ -13739,7 +13742,7 @@
         <v>47</v>
       </c>
       <c r="R237" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.25">
@@ -13795,7 +13798,7 @@
         <v>47</v>
       </c>
       <c r="R238" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="239" spans="1:18" x14ac:dyDescent="0.25">
@@ -13851,68 +13854,62 @@
         <v>47</v>
       </c>
       <c r="R239" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
-        <v>250111</v>
+        <v>220999</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G240" s="4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H240" s="4">
         <v>0</v>
       </c>
       <c r="I240" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J240" s="4">
         <v>0</v>
       </c>
       <c r="K240" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L240" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M240" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N240" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O240" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P240" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q240" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="R240" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
-        <v>250111</v>
+        <v>220999</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G241" s="4">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H241" s="4">
         <v>1</v>
@@ -13924,151 +13921,144 @@
         <v>1</v>
       </c>
       <c r="K241" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L241" s="4">
         <v>1</v>
       </c>
       <c r="M241" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N241" s="4">
         <v>1</v>
       </c>
       <c r="O241" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P241" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q241" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="R241" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="242" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A242" s="4">
-        <v>250111</v>
+        <v>220999</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G242" s="4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H242" s="4">
-        <v>1</v>
+        <v>499177</v>
       </c>
       <c r="I242" s="4">
-        <v>0</v>
+        <v>327756</v>
       </c>
       <c r="J242" s="4">
-        <v>0</v>
+        <v>234504</v>
       </c>
       <c r="K242" s="4">
-        <v>1</v>
+        <v>308557</v>
       </c>
       <c r="L242" s="4">
-        <v>0</v>
+        <v>514262</v>
       </c>
       <c r="M242" s="4">
-        <v>0</v>
+        <v>455293</v>
       </c>
       <c r="N242" s="4">
-        <v>1</v>
+        <v>519748</v>
       </c>
       <c r="O242" s="4">
-        <v>0</v>
+        <v>532090</v>
       </c>
       <c r="P242" s="4">
-        <v>3</v>
+        <f>SUM(H242:O242)</f>
+        <v>3391387</v>
       </c>
       <c r="Q242" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="R242" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="243" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
-        <v>250111</v>
+        <v>220999</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C243" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H243" s="4">
+        <v>2</v>
+      </c>
+      <c r="I243" s="4">
+        <v>3</v>
+      </c>
+      <c r="J243" s="4">
+        <v>2</v>
+      </c>
+      <c r="K243" s="4">
+        <v>3</v>
+      </c>
+      <c r="L243" s="4">
+        <v>3</v>
+      </c>
+      <c r="M243" s="4">
+        <v>2</v>
+      </c>
+      <c r="N243" s="4">
+        <v>2</v>
+      </c>
+      <c r="O243" s="4">
+        <v>2</v>
+      </c>
+      <c r="P243" s="4">
+        <f>SUM(H243:O243)</f>
         <v>19</v>
       </c>
-      <c r="G243" s="4">
-        <v>70000</v>
-      </c>
-      <c r="H243" s="4">
-        <v>70000</v>
-      </c>
-      <c r="I243" s="4">
-        <v>90000</v>
-      </c>
-      <c r="J243" s="4">
-        <v>90000</v>
-      </c>
-      <c r="K243" s="4">
-        <v>120000</v>
-      </c>
-      <c r="L243" s="4">
-        <v>100000</v>
-      </c>
-      <c r="M243" s="4">
-        <v>120000</v>
-      </c>
-      <c r="N243" s="4">
-        <v>70000</v>
-      </c>
-      <c r="O243" s="4">
-        <v>70000</v>
-      </c>
-      <c r="P243" s="4">
-        <v>800000</v>
-      </c>
       <c r="Q243" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="R243" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="244" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
-        <v>250111</v>
+        <v>220999</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G244" s="4">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H244" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I244" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J244" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K244" s="4">
         <v>0</v>
       </c>
       <c r="L244" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M244" s="4">
         <v>0</v>
@@ -14080,13 +14070,13 @@
         <v>0</v>
       </c>
       <c r="P244" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q244" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="R244" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="245" spans="1:18" x14ac:dyDescent="0.25">
@@ -14097,7 +14087,7 @@
         <v>92</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G245" s="4">
         <v>0</v>
@@ -14144,22 +14134,22 @@
         <v>92</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G246" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H246" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I246" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J246" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K246" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L246" s="4">
         <v>1</v>
@@ -14168,13 +14158,13 @@
         <v>1</v>
       </c>
       <c r="N246" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O246" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P246" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q246" s="4" t="s">
         <v>38</v>
@@ -14191,37 +14181,37 @@
         <v>92</v>
       </c>
       <c r="C247" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G247" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H247" s="4">
         <v>1</v>
       </c>
       <c r="I247" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J247" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K247" s="4">
         <v>1</v>
       </c>
       <c r="L247" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M247" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N247" s="4">
         <v>1</v>
       </c>
       <c r="O247" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P247" s="4">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q247" s="4" t="s">
         <v>38</v>
@@ -14238,37 +14228,37 @@
         <v>92</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G248" s="4">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="H248" s="4">
-        <v>200000</v>
+        <v>70000</v>
       </c>
       <c r="I248" s="4">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="J248" s="4">
-        <v>400000</v>
+        <v>90000</v>
       </c>
       <c r="K248" s="4">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="L248" s="4">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="M248" s="4">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="N248" s="4">
-        <v>500000</v>
+        <v>70000</v>
       </c>
       <c r="O248" s="4">
-        <v>200000</v>
+        <v>70000</v>
       </c>
       <c r="P248" s="4">
-        <v>1500000</v>
+        <v>800000</v>
       </c>
       <c r="Q248" s="4" t="s">
         <v>38</v>
@@ -14285,19 +14275,19 @@
         <v>92</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G249" s="4">
         <v>0</v>
       </c>
       <c r="H249" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I249" s="4">
         <v>0</v>
       </c>
       <c r="J249" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K249" s="4">
         <v>0</v>
@@ -14306,16 +14296,16 @@
         <v>0</v>
       </c>
       <c r="M249" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N249" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O249" s="4">
         <v>0</v>
       </c>
       <c r="P249" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q249" s="4" t="s">
         <v>38</v>
@@ -14326,13 +14316,25 @@
     </row>
     <row r="250" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
-        <v>40011</v>
+        <v>250111</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="G250" s="4">
+        <v>0</v>
+      </c>
+      <c r="H250" s="4">
+        <v>0</v>
+      </c>
+      <c r="I250" s="4">
+        <v>2</v>
+      </c>
+      <c r="J250" s="4">
+        <v>0</v>
       </c>
       <c r="K250" s="4">
         <v>0</v>
@@ -14341,19 +14343,19 @@
         <v>0</v>
       </c>
       <c r="M250" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N250" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O250" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P250" s="4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q250" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="R250" s="4" t="s">
         <v>21</v>
@@ -14361,19 +14363,31 @@
     </row>
     <row r="251" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
-        <v>40011</v>
+        <v>250111</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="G251" s="4">
+        <v>0</v>
+      </c>
+      <c r="H251" s="4">
+        <v>0</v>
+      </c>
+      <c r="I251" s="4">
+        <v>0</v>
+      </c>
+      <c r="J251" s="4">
+        <v>0</v>
       </c>
       <c r="K251" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L251" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M251" s="4">
         <v>1</v>
@@ -14382,13 +14396,13 @@
         <v>0</v>
       </c>
       <c r="O251" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P251" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q251" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="R251" s="4" t="s">
         <v>21</v>
@@ -14396,34 +14410,46 @@
     </row>
     <row r="252" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
-        <v>40011</v>
+        <v>250111</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="G252" s="4">
+        <v>1</v>
+      </c>
+      <c r="H252" s="4">
+        <v>1</v>
+      </c>
+      <c r="I252" s="4">
+        <v>1</v>
+      </c>
+      <c r="J252" s="4">
+        <v>1</v>
       </c>
       <c r="K252" s="4">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="L252" s="4">
-        <v>150000</v>
+        <v>1</v>
       </c>
       <c r="M252" s="4">
-        <v>140000</v>
+        <v>1</v>
       </c>
       <c r="N252" s="4">
-        <v>120000</v>
+        <v>1</v>
       </c>
       <c r="O252" s="4">
-        <v>80000</v>
+        <v>1</v>
       </c>
       <c r="P252" s="4">
-        <v>590000</v>
+        <v>9</v>
       </c>
       <c r="Q252" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="R252" s="4" t="s">
         <v>21</v>
@@ -14431,42 +14457,242 @@
     </row>
     <row r="253" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
-        <v>40011</v>
+        <v>250111</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="G253" s="4">
+        <v>0</v>
+      </c>
+      <c r="H253" s="4">
+        <v>200000</v>
+      </c>
+      <c r="I253" s="4">
+        <v>0</v>
+      </c>
+      <c r="J253" s="4">
+        <v>400000</v>
       </c>
       <c r="K253" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L253" s="4">
-        <v>2</v>
+        <v>200000</v>
       </c>
       <c r="M253" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N253" s="4">
-        <v>1</v>
+        <v>500000</v>
       </c>
       <c r="O253" s="4">
-        <v>1</v>
+        <v>200000</v>
       </c>
       <c r="P253" s="4">
-        <v>6</v>
+        <v>1500000</v>
       </c>
       <c r="Q253" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="R253" s="4" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A254" s="4">
+        <v>250111</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G254" s="4">
+        <v>0</v>
+      </c>
+      <c r="H254" s="4">
+        <v>1</v>
+      </c>
+      <c r="I254" s="4">
+        <v>0</v>
+      </c>
+      <c r="J254" s="4">
+        <v>1</v>
+      </c>
+      <c r="K254" s="4">
+        <v>0</v>
+      </c>
+      <c r="L254" s="4">
+        <v>0</v>
+      </c>
+      <c r="M254" s="4">
+        <v>1</v>
+      </c>
+      <c r="N254" s="4">
+        <v>0</v>
+      </c>
+      <c r="O254" s="4">
+        <v>0</v>
+      </c>
+      <c r="P254" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q254" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="R254" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A255" s="4">
+        <v>40011</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K255" s="4">
+        <v>0</v>
+      </c>
+      <c r="L255" s="4">
+        <v>0</v>
+      </c>
+      <c r="M255" s="4">
+        <v>1</v>
+      </c>
+      <c r="N255" s="4">
+        <v>0</v>
+      </c>
+      <c r="O255" s="4">
+        <v>1</v>
+      </c>
+      <c r="P255" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q255" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R255" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A256" s="4">
+        <v>40011</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K256" s="4">
+        <v>1</v>
+      </c>
+      <c r="L256" s="4">
+        <v>0</v>
+      </c>
+      <c r="M256" s="4">
+        <v>1</v>
+      </c>
+      <c r="N256" s="4">
+        <v>0</v>
+      </c>
+      <c r="O256" s="4">
+        <v>1</v>
+      </c>
+      <c r="P256" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q256" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R256" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A257" s="4">
+        <v>40011</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K257" s="4">
+        <v>100000</v>
+      </c>
+      <c r="L257" s="4">
+        <v>150000</v>
+      </c>
+      <c r="M257" s="4">
+        <v>140000</v>
+      </c>
+      <c r="N257" s="4">
+        <v>120000</v>
+      </c>
+      <c r="O257" s="4">
+        <v>80000</v>
+      </c>
+      <c r="P257" s="4">
+        <v>590000</v>
+      </c>
+      <c r="Q257" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R257" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A258" s="4">
+        <v>40011</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K258" s="4">
+        <v>1</v>
+      </c>
+      <c r="L258" s="4">
+        <v>2</v>
+      </c>
+      <c r="M258" s="4">
+        <v>1</v>
+      </c>
+      <c r="N258" s="4">
+        <v>1</v>
+      </c>
+      <c r="O258" s="4">
+        <v>1</v>
+      </c>
+      <c r="P258" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q258" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R258" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R249" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R254" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -22006,6 +22232,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B96036E30F13644F923D207E371C305D" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d197ceb99055fd1a93a3a14aec1bdd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f76aa77c-8923-4724-9a6d-d588cc513697" xmlns:ns3="89c54d5b-05ac-45d5-9242-aabb385cc5ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b86266bfd619f312673123d0bd20d23" ns2:_="" ns3:_="">
     <xsd:import namespace="f76aa77c-8923-4724-9a6d-d588cc513697"/>
@@ -22200,27 +22446,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BDC8EFC-C946-4B3C-B84E-1270F018751C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22237,29 +22488,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5CFE981-CBAC-4360-B0CE-AB3235A33930}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F919D1BA-3E11-4877-AEE4-5A5340B7B50A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>